--- a/res/data/annotate/sap sam/sap_sam_models.xlsx
+++ b/res/data/annotate/sap sam/sap_sam_models.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="353">
   <si>
     <t>ID</t>
   </si>
@@ -42,34 +42,16 @@
     <t>Comment</t>
   </si>
   <si>
-    <t>355dd7c8cfb740938efdd65917ae9246</t>
-  </si>
-  <si>
     <t>SAP SAM</t>
   </si>
   <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>47b22c3a19ce4d9cbf7617a757d1aee4</t>
-  </si>
-  <si>
-    <t>Language = English
-Gateway Check = True
-Has Unknown = False
-Has OR-Gateway = False
-Connectivity = 0-1
-Amount of Gateways = 0
-Amount of Basic Elems = 10-25
-Amount of Events = 0-10
-Rate Useless Elems Max = 0.1
-Rate Basic Elems Min = 0.30
-Average Element Degree = 1.5-2.5
-Average Element Length = 15.0-30.0
-Structural Elems = 0-5</t>
-  </si>
-  <si>
     <t>Medium</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>77428c7083cb43e0b6b90e250971b80b</t>
   </si>
   <si>
     <t>Language = English
@@ -87,7 +69,25 @@
 Structural Elems = 0-5</t>
   </si>
   <si>
+    <t>The process begins with a user starting the task of selecting a bank. The user can choose a bank using a specific method, which is noted as "Selection via BLZ."
+Once the bank is selected, the user encounters a decision point to determine if the bank was found. If the bank is found, the user proceeds to enter bank credentials. If the bank is not found, an error message is displayed to the user. After displaying the error message, the user decides whether to contact support. If the user chooses not to contact support, the process ends. If the user decides to contact support, they can either fill out a form or call the service, after which the process ends.
+If the bank is found and the user enters the bank credentials, the next step is to connect with the bank. After attempting to connect, there is another decision point to check if the connection was successful. If the connection fails, an error message is shown, and the user is directed back to the step of entering bank credentials. The error messages that might be shown include "Bank connection not found," "An unexpected error occurred," and "Incorrect authorization."
+If the connection is successful, the user retrieves all transactions. The user has the option to categorize transactions themselves or allow the system to categorize them. After retrieving transactions, the user searches for a possible renter. If a renter is found, the user selects the renter and transaction, then views a payment overview, and the process ends. If no renter is found, a message is shown, and the user manually selects transactions, views the payment overview, and the process ends. 
+Throughout the process, the "App System" is associated with various tasks, including showing error messages, connecting with the bank, retrieving transactions, finding possible renters, and showing messages.</t>
+  </si>
+  <si>
     <t>3b5958b76ac44674970c5b7c4592a27f</t>
+  </si>
+  <si>
+    <t>The process begins when a Level 1 Employee at the IT Helpdesk receives a request. The first task for the Level 1 Employee is to determine if the solution to the problem is already known. 
+If the solution is known, the Level 1 Employee proceeds to solve the problem and then informs the customer that the problem has been solved, concluding the process.
+If the solution is unknown, the Level 1 Employee forwards the request to a Level 2 Employee. The Level 2 Employee receives the request and evaluates it. After evaluating the request, the Level 2 Employee assigns a priority level to it. This priority level is then entered into the Job Tracking System.
+The Job Tracking System assigns the request to a Level 2 Employee, who receives it and begins researching and developing a solution. Once a solution is developed, the Level 2 Employee sends it back to the Level 1 Employee.
+The Level 1 Employee receives the solution and tests it. If the test is successful, the Level 1 Employee informs the customer that the problem has been solved, and the process ends.
+If the test is unsuccessful, the Level 1 Employee sends the request back to the Level 2 Employee for further research and development. This cycle continues until a successful solution is found and the customer is informed.</t>
+  </si>
+  <si>
+    <t>00f027dd6b1e404591f85c0daa4bf2b9</t>
   </si>
   <si>
     <t>Language = English
@@ -105,6 +105,20 @@
 Structural Elems = 0-5</t>
   </si>
   <si>
+    <t>The business process begins when the Sales department receives a purchase order from a customer. The Sales team then enters the order data into the system. Following this, the Accounting/Finance department performs a credit check on the customer.
+At this point, there is a decision to be made based on the credit check results. If the credit check fails, the process moves to setting the order status to blocked. The Accounting/Finance team then refers the case to a specialist for further evaluation. The specialist evaluates the case and makes another decision. If the case remains blocked, the Accounting/Finance department informs the customer why the sales order is blocked.
+If the credit check passes, the order is approved, and the Accounting/Finance team checks the availability of the items. If the items are available, the process continues with the Shipping/Receiving department releasing the sales order. If the items are not available, a purchase requisition is created and referred to the Procurement department.
+The Procurement department reviews the purchase requisition and decides whether to approve it. If not approved, the Procurement team informs the Sales department, which then informs the customer about the blocked order. If approved, the Procurement team chooses a vendor and converts the purchase requisition into a purchase order, which is then transmitted to the vendor.
+Once the vendor sends the materials, the Shipping/Receiving department receives them and proceeds to pick the materials, arrange transportation, and ship them to the customer. Meanwhile, the Accounting/Finance department sends an invoice to the customer.
+After the customer receives the invoice, they make a payment, which the Accounting/Finance department receives and processes. Finally, the receivable is cleared, and the sales order is marked as completed, concluding the process.</t>
+  </si>
+  <si>
+    <t>3a76ddad69984f23ad28f2cf09a48ee4</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
     <t>Language = English
 Gateway Check = True
 Has Unknown = False
@@ -120,52 +134,54 @@
 Structural Elems = 0-5</t>
   </si>
   <si>
-    <t>High</t>
+    <t>The process begins with the domain registration team at ACME Inc. initiating the project. They start by specifying and discussing the details of the website. Once the discussion is complete, they document the blueprints and prepare a proposal. After finalizing the proposal, they conclude the meeting about the specifications.
+Next, the team proceeds to create a prototype of the website. Following this, the process splits into two parallel activities. The first activity involves the team designing the website wireframe, while the second activity focuses on structuring the information architecture. Both activities are carried out simultaneously.
+Once the wireframe is ready, the team gathers the necessary content. At the same time, they also work on designing the website graphics. After these tasks, the team seeks client approval for the website.
+Upon receiving approval, the website launch team at ACME Inc. takes over to complete the design of the business tool. This leads to another set of parallel tasks. The team regulates the website content, manages online buying and selling functionalities, and completes the inventory setup.
+After these tasks, the team selects methods for improving the specifications. The quality assurance and testing team then identifies and implements these improvement methods. They review and process the specifications to ensure everything is in order.
+Finally, the site launch team launches the website, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>f1571a41756f429485487f475cb2865d</t>
+  </si>
+  <si>
+    <t>The process begins when an employee submits an expense form. This form is then received by a finance officer, who is responsible for handling the report. Once the report is received, the finance officer simultaneously performs two tasks: they notify the employee that the report has been received and review the expense report.
+After reviewing the expense report, the finance officer encounters a decision point. If there is no previous file associated with the report, the finance officer creates an account. If there is a previous file, they use that file. Regardless of the path taken, the next step is for the finance officer to verify the report.
+Following the verification, the finance officer reviews the amount requested. At this point, another decision is made based on the amount. If the amount is less than 2000, the process concludes with the employee receiving the reimbursement. If the amount is above 2000, the report is forwarded to the finance manager for approval.
+The finance manager reviews the request and makes a decision. If the request is rejected, the finance manager sends a rejection notice, ending the process with the reimbursement being rejected. If the request is approved, the finance officer records the details of the reimbursement. Subsequently, the employee transfers the requested amount, and the process concludes with the employee receiving the reimbursement.</t>
+  </si>
+  <si>
+    <t>959768fda5984592ae8e7bcf771bf9e2</t>
+  </si>
+  <si>
+    <t>The process begins when the supplier receives an invoice. The supplier then sends this invoice to the accounting department. The accounting department forwards the invoice to the business unit, which receives it and proceeds to order the necessary goods or services.
+Once the order is placed, the business unit must decide whether the invoice is approved or not. If the invoice is approved, the business unit sends an approval notification. This leads to the accounting department filling in the necessary accounting information.
+At this point, the process splits into three simultaneous tasks handled by the accounting department: assigning a project number, determining tax codes, and identifying the cost code. All three tasks must be completed before proceeding to the next step.
+After these tasks are completed, the accounting department proceeds to inform the supplier and updates the accounts payable. This marks the end of the process for the accounting department.
+If the invoice is not approved, the business unit informs the accounting department, which then sends a notification to the supplier. The supplier is informed, and this marks the end of the process for the supplier.</t>
+  </si>
+  <si>
+    <t>0dd8931c54064aa0812834e68a614c86</t>
+  </si>
+  <si>
+    <t>The process begins with the restaurant manager initiating the receiving process. The first task for the restaurant manager is to check if the items received are complete and undamaged. 
+After this check, a decision point arises. If there are no problems with the items, the restaurant manager proceeds to enter the receiving information into the system, marking the end of the process.
+However, if there is a problem, the restaurant manager records the issue. Following this, another decision point occurs. If the problem is due to damaged items, the restaurant manager records the product damage information. If the issue is due to an incomplete order, the restaurant manager records the incomplete order information. 
+In both cases of damage or incompleteness, the next step involves the Kozi management team contacting the supplier to address the issue, either for completion or change of the order. The supplier is then expected to respond, and the Kozi management team receives this response and notifies the restaurant manager.
+The restaurant manager waits for the supplier to complete or change the order. Once the items arrive, the restaurant manager rechecks them. If everything is in order, the restaurant manager enters the receiving information into the system, completing the process.
+If the items are still incomplete or damaged, the process would start again from the point of rechecking the items upon arrival.</t>
+  </si>
+  <si>
+    <t>8022ba7914cf4693925c6674490ee56c</t>
+  </si>
+  <si>
+    <t>The process begins when a customer's purchase order is received. The first task is to check if the product is available. If the product is available, the inventory is updated, and a payment request is sent to the customer. Once the payment is requested, the product is delivered, and the process ends.
+If the product is not available, the customer is asked if they want to place an order. If the customer decides to place an order, a quote is made and sent to the customer. The customer's response is then checked. If the customer agrees to the quote, the materials are checked to ensure there is enough stock. If there is enough stock, the units are produced, and a notification is sent that the units are ready. The process then continues with updating the inventory, requesting payment, and delivering the product.
+If there is not enough stock, a purchase order is sent, and the needed materials are bought. After acquiring the materials, the units are produced, and a notification is sent that the units are ready. The process then continues with updating the inventory, requesting payment, and delivering the product.
+If the customer does not want to place an order or does not agree to the quote, the process ends without further action.</t>
   </si>
   <si>
     <t>c5cd15f5fd3f443eaff73696b9ecd6cc</t>
-  </si>
-  <si>
-    <t>c02fd526a0d4465db1c26aa174c9c85d</t>
-  </si>
-  <si>
-    <t>d8c408c7e7504253bf052eceb786e676</t>
-  </si>
-  <si>
-    <t>1f19f57766fe482499fff95b4b5ee172</t>
-  </si>
-  <si>
-    <t>Manual</t>
-  </si>
-  <si>
-    <t>644ff4ec9fd244879fd60f823763bf88</t>
-  </si>
-  <si>
-    <t>efda927d1da24b49b9f5dd4be6b579f1</t>
-  </si>
-  <si>
-    <t>The process begins with the Sales Manager at Allganic's initiating the workflow. The first step involves the Sales Manager receiving an order request. Following this, the Sales Manager gathers information from the farm to proceed with the order.
-Next, the Sales Manager checks both the order and the product to ensure everything is in order. After this verification, the Sales Manager also checks the customer's order details. Once these checks are completed, the Sales Manager sends the farm's address to the Transportation team.
-The Transportation team receives the farm's address and arranges a time to collect the product from the farm. They then prepare a vehicle to transport the product from the farm. After the preparations, the Transportation team sends the transportation cost details to the Sales Manager.
-Upon receiving the transportation cost, the Sales Manager calculates the total cost of the order. The Sales Manager then sends the total price to the customer. After communicating the total price, the Sales Manager records the order details.
-The Manager at Allganic's reads the report generated from the recorded order and signs the necessary documents. Meanwhile, the Transportation team proceeds to collect the product from the farm.
-Once the product is collected, the Transportation team delivers it to the customer. After the delivery, the Transportation team sends a record of the sales transaction.
-The Market Research team at Allganic's receives the sales data for recording purposes. They analyze the sales data and write a summary report based on their analysis.
-Finally, the Sales Manager closes the sale, marking the end of the process. The process concludes with the Sales Manager at Allganic's completing the workflow.</t>
-  </si>
-  <si>
-    <t>The process begins with a customer looking for the CKH website. Once the customer finds the website, they proceed to create a Request for Quotation (RFQ) on the CKH website. After creating the RFQ, the customer completes and submits it. During this step, RFQ information data is generated.
-Next, the process moves to the CHK Company, where a sales assistant finalizes the RFQ. After finalizing, the sales assistant prints the RFQ. Following the printing, the sales assistant sends the RFQ to the estimator.
-The estimator at CHK Company receives the RFQ and then draws and adjusts the draw plan. Once the draw plan is adjusted, the estimator completes the draw plan and prepares a quote. After completing these tasks, the sales assistant mails all the documents, including the draw plan and quote, to the customer.
-The customer receives all the documents sent by the sales assistant. Finally, the process concludes with the customer responding to CHK Company.</t>
-  </si>
-  <si>
-    <t>The process begins when a Level 1 Employee at the IT Helpdesk receives a request. The first task for the Level 1 Employee is to determine if the solution to the problem is already known. 
-If the solution is known, the Level 1 Employee proceeds to solve the problem and then informs the customer that the problem has been solved, concluding the process.
-If the solution is unknown, the Level 1 Employee forwards the request to a Level 2 Employee. The Level 2 Employee receives the request and evaluates it. After evaluating the request, the Level 2 Employee assigns a priority level to it. This priority level is then entered into the Job Tracking System.
-The Job Tracking System assigns the request to a Level 2 Employee, who receives it and begins researching and developing a solution. Once a solution is developed, the Level 2 Employee sends it back to the Level 1 Employee.
-The Level 1 Employee receives the solution and tests it. If the test is successful, the Level 1 Employee informs the customer that the problem has been solved, and the process ends.
-If the test is unsuccessful, the Level 1 Employee sends the request back to the Level 2 Employee for further research and development. This cycle continues until a successful solution is found and the customer is informed.</t>
   </si>
   <si>
     <t>The process begins with the Risk Management team initiating the procedure. They start by performing a credit check. Once the credit check is completed, the Risk Management team confirms the credibility check.
@@ -174,6 +190,409 @@
 Once the loan offer is sent, there is another decision point. If the offer is accepted, the process continues. If there is no response within an hour, a reminder is set, and after another hour, the Customer Contact team reminds the client again. Once the offer is accepted, the process moves forward.
 Upon receiving the accepted offer, the Finance team simultaneously activates the loan application and sends a welcome letter. The loan application activation involves validating the loan activation and executing the initial payment. After these tasks, the Administration team returns the necessary documents to the client, concluding this branch of the process.
 The process ends with the Administration team sending a welcome letter and returning documents to the client, marking the completion of the entire procedure.</t>
+  </si>
+  <si>
+    <t>d6b33aca297248d1aeee6bb064181975</t>
+  </si>
+  <si>
+    <t>The process begins with the warehouse initiating the task of checking the quantity of stock using an automated system. This task is performed by the warehouse staff with the help of robotic process automation (RPA). Once the stock levels are checked, the process moves to a decision point where it is determined if there is enough stock available.
+If there is enough stock, the process concludes successfully. However, if there is not enough stock, the warehouse proceeds to check if a requested order has already been placed with the supplier. This leads to another decision point: if the products have been ordered, the process ends. If not, the warehouse sends a request to the supplier to order the necessary products.
+Upon receiving the order request, the supplier processes the order and sends the products to the warehouse. Once the products arrive at the warehouse, they are received and then checked for quality by the quality control department. At this stage, another decision is made to determine if there are any defective garments.
+If a defective garment is found, the product is sent back to the supplier, who then replaces the product and sends it back to the warehouse. If no defects are found, the warehouse scans the RFID tags of the products and updates the stock levels using RPA. Finally, the products are stocked in, completing the cycle and returning to the initial task of checking stock quantity.</t>
+  </si>
+  <si>
+    <t>d98f4d3b681c431eada23a0a5f99664f</t>
+  </si>
+  <si>
+    <t>The process begins when a request is received by the Project Manager. The Manager of Learning Spaces then reviews the job for allocation. After the review, the process splits into two parallel tasks. The first task involves the Project Manager liaising with the client to facilitate a walkthrough. Simultaneously, the Executive allocates a vendor.
+Once the vendor is allocated, the Project Manager liaises with the vendor to facilitate a walkthrough. Following this, the Project Manager drafts and sends a Bill of Materials (BOM) and wiring schematic to the vendor. The vendor then receives the quote and sends it back.
+Next, the Logistics Coordinator generates costings from the vendor's quote. The Project Manager then generates a Statement of Work (SOW). The Executive reviews and approves the SOW. After approval, the Project Manager sends the SOW to the client for review and approval.
+At this point, there is a decision point. If the client rejects the SOW, the Project Manager reviews and modifies it as required by the client, and the process loops back to drafting and sending the BOM and wiring schematic to the vendor. If the client approves the SOW, the Logistics Coordinator raises a Purchase Order (PO). If the works are no longer required, the process ends.
+Once the PO is raised, the Logistics Coordinator confirms its receipt and sends an email to the vendor. The vendor then sends an invoice. The Logistics Coordinator submits the vendor invoice for payment and manages assets as required. The process concludes with the Logistics Coordinator marking the job as complete.
+If the client gives the go-ahead for installation, the Project Manager schedules the installation and commissions it as per the user brief. This leads to the vendor sending an invoice, and the process continues with the submission of the invoice for payment.</t>
+  </si>
+  <si>
+    <t>b6a319ff222e460db7e2f7c32a8de60e</t>
+  </si>
+  <si>
+    <t>The process begins when a clerk receives an order. The clerk's first task is to check the parts inventory. After checking the inventory, the process reaches a decision point. Here, the clerk determines whether the necessary parts are available.
+If the parts are unavailable, which happens 4% of the time, the clerk checks if the relevant parts are in order and reschedules the assembly order for the next day, or cancels the assembly. This leads directly to logging the order and notifying the client and shipper.
+If the parts are available, which occurs 96% of the time, the assembly floor manager requests the parts from the warehouse. The process then waits for a worker to pick up the parts. Once the parts are picked up and logged by the warehouse, they are delivered to the assembly floor manager.
+The assembly floor manager oversees the assembly process. After the assembly is complete, the finished items wait to be sent to the warehouse. The assembly floor manager then sends the items to the warehouse, where they are placed in finished goods storage.
+Finally, the clerk logs the order and notifies both the client and the shipper. This marks the end of the process.</t>
+  </si>
+  <si>
+    <t>5709e97013004689a5250805f039b04c</t>
+  </si>
+  <si>
+    <t>The process begins when a junior salesman in the sales department receives a request for a quotation. The junior salesman first clarifies the request to ensure all necessary details are understood. After clarifying, the junior salesman determines whether the request is simple or complex.
+If the request is simple, the junior salesman checks the prices on the pricelist. Once the prices are checked, the junior salesman prepares the final quotation.
+If the request is complex, the junior salesman asks for assistance. A senior salesman then analyzes the request. Following the analysis, the senior salesman checks the knowledge database to see if the request is a known case.
+If it is a known case, the senior salesman prepares a new option based on the known cases and applies this option to the quotation proposal. The junior salesman then prepares the final quotation.
+If it is not a known case, the senior salesman asks an expert for an opinion. The manager analyzes the request and prepares an individual option. This option is then used to update the knowledge database by the senior salesman. After updating the database, the senior salesman applies the option to the quotation proposal, and the junior salesman prepares the final quotation.
+Finally, the junior salesman sends the prepared quotation to the customer, concluding the process.</t>
+  </si>
+  <si>
+    <t>314244d1f81a488ab13e5821970fd533</t>
+  </si>
+  <si>
+    <t>The process begins with an administrator at Acme Manufacturing initiating an engineering change request. This task sets the process in motion.
+Next, the administrator encounters a decision point where the nature of the change is evaluated. If the change is deemed minor, the draftsmen proceed to make the change. If the change is considered major, an engineer is tasked with analyzing the change and making recommendations.
+For a major change, after the engineer analyzes and recommends, they initiate an approval process. A manager then processes this approval. Following the manager's decision, there is another decision point. If the change is accepted, the draftsmen document the changes and check them into the PLM system, completing the process. If the change is rejected, the process is terminated.
+For a minor change, the draftsmen make the change and then initiate an approval process. The manager processes this approval, leading to another decision point. If the change is accepted, the draftsmen check the changes into the PLM system, completing the process. If the change is rejected, the process is terminated.
+In summary, the process involves initiating a change request, evaluating the change, processing approvals, and either completing the change or terminating the process based on the approval outcomes.</t>
+  </si>
+  <si>
+    <t>cc88d8b942aa4cf7b21fcfb651a14594</t>
+  </si>
+  <si>
+    <t>The process begins when a pharmacist receives a claim. The pharmacist then enters the claim details into the system. After entering the details, the pharmacist checks the form of the prescription to ensure it is correct. Once the form is verified, the pharmacy dispensing software checks the data of the prescription.
+The process then reaches a decision point where the pharmacy dispensing software determines if the prescription data matches the system's records. If the data does not match, the process ends here. If the data matches, the pharmacist proceeds to check the categories of the user.
+Next, the pharmacist evaluates whether the user belongs to the target group. If the user does not match the target group, the process ends. If the user matches, the pharmacist checks the item associated with the claim.
+Following this, the pharmacist assesses whether there is any missing documentation, a missing prescription, a rejected prescription, or if the item has not yet been supplied. If any of these conditions are true, the pharmacist removes the claim from the electronic claim data list, and the process ends. If none of these conditions are met, the pharmacist generates a new serial number or corrects the details for the description.
+The pharmacist then writes a note indicating that immediate supply is necessary. After this, the pharmacy dispensing software starts the process to close a claim transaction. The software acknowledges the certification of the supply statement.
+The Office of Human Service then sends the close claim transaction and receives a return message. Following this, the Office of Human Service prepares a separate claim and completes the necessary claim paperwork. Finally, the process concludes with the Office of Human Service.</t>
+  </si>
+  <si>
+    <t>9b8e781476924f6aaa6c92069724476b</t>
+  </si>
+  <si>
+    <t>The process begins with the initiation of a resupply cycle. The first step involves checking the inventory level to determine the current stock status.
+After checking the inventory, a decision is made based on the inventory level. If the inventory level is above the minimum required, the process ends there. However, if the inventory level is at or below the minimum, a purchase order is created.
+Once the purchase order is created, it is reviewed. During the review, another decision is made. If the purchase order is approved, the process continues. If it is rejected, the purchase order is marked as rejected, and it is sent back for reworking. After reworking, the purchase order is reviewed again.
+If the purchase order is approved, funds are reserved for it. Following this, the purchase order is sent to the supplier.
+The supplier then sends a packing slip, followed by an invoice. These documents are received and subsequently recorded.
+After recording the documents, the reserved funds are released. Finally, payment is issued to the supplier, and the process concludes.</t>
+  </si>
+  <si>
+    <t>ab698d0d639f48568d0706f87391e4d1</t>
+  </si>
+  <si>
+    <t>The process begins when a Level 1 employee at the IT help desk receives a help request. The Level 1 employee then checks if there is a known solution to the problem. At this point, there is a decision to be made:
+1. If the solution is known, the Level 1 employee proceeds to solve the problem and then informs the customer that the problem has been solved, concluding the process.
+2. If the solution is unknown, the Level 1 employee forwards the request to a Level 2 employee. The Level 2 employee receives the request and evaluates it. After evaluation, the Level 2 employee assigns a priority level to the request and enters this information into the job tracking system. The job tracking system then assigns the request back to a Level 2 employee, who receives it and begins researching and developing a solution.
+Once the Level 2 employee has developed a solution, they send it back to the Level 1 employee. The Level 1 employee receives the solution and tests it. Another decision point occurs here:
+1. If the test is successful, the Level 1 employee informs the customer that the problem has been solved, and the process ends.
+2. If the test is unsuccessful, the Level 1 employee sends the request back to the Level 2 staff for further research and development, repeating the cycle until a successful solution is found and the customer is informed.</t>
+  </si>
+  <si>
+    <t>1e3e8c5fe7ad46158e89fb38c8be6fb8</t>
+  </si>
+  <si>
+    <t>The process begins with the reception of parts by the warehouse team. Once the parts are received, an operator in the designated zone checks the part list. This task involves verifying the parts against a provided list, which is documented in a Part List File.
+After checking the part list, the process reaches a decision point. If the checklist is not okay, the warehouse team is tasked with obtaining the missing part. Once the missing part is acquired, the process returns to the operator, who then assembles the applicator.
+If the checklist is okay, the operator proceeds directly to assemble the applicator. Following the assembly, the operator undertakes the adjustment of the applicator in a subprocess.
+Once the applicator is adjusted, the process moves to the validation zone for a micro-cut and validation subprocess. After validation, another decision point is encountered. If the validation is not okay, the process loops back to the adjustment of the applicator. If the validation is okay, the warehouse team retrieves a roll of wire.
+The warehouse team then cuts and defoliates the wire to prepare samples. The operator in the designated zone uses these samples to make further samples, which are then measured.
+After measuring the samples, the operator performs an assembly report, documenting the entire process. Finally, the process concludes with the completion of the assembly report, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>793cb97cb029428eb376629063898c2c</t>
+  </si>
+  <si>
+    <t>The process begins when the client exits the vehicle. The first task is to check if the keys are present. If the keys are not in the car, the process ends with a task to retrieve the keys.
+If the keys are in the car, the next step is to measure the vehicle's emissions. Following this, the registration papers are examined to ensure they are in order. The process continues with checking the odometer to record the vehicle's mileage.
+Next, the gearing system is checked to ensure it is functioning correctly. The headlights are then inspected to confirm they are operational. Following this, the windshield is checked for any damage or obstructions.
+The rear lights are inspected next to ensure they are working properly. The license plate lights are also checked to confirm they are functioning. The tires are then examined to assess their condition and ensure they meet safety standards.
+The doors and trunk are checked to ensure they open and close properly. The engine components are inspected to verify they are in good condition. The vehicle's identification number is checked to confirm it matches the registration papers.
+The towing device is then checked. If there is no towing device, the process ends with the completion of the inspection at Base 2. If a towing device is present, it is inspected further. The database is checked for any records related to the towing device. Once this is done, the inspection at Base 2 is completed, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>2aaf9036d6214edfa70ef0100eac7b5b</t>
+  </si>
+  <si>
+    <t>The process begins when the notification department of the Car Insurer receives a claim. The notification department then checks the documentation to ensure it is complete. Once the documentation is verified, the claim is registered by the same department.
+Next, the handling department picks up the claim and checks the insurance details. At this point, a decision is made: if the claim is covered, the process continues; if not, the claim is rejected. If the claim is not covered, the handling department rejects the claim, and the process ends with the claim being marked as rejected.
+If the claim is covered, the handling department performs an assessment. Following the assessment, another decision is made based on the results: if the results are negative, the claim is rejected; if positive, the handling department contacts the garage to authorize repairs.
+After authorizing repairs, the handling department schedules the payment. Subsequently, a letter is sent to the customer, and the assessment results are communicated. The process concludes with the claim being assessed.</t>
+  </si>
+  <si>
+    <t>1af7cca2da4d496985fab343d02809f9</t>
+  </si>
+  <si>
+    <t>The process begins when a sales engineer receives a customer purchase order. The sales engineer then checks the purchase order to ensure all the data is correct. At this point, there are three possible outcomes:
+1. If the data is not good, the sales engineer requests a revision on the terms.
+2. If the data is good, the sales engineer confirms the purchase order and proceeds to create a work order.
+3. If the purchase order is deemed reject-worthy, the process ends with the purchase order being rejected.
+Once the purchase order is confirmed, the sales engineer creates a work order. The production engineer then determines the required raw materials and annotates the work order with a list of these materials. The procurement officer checks the listed raw materials to see if they are in stock. This leads to another decision point:
+1. If not all materials are in stock, the procurement officer selects a suitable supplier for the missing materials and sends a material purchase order to the selected supplier. Once the materials are received, production can start.
+2. If all materials are in stock, the production engineer starts production immediately.
+After production, the quality inspector checks the final product for defects. This leads to another decision point:
+1. If a defect is found, the production engineer reports the defect. If the defect is severe, the product is discarded, and the process loops back to determining the required raw materials. If the defect is not severe, the product undergoes a minor fix.
+2. If no defect is found, the sales engineer schedules the final product shipment.
+Once the shipment is scheduled, the sales engineer ships the product, and the customer is notified that the product has been shipped. The process concludes when the customer purchase order is fulfilled.</t>
+  </si>
+  <si>
+    <t>d56fc0ce496946e1a88a391b2c2e6d50</t>
+  </si>
+  <si>
+    <t>The process begins when a mechanic at Frumherji LTD. identifies a new vehicle at Base 2. The mechanic then checks if the keys are in the car. If the keys are not in the car, the mechanic goes to the reception to collect them. Once the keys are available, the mechanic proceeds to inspect the vehicle at Base 2.
+After the inspection at Base 2, the mechanic records the outcome of the inspection. Following this, the mechanic moves the vehicle to Base 3 for another inspection. The inspection at Base 3 typically takes between 1 to 2 minutes. Once the inspection is completed, the mechanic records the outcome.
+Next, the mechanic moves the vehicle to Base 4 for further inspection. This inspection usually takes between 4 to 12 minutes. After completing the inspection at Base 4, the mechanic records the outcome and then moves the vehicle to the Inspection Hall.
+Once the vehicle is in the Inspection Hall, the mechanic notifies the customer that the inspection is completed. This notification triggers the customer to collect the inspection results. After collecting the results, the customer proceeds to collect their vehicle.
+Finally, the process concludes with the customer leaving the station. Meanwhile, the mechanic's task of completing the inspection is also marked as finished.</t>
+  </si>
+  <si>
+    <t>744cddfa416b49d5987ba90e0cea0cdd</t>
+  </si>
+  <si>
+    <t>The process begins with an undergraduate student starting the application for IMIS. The student first checks the application procedure. After this, the student must determine if they are an EU applicant.
+If the student is not an EU applicant, they proceed as a non-EU or international applicant. The student then applies via Uni-Assist and sends the required documents to Uni-Assist. After submitting the documents, the student waits for a decision, which takes approximately 10 to 12 weeks. The process concludes with the student receiving either an admission or rejection letter.
+If the student is an EU applicant, the process splits into two simultaneous paths. In one path, the student, if they are an FH-SWF graduate, applies via the FH-SWF online portal and contacts the IMIS office. The student then waits for a decision, which takes about 4 to 6 weeks, before receiving the admission or rejection letter.
+In the other path, the EU applicant applies via the FH-SWF online portal and sends the required documents. The student then contacts the IMIS office and waits for a decision, which also takes about 4 to 6 weeks. Finally, the student receives the admission or rejection letter.</t>
+  </si>
+  <si>
+    <t>20bd5cf84b6547f5a201e289e676d8a9</t>
+  </si>
+  <si>
+    <t>The process begins when an Account Manager acknowledges that a sale has been made. Following this, the Account Manager reviews the sale details with the vendor to ensure everything is in order. After the review, the Account Manager creates a case in the CRM system to document the transaction and any necessary follow-up actions.
+Once the case is created, the Queue Manager takes over as the case owner. The Queue Manager then determines whether the vendor involved in the sale is new. If the vendor is new, the Product Management Team is tasked with verifying the vendor's details. After verification, the process continues to check if the case is missing any information.
+If the vendor is not new, the Queue Manager directly checks if the case is missing any information. If information is missing, the Account Manager gathers the necessary details to complete the case. Once all information is gathered, the process loops back to the point where the Queue Manager checks for missing information.
+If the case has all the required information, the Queue Manager exports an open case report. Following this, the Queue Manager assigns the case to an Integration Specialist and sets a completion date for the case. The Queue Manager then sends an email to introduce the Integration Specialist to the vendor.
+The Integration Specialist follows up by sending an introduction email to the vendor, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>7b04fdc80c4144d6856687b6d970609b</t>
+  </si>
+  <si>
+    <t>The process begins with the supplier initiating the procedure. The first step involves the supplier acquiring cash. Once the cash is acquired, the supplier forwards it for validity checking.
+The financial body then checks if the money is present in the account. At this point, a decision is made based on the account balance. If the cash is not enough, the financial body detects this insufficiency and proceeds to decline the payment. Following this, the financial body notifies the provider about the declined payment. Consequently, the supplier declines the shipment of items, and the process concludes.
+On the other hand, if the cash is sufficient, the financial body detects the adequacy of funds and determines the provider. The supplier then receives the necessary credentials. After receiving the credentials, the dispatcher ships the required items, leading to the end of the process.</t>
+  </si>
+  <si>
+    <t>7139592663a7445d9acc8619e04db06c</t>
+  </si>
+  <si>
+    <t>The process begins when a Level 1 employee at the IT Helpdesk receives a help request. The first task for the Level 1 employee is to check if the solution to the problem is already known. 
+At this point, there is a decision to be made. If the solution is known, the Level 1 employee proceeds to solve the problem. After solving the problem, the Level 1 employee informs the customer, and the request is then closed.
+If the solution is unknown, the Level 1 employee forwards the request to a Level 2 employee. The Level 2 employee receives the request and evaluates it. Following the evaluation, the Level 2 employee assigns a priority level to the request and enters this information into the job tracking system. The job tracking system then assigns the request to a Level 2 employee, who receives it and begins researching and developing a solution.
+Once the solution is developed, the Level 2 employee sends it back to the Level 1 employee. The Level 1 employee receives the solution and tests it. Another decision point occurs here. If the test is successful, the Level 1 employee informs the customer, and the process ends with the customer being informed. If the test is unsuccessful, the Level 1 employee sends the request back to the Level 2 employee for further action, and the process continues from there.</t>
+  </si>
+  <si>
+    <t>30f804a3e5e64ef298266e67acfecc4b</t>
+  </si>
+  <si>
+    <t>The process begins when a Level 1 Employee at the IT help desk receives a help request. The employee then checks if they know the solution to the problem. At this point, there are two possible paths:
+1. If the Level 1 Employee knows the solution, they proceed to solve the problem. After solving it, they inform the customer that the help request has been fulfilled, concluding the process.
+2. If the Level 1 Employee does not know the solution, they send a request to the Level 2 staff. The Level 2 staff receives the request and evaluates it to assign a priority level. They then enter this priority level into the job tracking system, which assigns the request back to the Level 2 staff. The Level 2 staff then researches and develops a solution. Once the solution is ready, they send it back to the Level 1 Employee.
+Upon receiving the solution, the Level 1 Employee tests it. There are two possible outcomes from this test:
+- If the test is successful, the Level 1 Employee informs the customer that the request has been fulfilled, ending the process.
+- If the test is unsuccessful, the Level 1 Employee sends the request back to the Level 2 staff for further research and development. This cycle continues until a successful solution is found and the customer is informed.
+Throughout the process, communication and task assignments are managed by the IT help desk, ensuring that each step is completed efficiently and effectively.</t>
+  </si>
+  <si>
+    <t>c0266568845e41b8ab7a99baa359b612</t>
+  </si>
+  <si>
+    <t>The process begins with the initiation of the press process at perslijn7. The first step involves determining the type of ingredients. This decision point leads to four possible paths:
+1. If the ingredients are manually added medicines, the process moves to the task of manually adding these medicines. Following this, there is another decision point regarding the allocation to a medicine bunker. The options are:
+   - Allocating to medicin bunker BU0101, which then proceeds to the task of Menger 7 ME0201.
+   - Allocating to medicin bunker BU0001, which also leads to the task of Menger 7 ME0201.
+2. If the ingredients are fluids from Tank 902-903 or Tank 913, the process continues to the task of handling these fluids, which then leads to the task of Fluid menger 6 ME0701.
+3. If the ingredients are fluids from Tank 905, the process moves directly to the task of Press motor 6/7 PE0301.
+4. If the ingredients are products from the M/M process KT2501, the process proceeds to the task of Pressed meal bunker PB617, which then leads to the task of Menger 7 ME0201.
+After the task of Menger 7 ME0201, the process continues to the task of Pressed meal bunker PB607, followed by the task of Dosing bunker BU0202. Next, the process moves to the task of Press motor 6/7 PE0301, then to the task of Press upper cooler 6/7 K0401, and subsequently to the task of Press under cooler 6/7 K0501. The process then proceeds to the task of Bunker press line 6/sieve BU0601.
+At this point, there is a decision on whether to continue to the menger. If the decision is "Yes," the process moves to the task of Fluid menger 6 ME0701, followed by the task of Bunker under vacuum coater BU0801, and finally ends the press process. If the decision is "No," the process loops back to the task of Pressed meal bunker PB607.
+Upon completion of the process, the pressed product is allocated to one of the five press drain lines by an IT system.</t>
+  </si>
+  <si>
+    <t>c8d11f6234f549bcbcea682c891da632</t>
+  </si>
+  <si>
+    <t>The process begins with the initiation of the program. Once the program is running, a decision point is reached where two paths are possible. 
+The first path involves selecting a file to scan. After selecting the file, the file is scanned, and the process continues to the next step, which is displaying the data.
+The second path involves selecting an option to display data directly. Once the option is selected, the data is displayed.
+After the data is displayed, the user can select the data they want to change by double-clicking on it. The selected data is then changed, and the change is validated. Once validated, the data is saved.
+After saving the data, another decision point is reached with three possible outcomes. The first outcome leads to the end of the process. The second outcome involves filtering and searching within the scanned database. The third outcome involves running table maintenance. Each of these outcomes represents a different path the process can take after saving the data.</t>
+  </si>
+  <si>
+    <t>9ff5bb3ce2c843dba9e1562c641365fd</t>
+  </si>
+  <si>
+    <t>The process begins with a student opening an application. Once the application is opened, the application itself welcomes the student. After the welcome message, the student enters the student section of the application.
+At this point, the student faces a decision on how to use the app. There are two possible paths the student can take:
+1. The student can choose to sign in. After signing in, the student proceeds to click on a map.
+2. Alternatively, the student can choose to be directed. In this case, the student is guided to click on a map.
+Regardless of the path chosen, the next step involves the student clicking on the map. Once the map is clicked, a sensor sends the map coordinates. Following this, the application displays the map to the student.
+With the map visible, the student can track the bus. After tracking the bus, the student arrives at the main location.
+Upon arrival, the application sends a notification. This notification is sent simultaneously to both the student and a manager. The student receives the notification and subsequently closes the application. Similarly, the manager receives the notification, concluding their part in the process.</t>
+  </si>
+  <si>
+    <t>6c5d8483fb51405096a01946d550b55d</t>
+  </si>
+  <si>
+    <t>The process begins with a message that initiates the workflow. Following this, there is a point where two tasks are carried out simultaneously.
+The first task involves deploying the database tier. Once this is completed, the next step is to deploy a virtual machine specifically for Apache. After the virtual machine is set up, the operating system for Apache is deployed. Following this, the Apache web server itself is deployed. The process continues with the deployment of PHP modules. After the PHP modules are in place, the SugarCRM application is deployed. The final step in this sequence is connecting the SugarCRM application to the database.
+Simultaneously, the second task involves deploying the web tier. After this, a virtual machine for mySQL is deployed. Once the virtual machine is ready, the operating system for mySQL is deployed. Following this, mySQL itself is deployed. The next step is to create the SugarCRM database. This sequence concludes by connecting to the task where the SugarCRM application is connected to the database.
+The process ends once the SugarCRM application is successfully connected to the database.</t>
+  </si>
+  <si>
+    <t>e29280012da84bd3a14aceaee0d6d114</t>
+  </si>
+  <si>
+    <t>The process begins with a storing employee checking the quality of a product. Once the quality check is complete, the storing employee proceeds to determine the product family.
+At this point, the process branches into three possible paths:
+1. If the product is identified as fast-moving, the storing employee moves it to the Fast-Moving Area. Here, the employee unwraps any gift sets before storing the product. This path concludes with the product being stored.
+2. If the product is not fast-moving, the storing employee moves it to the Autostore Refill area. The employee then checks if the product is classified as dangerous goods. If it is not dangerous, the product is stored directly. If it is dangerous, the employee applies safety measures, which include wrapping the product and storing it in a special box, before proceeding to store the product.
+3. Alternatively, the storing employee may move the product to the Hairtemple area. Here, the employee refills shampoo pipes before storing the product.
+The process concludes with the product being stored, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>76d9bdc2ae634edbaa67e809182e3688</t>
+  </si>
+  <si>
+    <t>The process begins when an online order is received by the order reception team at Online Orders Ltd. Once the order is received, the team prepares the order to be shipped.
+Next, there is a decision point to determine if bubble protection is needed for the shipment. If bubble protection is required, the order reception team adds bubble protection to the shipment. After adding bubble protection, or if it is not needed, the package is passed to the warehouse.
+In the warehouse, the team checks whether the package should be sent via normal post or fast courier. If the decision is to use a fast courier, the warehouse fills out the post label. If the decision is to use normal post, the warehouse gets a quote from the contracted courier.
+Once the quote is obtained, the warehouse prepares the necessary paperwork. This paperwork is then combined with the packaged goods.
+After the paperwork is combined with the package, the courier picks up the package. Finally, the package is sent, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>74538661264347fb8cdfbfbd5476d950</t>
+  </si>
+  <si>
+    <t>The process begins when a vehicle is prepared for inspection. The first step involves opening the customer file, which is handled by an employee. This task is followed by creating a digital inspection file, also managed by the same employee. Once the digital file is ready, the next step is to insert a sensor into the vehicle's exhaust pipe, which is performed by a technician.
+Following this, the vehicle undergoes an interior inspection, which is a subprocess involving various checks inside the vehicle. After the interior inspection, the vehicle's exterior is inspected, which is another subprocess focusing on the outside of the vehicle.
+Next, a technician checks for the presence of a towing device on the vehicle. At this point, a decision is made based on whether a towing device is installed. If a towing device is present, it is inspected to ensure it meets safety standards. This inspection is documented with a note to check if safety standards are met. After inspecting the towing device, the registration status of the vehicle is checked against the database to ensure it is up to date.
+If no towing device is installed, or after the registration status is checked, the digital inspection file is updated with the results of the inspection. This task is performed by an employee using the Frumherji IT system.
+Finally, the vehicle is driven to Base 3, marking the completion of the overall vehicle inspection process. The process concludes with the vehicle inspection being completed.</t>
+  </si>
+  <si>
+    <t>c6cf1da7e789466993ca214fa9e41763</t>
+  </si>
+  <si>
+    <t>The process begins with a driver needing to create an account. The driver starts by registering a driver account and setting a password. After this, the driver chooses the type of driver they want to be. Next, the driver must accept the cookies policy.
+At this point, the driver faces a decision. If the driver does not have a car, they proceed to upload their driver's document, hire a car, and then attain and upload a hire car license. If the driver already has a car, they upload both their driver's document and vehicle document.
+Once the necessary documents are uploaded, the driver applies for driver accreditation. This application is sent to Uber, who receives the driver accreditation request. Uber then arranges a vehicle inspection and assesses the driver's qualifications.
+After the assessment, there are three possible outcomes. If the driver is approved, Uber sends the driver's authority card, which is stored in the driver database and also sent to the driver. The driver then adds their credit card information, completing the sign-up process.
+If there is a lack of documents, Uber requests additional documents from the driver via email or text. The driver receives this request and must upload the missing documents, starting the process again from the document upload step.
+If the driver is not approved, Uber sends a rejection letter, ending the process for that driver.</t>
+  </si>
+  <si>
+    <t>096954d076984050902e9c92035a331c</t>
+  </si>
+  <si>
+    <t>The process begins when a customer sends a prescription to the pharmacy. A pharmacy technician receives the prescription and checks the method of delivery. There are two possible methods: immediate delivery or pickup. If the delivery is immediate, the technician inputs the prescription details into the system. If the pickup method is chosen, the technician stores the prescription along with the scheduled hour of pickup. One hour before the pickup time, the technician inputs the prescription details.
+Once the prescription details are entered, the pharmacy system performs Drug Utilization Review checks, followed by an insurance check. After these checks, the pharmacy technician collects the drugs. The pharmacist then double-checks the drugs to ensure accuracy. If the drugs are correct, the pharmacist prepares them for pickup. If there is an error, the pharmacist requests the technician to re-collect the drugs, and the process of collecting and checking the drugs is repeated.
+When the customer arrives at the pharmacy, the pharmacy technician determines if a payment is required. If no payment is needed, the technician proceeds to deliver the drugs to the customer. If payment is required, the technician collects the payment before delivering the drugs. Upon delivery, a receipt is sent to the customer, and the process concludes with the drugs being successfully delivered.</t>
+  </si>
+  <si>
+    <t>f1aaad76e4d845a2bd7e45dda90e32af</t>
+  </si>
+  <si>
+    <t>The process begins when an Administrator from the Product Development Department decides to change a design. The Administrator initiates a change request, which takes approximately 30 minutes.
+Next, the process reaches a decision point where the Administrator determines if the change is major. If the change is not major, which happens 70% of the time, a Draftsman makes the changes, taking about 2 hours. After making the changes, the Draftsman initiates an approval process in the PLM system, which takes 1 hour. The PLM system then sends an approval request, taking around 30 minutes with a possible variation of 10 minutes.
+At this point, another decision is made regarding acceptance. If the changes are accepted, which occurs 95% of the time, the Draftsman checks the changes, a task that takes 1.5 hours, and the process ends. If the changes are not accepted, which happens 5% of the time, the process ends without further action.
+Returning to the earlier decision point, if the change is major, which occurs 30% of the time, Engineers analyze the changes and make recommendations, a task that takes approximately 8 hours with a possible variation of 25%. Following this, Engineers initiate an approval process in the PLM system, taking 1 hour. The Engineers' manager then waits for the approval process to be completed, which takes about 1 hour with a possible variation of 15 minutes.
+Another decision is made regarding acceptance. If the changes are accepted, which happens 60% of the time, a Draftsman documents the changes, a task that takes 8 hours. The Draftsman then checks the changes into the PLM system, taking 1.5 hours, and the process ends. If the changes are not accepted, which occurs 40% of the time, the process ends without further action.</t>
+  </si>
+  <si>
+    <t>1240884060c64c629dc7c13357555caa</t>
+  </si>
+  <si>
+    <t>The process begins with the Administrator initiating the registration of a new administrator member. Once the registration task is completed, the Online Group Purchasing System takes over to verify the input provided. 
+At this point, the system checks the validity of the input. If the input is invalid, the system prompts an error message and sends it back to the Administrator, who must then reattempt the registration process. If the input is valid, the system proceeds to create a new account.
+After the account is created, the Administrator logs in as a member. Following this, three tasks are carried out simultaneously:
+1. The Administrator maintains seller and buyer information. This task results in the Online Group Purchasing System sending a new password requested by the member. The system then updates the new member password, concluding this branch of the process.
+2. The Administrator maintains rules and regulations. This leads to the Online Group Purchasing System updating the new rules and regulations, which marks the end of this branch.
+3. The Administrator handles approval and notification tasks. The Online Group Purchasing System then approves or rejects membership requests. If approved, a successful notification is sent, ending this branch of the process.
+Each of these branches concludes with the Online Group Purchasing System marking the end of the respective process paths.</t>
+  </si>
+  <si>
+    <t>92541a4399cf48429283280ba0f30594</t>
+  </si>
+  <si>
+    <t>The process begins with operator 1 initiating the task. The first step involves a parallel action where two separate tasks are carried out simultaneously.
+In the first branch, operator 1 places a glass panel on the work station. Following this, the glass panel is cleaned by operator 1. After cleaning, operator 1 applies primer to the glass panel. The glass panel is then placed in a curing area for 5 minutes by operator 1.
+Simultaneously, in the second branch, operator 2 places brackets on the work station. Operator 2 then cleans the brackets. After cleaning, primer is added to the brackets by operator 2. The brackets are then placed in a curing area for 5 minutes by operator 2.
+After both branches are completed, the process continues with operator 3 adding spacers. Operator 3 then places the brackets in the station. Following this, operator 3 places the panel in the station upon the brackets.
+Next, a machine adds glue to the panel. The machine then presses the panel upon the brackets. The panel and brackets are allowed to dry by the machine. Finally, the machine places the glued panel in a batch, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>599bc5727aa347d28056f245abc3fd6c</t>
+  </si>
+  <si>
+    <t>The process begins when a claim is submitted. The first task involves submitting the claim, which is handled by the claimant. Once the claim is submitted, the process splits into two parallel tasks.
+The first parallel task is to post the original documents, which is the responsibility of the claimant. After posting the documents, the next step is to retrieve and record the claim, managed by the claims processor. Following this, the claims processor triggers the payment, leading to the completion of the claim process.
+Simultaneously, the second parallel task involves verifying the policy's validity, conducted by the policy verifier. If the policy is found to be invalid, the policy verifier must double-check the policy. After double-checking, a decision is made: if the policy is valid, the process continues to verify the claim's completeness. If the policy remains invalid, the customer is notified, and the claim is rejected.
+If the policy is valid, the claim completeness is verified. If there are incomplete items, the claimant is required to resubmit the completed claim, which then leads back to assessing the claim. If the claim is complete, the claims assessor evaluates the claim. The decision is then recorded by the claims processor, and the decision is received, leading back to the retrieval and recording of the claim.
+This process ensures that all necessary steps are taken to handle a claim efficiently, from submission to completion or rejection.</t>
+  </si>
+  <si>
+    <t>a922ed6455094ebca47ab19950189ab4</t>
+  </si>
+  <si>
+    <t>The process begins when employees require training. The supervisor is responsible for selecting the appropriate training. Once the training is selected, the supervisor submits a training request.
+Next, the director evaluates the training request. At this point, a decision is made to determine if the correct training has been chosen. If the training is incorrect, the request is denied, and the supervisor is notified with the reason for denial. This concludes the process.
+If the correct training is chosen, the director then evaluates whether the training fits within the budget. If the training is over budget, the request is denied, and the supervisor is notified with the reason for denial. This also concludes the process.
+If the training fits within the budget, the supervisor is notified of the approval. The process ends with the supervisor scheduling the training.</t>
+  </si>
+  <si>
+    <t>1dafcaa36034450d98dd6c785ed4e026</t>
+  </si>
+  <si>
+    <t>The process begins when a customer enters the restaurant and places an order. The customer first decides on their preferred sandwich. After choosing the sandwich, the customer selects their preferred type of bread. Following this, the customer decides on the type of cheese they would like.
+Once these decisions are made, the customer prepares the sandwich. After preparation, there is a check to see if another customer has entered the store. If no other customer has entered, the sandwich is put into the oven. If another customer has entered, the process checks if one of the two spots in the oven is free. If a spot is free, the process loops back to deciding on the preferred sandwich for the new customer. If no spot is free, the sandwich is put into the oven.
+Once the sandwich is in the oven, there is a waiting period until the sandwich is ready. After the waiting period, the customer takes the order out of the oven. The customer then specifies their preferred toppings.
+Next, the process checks if the customer wants sauce. If the customer wants sauce, they decide on their preferred sauce. After deciding on the sauce, or if no sauce is desired, the customer decides whether to eat in the store or take the order away.
+Following this decision, the customer chooses their payment method. The customer then performs the payment. Finally, the ordering process ends.</t>
+  </si>
+  <si>
+    <t>4fa9326b71d94920993720520b2712e5</t>
+  </si>
+  <si>
+    <t>The process begins with the China Warehouse receiving a message to start the operation. The first task is for the China Warehouse to scan the label of the tracking number. Once the label is scanned, the next step is to identify the customer associated with the parcel.
+After identifying the customer, the China Warehouse calculates the volume and weight of the parcel. Following this, a photo of the parcel is taken. The information gathered, including the photo, is then sent to the customer.
+Simultaneously, the China Warehouse updates the status to indicate that they are waiting for the customer to fulfill additional details. The warehouse then asks the customer to provide these details.
+At this point, there is a decision to be made. If the customer fulfills the details, the parcel's status is changed to "Ready for delivery to New Zealand." If the details are not fulfilled, the parcel is placed in an unknown parcel area, and the process ends with the parcel being declined.
+If the parcel is ready for delivery, the China Warehouse waits for customer confirmation of the parcel list to be sent to New Zealand. Once confirmation is received, another decision is made regarding the mode of transport: by sea or by air.
+If the parcel is to be sent by air, the China Warehouse calculates the fee according to air freight rates and sends an email to the accountant with the fee details. The accountant then generates an invoice and sends a message to the customer. After receiving payment, the accountant notifies the China Warehouse that the order is ready to ship.
+The China Warehouse then repackages the parcels. Another decision is made regarding the mode of transport: by sea or by air. If by air, the parcels are put on a pallet and sent to the agent freight company warehouse. A notification is also sent to the New Zealand operation team.
+The New Zealand operation team prepares the clearance document and sends it to New Zealand customs. If the parcel is approved by customs, the team receives confirmation to release the parcels and dispatches them to the customer's address, completing the order. If not approved, the customer is notified, and the parcel is discarded, ending the process with the order declined.
+If the parcel is to be sent by sea, the China Warehouse calculates the fee according to sea freight rates and follows the same steps as for air transport, leading to the same potential outcomes.</t>
+  </si>
+  <si>
+    <t>49a24f70597040208f977637c5f4ba2f</t>
+  </si>
+  <si>
+    <t>The process begins with the Auction Service initiating a timer. Once the timer starts, the Auction Service checks the duration time to determine if the auction period has ended.
+At this point, there is a decision to be made. If the time is up, the Auction Service proceeds to inform the winner of the auction. After informing the winner, the process concludes with a message indicating the end of the auction.
+If the time is not up, the Auction Service checks if there is a new bidder. If there is no new bidder, the process loops back to checking the duration time again.
+If there is a new bidder, the Auction Service receives the buyer's maximum price. The next step involves comparing this maximum price with the highest bidders' prices.
+Another decision point arises here. If the buyer's maximum is not the highest, the Auction Service increases the buyer's maximum by one increment and then outbids the buyer. Following this, a notification is sent to the buyer, and the process ends with a message indicating the conclusion of this action.
+If the buyer's maximum is the highest, the Auction Service bids on behalf of the buyer by a small increment above the closest competitor's highest bid. Subsequently, the previous maximum is set as a new minimum, and the process loops back to checking the duration time again.</t>
+  </si>
+  <si>
+    <t>c1f695e4abf74245b749b0b443c699e8</t>
+  </si>
+  <si>
+    <t>The process begins with the initiation of change management. Once this is triggered, four tasks are carried out simultaneously:
+1. **Preparing for Change**: This task involves getting ready for the upcoming changes.
+2. **Define Change Management Strategy**: This task focuses on outlining the strategy for managing the change.
+3. **Prepare Change Management Team**: This task involves getting the team ready to handle the change management process.
+4. **Develop your sponsorship model**: This task involves creating a model to support the change process.
+After these tasks are completed, the process continues with managing the change. This involves overseeing the change process to ensure it is on track.
+Next, the task of developing change management plans is undertaken. This involves creating detailed plans to manage the change effectively.
+Following the development of plans, the implementation of these plans takes place. This task involves putting the plans into action.
+Once the plans are implemented, three tasks are carried out simultaneously:
+1. **Reinforcing Change**: This task involves strengthening the change to ensure it is sustained.
+2. **Collect and analyze feedback**: This task involves gathering feedback on the change and analyzing it to understand its impact.
+3. **Diagnose gaps and manage Resistance**: This task involves identifying any gaps in the change process and addressing any resistance to the change.
+After these tasks, the process moves to implementing corrective actions. This task involves making necessary adjustments to address any issues identified in the previous steps.
+Finally, the change management process concludes, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>4812b60389444ba4b480cdcd51c9eb2c</t>
+  </si>
+  <si>
+    <t>The process begins when a revised purchase order is received. The first step involves retrieving the details of the order. Once the order details are retrieved, the next step is to check if the product is in stock.
+At this point, there is a decision to be made based on the stock availability. If the product is in stock, the process continues with confirming that the product is available. Following this, the order is processed, and the system waits for order confirmation.
+Once the order is confirmed, two tasks occur simultaneously. One task involves emitting an invoice, which is followed by confirming payment by the customer. After payment is confirmed, the order is archived, marking the completion of the process.
+Simultaneously, the other task involves awaiting the shipment address. Once the shipment address is received, the requested product(s) are shipped. After shipping, the process also leads to archiving the order, completing the process.
+If the product is not in stock, the order is rejected, and the process ends there.</t>
+  </si>
+  <si>
+    <t>c02fd526a0d4465db1c26aa174c9c85d</t>
   </si>
   <si>
     <t>The process begins with an administrator initiating the workflow. The first task involves the administrator performing an automated credit check. Once the credit check is completed, the administrator confirms the credibility check.
@@ -185,9 +604,605 @@
 Throughout the process, the administrator is responsible for each task, ensuring that all steps are completed efficiently and accurately.</t>
   </si>
   <si>
+    <t>1075135c161b40e7a6655dd68aa1c5e0</t>
+  </si>
+  <si>
+    <t>The process begins with the task of defining the country on the Citrix Active Directory. Once the country is defined, the next step is to prepare the infrastructure. After the infrastructure is prepared, two tasks are initiated simultaneously.
+The first task involves creating roles on the Fiori LaunchPad. Following this, the on-set IT team is trained on these Active Directory groups. After the training, contact is made with the MO (Management Office). During this contact, a document is generated that includes finding the responsible local person, checking their responsibilities, organizing training, and creating an application to assign to roles. Subsequently, the MO and local IT provide the required apps template. This is followed by testing with local pilot groups.
+Simultaneously, the second task involves creating Active Directory groups. After this task, the process continues with training the on-set IT on these groups, similar to the first branch.
+After testing with local pilot groups, the process moves to the preparation for roll-out. Once the roll-out is prepared, three tasks are carried out at the same time.
+The first task is to communicate with end-users. This is followed by onboarding the end-users, which leads to the end of the process.
+The second task involves adding users to the created Active Directory groups. This task also leads to onboarding the end-users, concluding the process.
+The third task is to create a communication package, which includes a training package, upfront. This task also leads to onboarding the end-users, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>fd2c9f678fea49218a54235507d654bb</t>
+  </si>
+  <si>
+    <t>The process begins when the customer receives an acceptance pack. The customer then opens the acceptance pack and reads the repayment schedule included within it. After reviewing the schedule, the customer must decide whether they agree with the terms.
+If the customer agrees, they proceed to sign the document. Once signed, the customer sends the signed document back. This action triggers a notification to the loan provider, indicating that the customer has responded.
+If the customer does not agree with the terms, they choose to ignore the document. Subsequently, the customer informs the loan provider officer about their decision. This notification prompts the loan provider to verify the repayment agreement.
+The loan provider then checks if the repayment agreement has been signed. If it is signed, the loan provider approves the application and notifies the applicant about the status of their application. The customer receives this notification, marking the end of the process for them.
+If the repayment agreement is not signed, the loan provider cancels the application. Despite the cancellation, the loan provider still notifies the applicant about the status of their application.
+Separately, when a loan application is approved, the loan provider prepares an acceptance pack and sends it to the customer. This pack includes the terms and conditions, along with the repayment schedule. The customer then receives this pack, which initiates the process described above.</t>
+  </si>
+  <si>
+    <t>7df0261769274726b341a9a2ab2dcdd2</t>
+  </si>
+  <si>
+    <t>The process begins when the supplier receives an invoice. The supplier then sends the invoice to the accounting department. Once the accounting department receives the invoice, they forward it to the business unit.
+The business unit checks the invoice for approval. At this point, there are two possible outcomes:
+1. If the invoice is approved, the business unit sends it back to the accounting department. The accounting department then fills in the necessary accounting information. After this, two tasks occur simultaneously: the accounting department pays the supplier and updates the accounts payable. Once both tasks are completed, the process ends with the invoice marked as completed.
+2. If the invoice is not approved, the business unit informs the accounting department. The accounting department then informs the supplier that the invoice was not approved. The process concludes with the invoice being declined.</t>
+  </si>
+  <si>
+    <t>9864e8a829b54588bf70ed08b9049979</t>
+  </si>
+  <si>
+    <t>The process begins when Bob is hungry, and Jane Doe, who is responsible for making a peanut butter and jelly sandwich, starts the process. Jane decides that Bob wants a peanut butter and jelly sandwich.
+Jane first grabs some bread. She then faces a choice between using wheat or white bread. If she chooses white bread, the process ends with Jane deciding not to make a sandwich as she is trying to be healthy.
+If Jane chooses wheat bread, she proceeds to look for peanut butter. At this point, she must decide between creamy or chunky peanut butter. If she selects chunky peanut butter, she applies it along with jelly to the bread, and the process concludes with a happy Jane Doe.
+If Jane opts for creamy peanut butter, she checks if there are bananas and apples available. She then decides whether to use bananas or apples. If she chooses bananas, she toasts the wheat bread, applies creamy peanut butter, and places bananas on the toast. This leads to the end of the process with a happy Jane Doe.
+If Jane decides to use apples, she applies peanut butter and jelly to the wheat bread and adds the apples. This also results in a happy Jane Doe at the end of the process.</t>
+  </si>
+  <si>
+    <t>495162891d3747a98b9da1b50a7a1336</t>
+  </si>
+  <si>
+    <t>The process begins when an agent at the Transport Agency identifies the need for a full driver's license. The agent first asks the customer to provide an application form. Once the application form is received, the agent requests the customer's identification. After obtaining the ID, the agent copies the necessary information and inputs it into the database.
+Next, the Driver's License System checks if the customer already exists in the database. At this point, there are two possible outcomes:
+1. If the customer exists in the database, the system notifies the agent. The agent then asks the customer to fill out an application for reinstatement. This leads to the successful completion of the application process.
+2. If the customer does not exist in the database, the system informs the agent. The agent then informs the customer that an eye test is required. The agent proceeds to check the customer's eyesight.
+After the eyesight check, there are two possible outcomes:
+- If the customer fails the eye test, the agent requests an eyesight certificate from the customer. This results in the application being put on hold.
+- If the customer passes the eye test, the agent's assistant takes a photo of the customer. The assistant then checks the captured photo.
+Following the photo check, there are two possible outcomes:
+- If the photo is successful, the agent books a test time and location for the customer. The agent then requests payment from the customer. Once the payment is successful, the process concludes.
+- If the photo is not successful, the process loops back to retake the photo of the customer.
+Throughout this process, the agent and the agent's assistant work together to ensure all necessary steps are completed, and the Driver's License System provides support by checking the database and notifying the agent as needed.</t>
+  </si>
+  <si>
+    <t>7ca4ed9ebdca4945b21aa9c71b974b1e</t>
+  </si>
+  <si>
+    <t>The process begins with the Performance Manager initiating the task of editing focus improvement. The first step involves accessing the focus improvement page. During this step, a list of focus improvements is referenced.
+Next, the Performance Manager selects a specific improvement from the list. Following this, the manager proceeds to edit the chosen focus improvement. After making the necessary edits, the manager updates the data form related to the focus improvement.
+At this point, a decision needs to be made. The manager can either choose to cancel the process or save the changes. If the decision is to cancel, the process loops back to the focus improvement page. If the decision is to save, the manager previews the edited focus improvement. During this preview, a verification pop-up is displayed.
+Another decision point arises after the preview. The manager can either update the changes or cancel them. If the manager decides to update, the process moves forward to the focus improvement page again, eventually leading to the end of the process. If the decision is to cancel, the process returns to the step of editing the data form for focus improvement.
+The process concludes once the manager has successfully updated the focus improvement and returned to the focus improvement page.</t>
+  </si>
+  <si>
+    <t>2880b7e234cf4d1cae1cdd1ec36abee1</t>
+  </si>
+  <si>
+    <t>The process begins with the customer initiating the action. The customer places an order, which involves queuing and informing the cashier of their desired items. This action generates a document detailing the queue and the order specifics.
+Once the order is placed, the cashier at McDonald's receives the order. The cashier then checks the availability of the meal. At this point, there is a decision to be made: if the meal is not available, the cashier will choose another order and communicate this back to the customer, prompting them to place a new order. If the meal is available, the cashier proceeds to enter the order details into the system.
+Following the entry of order details, the cashier asks the customer for payment. The customer then makes the payment. After the payment is made, the cashier receives the payment and enters the payment information into the system.
+Next, the kitchen staff at McDonald's receives the order and prepares it. Once the order is prepared, it is handed over to the cashier, who then informs the customer that their order is ready for collection. The customer collects the order, marking the end of the process.
+During the payment process, the customer decides on the payment method. They can choose between using an e-wallet, a debit/credit card, or cash. If the customer chooses to pay with cash, the cashier receives the cash and checks if change is needed. If change is needed, the cashier returns the change to the customer. If no change is needed, the cashier returns the receipt to the customer. In both cases, the customer waits for their meal to be prepared.
+If the customer chooses to pay with a debit/credit card, they enter their password, and the cashier returns the receipt. If the customer opts for an e-wallet, they scan a QR code, and the cashier returns the receipt. After receiving the receipt, the customer waits for their meal to be prepared.
+Throughout the process, the customer and the cashier communicate through various message flows, ensuring that each step is completed before moving on to the next. The process concludes with the customer collecting their order.</t>
+  </si>
+  <si>
+    <t>ee048ea75e6948c7bdc72b40427d6dfd</t>
+  </si>
+  <si>
+    <t>The process begins with a customer initiating a request to make a reservation. This is the starting point of the process.
+The customer then places an order for the reservation. This task is performed by the customer.
+Once the order is placed, the airline company acquires the requisition. This task is handled by the airline company.
+Following this, the process splits into two parallel tasks that occur simultaneously. The airline company is responsible for both tasks. One task involves reserving accommodation, while the other involves reserving an airline ticket.
+After both reservations are made, the airline company edits the reservation details in their system.
+Next, the airline company takes payment for the reservation.
+At this point, the process reaches a decision point where the airline company checks if the payment is sufficient. There are two possible outcomes:
+1. If the payment is detected as sufficient, the airline company informs the customer that the reservation is declined and proceeds to cancel the reservation.
+2. If the payment is not sufficient, the airline company detects this and the bank modifies the payment. After the payment is modified, the airline company informs the client about the reservation.
+Finally, the process concludes with the airline company completing the necessary actions based on the payment outcome, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>947b47653378445eb06f47d4363d848d</t>
+  </si>
+  <si>
+    <t>The process begins with students at GG Institute of Arts starting the application procedure. The first step involves students filling out an online form. Once the form is completed, students submit it online. After submission, students are required to print and sign a PDF document. This signed document, along with any necessary attachments, is then posted by the students.
+The next step involves a staff member or clerk at GG Institute of Arts checking the completeness of the submitted documents. If the documents are not complete, the staff member sends an email notification to the students, informing them of the missing documents. The students then need to post the missing documents, after which the completeness check is repeated.
+If the documents are complete, the process moves to the executive of the admission office, who verifies the validity of the certified documents. If the documents are not valid, the executive sends a rejection notification via email, and the process ends there for those applications.
+If the documents are valid, the process continues with the academic committee. The committee decides on the admission offer and then meets to evaluate the participant. Following this evaluation, the committee generates a list of successful and unsuccessful applications. An outcome notification is then sent by email to the applicants, informing them of the result. This marks the end of the process for those applications.
+For applications that are rejected due to invalid documents, the executive of the admission office sends a rejection notification by email, concluding the process for those applicants.</t>
+  </si>
+  <si>
+    <t>a30afaed2e524845ae093459f3f503a3</t>
+  </si>
+  <si>
+    <t>The process begins with the foreman initiating the task of picking up a component known as the Längsträger. Once the Längsträger is picked up, the foreman inserts it into a device called Poka Yoke. The Poka Yoke then scans the pair of components.
+At this point, the process checks if the pair is correct. If the pair is not correct, the Poka Yoke substitutes the incorrect pair and the scanning process is repeated. If the pair is correct, the foreman proceeds to clip an RFID label onto the component.
+After clipping the RFID label, the Poka Yoke reads the RFID label. This reading is also communicated to an IT system known as AC4+. The process then checks if the RFID label is correct. If the RFID label is not correct, the Poka Yoke substitutes the RFID and the label reading is repeated. If the RFID label is correct, the foreman loads the component into an expedition container.
+Following this, a printer prints a rack list. This printed rack list is also communicated to an IT system associated with the printer. The foreman then clips the rack list onto the appropriate location.
+Finally, the process concludes with the foreman completing the task, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>dd81de6e1cf147b79457934cc6480968</t>
+  </si>
+  <si>
+    <t>The process begins with the initiation of the workflow. The first task is performed by an actor who joins data, utilizing three data objects: DM_WUR_PERCEEL_V2, DM_WUR_NDVI_V2, and DM_WUR_GEWAS_V2. Once the data is joined, the next task involves extracting non-centroid parcels. Following this, a user-written task is executed to identify differences.
+After identifying differences, the process reaches a point where two tasks are carried out simultaneously. One task involves extracting total sums, while the other involves extracting maaimomenten. The task of extracting total sums leads to another task where data is joined again. This is followed by extracting weighted averages, and then filtering on grass. Subsequently, a user-written interpolation task is performed, resulting in the creation of a data object labeled ALL_REGIO_GRASS_INTERPOLATED_V4.
+Simultaneously, the task of extracting maaimomenten is followed by extracting weekly differences, which then converges back to the task of joining data. The process concludes after the user-written interpolation task is completed, marking the end of the workflow.</t>
+  </si>
+  <si>
+    <t>875870ab3de2450e830d6243f8f9d212</t>
+  </si>
+  <si>
+    <t>The process begins with the reception team at Hesthals initiating the reception process. The first task involves the reception calling the customer's number. Following this, the reception requests the necessary documents from the customer.
+Once the documents are received, the reception checks the customer's insurance and vehicle tax. After this check, there is a decision point to determine if the information is correct. If the information is correct, the reception proceeds to request payment from the customer. If the information is not correct, the reception turns the customer away.
+If the customer is turned away, another decision is made on whether to call the insurance company. If the decision is to call, the reception arranges for payment. If not, the service is rejected, and the process ends.
+When the information is correct, and payment is requested, the process splits into two simultaneous tasks. The reception provides the customer with a form known as Exhibit 3 and positions the line number for the customer. After these tasks, the reception instructs the customer to return to their car, completing the reception task.
+In parallel, after arranging payment, the reception changes the car status, which leads to restarting the process. The process concludes with the reception task being completed.</t>
+  </si>
+  <si>
+    <t>d8c408c7e7504253bf052eceb786e676</t>
+  </si>
+  <si>
     <t>The process begins with an engineer conducting regular engine checks. The engineer first selects an engine to work on. After selecting the engine, the engineer checks the engine's status.
 At this point, the engineer must decide based on the engine's condition. If a part needs to be replaced, the engineer selects the specific part. If maintenance is required, the engineer checks the end-of-life status of the parts and performs the necessary maintenance. After maintenance, the engineer scans the engine, and the process concludes with the problem being fixed.
 If a part replacement is necessary, the engineer selects the part and then faces another decision. If an overhaul is required, the engineer replaces the part and scans the new part. This leads back to the decision about whether an overhaul is needed. If no overhaul is needed and only damage is present, the engineer fills in a claim form, performs a warranty check, and sends the claim to MAN. The process ends with the claim being sent.</t>
+  </si>
+  <si>
+    <t>69a6f00c8edb4c44874fe1f7181fdc23</t>
+  </si>
+  <si>
+    <t>The process begins with a barista who is ready to serve customers. When a customer arrives, the barista records the order in the register. Once the order is recorded, the process splits into two tasks that happen at the same time.
+The first task involves preparing the coffee. The barista fills a cup with coffee and then puts a lid on it. After the coffee is ready, it is delivered to the customer.
+Simultaneously, the second task involves handling the muffin order. The barista retrieves a muffin and places it in a bag. Once the muffin is bagged, it is also delivered to the customer.
+After delivering the items, the barista accepts payment from the customer. The payment can be made using one of three methods: credit card, cash, or gift card. Regardless of the payment method chosen, the barista provides a receipt to the customer.
+Finally, the process concludes with the customer receiving their receipt, marking the end of the transaction.</t>
+  </si>
+  <si>
+    <t>ee097c609dea4c52a6e7a941627332a6</t>
+  </si>
+  <si>
+    <t>The process begins with Junior Ecologists selecting a species list. They then enter species information from an external source. This information is sent to an Excel Tool, which searches the "Base Data" for the species name.
+At this point, the process branches based on whether the species is found in the "Base Data." If the species is found, the Excel Tool sends a message saying "Right On!" and displays this message. If the species is not found, the Excel Tool sends a message saying "Fix it Dude" and displays this message.
+After displaying the message, Junior Ecologists receive feedback. They then check if the spelling of the species name is correct. If the spelling is correct, they move to the next section, and the process ends successfully.
+If the spelling is incorrect, Junior Ecologists check the spelling against the "Base Data." This leads to another decision point. If a similar name is found in the "Base Data," Junior Ecologists adjust the name in the "Species List" and move to the next section, ending the process successfully.
+If no similar name is found, Junior Ecologists notify a Senior Ecologist. The Senior Ecologist receives the notification and adjusts the "Base Data." They then save the changes and notify the Junior Ecologist. Upon receiving this notification, the Junior Ecologist restarts the process by entering species information from the external source again.</t>
+  </si>
+  <si>
+    <t>659bdd2ae4ce46af834eaecdf4a26038</t>
+  </si>
+  <si>
+    <t>The process begins with the Human Resources Department identifying a job vacancy. They proceed to create a job advertisement. Once the advertisement is ready, it is placed by the Human Resources Department.
+After the job advert is placed, the Human Resources Department waits to receive applications. Upon receiving an application, they check if it was submitted within the deadline. If the application is not within the deadline, the Human Resources Department rejects the application and sends a rejection letter to the applicant.
+If the application is within the deadline, the Human Resources Department assesses the application for suitability. The Interviewing Panel then takes over to assess the applications further and creates a shortlist of candidates.
+The Interviewing Panel checks if an applicant is on the shortlist. If the applicant is not on the shortlist, the application is rejected, and a rejection letter is sent. If the applicant is on the shortlist, the Interviewing Panel sends an invitation to attend an interview.
+The process then splits into two parallel paths. The Interviewing Panel conducts interviews with the candidate, while the Human Resources Department also interviews the candidate. After the interviews, the Human Resources Department collects feedback.
+Based on the feedback, the Human Resources Department decides if the candidate is accepted. If the candidate is not accepted, a rejection letter is sent. If the candidate is accepted, the Human Resources Department sends an offer letter.
+Meanwhile, the applicant, upon noticing the job vacancy, creates an application and replies to the advert with their application. If they receive an interview invitation, they attend the interview.
+The process concludes with the Interviewing Panel ending their involvement after conducting interviews.</t>
+  </si>
+  <si>
+    <t>663ef9193c9b471a87c214bf2ea14489</t>
+  </si>
+  <si>
+    <t>The business process begins with the Auction Service initiating a timer. Once the timer starts, the Auction Service checks the duration time to determine if the auction period has ended.
+At this point, a decision is made. If the time is up, the Auction Service proceeds to inform the winner of the auction. After informing the winner, the process concludes with a message indicating the end of the auction.
+If the time is not up, the Auction Service checks if there is a new bidder. If there is no new bidder, the process loops back to checking the duration time again.
+If there is a new bidder, the Auction Service receives the buyer's maximum price. The next step involves comparing this maximum price with the highest bidders' prices.
+Another decision is made here. If the buyer's maximum is not the highest, the Auction Service increases the buyer's maximum by one increment and then outbids the buyer. Following this, a notification is sent to the buyer, and the process ends with a message indicating the end of the auction.
+If the buyer's maximum is the highest, the Auction Service bids on behalf of the buyer by a small increment above the closest competitor's highest bid. Subsequently, the previous maximum is set as a new minimum, and the process loops back to checking the duration time again.</t>
+  </si>
+  <si>
+    <t>e8fc095af9734c7598bbd88eaac97421</t>
+  </si>
+  <si>
+    <t>The process begins when there is a need for training. The first step involves a supervisor selecting a training vendor. Once the vendor is chosen, the next task is to fill out a training request form. After completing the form, it is sent to the supervisor for review.
+The supervisor then checks if the proposed training is appropriate. At this point, there is a decision to be made. If the training is deemed appropriate, the process continues to the next step. If not, the approval is denied, and the reason for denial is communicated. This concludes the process without scheduling the training.
+If the training is appropriate, the next step is to check if there is enough budget available. Another decision is made here. If the budget is sufficient, the training is approved. If the budget is not enough, the process follows the same path as when the training is not appropriate, leading to denial and communication of the reason.
+Once the training is approved, the supervisor is notified. Following this notification, the training is scheduled. The process concludes with the training being successfully scheduled.</t>
+  </si>
+  <si>
+    <t>3b239cd2ee9a422687c65c2558f81462</t>
+  </si>
+  <si>
+    <t>The process begins with an employee initiating the procedure by sending a holiday application. Once the application is sent, an administrative assistant receives it. The assistant then files the application and forwards it to the current manager.
+The supervisor, acting as the manager, receives the holiday application and examines it thoroughly. After reviewing the application, the supervisor reaches a decision point. There are two possible outcomes from this decision:
+1. If the application is accepted, the supervisor proceeds to the next step where the HR department receives the accepted conclusion and updates the databases accordingly. Following this, the HR department informs the applicant about the acceptance. The employee then receives an approval notification, marking the end of the process.
+2. If the application is declined, the supervisor forwards the declined application to the administrative assistant. The assistant receives the conclusion and the original application, classifies them, and forwards them to the employee. The employee then receives a decline letter, which also leads to the end of the process.
+In summary, the process involves the employee, administrative assistant, supervisor, and HR department, each playing a specific role in handling the holiday application from submission to final notification. The process concludes once the employee is informed of the decision, whether it is an approval or a decline.</t>
+  </si>
+  <si>
+    <t>0fe73faca0fd4b85b7b1ba795871ff46</t>
+  </si>
+  <si>
+    <t>The process begins when the information systems of Immigration Wonderland receive an online application. The information systems then fetch the details of this new application. After retrieving the details, the information systems create a PDF document of the application. Once the document is prepared, the information systems notify a junior officer about the new application.
+The junior officer receives the notification and proceeds to check the completeness of the document. At this point, there is a decision to be made based on the completeness of the application. If the application is incomplete, the junior officer notifies the applicant to provide the missing documents. The applicant then sends the missing documents back to the junior officer, who rechecks the document completeness.
+If the application is complete, the junior officer sends it to a senior officer. The senior officer receives the application and checks the validity of the information provided. Another decision point arises here. If the information is not valid, the senior officer rejects the application, and the information systems notify the applicant of the rejection. This concludes the process for applications with invalid information.
+If the information is valid, the senior officer conditionally approves the application. The junior officer then checks the database to see if the applicant has passed the "Life in Wonderland" test. If the test is not passed, the information systems notify the applicant of the rejection, ending the process.
+If the applicant has passed the test, the junior officer sends a confirmation to the applicant, marking the end of the process with the confirmation received by the applicant.</t>
+  </si>
+  <si>
+    <t>a8902208793d43d5854db238120279f1</t>
+  </si>
+  <si>
+    <t>The process begins with a Function Developer initiating the task of collecting Lessons Learned (LL). Once the collection is complete, the Function Developer proceeds to check the LL.
+At this point, the Function Developer evaluates whether the LL is useful for other areas. If it is deemed useful, the Function Developer inserts and tracks the LL in the system. Following this, a Coordinator makes a decision about further handling.
+The process then splits into two parallel paths. In one path, the Coordinator checks for any LL issues. If issues are found, the Process Owner tracks the LL internally within the project. The Coordinator then checks the LL status. If the LL transfer is not complete, the process loops back to tracking the LL internally. If the transfer is complete, the Coordinator fixes any issues, leading to the end of this path.
+Simultaneously, in the other path, the Coordinator checks if the LL issue needs to be transferred to an interim magazine. If necessary, a Function Developer documents the issue within a "Lessons Learned Report." The Coordinator then tracks the LL internally within the project, which leads to the end of this path.
+If the LL is not useful for other areas, the Project Manager tracks the LL internally within the project. The Project Manager then discusses the matter with project management and fixes any project-related issues, concluding this path of the process.</t>
+  </si>
+  <si>
+    <t>6301a8f360854cf39e9df4f0341990ec</t>
+  </si>
+  <si>
+    <t>The process begins when the lender initiates the business loan tracker. The lender then tracks the loan process files to ensure everything is in order. Following this, the lender sends the application status to the relevant parties. Next, the lender updates the customer's information in the tracker to keep records current.
+The process then moves to the risk assessment team, who carry out a loan assessment. After the assessment, a decision point is reached. If the file is assessed, the risk assessment team updates the status in the tracker. This update is then sent to the loan center, where the file is received, and customer information is processed. If there is no tracker update, the loan document processing occurs at the loan center.
+At the loan center, customer information is received, and any required customer documents are identified. Existing customer information is referenced as needed. If manual data entry is required, it is performed to ensure all data is accurate. Once the files are error-free, they are sent back to the lender for document re-checking.
+The lender re-checks the documents and reviews them thoroughly. Another decision point is reached: if no errors are found, the documents are reviewed again by the lender. If errors are found, corrections are made at the loan center, and the documents are sent back for re-checking.
+Once the documents are reviewed again and verified by the lender, an intermediate message is sent to the customer for application approval. The lender then assesses the documents again for completeness and accuracy. Finally, the process concludes with the creation of the final loan document. Throughout the process, assumptions are made to streamline document checks once cleared by the risk assessment team, aiming to save time.</t>
+  </si>
+  <si>
+    <t>0396fb06704347bf9bf47c2aa4f79379</t>
+  </si>
+  <si>
+    <t>The process begins when the picker receives an order displayed on their reader. This marks the start of the workflow.
+Next, the process splits into two parallel paths. In the first path, the picker takes a dry box. They then proceed to collect goods from the shelves and place them into the box. After gathering the items, the picker scans both the goods and the box. Once scanned, the picker places the box onto a conveyor belt. The conveyor belt, using barcodes, directs all goods of a single order to an assigned cash register. At this point, the cashier receives the sorted box.
+The cashier then checks out the order using the system. After checkout, the cashier places the items into bags. These bags are then put away into buffer areas located next to the cash registers.
+Simultaneously, in the second path, couriers (drivers) arrive at the ramp. They locate the orders in one assigned buffer, which is determined by the system. This path concludes when the order is ready to be picked up by the courier.
+Both paths eventually converge, ensuring that the order is prepared and ready for the courier to collect.</t>
+  </si>
+  <si>
+    <t>a601e32c53c4467d8ed98f9621036ff4</t>
+  </si>
+  <si>
+    <t>The process begins when a customer makes a claim, which is handled by a Service Center Agent at the Fridge Service Center. The agent first gathers a description of the problem and the type of fridge involved. After obtaining this information, the agent opens a ticket to document the issue.
+Next, the agent generates a ticket number to uniquely identify the case and allocates the ticket for further processing. The ticket is then received by the Local Facility Service, which is also part of the Fridge Service Center.
+The Local Facility Service schedules an appointment to address the issue. After a random period, they check if the customer is at home to proceed with the service. Once confirmed, they inspect the fridge to assess the problem.
+At this point, a decision is made on whether additional parts are necessary. If additional parts are needed, the Local Facility Service orders them and then checks the problem again. If no additional parts are required, they proceed directly to check the problem.
+Following the problem assessment, the Local Facility Service repairs the fridge. After completing the repair, they document a repair report detailing the work done. This report is then sent to the Service Center Agent.
+The Service Center Agent edits the ticket to include the repair details and generates an execution report. They then ask the customer for confirmation of the service completion. Once the customer confirms, the process splits into two parallel tasks.
+In one task, the Service Center Agent edits the ticket to include the customer's confirmation and then closes the ticket, marking the end of the process. In the other task, the agent asks the customer for a service rating. The customer's response is received, and the process concludes with the ticket closure.</t>
+  </si>
+  <si>
+    <t>ee5fa56b9ef74ed3b1f85dcab54fb9b9</t>
+  </si>
+  <si>
+    <t>The process begins with the task of creating a map of application controls. Once this is completed, the next step is to identify the key processes involved. Following this, the control objectives are determined to ensure that the processes are aligned with the desired outcomes.
+After setting the control objectives, the key control is tested to verify its effectiveness. Subsequently, the assertions addressed by the control are also tested to ensure they meet the required standards.
+At this point, a decision is made regarding whether re-performance is needed. If re-performance is necessary, the task of executing re-performance is carried out. Once re-performance is executed, the process continues with understanding and documenting the transaction flow.
+If re-performance is not needed, the process directly moves to understanding and documenting the transaction flow. After documenting the transaction flow, the process is confirmed to ensure accuracy and completeness.
+The next step involves conducting interviews to gather additional insights and information. Following the interviews, individual items are tested to ensure they meet the necessary criteria.
+A decision is then made to determine if the audit evidences are sufficient. If the evidences are deemed sufficient, a review of corrective actions is conducted, and inquiries about their follow-up are made. This leads to the end of the process.
+If the audit evidences are not sufficient, sampling procedures are used to test individual items further. After this additional testing, the process returns to reviewing corrective actions and inquiring about their follow-up, eventually leading to the conclusion of the process.</t>
+  </si>
+  <si>
+    <t>3db43399d426454eb42ba9bd4030bf2f</t>
+  </si>
+  <si>
+    <t>The process begins when a customer arrives at the restaurant. Upon arrival, the staff checks if the customer has a reservation. If the customer has a reservation, the staff confirms it and then takes the customer to their table. If the customer does not have a reservation, the staff checks for available tables. Once a table is available, the staff takes the customer to the table.
+After the customer is seated, the staff introduces the menu to the customer. The customer then places their order, which the staff takes. Once the order is taken, the staff serves the dishes to the customer.
+After the meal, the staff prepares the bill. The bill is then brought to the customer's table. The customer makes the payment for their meal. Once the payment is completed, the customer leaves the restaurant.
+After the customer leaves, the staff cleans the table to prepare it for the next customer. This marks the end of the process.</t>
+  </si>
+  <si>
+    <t>cefef269825442389ec099316243fd76</t>
+  </si>
+  <si>
+    <t>The process begins with a Claim Officer receiving a claim. The Claim Officer then checks if the claimant is insured. At this point, there are two possible outcomes:
+1. If the claimant is insured, the process continues with a Senior Claim Officer evaluating the severity of the claim. Following this evaluation, the Senior Claim Officer sends the relevant forms, which could be simple or complex, to the claimant via the SAP system. Once the forms are returned, the Senior Claim Officer checks them for completeness. If the forms are complete, the claim is registered in the claims management system, and the process is complete. If the forms are not complete, the claimant is informed via the SAP system to update the forms, and the process loops back to the step where the forms are sent to the claimant.
+2. If the claimant is not insured, the Claim Officer informs the claimant that the claim has been rejected via the SAP system, and the process is complete.
+Throughout the process, the Claim Officer and Senior Claim Officer are responsible for ensuring that all necessary steps are followed and that the claimant is kept informed of the status of their claim. The process concludes once the claim is either registered in the system or the claimant is informed of the rejection.</t>
+  </si>
+  <si>
+    <t>192c32688fd843d5b6e0a17118135705</t>
+  </si>
+  <si>
+    <t>The process begins with the China Warehouse receiving a start message. The first task is for the China Warehouse to scan the label of the tracking number. Once the label is scanned, the next step is to identify the customer associated with the parcel.
+After identifying the customer, the China Warehouse calculates the volume and weight of the parcel. Following this, a photo of the parcel is taken. The information gathered, including the photo, is then sent to the customer.
+Simultaneously, the China Warehouse updates the status to "wait for customer to fulfill" and asks the customer to provide additional details. At this point, there is a decision to be made: if the customer fulfills the details, the parcel's status is changed to "Ready for delivery to New Zealand." If the details are not fulfilled, the parcel is placed in the unknown parcel area, and the process ends with the parcel being declined.
+If the parcel is ready for delivery, the China Warehouse receives confirmation from the customer for the parcel list to be sent to New Zealand. Another decision is made regarding the mode of transport: by sea or by air. If by sea, the fee is calculated according to sea freight rules. If by air, the fee is calculated according to air freight rules. In both cases, an email detailing the fee is sent to the accountant.
+The accountant then generates an invoice and sends a message to the customer. Upon receiving payment, the accountant notifies the China Warehouse that the order is ready to ship. The China Warehouse repackages the parcels and decides again on the mode of transport: by sea or by air. If by sea, the parcels are put into a container; if by air, they are placed on a pallet.
+The parcels are then sent to the agent freight company warehouse, and a notification is sent to the New Zealand operation team. The New Zealand operation team prepares the clearance document and sends it to New Zealand customs. If the parcel is approved by customs, the New Zealand operation team receives confirmation to release the parcels and dispatches them to the customer's address, completing the order. If not approved, the customer is notified, and the parcel is discarded, ending the process with the order declined.</t>
+  </si>
+  <si>
+    <t>e2fd6ab82aa74bce9c6fa852e9b17f68</t>
+  </si>
+  <si>
+    <t>The process begins with the Production Designer initiating the task of informing the Purchasing Officer that a component is required. Once informed, the Purchasing Officer checks the availability of the stock.
+After checking the stock, the Purchasing Officer encounters a decision point with three possible outcomes:
+1. If there is no material to replace, the process moves to the task where the Production Planning Manager is informed that production is no longer possible and is stopped.
+2. If a replacement is found, the Purchasing Officer proceeds to key in the master data and creates a new bill of material. This leads to the continuation of production by the Production Planning Manager.
+3. If the material is outsourced, another decision point arises:
+   - If the outsourcing is not approved, the Production Designer informs the Production Planning Manager that production is no longer possible and is stopped.
+   - If the outsourcing is approved, the Production Designer confirms the approval, and the Production Planning Manager continues with the production.
+The process concludes with the Production Planning Manager either stopping or continuing production based on the outcomes of the decision points.</t>
+  </si>
+  <si>
+    <t>ce5eea23801144bbafcfe5bc8539c76a</t>
+  </si>
+  <si>
+    <t>The process begins when a student receives an email about their eligibility to graduate. The student must then decide whether they intend to graduate. If the student chooses not to graduate, they are removed from the list, and the process ends for them.
+If the student decides to graduate, they must declare their intent to graduate. Once this declaration is made, the registrar pulls audits from the eDDS system. After obtaining the audits, the registrar sends graduation verification to the relevant schools.
+The program chair receives the verification form and completes it. Once completed, the form is returned to the registrar. At this point, the registrar checks if the graduation is approved. If the graduation is approved, the registrar updates the Yellow List, and the process concludes with the commencement.
+If the graduation is not approved, the registrar sends an email to the student. The student must then fix any outstanding requirements. After addressing these requirements, the student checks if all requirements are met. If the requirements are not met, the student is removed from the list, ending the process for them.
+If the requirements are met, the student updates the registrar. The registrar then updates the Yellow List, leading to the commencement, which marks the end of the process.</t>
+  </si>
+  <si>
+    <t>a06503d2a935460f930219a268165a14</t>
+  </si>
+  <si>
+    <t>The process begins when a customer approaches the Fly-High Kiosk to initiate a check-in request. The first step involves the kiosk scanning the customer's online ticket. Once the ticket is scanned, the kiosk prompts the customer to confirm their name and flight number.
+At this point, the process reaches a decision point. If the customer indicates that the details are incorrect, the kiosk advises them to proceed to the counter for assistance. If the details are correct, the customer clicks a button to confirm this. If no information is received from the customer, the kiosk remains inactive for five minutes and then displays a message indicating that the process was not fulfilled.
+If the customer confirms that the flight details are correct, the process continues to another decision point regarding luggage. If the customer has luggage to check in, they confirm the number of items at the kiosk. The kiosk then prints baggage tags and advises the customer to proceed to the bag-drop area. The customer takes the baggage tags and their luggage to the bag-drop, completing the check-in process for their luggage.
+If the customer does not have any luggage to check in, they confirm this at the kiosk. The kiosk then advises the customer to proceed directly to the security check, concluding the check-in process for customers without luggage.</t>
+  </si>
+  <si>
+    <t>c112d84b30bb4ea4beb8f319c4eabada</t>
+  </si>
+  <si>
+    <t>The process begins with the ACME Warehouse initiating the resupply cycle. The first task is to check the inventory level. If the inventory is at or below the minimum required level, the process continues to create a purchase order. If the inventory is above the minimum level, the process ends.
+When a purchase order is created, it is then reviewed. During the review, there are two possible outcomes: the purchase order can be approved or rejected. If the purchase order is rejected, it is sent back for rework, after which it is reviewed again. If the purchase order is approved, the next step is to reserve funds for the purchase.
+Once the funds are reserved, the purchase order is sent to the supplier. After sending the purchase order, two tasks occur simultaneously: receiving the invoice and receiving the packaging slip. Both tasks lead to recording the information.
+After recording the information, the reserved funds are released, and payment is issued to the supplier. This marks the end of the process.</t>
+  </si>
+  <si>
+    <t>9ddec87747bf4637b51924e14ca31107</t>
+  </si>
+  <si>
+    <t>The process begins when a customer submits a loan application. Once the application is received, a clerk checks it for completeness. If the application is incomplete, it is returned to the customer for completion. If the application is complete, the clerk proceeds to check the customer's credit history.
+After the credit history is checked, a loan officer assesses the loan application. At this point, there are two possible outcomes. If the credit is denied, the customer is notified of the decision. Following this notification, there is a possibility for the customer to request a review of the decision. If a review is requested, the process loops back to the loan assessment by the loan officer. If no review is requested, the loan is considered processed, and the process ends.
+If the credit is extended, a packet containing the offer is sent to the customer. Once the packet is sent, the loan is considered processed, and the process concludes.</t>
+  </si>
+  <si>
+    <t>552fceee752c4d9988ace97e9463f344</t>
+  </si>
+  <si>
+    <t>The airport check-in process begins with the passenger deciding how they would like to check in. There are two options available: online check-in or in-person check-in.
+If the passenger chooses online check-in, they must submit and verify their documents online. Once this is completed, they receive their boarding pass. After obtaining the boarding pass, the passenger proceeds to the airport. Upon arrival at the airport, the passenger must determine if they have any luggage. If they do not have luggage, they proceed directly to the security screening of the passenger. If they have luggage, the luggage undergoes a security screening before the passenger proceeds to the security screening.
+If the passenger opts for in-person check-in, they go to the appropriate check-in desk at the airport. At this point, they must decide if they have any luggage. If they do not have luggage, they proceed to document verification. After verifying their documents, they receive their boarding pass. If they have luggage, the luggage undergoes a security check before the passenger proceeds to document verification and receives their boarding pass.
+After receiving the boarding pass, regardless of the check-in method, the passenger undergoes security screening. Following the security screening, the passenger proceeds to the appropriate gate. Finally, the passenger boards the plane, concluding the check-in process.</t>
+  </si>
+  <si>
+    <t>b8475caa0a3f4fe7a1873247964f8a5a</t>
+  </si>
+  <si>
+    <t>The process begins when the Supply Chain Department receives a request to issue materials. The department then navigates to the goods issue section. Once there, they click on the goods issue option.
+At this point, the process splits into two parallel tasks. The Supply Chain Department enters the movement type and the storage location simultaneously. After entering the storage location, they proceed to click the order button. Following this, they enter the production number.
+Next, the department checks the availability of the material inventory. The ERP System then verifies the material inventory. Based on the inventory check, there are two possible outcomes:
+1. If the material inventory is not sufficient, a message is sent indicating that the material is not available, and the process ends there.
+2. If the material inventory is sufficient, the ERP System reduces the inventory for raw materials. It then posts the raw material costs and updates the general ledger account. After these updates, the ERP System posts the goods issue.
+Following the posting of the goods issue, the ERP System generates a document number. The process concludes with the materials being issued. Additionally, a production order is associated with the goods issue posting.</t>
+  </si>
+  <si>
+    <t>8cf7ace8e12f4f29acb30bb9910b53a4</t>
+  </si>
+  <si>
+    <t>The process begins with the staff from another department identifying the need to make a purchase. They start by selecting a sub-module relevant to their needs. Once the sub-module is selected, they reach a decision point where they must choose one of three paths: creating a Material Request (MR), a Bill of Materials (BOM), or a Purchase Request (PR).
+If the decision is to create a PR, the staff enters the PR details and then submits the PR. The Purchase Manager retrieves the submitted PR and reviews it. After reviewing, the Purchase Manager decides whether to approve it. If approved, the Purchase Manager completes the PR, and the process ends. If not approved, the Purchase Manager sends it back to the staff with the reason for rejection, and the process ends there.
+If the decision is to create a BOM, a Product Engineer enters the BOM details and submits it. Once submitted, the process successfully concludes with the creation of the BOM.
+If the decision is to create an MR, the staff enters the MR details and submits it. The Purchase Manager retrieves and reviews the MR, following the same approval process as with the PR. If approved, the Purchase Manager completes the MR, and the process ends. If not approved, it is sent back to the staff with the reason for rejection, concluding the process.</t>
+  </si>
+  <si>
+    <t>c55ede3b5d854c99bcd96dacf4b0c1b9</t>
+  </si>
+  <si>
+    <t>The business process begins with checking the inventory. Once the inventory is checked, an order is created. After creating the order, it is reviewed. 
+Following the review, two tasks occur simultaneously. One task involves reserving funds, and the other involves reprocessing the order. 
+For the task of reserving funds, once completed, the order is sent. After sending the order, two more tasks happen at the same time. One task is receiving the packing slip, and the other is receiving the invoice. 
+Upon receiving the packing slip, it is reported, and then funds are discharged. After discharging the funds, the process moves to issuing payment. 
+Simultaneously, after receiving the invoice, it is reported, which also leads to discharging the funds. 
+Once the funds are discharged, the process continues to issuing payment. 
+Finally, the process concludes after the payment is issued.</t>
+  </si>
+  <si>
+    <t>080284b2437741a89d278a23b13b51ce</t>
+  </si>
+  <si>
+    <t>The process begins with the candidate sending a registration form. Once the form is sent, the election commission receives the applicant form. The election cell then determines the applicant's qualifications.
+At this point, a decision is made by the election cell. If the applicant is not qualified, the election cell detects this and informs the applicant of the reasons for their disqualification. This concludes the process for unqualified applicants.
+If the applicant is qualified, the election cell detects this and notifies the election authority. The election commission then thoroughly reviews the applications. If any application is found to be faulty, the election commission notifies the relevant parties.
+Following this, the election cell generates the outcomes. These outcomes are processed in parallel. One branch involves the election cell publishing the outcome online. Simultaneously, the election cell forwards the outcome to the applicant. Both branches lead to the conclusion of the process.</t>
+  </si>
+  <si>
+    <t>365f66984b454c18a8d3438487cda5a9</t>
+  </si>
+  <si>
+    <t>The hospital procurement process begins with the hospital labeling RFID tags for existing products. Once the products are labeled, the hospital automatically tracks and manages these items. Following this, the hospital conducts an assessment of order requirements. During this task, details of suppliers are referenced.
+Next, the process reaches a decision point. If items are out of stock, the E-Procurement system automatically calculates the forecasted cost and creates a new order. The system then checks long-term suppliers using RFID tags and updates the inventory automatically. Another decision point follows: if items are in stock, the process proceeds to email suppliers. If items are out of stock, the E-Procurement system selects suppliers based on business rules, confirms the new supplier, and cancels the old order before emailing suppliers.
+If the items are in stock after the inventory update, the process continues with the supplier receiving the order along with a Goods Received Note (GRN) form. The E-Procurement system then uses RFID tags to track items and checks if they meet product requirements. If they do, the supplier is contacted to solve any problems. If they do not meet requirements, the system adds items to the system and emails a receipt of e-invoices.
+The process then checks whether e-invoices match with the Purchase Order (PO) and GRN. If there are errors, the E-Procurement system contacts suppliers to resolve them. If there are no errors, the supplier is paid, marking the end of the process. Throughout the process, various documents such as invitations to tender and e-invoices are generated and referenced.</t>
+  </si>
+  <si>
+    <t>381801f4fae447889fb0ea36001c27be</t>
+  </si>
+  <si>
+    <t>The process begins when a customer arrives. The first step involves the customer selecting a coffee or pastry. Once the selection is made, the customer proceeds to order the chosen coffee or pastry.
+After placing the order, there is a waiting period while the customer drives to the window. During this time, the staff prepares the order by filling the coffee or retrieving the pastry. If the preparation takes longer, the staff asks the customer if they would like to wait. If the customer agrees, there is an additional waiting period of five minutes.
+Once the customer reaches the window, the staff hands the order to the customer. Following this, the staff identifies the customer's preferred payment method. At this point, there are three possible payment methods: gift card, credit card, or cash.
+If the customer chooses to pay with a gift card, the staff processes the payment and then returns the card and receipt to the customer. If the customer opts for a credit card, the payment is processed similarly, and the card and receipt are returned. If the customer decides to pay with cash, the staff handles the cash transaction and then returns any change along with the receipt.
+The process concludes once the payment is completed and the customer receives their order and receipt.</t>
+  </si>
+  <si>
+    <t>b154d4c8fa2a4677b37d02f8108b92bd</t>
+  </si>
+  <si>
+    <t>The process begins when the accounting department receives an online order. The first step involves the accounting department sending an invoice to the business unit. Once the business unit receives the invoice, they proceed to order the goods or services.
+After placing the order, the business unit encounters a decision point. They must decide whether to approve the order or not. If the order is approved, the business unit sends the invoice back to the accounting department. If the order is not approved, the business unit also sends the invoice back to the accounting department, but with a note indicating the lack of approval.
+Upon receiving the invoice, the accounting department staff acknowledges receipt and fills in the necessary accounting information on the invoice. Following this, the accounting department pays the supplier and simultaneously updates the accounts payable records.
+The process then reaches another decision point within the accounting department. They must determine if the payment and updates are approved. If approved, the process concludes with the accounting department marking the transaction as approved. If not approved, the accounting department informs the business unit, who then informs the supplier about the situation, bringing the process to an end.</t>
+  </si>
+  <si>
+    <t>ffd1d4e5b137499f8bbd7be5e113887b</t>
+  </si>
+  <si>
+    <t>The process begins when the information system of the company receives an order. Once the order is received, the information system sends a confirmation email to the customer. After sending the confirmation email, the order fulfillment department takes over to pack the product.
+Following the packing of the product, the order fulfillment department checks if bubble packaging is required. This leads to a decision point. If bubble packaging is needed, the order fulfillment department adds bubble protection to the package. If it is not needed, the process skips this step.
+After the decision regarding bubble packaging, the product is passed on to the warehouse staff. The warehouse department then checks the type of courier required for shipping. This leads to another decision point. If a normal courier is chosen, the warehouse department fills in the post label. If a fast courier is selected, the warehouse department prepares the necessary courier paperwork and gets a quote from the contracted courier.
+Regardless of the courier type, the next step involves combining the post paperwork with the packaged goods. Finally, the order is prepared for the warehouse staff to pick up, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>257ede1b23f94c839202dc36f26473d8</t>
+  </si>
+  <si>
+    <t>The process begins when the sales consultant receives the documents for a car rental request. The sales consultant then validates these documents. If the documents are valid, the process continues; if they are invalid, the process ends.
+Once the documents are validated as valid, the sales consultant registers the request. Following this, the sales consultant calculates the final price for the rental. After calculating the price, the sales consultant prints the necessary documents.
+Next, the sales consultant requests payment from the customer. There is a waiting period for the payment terms to be fulfilled. After this period, the sales consultant checks if the payment has been made. If the payment is not made, the process ends. If the payment is made, the sales consultant gives the documents to the parking staff.
+The parking staff then prepares the documents and car keys. The customer is asked to sign the documents. After the customer signs, the parking staff hands over the keys and the car to the customer.
+Later, the returning person returns the car and signs the return papers. Once the return papers are signed, the process is considered fulfilled and comes to an end.</t>
+  </si>
+  <si>
+    <t>0fa69773765e45a68b15a31c52f9dc36</t>
+  </si>
+  <si>
+    <t>The process begins with the start of the season. The first task is to analyze the field, which is carried out by a designated actor. After analyzing the field, a decision is made to determine if the field is ready. If the field is not ready, the task of pruning the tree is performed, followed by applying chemicals. Once these tasks are completed, the process loops back to analyzing the field again.
+If the field is ready, the next step is to remove small fruits. After removing the small fruits, the fruits are collected. Following the collection, the safety standards are checked. If the safety standards are not met, the workers are consulted, and the process returns to the task of removing small fruits.
+If the safety standards are met, the fruits are calibrated. After calibration, the quality of the fruits is controlled. Once the quality control is completed, a decision is made regarding where to export the fruits. If the decision is to package the fruits for national distribution, the fruits are packaged accordingly, and sellers are contacted to complete the process.
+If the decision is to package the fruits for international distribution, the fruits are packaged for international delivery. After packaging, the order is delivered, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>2a8f497c99b345b68f74158e8e35e9a4</t>
+  </si>
+  <si>
+    <t>The process begins with the passenger at home initiating the journey. The passenger has two options for checking in: using a mobile check-in or a web check-in.
+1. **Mobile Check-In**: 
+   - The passenger uses their mobile device to check in. This action generates a 2D barcode, which is sent to the passenger's mobile device.
+   - Upon arrival at the airport (KLIA 2), the passenger proceeds to use a kiosk for check-in.
+   - The passenger prints and collects their boarding pass at KLIA 2.
+2. **Web Check-In**:
+   - The passenger uses a web platform to check in from home.
+   - After checking in online, the passenger prints the boarding pass at home.
+   - The passenger then heads to the airport (KLIA 2) with the printed boarding pass.
+Once at the airport, the passenger encounters a decision point regarding their luggage:
+- **If the passenger has check-in luggage**:
+  - The passenger drops off their baggage at the designated area.
+  - After dropping off the baggage, the passenger proceeds to the next decision point.
+- **If the passenger does not have check-in luggage**:
+  - The passenger directly proceeds to the next decision point.
+The next decision point determines the type of flight:
+- **If the flight is domestic**:
+  - The passenger proceeds to the security check.
+- **If the flight is international**:
+  - The passenger first checks their travel documents.
+  - The passenger then scans their passport and thumbprint.
+  - After completing these steps, the passenger proceeds to the security check.
+After passing through security, the passenger heads to the boarding gate for departure. This marks the end of the process, and the passenger is ready to board their flight.</t>
+  </si>
+  <si>
+    <t>10ec5606971a42bba3dbf7b7c3eda017</t>
+  </si>
+  <si>
+    <t>The process begins when a truck arrives at the goods entry point. The goods entry team is responsible for this initial step.
+Next, the goods entry team assigns an unloading location for the truck. Once the location is assigned, the team proceeds to unload the truck.
+After unloading, the goods entry team checks the goods to ensure everything is complete. Following this, the quality control team takes over to perform a sample control of the goods.
+The quality control team then evaluates whether the goods are satisfactory. If the goods are deemed satisfactory, the quality control team releases the goods. The goods entry team then stores the goods, marking the end of the process with the goods successfully stored.
+If the goods are not satisfactory, the quality control team locks the goods and creates a report for the dispocontrolling team. The dispocontrolling team then clarifies the situation with the supplier and evaluates the supplier's performance.
+After the supplier evaluation, the goods entry team checks if the goods have been picked up. If the goods have been picked up, the goods entry team prepares them for pick-up, leading to the end of the process with the goods being rejected.
+If the goods have not been picked up, the goods entry team scratches the goods, which also leads to the end of the process with the goods being rejected.</t>
+  </si>
+  <si>
+    <t>0eb6dbd2f0ae4339b3bcaa58648ddbfc</t>
+  </si>
+  <si>
+    <t>The process begins with the front office receiving an order. Once the order is received, a front office employee prepares the product specification. After the specification is ready, the front office checks if there are enough materials in the inventory.
+Next, the process splits into two parallel tasks handled by the manufacturing department. One task involves a specialist preparing the active substance, while the other involves a technician preparing the basis of the product. Both tasks proceed independently and simultaneously.
+For the active substance preparation, after the specialist completes this task, they update the inventory. Following the inventory update, the specialist prepares a sample of the product. This sample is then tested by the specialist. If the test fails, the process loops back to the preparation of the active substance. If the test is successful, the specialist prepares the product for the customer.
+Simultaneously, for the basis preparation, after the technician completes this task, they also update the inventory. The basis is then tested, and the process waits for the result. If the result is not satisfactory, the process loops back to the preparation of the basis. If the result is satisfactory, the process continues to the preparation of the sample.
+Once both the active substance and the basis are successfully prepared and tested, the manufacturing department hands over the product to the front office. The front office then prepares the package for the customer. Finally, the process concludes with the completion of the package preparation.</t>
+  </si>
+  <si>
+    <t>99045ae01e524bfbb067dae6996637d3</t>
+  </si>
+  <si>
+    <t>The process begins with the execution of a project. Once the project is initiated, several tasks are carried out simultaneously.
+1. One task involves writing the final report, which takes 20 units of time. After the report is written, it is uploaded to the project database, taking an additional 0.5 units of time. Once uploaded, a notification is sent to the national team, which takes 0.5 units of time.
+2. Another task is to fix a date for an internal presentation, which takes 1 unit of time. After setting the date, the work is presented to all members, taking 0.5 units of time.
+3. A separate task involves updating the project database, which takes 0.5 units of time.
+4. Additionally, an evaluation questionnaire is sent to team members, taking 0.5 units of time. Once the questionnaire is received, it is filled out, taking 5 units of time. The filled questionnaire is then sent to HR, taking 0.5 units of time.
+5. Lastly, a task involves writing text for the website, which takes 10 units of time. After the text is written, it is sent to the national team, taking 0.5 units of time.
+All these tasks, once completed, lead to the conclusion of the project.</t>
+  </si>
+  <si>
+    <t>4b69ca8c3ed1435a92b24d9e0d7d5086</t>
+  </si>
+  <si>
+    <t>The process begins when a tax consultant receives documents from a client. The tax consultant then checks the completeness of these documents. If the documents are complete, the tax consultant sends them to their assistant. The assistant receives the documents and familiarizes themselves with them.
+At this point, the assistant decides whether they have any questions. If there are no questions, the assistant proceeds to create the tax declaration and sends it to the IRS. The IRS receives the tax declaration, processes it, and creates the client's tax return. The IRS then sends the tax return back to the assistant.
+Upon receiving the tax return, the assistant checks it. After checking, two tasks occur simultaneously: the assistant makes a copy of the tax return for the tax consulting office and sends the tax return to the client. This marks the end of the process.
+If the assistant has questions after familiarizing themselves with the documents, they note these questions on a pad and send them to the tax consultant. The tax consultant answers the questions and sends the responses back to the assistant, who then continues with the process of creating the tax declaration.
+If the initial check by the tax consultant finds that the documents are incomplete, they create a list of missing documents and send a letter to the client. The process then waits for the client's response before returning to the step of checking the completeness of the documents.</t>
+  </si>
+  <si>
+    <t>8010792df10c43dfab130131e36744d6</t>
+  </si>
+  <si>
+    <t>The process begins when a customer identifies the need for a locker. The customer then searches for locker providers. Upon finding potential providers, the customer contacts our company. Our company responds by identifying the client's needs and submitting offers.
+The customer considers the available solutions. At this point, the customer decides whether the company's offer meets their needs. If the offer does not meet their needs, the process ends. If the offer is satisfactory, the customer accepts the offer.
+Following acceptance, our company creates a contract and sends it to the customer. The customer then signs the contract. Once the contract is signed, our company initiates the locker design process.
+After the design process, the customer reviews and accepts the final design. The customer then makes a prepayment for the locker. At this stage, two parallel activities occur simultaneously.
+Firstly, our company begins software customization. Once the software is customized, the customer accepts the customization. Our company then creates a client software package and installs it. The customer conducts acceptance testing to ensure everything is in order. If successful, this part of the process concludes.
+Simultaneously, our company places a manufacturing order. HansaAB AS, a partner company, handles the locker manufacturing, assembly, and delivery. Finally, HansaAB AS installs the locker. The process concludes with the customer's acceptance testing of the installed locker and software.</t>
+  </si>
+  <si>
+    <t>f186ed179743406583486f9665f9b14a</t>
+  </si>
+  <si>
+    <t>The process begins when a person submits a request for legal help. This request is then reviewed by a legal assistant to determine the legal requirements associated with it. At this point, the process reaches a decision point where the legal assistant evaluates whether the request for help is possible.
+If the request is deemed not possible, the legal assistant proceeds to refuse the legal help request. This refusal is then communicated to the relevant parties.
+If the request is possible, the legal assistant identifies the specific requirements and provides a reference for the customer. Following this, the legal assistant outlines the necessities of the request and prepares a statement of legal facts. An application bill is then identified, and the legal help documents are signed.
+Once the documents are signed, they are handed over to the requesting body. The legal authority then collects these documents and checks the request requirements. Another decision point is reached where the legal authority assesses whether the legal help request is complete.
+If the request is not complete, the legal authority refuses the legal help request. If the request is complete, the legal authority proceeds with making a decision. The result of this decision is then shared by the legal assistant, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>e64bd459cfd4440fabc1a78bc921f073</t>
+  </si>
+  <si>
+    <t>The process begins when a customer places an order. The first step involves gathering orders from all sales channels. Once all orders are collected, the next task is to check the inventory to ensure that the items are available.
+At this point, a decision is made based on the inventory check. If the stock is sufficient, the order information is sent to the warehouse. The warehouse then picks the items needed for the order. After picking the items, they are parked as parcels.
+Following this, the process splits into four simultaneous tasks. The first task is to load the parcels onto a truck. The second task involves giving delivery instructions to the transporter. The third task is to update the shipping status. The fourth task is to adjust the stock level to reflect the items that have been picked and shipped.
+If the initial inventory check reveals that the stock is insufficient, an inventory order is created. This order is then sent to a supplier. Another decision point occurs here: if the supplier can fulfill the request, the inventory is sent to the warehouse, and the process continues with picking the items. If the supplier cannot fulfill the request, another supplier is chosen, and the order is sent again.
+The process concludes when all tasks are completed, and the order is shipped.</t>
+  </si>
+  <si>
+    <t>85fc17ee78494a77bab34650f7c5566d</t>
+  </si>
+  <si>
+    <t>The process begins when an employee submits a travel request. The first step is to determine if the travel advance requested is under the specified limit. If the advance is not under the limit, the employee must modify the travel request. If the advance is under the limit, the request moves forward for validation by a manager.
+The manager then validates the travel request. If the request is rejected, the manager notifies the employee of the rejection, and the process ends with the request being marked as rejected. If the request needs modification, it is sent back to the employee for changes. If the request is approved, the manager notifies the employee of the approval.
+Once approved, a planner prepares the booking information. The planner then books the tickets and hotel accommodations. After booking, the planner arranges the travel advance. The employee then prepares the necessary documents for validation.
+The manager validates the booking. If the booking is rejected, the process ends with the request being marked as rejected. If modifications are needed, the planner revisits the booking information. If the booking is approved, the process continues.
+Upon approval of the booking, an accountant pays for the travel. The planner then confirms the booking. Following confirmation, the manager sends a message to the employee, informing them that the travel arrangements are complete. The process concludes with the request being marked as completed.
+If at any point the booking validation is not completed within seven days, the request is automatically rejected.</t>
+  </si>
+  <si>
+    <t>6e22c064ee534815a0594cb2cdf5e31e</t>
+  </si>
+  <si>
+    <t>The process begins with a data collector needing to determine the verified default date. The data collector starts by copying the customer ID from a template. Next, they proceed to the Archives II - KUUA to continue the process. Once there, the data collector pastes the ID into the search function to find relevant documents.
+After pasting the ID, the data collector opens all documents found related to the customer. The next step involves searching for the document with the earliest date when the risk grade dropped to zero.
+At this point, the process branches based on whether a date is found. If a date is found, the data collector uses the exact date when the risk grade goes from one to zero as the verified default date. If a date is not found, the data collector checks the CMS 12-months overview.
+From the CMS overview, another decision is made. If the data collector can determine when the risk grade changed from one to zero, they use the last day of the zero month as the verified default date. If they cannot determine this change, they check if the client has had a default or has been performing.
+If the client is performing, which happens rarely, it indicates that LGD has made a mistake, and the customer is out of scope, making the verified default date unavailable. If the data collector cannot identify the client's status, they use the previous month of the pre-filled default date month as the verified default date.
+The process concludes with the verified default date being determined.</t>
+  </si>
+  <si>
+    <t>a708b49aa0dd41cc98a263d1c95e1403</t>
+  </si>
+  <si>
+    <t>The process begins when a help request is received by the Level 1 Support Staff at the IT Help Desk. The first task for the Level 1 Support Staff is to check if the solution to the problem is already known. 
+At this point, there is a decision to be made. If the solution is found, the Level 1 Support Staff proceeds to solve the problem and then informs the customer that the problem is solved, concluding the process.
+If the solution is unknown, the Level 1 Support Staff forwards the request to the Level 2 Support Staff. The Level 2 Support Staff receives the request and evaluates it. After evaluation, they assign a priority level to the request and enter this information into the job tracking system. The job tracking system then assigns the request to a Level 2 Support Staff member.
+Once the request is assigned, the Level 2 Support Staff receives it and begins researching the problem to develop a solution. After developing a solution, they send it back to the Level 1 Support Staff. The Level 1 Support Staff receives the solution and tests it.
+Another decision point occurs here. If the test is successful, the Level 1 Support Staff informs the customer that the problem is solved, ending the process. If the test is unsuccessful, the request is sent back to the Level 2 Support Staff for further investigation and solution development, repeating the cycle until a successful solution is found.
+Throughout this process, communication between the support staff and the customer is maintained to ensure the problem is resolved efficiently.</t>
+  </si>
+  <si>
+    <t>82ae37ec8d4244d48283ea0ba54f07d7</t>
+  </si>
+  <si>
+    <t>The process begins with a coordinator or intern checking for any new clients or changes. If there are new clients or changes, the coordinator or intern inputs the client information into the database. Once this is done, or if there are no new clients or changes, the coordinator or intern prints all weekly lists, bag tags, and delivery instructions.
+Next, the shift captain collects food. After collecting the food, the shift captain plans the meals. Once the meals are planned, the shift captain cooks the food. After cooking, the shift captain packages the meals.
+Following the packaging, the shift captain drives to the client's home. At this point, there is a decision to be made: if the client is home, the shift captain delivers the meal and food. If the client is not home, the shift captain hangs a door tag.
+If the client is home and the meal is delivered, the shift captain retrieves the containers from the client. After retrieving the containers, or if the client was not home and a door tag was hung, the shift captain edits and returns the delivery report.
+Finally, the process concludes with the coordinator or intern updating the reports.</t>
+  </si>
+  <si>
+    <t>1f19f57766fe482499fff95b4b5ee172</t>
   </si>
   <si>
     <t>The process begins with the PR department initiating the assessment of the company's needs. Once the company's needs are assessed, the process moves forward to a point where two tasks are carried out simultaneously. The PR department assesses the market situation, including offers and feelings, while also assessing customers' feelings and needs.
@@ -195,6 +1210,248 @@
 At this stage, a decision is made regarding the type of customers to target. If the target is current VIP customers, the PR department creates personalized offers. If the target is current customers, the PR department creates general offers. If the target is potential customers, the PR department creates commercials and advertisements.
 Regardless of the type of customer targeted, the next step involves the target audience making decisions and expressing their feelings about the offers or advertisements. The PR department then monitors the outcome of the advertising efforts, evaluating the impact, financial results, and the acquisition of new customers, as well as gathering feedback on feelings.
 Finally, the process concludes with the PR department ending the monitoring phase, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>bbc0fcd2383844fe8ef1bd70502843b5</t>
+  </si>
+  <si>
+    <t>The process begins with the Senior Risk Manager initiating the procedure. The first task involves the Senior Risk Manager performing an automated BKR check. Once this check is completed, the Senior Risk Manager proceeds to perform an automated Jane Doe check. Following this, the Senior Risk Manager conducts a manual credibility check. After the manual check, the Senior Risk Manager confirms the results of the credibility check.
+At this point, a decision is made based on the outcome of the credibility assessment. If the assessment is rejected, the Administrator sends a rejection letter, concluding this branch of the process. If the assessment is accepted, the Customer Responsible contacts the client to gather additional information. After obtaining the necessary information, the Customer Responsible creates a loan offer and subsequently sends it to the client.
+Once the loan offer is sent, there is a decision point. If the client accepts the offer, the Administrator receives the accepted offer. The Administrator then sends a welcome letter to the client. Following this, the Finance Manager activates the loan application and executes the initial payment. Finally, the Administrator returns the documents to the client, marking the end of this branch of the process.
+If there is no immediate response from the client after the loan offer is sent, a timer is set for one hour. After this period, the Customer Responsible reminds the client. This reminder loops back to the decision point regarding the client's response to the loan offer. The process continues until a response is received, leading to either the acceptance or rejection path.</t>
+  </si>
+  <si>
+    <t>6eac3421b2d448748b5097eb336fda1f</t>
+  </si>
+  <si>
+    <t>The process begins when a client identifies a need for help. The client initiates the process by calling the help desk. The IT Help Desk at Level 1 receives the request and gathers the necessary information.
+Next, the IT Help Desk at Level 1 determines whether the request is known. If the request is known, the IT Help Desk at Level 1 sends the developed resolution to the client. If the request is not known, the IT Help Desk at Level 1 emails the request to Level 2 for further assistance.
+Upon receiving the request, the IT Help Desk at Level 2 conducts research and evaluates the situation. After developing a resolution, they send it back to Level 1. The IT Help Desk at Level 1 then receives the developed resolution and sends it to the client.
+The client tests the resolution to see if it resolves the issue. After testing, the client notifies the outcome via email. The IT Help Desk at Level 1 checks if the issue is fixed. If the issue is resolved, the process is marked as complete. If the issue is not resolved, the IT Help Desk at Level 1 sends the request for further action, looping back to the point where Level 2 receives the request for additional evaluation and resolution development. The process continues until the issue is resolved and marked as complete.</t>
+  </si>
+  <si>
+    <t>a128b8b197314ab3a26fa23f68daa8ee</t>
+  </si>
+  <si>
+    <t>The process begins with the customer initiating a request for help. The customer reaches out to the organization to describe the problem they are experiencing.
+Once the request is made, the front office of the organization receives the problem description. The front office then evaluates whether the problem is clear. If the problem is clear, the process moves forward to providing an answer. If the problem is not clear, the front office creates a ticket to document the issue.
+After creating a ticket, the back office is tasked with locating the appropriate product support agents. Once the agents are located, the back office receives the ticket and begins handling the issue. After addressing the issue, the back office documents the outcome of their efforts.
+The process then checks if the issue has been resolved. If the issue is resolved, the front office provides an answer to the customer. If the issue is not resolved, the back office engages in further discussions with the engineering team to find a solution.
+Following further discussions, the process again checks if the issue is resolved. If resolved, the front office provides an answer to the customer. If not resolved, the back office updates the list of product issues and then provides an answer to the customer.
+Finally, the customer receives the answer from the organization, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>e13ef73f335d49a8a7af3fe561737987</t>
+  </si>
+  <si>
+    <t>The process begins with a medic examining a patient. After the examination, a decision is made regarding the patient's health status. If the patient is deemed healthy, an exam form is created, and the patient is released.
+If the patient is not healthy, the process continues with the medic making an exam. Following this, a treatment order is created, and then a petition form is prepared. The patient is then informed about the risks involved.
+At this point, the patient must decide whether to agree to the proposed actions. If the patient does not agree, they are released from the process. If the patient agrees, a delegate arranges an appointment for further procedures.
+Once the appointment is arranged, a nurse takes a sample from the patient. The laboratory then validates the state of the sample. If the sample is not suitable, the process loops back to the nurse taking another sample. If the sample is suitable, it is analyzed.
+After the sample analysis, the results are validated. Based on the validated results, a diagnostic is made. Finally, a therapy is prescribed, concluding the process.</t>
+  </si>
+  <si>
+    <t>b446c2a196c14b55957c421adab5638e</t>
+  </si>
+  <si>
+    <t>The process begins when an employee makes a product purchase. Following this, the employee is responsible for filling out an expense claim. Once the claim is filled out, the employee submits the expense claim form.
+Next, the system checks if the employee has an existing account. At this point, there is a decision to be made: if the employee has an account, the process continues to the financial employee for a report review. If the employee does not have an account, they must create a new account before proceeding to the report review.
+After the report is reviewed by the financial employee, the system evaluates the amount of the claim. If the claim is less than $200, the system automatically approves it. If the claim exceeds $200, a supervisor reviews the approval of the claim.
+The supervisor's review leads to another decision point: if the claim approval is accepted, the system deposits the reimbursement, and the process concludes with the reimbursement claim being completed. If the claim is rejected, the supervisor formally rejects the reimbursement, and the employee receives an email notification about the rejection. The process then ends with the reimbursement claim being completed.</t>
+  </si>
+  <si>
+    <t>c486e638c1de49de9b20bd38e8f81d49</t>
+  </si>
+  <si>
+    <t>The process begins when there is a need for employee training. The first step involves the supervisor selecting a vendor for the training. Once the vendor is chosen, the supervisor fills out a training request form that needs to be approved.
+After the form is completed, two tasks occur simultaneously. The director checks the budget for the training, and the department director evaluates the training itself. These tasks are independent and happen at the same time.
+Once both tasks are completed, a decision is made based on the outcomes. If both the budget check and the training evaluation are satisfactory, the director approves the training. The supervisor is then notified of this approval, and they proceed to schedule the training. This marks the end of the process.
+However, if either the budget check or the training evaluation is not satisfactory, the director does not approve the training. In this case, the supervisor is notified of the disapproval, and they are informed of the reasons for the denial. This also concludes the process.</t>
+  </si>
+  <si>
+    <t>afce9b024b3c4172adcb4f6b1757335f</t>
+  </si>
+  <si>
+    <t>The process begins with a pharmacist reviewing the situation. After this initial review, the pharmacist encounters a decision point. At this decision point, there are two possible paths:
+1. If the pharmacist receives a GP referral, they proceed to receive the GP referral and then move on to receive the medication list.
+2. Alternatively, if the pharmacist receives an online patient request, they handle the request and then proceed to receive the medication list.
+Once the medication list is received, the pharmacist conducts research on the medication. Following this research, the pharmacist prints educational handouts. With the handouts ready, the pharmacist travels to the patient's home.
+Upon arrival at the patient's home, the pharmacist checks the medication situation. After assessing the situation, the pharmacist educates the patient on medication usage and potential side effects. The pharmacist then suggests a medication management plan.
+After completing the tasks at the patient's home, the pharmacist travels back. Upon returning, another decision point is reached. Here, the pharmacist has two options:
+1. If the process is initiated by a patient application, the pharmacist sends a report to the patient.
+2. If the process is initiated by a GP referral, the pharmacist generates a medication report on MyHealthRecord.
+Finally, the process concludes with the application being filled, marking the end of the pharmacist's tasks.</t>
+  </si>
+  <si>
+    <t>42edc42c2e6c415c87b6dec2b2d1c91f</t>
+  </si>
+  <si>
+    <t>The process begins when a client identifies the need for a loan. The client then submits a loan application. At this point, a decision is made on whether the application is submitted online. If the application is not submitted online, the client talks to a loan officer directly. If the application is submitted online, the client proceeds to submit the online application.
+Once the online application is submitted, it is captured by a loan officer at ACME Bank. The loan officer uses the Mortgage Orientation System to assist in capturing the application details. After capturing the application, the loan officer sends an application receipt to the client.
+The loan officer then receives the application and creates a customer record, utilizing the CRM Platform for this task. Following this, the lending operations team at ACME Bank performs a background check on the applicant.
+A decision is then made on whether the business can be conducted legally. If the answer is no, the loan application is rejected, and the client receives a letter informing them of the rejection. This concludes the process with no loan being received.
+If the business can be conducted legally, the loan officer gathers information on the property the applicant is interested in and assesses the applicant's credit risk. The loan officer then reviews all inputs and makes a decision on the application.
+Another decision point occurs to determine if the application is approved. If the application is not approved, the process follows the same path as a legal rejection, with the client receiving a rejection letter. If the application is approved, the loan officer accepts the loan application, and the client receives a letter informing them of the approval. This concludes the process with the application being accepted.</t>
+  </si>
+  <si>
+    <t>39b43a25682f4a69aebe0584ab703040</t>
+  </si>
+  <si>
+    <t>The process begins with an Admin starting the procedure. The Admin then spends 30 minutes initiating a change request. Following this, the Admin must determine whether the change is major or minor. If the change is considered minor, which happens 70% of the time, a Draftsman takes over to make the necessary changes, a task that takes 2 hours. After making the changes, the Draftsman initiates an approval process, which takes 1 hour. A Manager then conducts the approval process, which can take between 20 to 40 minutes.
+Once the approval process is complete, the Draftsman checks if the changes are accepted. If accepted, which occurs 95% of the time, the Draftsman spends 1 hour and 30 minutes checking the changes into the PLM system, concluding this path of the process. If the changes are not accepted, which happens 5% of the time, the process ends without further action.
+If the change is determined to be major, which occurs 30% of the time, Engineers spend approximately 8 hours analyzing and making recommendations. The time can vary by 25%. After the analysis, a Draftsman initiates another approval process, taking 1 hour. The Manager then conducts this approval process, which can take between 45 minutes to 1 hour and 15 minutes.
+Following the approval, the Manager checks if the changes are accepted. If accepted, which happens 60% of the time, the Draftsman documents or updates the changes, a task that takes 8 hours. After documentation, the Draftsman spends 1 hour and 30 minutes checking the changes into the PLM system, concluding this path of the process. If the changes are not accepted, which occurs 40% of the time, the process ends without further action.</t>
+  </si>
+  <si>
+    <t>4fde031ee7a14df6a5f90accda243051</t>
+  </si>
+  <si>
+    <t>The process begins with a Level 1 Employee initiating a client call. After the call, the same employee checks the client's request. At this point, a decision is made: if the request is solvable, the Level 1 Employee proceeds to resolve the issue. If there are no immediate resolutions, the request is forwarded to a Level 2 Employee.
+When the request is forwarded, the Level 2 Employee receives it and evaluates the situation. They then create a priority level for the request and conduct research to understand the problem better. Following this, the Level 2 Employee creates a resolution and sends it back to the Level 1 Employee.
+The Level 1 Employee then reverts back to the client with the resolution. After this, they check the client's feedback. If the issue is resolved according to the client's feedback, the process is marked as complete. If the issue is not resolved, the request is forwarded again to a Level 2 Employee for further evaluation.
+Throughout this process, communication with the client is maintained, ensuring that the client is kept informed and their feedback is considered. The process concludes when the issue is resolved and marked as complete by the Level 1 Employee.</t>
+  </si>
+  <si>
+    <t>8e5b81a49145488693e735e32eb48da5</t>
+  </si>
+  <si>
+    <t>The process begins when a user decides to withdraw cash. The first step involves opening the Sonect feature on the Point of Sale (POS) system. Once this feature is activated, two tasks occur simultaneously.
+The first task is to open the barcode scanner. After the scanner is opened, the cash till is also opened. Following this, a confirmation is obtained, and then the cash is handed out to the user. This sequence of actions concludes the process.
+Simultaneously, the second task involves asking the user for the barcode. The user then generates or displays the barcode on their side. Once the barcode is available, it is scanned. After scanning, the amount to be withdrawn is verified. The correct amount of cash is then prepared. Finally, the request is confirmed through Strong Customer Authentication (SCA), and the process loops back to obtaining confirmation before handing out the cash.
+The process ends once the cash is successfully handed out to the user.</t>
+  </si>
+  <si>
+    <t>3fde31e153584d039958ab3af001f339</t>
+  </si>
+  <si>
+    <t>The process begins when a course request is received. The first task is to book a room, which is handled by the responsible person. Once the room is booked, the next step is to create an account, which is also managed by the designated individual.
+After the account is created, the process splits into three parallel tasks that occur simultaneously. The first task is to set up a registration website. The second task involves creating a course website. The third task is to promote the course. All these tasks are carried out by the respective team members.
+Once these tasks are completed, the process continues with closing the registrations. After closing the registrations, a decision point is reached. If there are insufficient registrations, the course is canceled. The responsible person then cancels the scheduled course and notifies the registered participants, marking the end of the process with the course being canceled.
+If there are sufficient registrations, the process moves forward to manage payments. After managing payments, the process again splits into three parallel tasks. The first task is to print name badges. The second task is to create a blackboard website. The third task is to arrange catering. These tasks are handled by the respective team members.
+Once these tasks are completed, the final step is to deliver the course. After the course is delivered, the process concludes with the course being successfully delivered.</t>
+  </si>
+  <si>
+    <t>e4152a44e9774d1e994b822c3aef83df</t>
+  </si>
+  <si>
+    <t>The process begins with the Hackathon Team planning a hackathon. Once the planning is complete, the team prepares for the hackathon. After preparation, the doors are opened to welcome guests. The Hackathon Team then welcomes the guests and briefs them about the event.
+Following the briefing, the team holds a lecture. After the lecture, the team monitors the idea generation and brainstorming session. At this point, a decision is made on whether enough ideas have been generated. If not, the team generates more ideas and revisits the decision point. If enough ideas have been generated, the gathered ideas are summarized.
+Next, the Hackathon Team subscribes to an idea. A decision is then made on whether more than five subscriptions have been made to an idea. If not, the team subscribes to another idea and revisits the decision point. If there are more than five subscriptions, teams are formed.
+The Hackathon Team supervises the teams as they work. A decision is then made on whether to take a break. If a break is desired, the team takes a break and then continues with team work. If no break is needed, the team continues with their work directly.
+After the team work, the Hackathon Team presents the results. Following the presentation, two parallel tasks occur simultaneously: summarizing and documenting the presented results, and collecting feedback through smileys.
+The summarized results are received by the Product Development team, who then analyze the results. They choose the top two ideas for development and select a winning project from these two. The process concludes with the awarding of a prize.
+Meanwhile, the feedback collection concludes with a debriefing session by the Hackathon Team.</t>
+  </si>
+  <si>
+    <t>c811897bb46e487da757021bced7119d</t>
+  </si>
+  <si>
+    <t>The process begins on March 1st, initiated by the management team of ACME Inc. The first task involves the management specifying the budget for an upcoming event. Once the budget is set, the management team proceeds to establish a date for the event. Following this, the marketing team takes over to specify the event schedule.
+Next, the marketing team is responsible for finding a suitable location for the event. Once a location is identified, they proceed to book it. After booking the location, the process splits into two parallel tasks. The marketing team simultaneously books the catering services and the DJ for the event.
+Once both the catering and DJ are booked, the marketing team enters the final costs into the system. This information is then sent to the management team, who receives the plan and budget details. The management team then decides on the event's placement and checks the plan against the requirements.
+At this point, a decision is made. If everything is okay, the marketing team prepares the invitations and generates a participants list. The invitations are then sent out. After a waiting period of two weeks, the marketing team receives confirmation of attendance.
+Upon receiving confirmation, the process again splits into two parallel tasks. The marketing team handles any cancellation confirmations and decides on the settings arrangements for the event. Simultaneously, they process the confirmations that have come in. Once these tasks are completed, the celebration is organized, marking the end of the process.
+If the plan is not approved, the marketing team cancels the booking, and the process concludes with the decision that the celebration will not be approved.</t>
+  </si>
+  <si>
+    <t>bd01e5bdb1714f83a8d42d4b135186f9</t>
+  </si>
+  <si>
+    <t>The process begins when the Wedding Planner receives a cake order. The Wedding Planner then sends the client's requirements to Jane Doe. Jane Doe analyzes these requirements and prepares a sample. Once the sample is ready, the Assistant receives it and sends it to the client for approval.
+At this point, there is a decision to be made: if the client approves the sample, the process continues; if not, the requirements are sent back to Jane Doe for further analysis and sample preparation.
+If the sample is approved, the process splits into three parallel tasks. The Wedding Planner designs the cake, decides on the color scheme, and the Assistant emails guests to gather an allergy list. After these tasks are completed, the Assistant finalizes the cake plan and sends it to Jane Doe.
+The process then splits again into two parallel tasks. Jane Doe prepares the cake batter and creates the invoice for the cake. The invoice is documented as an output. Jane Doe then bakes the cake in the oven, prepares the cake filling, assembles the cake, and decorates it.
+After the cake is decorated, the Wedding Planner performs a quality check. Following the quality check, the Assistant arranges for the cake's delivery, marking the end of the process with the cake being delivered to the client.</t>
+  </si>
+  <si>
+    <t>415ebec39c364b5f90299aed9b11bb98</t>
+  </si>
+  <si>
+    <t>The process begins when a customer hands a prescription to the pharmacist. The pharmacist receives the prescription and then asks the customer for their Medicare card. Once the card is provided, the pharmacist matches it with the prescription details.
+At this point, the pharmacist checks if the information is verified. If the verification fails, the pharmacist returns the card and prescription to the customer, ending the process without dispensing any medicine. If the verification is successful, the pharmacist determines whether the customer is new or returning.
+If the customer is new, the pharmacist enters the new customer details into the system. For returning customers, the pharmacist enters the customer's name. Following this, the pharmacist enters the prescriber or doctor's details and selects the appropriate medicine.
+The pharmacist then prints labels needed to fill the prescription and obtains the medicine from the shelf. The pharmacist checks if the medicine is available. If it is not available, the pharmacist confirms the stock status in the inventory system. If the medicine is out of stock, the pharmacist informs the customer, and the process ends without the customer receiving the medicine. If the medicine is in stock, the pharmacist locates it.
+Once the medicine is available, the pharmacist scans the medicine's barcode and sticks the printed labels on the medicine box. The pharmacist also prints drug use instructions, which are provided to the customer along with the medicine.
+The pharmacist verifies the customer's medical conditions and provides a consultation on drug consumption. Afterward, the pharmacist hands over the medicine to the customer, who then proceeds to payment. The process concludes with the medicine being dispensed to the customer.</t>
+  </si>
+  <si>
+    <t>1be181ba148f4caab708fab443332493</t>
+  </si>
+  <si>
+    <t>The process begins with the IT Centre receiving the requirement. Once the requirement is received, the IT Centre proceeds to analyze the market. After completing the market analysis, the IT Centre sends the analysis via email.
+The Marketing and Sales Manager receives the market analysis and then proposes a development strategy. This proposed strategy is sent by email to the Process Manager.
+Upon receiving the strategy, the Process Manager implements it in offline retail settings. If the implementation functions well, the Process Manager sends the strategy by email. If it does not function well, the process loops back to the Marketing and Sales Manager to propose a new development strategy.
+Once the strategy is sent by email, the Marketing and Sales Manager receives it and improves it based on the online retail environment. The improved strategy is then sent by email to the IT Centre.
+The IT Centre receives the improved strategy and simulates online retail operations based on it. If the simulation yields good results, the IT Centre informs the Process Manager. If the results are bad, the process loops back to the Marketing and Sales Manager to improve the strategy further.
+When informed of good results, the Process Manager receives the information and implements the strategy in a few online stores. If this implementation proves profitable, the strategy is gradually implemented across all online retail operations. If it is unprofitable, the process loops back to the Marketing and Sales Manager for further improvements.
+Finally, once the strategy is successfully implemented across all online retail operations, the process concludes with the strategy being fulfilled.</t>
+  </si>
+  <si>
+    <t>7baeb920f88745eea8fb739bd925b455</t>
+  </si>
+  <si>
+    <t>The process begins with a customer initiating the task of making a reservation. Once the reservation is made, the customer proceeds to choose their preference for the room.
+At this point, a decision is made to check if the customer's preferred room is fully booked. If the room is not fully booked, the customer can proceed to book the room. If the room is fully booked, the customer must reset their preference and check again if the new preference is fully booked. This cycle continues until a room is available.
+If a room is available, the customer can book the room. After booking, the customer needs to provide their information by typing it in. Following this, the customer must insert their card and input their password.
+Another decision point checks if the password entered is correct. If the password is correct, the booking is successful, and the customer can proceed to get the key from the front desk and go into their room, marking the end of the process.
+If the password is incorrect, the customer is prompted to retype the password. After retyping, if the password is correct, the process continues with the booking being successful. If the password is still incorrect, the process ends with the customer needing to check with their bank to understand what happened with the card.
+If at any point there are no rooms available, the process ends by showing the nearest Hilton or logging out.</t>
+  </si>
+  <si>
+    <t>11ef1dbacfab4ed784a40315315aea76</t>
+  </si>
+  <si>
+    <t>The process begins with the manager initiating the order preparation. The manager is responsible for tasting the cake, tasting the cream, and ensuring the decoration is appropriate. Once the manager has completed these tasks, a decision is made regarding the type of cake being prepared. 
+If the cake is a special cake, the cook takes over to prepare the cake. After the cake preparation, the process splits into two simultaneous tasks: baking the cake and preparing the cream. The oven bakes the cake, while the cook prepares the cream. Once both tasks are completed, the process continues with the cook making decorations and the helper spreading cream between different layers. The helper then covers the cake with frosting and adds decorations. 
+If the cake is a standard cake, the process also splits into two simultaneous tasks: the helper prepares the cake, and the cook prepares the cream. The oven bakes the cake, and once both tasks are completed, the process continues with the helper spreading cream between different layers. The helper then covers the cake with frosting and adds decorations.
+After the cake is decorated, the manager checks the quality of the finished product. If the quality is satisfactory, the manager updates the order status to 'finished.' Finally, the process concludes with the manager marking the end of the process.</t>
+  </si>
+  <si>
+    <t>45694a407bed4df1b789e16fc0ea5ec6</t>
+  </si>
+  <si>
+    <t>The process begins with a user initiating the connection to the management system. Once connected, the stock management system reads an order from the system. The system then checks if this is the first order in stock. If it is not the first order, the stock management system contacts the wholesaler and places a reorder. If it is the first order, the system proceeds to browse the warehouse.
+After browsing, the stock management system withdraws the product from the warehouse. The system then evaluates the arrival time of the product. If the product is expected to arrive in more than 10 days, a delivery delay penalty is applied from the wholesaler. If the product arrives within 10 days, the stock management system gives the approval for the arrived product.
+Following approval, the product is registered in the management system. The user then checks if the product is ready for shipment. If it is not ready, the process loops back to reading the order from the system. If it is ready, two tasks are carried out simultaneously: the user requests a courier and packs the product.
+Once the product is packed, it is shipped for delivery. The process concludes with the successful delivery of the product.</t>
+  </si>
+  <si>
+    <t>ef4c027c3a8041f1a6939966b06ca682</t>
+  </si>
+  <si>
+    <t>The process begins when a pharmacist receives a prescription. The pharmacist then examines the prescription to ensure its validity. If the prescription is not valid, the process ends with the prescription remaining unfilled. If the prescription is valid, the pharmacist proceeds to check the customer's details.
+Next, the pharmacist determines whether the customer is new. If the customer is new, the pharmacist adds the customer's details. Following this, the pharmacist checks if the prescribing doctor is new. If the doctor is new, the pharmacist adds the doctor's details. After these details are added, the pharmacist proceeds to add the prescription details.
+Once the prescription details are added, the pharmacist prints the necessary labels. The pharmacist then checks if the prescribed drug is in stock. If the drug is out of stock, the pharmacist informs the customer of alternative options, and the process ends with the prescription unfilled. If the drug is in stock, the pharmacist picks up the drug.
+After picking up the drug, the pharmacist verifies that the correct drug has been picked up. If the wrong drug is picked up, the pharmacist retrieves the correct drug. Once the correct drug is confirmed, the pharmacist attaches the printed labels to the drug.
+The pharmacist then prints the Consumer Medicine Information (CMI) and prepares the prescription basket. Finally, the pharmacist provides the customer with directions for using the medication. The process concludes with the prescription being successfully filled for the patient.</t>
+  </si>
+  <si>
+    <t>9f992e72a99044318c76da9c3e88cc1d</t>
+  </si>
+  <si>
+    <t>The process begins when Jane Doe receives a request. She starts by checking the computer. After this, she encounters a decision point where she must determine if the computer is new or used.
+If the computer is used, Jane Doe backs up data from the user profile. She then updates the BlueCat information and verifies the details in Ivanti. Following this, she configures the BIOS and verifies or installs any necessary computer add-ons. Next, she adds a description to the computer and checks for any client software requests.
+At this point, another decision is made. If the client has software requests, Jane Doe adds the required software. If there are no requests, she proceeds to activate the directory. After activation, she checks for finalization.
+If the process is finalized, the imaging is completed. If not, Jane Doe transfers data and moves the IP in BlueCat to its previous location before completing the imaging.
+If the computer is new, Jane Doe tags the item, adds the IP to BlueCat, and includes it in Baremetal in Ivanti. She then configures the BIOS and verifies or installs any necessary computer add-ons. Following this, she adds a description to the computer and checks for any client software requests.
+Again, if the client has software requests, Jane Doe adds the required software. If there are no requests, she activates the directory and checks for finalization. If finalized, the imaging is completed. If not, she transfers data and moves the IP in BlueCat to its previous location before completing the imaging.
+Throughout the process, Jane Doe is responsible for each task, ensuring that all steps are completed accurately and efficiently.</t>
+  </si>
+  <si>
+    <t>a990204e0055488383f86b9af9e20150</t>
+  </si>
+  <si>
+    <t>The process begins with a passenger or traveler starting their journey at KLIA 2. The first step involves the passenger performing a self check-in. After completing the self check-in, the passenger reaches a decision point where they must choose one of three check-in methods: web check-in, mobile check-in, or kiosk check-in.
+If the passenger chooses web check-in, they proceed to print their boarding pass at home. Once printed, they move on to the next step, which is checking in their luggage at the departure hall.
+If the passenger opts for mobile check-in, they generate a 2D barcode on their mobile device. This barcode is then used to proceed to the next step, which involves a time constraint where the check-in process must be completed 60 minutes before departure. Following this, the passenger performs a kiosk check-in, prints, and collects their boarding pass, and then checks in their luggage.
+If the passenger selects kiosk check-in directly, they proceed to print and collect their boarding pass at the kiosk and then check in their luggage.
+After checking in luggage, the passenger encounters another decision point: whether they have check-in baggage. If they do, they drop off their baggage at the designated area. If they do not have check-in baggage, they proceed to the next decision point, which determines if their flight is international or domestic.
+For international flights, the passenger's travel documents are checked, followed by an immigration check. After passing through immigration, they proceed to security screening, where their hand luggage and body are checked.
+For domestic flights, the passenger directly proceeds to security screening without the need for document or immigration checks.
+After passing security screening, the passenger waits until 20 minutes before departure. At this point, they enter the boarding gate, marking the end of the process at KLIA 2.</t>
+  </si>
+  <si>
+    <t>644ff4ec9fd244879fd60f823763bf88</t>
   </si>
   <si>
     <t>The process begins with the ACME Warehouse initiating the resupply cycle. The first task is to check the current inventory. After checking the inventory, a decision is made to determine if the inventory is at or below the minimum required level.
@@ -205,6 +1462,370 @@
 Simultaneously, after receiving the packing slip, it is recorded. This task also leads to the release of reserved funds and the issuance of payment to the supplier, marking the end of the process.</t>
   </si>
   <si>
+    <t>af94d71112594cefb93817d8bc844362</t>
+  </si>
+  <si>
+    <t>The process begins when a formalized application is received. The first step involves conducting credit checks. If the credit check reveals an unacceptable risk, the application is rejected, and the process ends with the application being marked as rejected.
+If the credit check shows an acceptable risk, the next step is to arrange a customer reference report. Once the report is arranged, it is evaluated. If the reference report is unsatisfactory, the application is rejected, and the process concludes with the application being marked as rejected.
+If the reference report is satisfactory, the complete submission is reviewed. If the review is unsuccessful, the application is rejected, and the process ends with the application being marked as rejected.
+If the review is successful, the client is advised of the loan offer. The client then has the opportunity to accept the offer. Once the client accepts the offer, two tasks occur simultaneously: preparing legal documents and collecting the initial loan fee.
+After the legal documents are prepared, and the initial loan fee is collected, an online customer profile is created. Following this, a document is sent to the loan center, marking the end of the process with the document being sent to the loan center.</t>
+  </si>
+  <si>
+    <t>ffe9c97d57014ec5864fb39153a6fab6</t>
+  </si>
+  <si>
+    <t>The process begins when the sales department receives a purchase order. The sales team then checks the order to ensure everything is correct. At this point, a decision is made: if the order is not acceptable, the sales team will reject the order, and the process ends there. If the order is acceptable, the sales team confirms the order and inputs it into the ERP system.
+Once the order is in the ERP system, the system performs necessary IT tasks. Afterward, two activities occur simultaneously: the ERP system generates a production order for ME &amp; MII, and it also emits an invoice. The production team then initializes the process at the magazine.
+The production team checks if the product is black. If it is black, they proceed to load the magazine with the Bund cover. If it is not black, manual work is required to cover the Bund with a different color. Following this, the production team drills the necessary parts and assembles them using a robot. A camera check is then conducted to ensure quality.
+If the product passes the camera check, it moves on to packaging. If it does not pass, manual rework is required. After rework, if the product has been reworked less than three times, it goes back to the robot assembly stage. If it has been reworked three times, the product is scrapped, and the process ends.
+Once the product is packaged, the distribution team ships the goods, marking the order as fulfilled. Meanwhile, the ERP system waits for payment. Once payment is received, the process concludes with the shipment of goods.</t>
+  </si>
+  <si>
+    <t>2d5a6476e6184d16bbeb5c916d82b3da</t>
+  </si>
+  <si>
+    <t>The process begins when a request to cancel a trip is made. The first step involves receiving the trip cancellation request. Once the request is received, the next step is to confirm that the cancellation request has been received.
+After confirming receipt, the person responsible logs into their personal portal to access the necessary information. They then look up the details of the trip in question.
+At this point, a decision is made based on the available information. If the trip reference number is available, the process continues to retrieve a summary of the trip details. If the contact details are available instead, the process also proceeds to retrieve the trip summary details.
+Once the trip summary details are obtained, the trip cancellation is processed. After processing the cancellation, confirmation of the trip cancellation is provided.
+Following the confirmation, another decision point is reached. If the cancellation is made more than 72 hours before the trip, a full refund is processed. If the cancellation is made 72 hours or less before the trip, no refund is provided.
+For cancellations eligible for a full refund, the process involves requesting the customer's bank details and then seeking authorization for the full refund. Once authorization is obtained, the refund is processed.
+After processing the refund, a check is made to determine if the refund was successful. If successful, the funds are released to the customer's account, and the customer is notified of the refund. If the refund is unsuccessful, the process loops back to request the customer's bank details again.
+Finally, regardless of whether a refund is issued or not, the customer is notified of the trip cancellation. The process concludes with the trip being officially cancelled.</t>
+  </si>
+  <si>
+    <t>73edc1dd255c4ad38cecd191878300b3</t>
+  </si>
+  <si>
+    <t>The process begins when a Junior Claims Officer receives a claim. The IT System then creates a record for this claim. Following this, the IT System retrieves the insurance details associated with the claim. Once the details are retrieved, a Junior Claims Officer checks the insurance information.
+At this point, the Junior Claims Officer determines whether the claim is insured. If the claim is not insured, the Junior Claims Officer informs the claimant that their claim has been rejected. The IT System then updates the record, and the process concludes.
+If the claim is insured, a Senior Claims Officer evaluates the claim. After evaluation, the Senior Claims Officer decides whether to accept the claim. If the claim is not accepted, the Senior Claims Officer rejects the claim, and the process returns to the Junior Claims Officer, who informs the claimant of the rejection, followed by updating the record and ending the process.
+If the claim is accepted, the Senior Claims Officer decides the benefit amount. The officer then prepares the claim discharge. After this, two tasks occur simultaneously: the Senior Claims Officer processes the payment and closes the claim. Once both tasks are completed, the IT System updates the record, and the process ends.</t>
+  </si>
+  <si>
+    <t>7c7b1963e2314bf0baf144becb5abc9d</t>
+  </si>
+  <si>
+    <t>The process begins when a customer cannot find a product. The customer approaches a clerk to inquire about the product. This request is communicated to the clerk at the local shop, who then checks the stock availability.
+If the item is in stock, the clerk requests the warehouse manager to deliver the product to the clerk's desk, concluding with the product being found.
+If the item is not in stock, the clerk asks the customer if they would like to place an order. At this point, there are two possible outcomes: the customer can either confirm the order or reject it. If the order is rejected, the process ends with the order being rejected.
+If the order is confirmed, the clerk verifies whether the customer exists in the ERP system. If the customer does not exist, the clerk creates a new client profile. Once the client is verified or created, the clerk proceeds to make the order.
+The order process involves two simultaneous tasks: printing the order and printing the invoice. After printing, the clerk waits for the payment. If the payment is received, the process continues. If no payment is received within two days, the order is canceled.
+Upon receiving the payment, the central warehouse is notified, and they send a message to the customer. After a waiting period of five days, the central warehouse delivers the product. The clerk at the local shop receives the product and informs the customer. Finally, the clerk delivers the product to the customer, marking the end of the process with the product being delivered.</t>
+  </si>
+  <si>
+    <t>3895e2c8df2e414095ba527b5d31ef77</t>
+  </si>
+  <si>
+    <t>The process begins with the preparation of necessary implements. Once the implements are ready, the individual proceeds to wash their hands thoroughly. After hand washing, the next step is to get into sterile clothing to maintain a clean environment.
+Following this, the puncture area is cleaned to ensure it is free from contaminants. Once cleaned, the area is draped to maintain sterility. The next task involves configuring the ultrasound equipment to ensure it is ready for use.
+With the ultrasound configured, gel is applied to the probe, and the probe is then covered to maintain sterility. Sterile gel is then placed on the area to be examined. The probe is positioned correctly, followed by positioning the patient appropriately for the procedure.
+At this point, a decision is made between three identification methods: compression identification, anatomic identification, or Doppler identification. Each method leads to the task of anesthetizing the area.
+After anesthetization, the puncture is performed. The next step is to check for blood return. If blood return is not satisfactory, the process loops back to the puncture step. If blood return is confirmed, the probe is dropped, and the syringe is removed.
+The guidewire is then installed, and the trocar is removed. Another decision point arises where the wire is checked in either the short axis or the long axis. If the wire is not in a good position, the process loops back to the puncture step. If the wire is correctly positioned, the pathway is widened.
+The catheter is then advanced through the widened pathway. Once the catheter is in place, the guidewire is removed. The flow and reflow are checked to ensure proper function. Finally, the catheter position is verified to be correct, concluding the process.</t>
+  </si>
+  <si>
+    <t>f9df2d36f7d04843b613f94e8de928f4</t>
+  </si>
+  <si>
+    <t>The process begins when a Junior Claims Officer receives a claim. The IT System then creates a record for this claim. Following this, the IT System retrieves the insurance details associated with the claim. Once the details are retrieved, a Junior Claims Officer checks the insurance information.
+At this point, the Junior Claims Officer determines whether the claimant is insured. If the claimant is not insured, the Junior Claims Officer informs the claimant that their claim has been rejected. The IT System then updates the record, and the process concludes.
+If the claimant is insured, the process continues with a Senior Claims Officer evaluating the claim. The Senior Claims Officer then decides whether to accept the claim. If the claim is not accepted, the Senior Claims Officer rejects the claim, and the Junior Claims Officer informs the claimant of the rejection. The IT System updates the record, and the process ends.
+If the claim is accepted, the Senior Claims Officer decides the benefit amount. The officer then prepares the claim discharge. After this, two tasks occur simultaneously: the Senior Claims Officer processes the payment and closes the claim. Once both tasks are completed, the IT System updates the record, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>274a2b2a8f29408e8904cfdffb41980a</t>
+  </si>
+  <si>
+    <t>The process begins when the call center receives a call. The call center then picks up the call and proceeds to ask the caller a series of questions. After gathering initial information, the call center evaluates whether they have enough information to proceed. If the information is insufficient, they will continue asking questions until they have gathered enough details.
+Once enough information is collected, the call center goes through a questionnaire to ensure all necessary details are covered. Following this, they enter the collected details into the system and check for completeness. If everything is complete, the call center registers the claim.
+The process then moves to the Claim Handling Office, where they determine the liability associated with the claim. After determining liability, they assess the claim to decide whether it should be accepted or rejected. If the claim is rejected, the Claim Handling Office formally rejects the claim, and the process ends with the claim being marked as failed.
+If the claim is accepted, the process continues with two tasks happening simultaneously. The Claim Handling Office advises the customer of the claim amount and initiates the payment process. Advising the amount involves sending a message to the customer, while initiating the payment ensures the financial transaction is set in motion.
+After advising the amount and initiating the payment, the Claim Handling Office closes the claim. The process concludes with the claim being fulfilled, marking the successful completion of the claim handling process.</t>
+  </si>
+  <si>
+    <t>f779331026664514925cdd5915e9ddcc</t>
+  </si>
+  <si>
+    <t>The process begins with the preparation of implements by a designated actor. Following this, the actor performs hand washing to ensure cleanliness. Next, the actor gets into sterile clothes to maintain a sterile environment. The puncture area is then cleaned thoroughly by the actor, followed by draping the area to keep it sterile.
+The actor proceeds to configure the ultrasound equipment, ensuring it is ready for use. Gel is applied to the probe, and the probe is covered to maintain sterility. The actor then applies sterile gel to the area and positions the probe correctly.
+The patient is positioned appropriately by the actor. At this point, a decision is made between three options: compression identification, anatomic identification, or Doppler identification. Each of these tasks is performed by the actor, leading to the anesthetization of the area.
+Once anesthetized, the actor performs a puncture. The process checks for blood return, and if successful, the actor drops the probe and removes the syringe. If blood return is not successful, the process loops back to the puncture step.
+After removing the syringe, the actor installs a guidewire and then removes the trocar. Another decision point arises, where the actor checks the wire in either the short axis or the long axis. If the wire is in a good position, the actor proceeds to widen the pathway.
+The actor then advances the catheter and removes the guidewire. The flow and reflow are checked to ensure proper function. Finally, the actor checks the catheter position to confirm it is correct. The process concludes successfully at this point.</t>
+  </si>
+  <si>
+    <t>1930f3f9837b4c40ab088a610f3f81bd</t>
+  </si>
+  <si>
+    <t>The process begins when the pharmacy receives a prescription. Once the prescription is received, the pharmacy simultaneously verifies the prescription and checks if it is the customer's first time visiting.
+For the verification of the prescription, if any issues are identified, the pharmacy contacts the doctor to request details about the issue. The doctor then provides verification or authority and issues the necessary document to fulfill the dispensing. This document is sent back to the pharmacy for review. If no issues are identified, the pharmacy proceeds to review the prescription.
+After reviewing the prescription, the pharmacy checks if a generic brand is available. If a generic brand is available, the pharmacy recommends it to the customer. If not, the pharmacy proceeds with the prescribed brand. In both cases, the pharmacy inputs the details into the system and prints labels for the medication.
+Simultaneously, the pharmacy checks if it is the customer's first time. If it is, the pharmacy obtains the customer's details and inputs them into the system. If it is not the customer's first time, the pharmacy checks the customer's details in the system.
+Next, the pharmacy checks the stock availability on the shelves. If the medication is available, the pharmacy prepares the prescriptions and scans them. If the medication is not available, the pharmacy contacts another pharmacy to order the prescriptions on the script and informs the customer about the situation.
+The process concludes with the pharmacy either preparing and scanning the prescriptions if the stock is available or informing the customer if the stock is not available.</t>
+  </si>
+  <si>
+    <t>9da4a71e3def4f41bc2d94f53689d384</t>
+  </si>
+  <si>
+    <t>The process begins with a patient examination. A healthcare professional examines the patient to assess their condition. Following the examination, a decision is made based on the patient's health status.
+If the patient is deemed healthy, the healthcare professional fills out an examination form documenting the findings. After completing the form, the patient is informed that they can leave, concluding the process.
+If the patient requires further examination or treatment, the healthcare professional orders additional tests and follow-up treatment. A request form is filled out to initiate these procedures. The patient is then informed about any potential risks associated with the upcoming tests or treatments.
+The patient must decide whether to sign an informed consent document. If the patient agrees and signs the document, they proceed to leave, ending the process. If the patient does not sign, a nurse prepares for sampling and examination.
+The physician then takes a sample from the patient, which is sent to the laboratory for analysis. The lab assesses whether the sample is adequate for testing. If the sample is not adequate, the process returns to the nurse preparing for sampling and examination.
+If the sample is adequate, it is received by the physician, who validates it. A technician then performs the necessary analysis on the sample. Based on the analysis, a physician makes a diagnosis and prescribes the appropriate therapy. After prescribing therapy, the patient is informed and can leave, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>939514e86660450ba99ada89f9a1d85f</t>
+  </si>
+  <si>
+    <t>The process begins with a candidate for study initiating the application for admission to bachelor studies. The candidate proceeds to apply for admission, which involves two simultaneous actions: filling out the application and paying the fee for the admission procedure.
+Once the application is filled, the candidate prints the filled application and confirms their high school evaluation. After these steps, the candidate sends the application along with the confirmation of payment to the study department of the chosen faculty.
+The study department then accepts the candidate's application and adds a confirmation about the fulfillment of prerequisites to the information system. At this point, the process reaches a decision point based on the candidate's marks. If the marks are not good enough, the study department sends an invitation for an entrance test. The candidate then takes a written test, which is evaluated by the study department. The process then returns to the decision about admission.
+If the candidate has good marks, the study department makes a decision about admission and sends this decision to the candidate. The candidate then faces another decision point. If accepted, the candidate appears for registration. The study department then accepts the candidate as a student and writes them into the information system, managing all state requirements. This leads to the end of the process.
+If the candidate is not accepted and disagrees with the decision, they can appeal the decision. The study department then reconsiders the decision, and the process loops back to the point where the decision is sent to the candidate. If the candidate agrees with the decision of not being accepted, the process ends.</t>
+  </si>
+  <si>
+    <t>c88f2aa1750c49af9bc3327391d94dee</t>
+  </si>
+  <si>
+    <t>The process begins when a customer places an order. The customer initiates the order, selects the desired car model, and confirms the design and specifications. Once the order is confirmed, the plant gathers the necessary supplies for production.
+At this point, the plant checks if the supplies are available. If the supplies are not available, the customer is notified of a delay, and the process ends there for the time being. If the supplies are available, the plant places the order in the manufacturing sequence.
+The manufacturing process involves two simultaneous tasks. The plant manufactures the car model according to the specified requirements and sends a tentative delivery date to the delivery department. After manufacturing, the plant conducts an electronics test on the car.
+Following the electronics test, the plant checks if the car passes the emission test. If the car does not pass, it undergoes reconfiguration of the electronics and an engine check before being retested. If the car passes the emission test, it proceeds to a road test.
+The road test determines if the car is ready for delivery. If the car does not clear the road test, it is sent back for a comprehensive check and retesting. If the car clears the road test, it is moved to the delivery station.
+The delivery department then prepares for the order delivery. Finally, the car is delivered to the customer, marking the completion of the process.</t>
+  </si>
+  <si>
+    <t>e9336283b37b4486b47ca392e53bbe6e</t>
+  </si>
+  <si>
+    <t>The process begins with a passenger or traveler starting their journey at KLIA 2. The first step involves the passenger performing a self check-in. After completing the self check-in, the passenger is presented with a choice of check-in options.
+At this decision point, the passenger can choose one of three paths:
+1. **Mobile Check-In**: If the passenger selects mobile check-in, they proceed to generate a 2D barcode. Once the barcode is generated, the process waits until 60 minutes before departure.
+2. **Web Check-In**: If the passenger opts for web check-in, they print their boarding pass. After printing the boarding pass, they move on to check in their luggage.
+3. **Kiosk Check-In**: If the passenger chooses kiosk check-in, they proceed to print and collect their boarding pass. Following this, they check in their luggage.
+After checking in luggage, the process checks if the passenger has baggage to check in. If the passenger has baggage, they drop it off. If not, the process continues to determine if the flight is international.
+For international flights, the passenger must check their travel documents and then proceed to immigration for check-in. After immigration, they pass through security screening, which includes checking hand luggage and a body check. For domestic flights, the passenger directly proceeds to security screening.
+Once security screening is complete, the process waits until 20 minutes before departure. Finally, the passenger enters the boarding gate, concluding the process at KLIA 2.</t>
+  </si>
+  <si>
+    <t>74ed36054c7c41c8a2ef358dfb75ea9a</t>
+  </si>
+  <si>
+    <t>The process begins when a customer decides they want a cake. The customer then sends an inquiry to the patisserie to ask about the price of the cake. The manager at the patisserie receives this inquiry and calculates the price of the cake. After determining the price, the manager sends a response back to the customer with the price information.
+At this point, the customer has a decision to make. If the customer does not respond, the process ends with no order being placed. If the customer responds within five days, they have two options: they can either accept the offer or reject it. If the customer rejects the offer, the process ends with no order. If the customer accepts the offer, the manager updates the database to reflect the new order.
+Once the order is confirmed, the manager prepares the order details from the database. The manager then determines whether the order is for a standard cake or a design cake. If it is a design cake, the main cook begins creating the cake for baking. The process then splits into two parallel tasks: the main cook prepares the cream, and the cook's helper prepares the cake for baking. Once both tasks are completed, the cake is baked.
+After baking, the process continues with two parallel tasks: the cook's helper spreads cream between the cake layers and covers the cake with frosting, while the main cook makes decorations. Once these tasks are completed, the cook's helper decorates the cake.
+Following decoration, the manager performs a quality check on the cake. If the cake passes the quality check, the manager informs the customer that the cake is ready. The customer then collects the cake from the patisserie. Finally, the manager updates the database to indicate that the order is finished, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>55314a432dc444398c06093eb63c55c5</t>
+  </si>
+  <si>
+    <t>The process begins when the resupply cycle is triggered. The first task involves an actor checking the inventory level. After checking the inventory, a decision point is reached. If the inventory is below the minimum required level, the process continues with creating a purchase order. If the inventory is above the minimum, the process ends.
+If a purchase order is created, it is then reviewed. At this point, another decision is made. The purchase order can either be approved or rejected. If it is rejected, the order is reworked and sent back for review. If the purchase order is approved, the process moves forward.
+Once approved, two tasks occur simultaneously. One task involves reserving funds, while the other involves sending the purchase order to the supplier. After sending the purchase order, another parallel set of tasks is initiated. One task involves receiving the package slip, and the other involves receiving the invoice.
+After receiving the invoice, the next task is to record both the packing slip and the invoice. Following this, reserved funds are released. The final task in this sequence is issuing payment to the supplier, after which the process concludes.
+Throughout the process, each task is handled by specific actors responsible for ensuring the smooth flow of operations from start to finish.</t>
+  </si>
+  <si>
+    <t>96de873b8681432b900ac2ca5fe17c4d</t>
+  </si>
+  <si>
+    <t>The process begins with an administrator initiating the workflow. Immediately, two tasks are carried out simultaneously. The first task involves the administrator performing a manual check on Jane Doe. The second task involves the administrator conducting a manual BKR check. 
+Once both tasks are completed, the administrator proceeds to perform an automated credibility check. Following this, the administrator confirms the results of the credibility check.
+Next, a decision point is reached. If the credibility assessment is accepted, the administrator calls the client to gather additional information. After this call, the administrator creates a loan offer and then sends it to the client. The process waits for the client to accept the offer. Once the offer is accepted, two actions occur simultaneously. The administrator activates the loan application and sends a welcome letter to the client.
+After activating the loan application, the administrator executes the initial payment. Following this, the administrator returns the necessary documents to the client, concluding this branch of the process.
+If the credibility assessment is rejected, the administrator sends a rejection letter to the client, which concludes this branch of the process.</t>
+  </si>
+  <si>
+    <t>68f04cb4b8c74e89b09fd4d76ec1f589</t>
+  </si>
+  <si>
+    <t>The process begins with the appointment agency planning a screening. Once the screening is planned, the agency sends an invitation to the client. After sending the invitation, the agency checks if the client is satisfied with the appointment. If the client is satisfied, the process continues with the nurse going to the school.
+If the client is not satisfied, the client calls the appointment agency. The agency then determines if the client wants to cancel or reschedule the appointment. If the client chooses to cancel, the agency records the reason for cancellation in the system, and the process ends without a screening. If the client decides to reschedule, the process loops back to planning the screening again.
+When the client is satisfied, the nurse goes to the school and introduces themselves in the class. The nurse then explains the screening methods to the children. After the explanation, the nurse receives a questionnaire from the child and discusses the answers with them. Following this, the nurse measures the child's length and weight.
+Next, the nurse checks if both parents have an eye deviation or if there is a request for an eye test. If yes, the nurse conducts an eye test. If not, the nurse checks if a hearing test is requested by the parents, teacher, or the child. If a hearing test is requested, the nurse performs the hearing test. If no hearing test is requested, the nurse fills in a findings form and gives it to the child to take along. The process concludes with the screening ending.</t>
+  </si>
+  <si>
+    <t>fe0d9816a88e4ee6b7fa362e1a74eed5</t>
+  </si>
+  <si>
+    <t>The process begins with the Risk Management team initiating the procedure. Immediately, two tasks are carried out simultaneously. The first task involves the Risk Management team performing a Jane Doe check. The second task involves the same team conducting a BKR check. 
+Once the Jane Doe check is completed, the Risk Management team proceeds to perform a credibility check. After this, they confirm the results of the credibility check. 
+At this point, a decision is made. If the outcome is positive, the process moves to the Customer Service team, who will call the client to gather additional information if needed. Following this, the Customer Service team creates a loan offer, checks it, and then sends it to the client.
+After sending the loan offer, there is a waiting period. If the client does not respond within an hour, the Customer Service team sends a reminder. If the client accepts the offer, the Customer Service team receives the acceptance and the process continues.
+If the offer is accepted, the Administration team sends a welcome letter to the client. Subsequently, the Risk Management team activates the loan application. 
+Following the activation, two tasks are executed simultaneously. The Risk Management team validates the loan activation, and they also execute the initial payment. Meanwhile, the Administration team returns the necessary documents to the client, marking the end of the process.
+If the decision after confirming the credibility check is negative, the Administration team sends a rejection letter to the client, concluding the process.</t>
+  </si>
+  <si>
+    <t>7c82d73ef986488b927e6c1b186f1761</t>
+  </si>
+  <si>
+    <t>The process begins when a customer enters the department store. Upon entering, the customer is expected to get a shopping cart or basket to carry their selected items. Next, the customer chooses the desired product they wish to purchase. After selecting a product, the customer examines it to ensure it meets their needs and preferences. The customer then checks the price of the product.
+At this point, the customer must decide whether they want to buy the product. If the customer decides not to purchase the product, they will put the item back. If the customer decides to buy the product, they proceed to the checkout area.
+Once at the checkout, the cashier determines the category of the product. If the product is a book, the cashier applies a 10% discount. If the product is electronics, no discount is applied. If the product is food, a 5% discount is applied.
+After determining the product category and applying any applicable discounts, the cashier assesses the customer's loyalty status. If the customer has a silver status, an additional 2% discount is applied. If the customer has a gold status, a 5% discount is applied. If the customer has a titanium status, a 10% discount is applied.
+Following the loyalty status assessment, the cashier checks if the customer qualifies for a special discount. If the customer is eligible, a student or veteran discount is applied. If not, the price remains constant.
+Finally, the process concludes, and the transaction is completed.</t>
+  </si>
+  <si>
+    <t>3b7d6afa91d94ac6907693e3a02f1d58</t>
+  </si>
+  <si>
+    <t>The process begins with the initiation of engaging Dimuto for traceability solutions. The first step involves logging into the Dimuto account. Once logged in, the next task is to create user accounts for employees, ensuring they have access to the necessary tools and information.
+Following this, the creation of a Stock Keeping Unit (SKU) is required. This step is crucial for organizing and tracking products within the system.
+After the SKU is created, the process splits into four simultaneous tasks. The first task is to create pack plans, which are essential for organizing how products will be packed. The second task involves creating pallets, which are used for transporting goods efficiently. The third task is to create load plans, which detail how products will be loaded for shipment. The fourth task is to handle the trade contract, which involves preparing the necessary documentation for trade agreements.
+Once the trade contract is prepared, it must be fulfilled. This involves ensuring that all terms and conditions of the contract are met. After fulfilling the trade contract, the next step is to create a shipment, which involves organizing the transportation of goods to the buyer.
+The shipment is then received by the buyer, marking the end of the process.
+Simultaneously, while the trade contract is being handled, the load plans are further detailed by assigning pallets and cartons to them. Pallets are assigned to load plans, and cartons are assigned to pallet plans, ensuring that all items are accounted for and organized efficiently.
+The process concludes when the buyer receives the goods, completing the transaction and ensuring that all parties are satisfied with the outcome.</t>
+  </si>
+  <si>
+    <t>0254a74de2614dfda2b6d6594dfd98c6</t>
+  </si>
+  <si>
+    <t>The process begins when a customer arrives at the restaurant. Upon arrival, the customer faces a decision point: whether they are a walk-in or have a reservation. If the customer is a walk-in, they proceed to the task of walking in and then read through the menu. After reviewing the menu, the customer decides if they are satisfied with the food options. If satisfied, they place an order; if not, they leave the restaurant.
+If the customer has a reservation, they show their reservation information. A clerk then checks the reserved table and the meal ordered. The POS terminal tracks and displays the reservation information. The clerk then brings the customer to the reserved table and confirms the meal ordered. The customer gets seated and confirms their order, followed by placing the order.
+Once the order is placed, a clerk determines if the order is for a walk-in or a reserved customer. If it is a reserved order, the clerk confirms the order. The kitchen then prepares the food, and the clerk serves it to the customer. After enjoying the meal, the customer pays the bill, and the clerk checks out the order. The POS terminal displays the bill information, and the clerk prints the bill. The customer makes the payment, and the clerk receives it.
+The clerk then keys in the payment details and asks the customer about their preferred payment method. If the customer pays by cash, the clerk prepares the change. If the customer pays by credit or debit card, the clerk prints the receipt. The process then splits into two parallel tasks: the clerk saves the payment details using the POS terminal, and the customer is considered served, concluding the process.
+If the kitchen finds there is not enough food supply, they notify the clerk, who then informs the customer. The customer decides whether to confirm the order with the available options or leave the restaurant. If the customer chooses to confirm, they replace the order, and the process continues with the clerk keying in the order details. If the customer decides not to confirm, they leave the restaurant, ending the process.</t>
+  </si>
+  <si>
+    <t>05ab849c028f470ba5e240712b68a116</t>
+  </si>
+  <si>
+    <t>The process begins with the preparation of implements by the assigned individual. Following this, the same person performs hand washing to ensure cleanliness. Next, they put on sterile clothes to maintain a sterile environment.
+The process continues with cleaning the puncture area, followed by draping it to prepare for the procedure. The next step involves configuring the ultrasound equipment, after which gel is applied to the probe. The probe is then covered to maintain sterility, and sterile gel is applied to the area.
+The probe is positioned correctly, and the patient is positioned appropriately for the procedure. At this point, a decision is made between three options: compression identification, anatomic identification, or Doppler identification. Each of these tasks leads to the anesthetization of the patient.
+Once the patient is anesthetized, the puncture is performed. The process checks for blood return, and if successful, the probe is dropped, and the syringe is removed. The guidewire is then installed, and the trocar is removed.
+Another decision point arises, where the wire is checked in either the short axis or the long axis. If the wire is in a good position, the pathway is widened, and the catheter is advanced. The guidewire is then removed, and the flow and reflow are checked. Finally, the catheter position is verified, concluding the process.</t>
+  </si>
+  <si>
+    <t>fa33f504903b4253850d1995fd07af2a</t>
+  </si>
+  <si>
+    <t>The process begins when a claims officer at the insurance company receives a claim. The first task for the claims officer is to review the application. After reviewing the application, the claims officer checks the validity of the claim.
+At this point, there is a decision to be made. If the claim is valid, the claims officer proceeds to check the completeness of the documents. If the claim is invalid, the claims officer rejects the claim and informs the claimant. The process ends with the claim being rejected.
+If the documents are complete, the claims officer assesses the complexity of the claim. If any documents are missing, the claims officer requests further documents from the claimant and waits to receive them. If there is an information mismatch, the fraud control team reassesses the claim and may request further documents, which they then receive and validate.
+Once the claim complexity is assessed, another decision is made. If the claim is deemed low complexity, the claims officer valuates the claim, processes the payment, and approves the payment, concluding with the claim being handled. If the claim is high complexity, a senior officer rechecks the application and validates the claim before it is passed back to the claims officer for valuation and payment processing.
+Throughout the process, communication with the claimant is maintained, especially when additional documents are required or when the claim is rejected. The process ensures that all claims are thoroughly reviewed, validated, and processed efficiently.</t>
+  </si>
+  <si>
+    <t>5f94d7b0879f445593bde225410e865f</t>
+  </si>
+  <si>
+    <t>The process begins when a passenger arrives at the airport. The first step for the passenger is to check in. After checking in, the passenger encounters a decision point where they must choose one of three options for checking in: using a kiosk, using a mobile device, or using the web.
+If the passenger chooses to check in using a kiosk, they proceed to print their boarding pass at the airport. After printing the boarding pass, the passenger faces another decision point: whether they need to drop baggage. If they need to drop baggage, they proceed to do so. If not, they move on to the next decision point, which determines whether their flight is international or domestic.
+If the passenger chooses to check in using a mobile device, they are directed back to the option of checking in using a kiosk, where they can print their boarding pass at the airport.
+If the passenger chooses to check in using the web, they print their boarding pass at home. After printing the boarding pass at home, they face the decision point about dropping baggage. If they need to drop baggage, they proceed to do so. If not, they move on to the next decision point, which determines whether their flight is international or domestic.
+If the passenger's flight is domestic, they go to the domestic departure gate and then proceed to boarding. Once boarding is complete, the process ends with the passenger's departure.
+If the passenger's flight is international, they go to the international departure gate. Here, they must check their documents, scan their passport and thumbprint, and perform a security check. After completing these steps, they proceed to the domestic departure gate, followed by boarding. The process concludes with the passenger's departure.</t>
+  </si>
+  <si>
+    <t>e7913c15552c491296aa55e04d14b953</t>
+  </si>
+  <si>
+    <t>The process begins with the preparation of implements by the assigned actor. Once the implements are ready, the actor proceeds to wash their hands thoroughly. Following hand washing, the actor dresses in sterile clothes to maintain a clean environment.
+Next, the actor cleans the puncture area to ensure it is free from contaminants. After cleaning, the puncture area is draped to maintain sterility. The actor then configures the ultrasound equipment to prepare for the procedure.
+With the ultrasound configured, the actor applies gel to the probe and covers it to maintain sterility. Sterile gel is then applied to the puncture area. The actor positions the probe correctly and then positions the patient for the procedure.
+At this point, a decision is made regarding the identification method to be used. The actor can choose between compression identification, anatomic identification, or Doppler identification. Each choice leads to the anesthetization of the area.
+After anesthetization, the actor performs the puncture. They then check for blood return to confirm the puncture's success. If blood return is not confirmed, the process loops back to the puncture step. If blood return is confirmed, the actor drops the probe and removes the syringe.
+The actor then installs the guidewire and removes the trocar. Another decision point arises where the actor checks the wire's position. They can choose to check the wire in either the short axis or the long axis. If the wire is not in a good position, the process loops back to the puncture step. If the wire is in a good position, the actor proceeds to widen the pathway.
+Following the pathway widening, the actor advances the catheter and then removes the guidewire. The actor checks the flow and reflow to ensure proper function. Finally, the catheter position is checked to confirm it is correctly placed. The process concludes successfully at this point.</t>
+  </si>
+  <si>
+    <t>9a05b77363944304b7e9372e520b4a28</t>
+  </si>
+  <si>
+    <t>The process begins with the preparation of implements by a designated actor. Following this, the actor performs hand washing to ensure cleanliness. Next, the actor gets into sterile clothes to maintain a sterile environment.
+The process continues with the actor cleaning the puncture area, followed by draping the area to prepare for the procedure. The actor then configures the ultrasound equipment, applies gel to the probe, and covers the probe to maintain sterility. Afterward, the actor puts sterile gel on the puncture area and positions the probe correctly.
+Subsequently, the actor positions the patient appropriately for the procedure. At this point, a decision is made between three options: compression identification, anatomic identification, or Doppler identification. Each of these tasks leads to the anesthetization of the patient.
+Once anesthetized, the actor performs the puncture and checks for blood return. If blood return is not satisfactory, the process loops back to the puncture step. If blood return is confirmed, the actor drops the probe and removes the syringe.
+The next step involves installing the guidewire, followed by removing the trocar. Another decision point arises where the actor checks the wire in either the short axis or the long axis. If the wire is in a good position, the process continues; otherwise, it loops back to the puncture step.
+If the wire is correctly positioned, the actor widens the pathway and advances the catheter. The guidewire is then removed, and the actor checks the flow and reflow. Finally, the actor checks the catheter position to ensure it is correct.
+The process concludes successfully once the catheter position is verified.</t>
+  </si>
+  <si>
+    <t>28c5aedad9f347528214b9a6cb74dc3c</t>
+  </si>
+  <si>
+    <t>The process begins when a loan application is received. The first task involves checking the customer's details. Once this is completed, the process splits into two parallel tasks. One task involves appraising the property, while the other involves checking the customer's history. Both tasks proceed simultaneously.
+After the property appraisal is completed, the applicant's eligibility is assessed. Meanwhile, the customer's history check leads to an assessment of the customer's loan risk. Once both parallel tasks are completed, the process reaches a decision point where the applicant's eligibility is evaluated.
+If the applicant is not eligible, the application is rejected, and the process ends. If the applicant is eligible, an acceptance pack is prepared. This pack is then sent to the customer. The customer is expected to return signed documents, which are then received and processed.
+Following the receipt of signed documents, the payment agreement is verified. At this point, another decision is made. If the payment agreement is agreed upon, the application is approved. If the payment agreement is not agreed upon, the application is canceled, and the customer is notified. In both cases, the process concludes with the loan application process ending.</t>
+  </si>
+  <si>
+    <t>495a5ccccc184034aea09b1866194dc0</t>
+  </si>
+  <si>
+    <t>The process begins when the information system receives a new visa application. The system then retrieves the details of this new application. After fetching the details, the system creates a PDF document containing the application information. Once the document is prepared, the system notifies a junior officer about the new application.
+The junior officer then checks the application for completeness. At this point, there is a decision to be made: if any documents are missing, the junior officer notifies the applicant to provide the missing documents. If the application is complete, the junior officer forwards it to a senior officer for further review.
+The senior officer checks the validity of the application. If the application is not valid, the senior officer rejects it, and the information system notifies the applicant of the rejection. If the application is valid, the senior officer ensures it meets immigration requirements. Once the requirements are met, the senior officer approves the application.
+After approval, the junior officer conducts a "Lift in Wonderland" test. If the application passes this test, the junior officer sends a confirmation to the applicant, marking the application as approved. If the application does not pass the test, the information system notifies the applicant that the application has failed.
+The process concludes with either the application being approved or the applicant being informed of the failure.</t>
+  </si>
+  <si>
+    <t>d4dc0f1a4fc94a49bb55631dc05f205b</t>
+  </si>
+  <si>
+    <t>The process begins when a guest contacts the room service manager to place an order. The room service manager takes down the order details and then checks the order for accuracy.
+Once the order is checked, the process splits into two parallel paths. One path handles orders containing alcoholic beverages, and the other handles food orders. Both paths proceed simultaneously.
+For orders containing food, the room service manager gives the food order to the kitchen staff. The kitchen staff receives the order and prepares the food. Once the food is ready, it is handed back to the room service manager.
+For orders containing alcoholic beverages, the room service manager gives the order to the barkeeper. The barkeeper receives the order and prepares the alcoholic beverages. Once ready, the beverages are handed back to the room service manager.
+After receiving either the food or alcoholic beverages, the room service manager checks if the entire order is complete. If the order is complete, the room service manager assigns it to a waiter. If the order is not complete, the process returns to the order checking step.
+The waiter receives the complete order and checks if non-alcoholic beverages are included. If non-alcoholic beverages are ordered, the waiter prepares them. If not, the waiter proceeds to deliver the order.
+Finally, the waiter delivers the ordered food and/or drinks to the guest's room, marking the end of the process with the meal being delivered.</t>
+  </si>
+  <si>
+    <t>11535b315b1e49b7a1e97cb49ce87871</t>
+  </si>
+  <si>
+    <t>The process begins with the reception of loan details. Once the loan details are received, two tasks are carried out simultaneously. One task involves performing a BKR assessment, and the other involves performing a task labeled "Perform Jane Doe." 
+After the BKR assessment is completed, a credibility assessment is performed. Following this, the credibility assessment is checked. Based on the results of this check, a decision is made. If the credibility assessment is accepted, additional information is retrieved, leading to the creation of a loan offer. This loan offer is then sent out. If the offer is accepted, the process continues with two tasks happening at the same time: sending a welcome letter and activating the loan. 
+Once the loan is activated, an initial payment is executed, and documents are returned to the client. Both the sending of the welcome letter and the return of documents lead to the end of the process.
+If the credibility assessment is rejected, a rejection letter is sent, which also leads to the end of the process.</t>
+  </si>
+  <si>
+    <t>dddce5647c6a4c84a69ad91cfadfb6f9</t>
+  </si>
+  <si>
+    <t>The process begins with the initiation of a purchase request. The first step involves creating a purchase request. Once the request is created, it is analyzed to ensure all necessary details are included. If any amendments are needed, the purchase request is amended accordingly.
+After the amendments, the purchase request is sent to a manager for further evaluation. The manager evaluates the request and then notifies the requester of the decision. At this point, a decision is made on whether the request is approved or not.
+If the request is not approved, the process ends. However, if the request is approved, it is sent to a purchasing agent. The purchasing agent takes charge of the request and analyzes it further. The agent then handles the comparison of quotations and creates an order based on the best option. Following this, a purchase order is released.
+The process then reaches a point where two paths are possible. One path involves approving the purchase order for payment, while the other involves settling any disputes with the supplier. If there is a dispute, it is settled before proceeding to approve the purchase order for payment.
+Once the purchase order is approved, two activities occur simultaneously. The goods are received, and an invoice is sent to the manager. After receiving the goods, the process concludes. Meanwhile, the manager handles the payment, which also leads to the conclusion of the process.</t>
+  </si>
+  <si>
+    <t>0b9081e19b964ee69de5d673f318709a</t>
+  </si>
+  <si>
+    <t>The process begins with the customer initiating a request for a printing service through an app. The customer then fills in the necessary metadata required for the print request. Afterward, the customer locates the desired printing location and submits the print request.
+Once the request is submitted, the printer receives it and proceeds to load the appropriate paper and ink. The printer then prints the document based on the specified requirements. After printing, the printer validates the print request.
+At this point, a decision is made to determine if the request is for delivery. If it is a delivery request, the printer notifies the customer that the print request is ready for delivery. The printer then delivers the print request at the requested time. Upon delivery, another decision is made to check if the customer is home. If the customer is home, the printer hands the print request to the customer. If the customer is not home, the printer leaves the print request on the customer's doorstep and informs the customer via email with a picture of the drop-off.
+If the print request is not for delivery, the printer sends a notification to the customer that the print request is ready for pick-up. The customer receives the print completion notice and leaves to pick up the print request at the specified location during the pick-up window. The customer then receives the print request.
+After receiving the print request, the customer acknowledges in the app that the print request has been received and rates the print service. Simultaneously, the printer acknowledges that the print service has been provided to the customer. The process concludes with both the customer and the printer marking the print service as complete.</t>
+  </si>
+  <si>
+    <t>d17524f4567a4903aa503b48a4ec1d1e</t>
+  </si>
+  <si>
+    <t>The process begins with a change request initiated by the Quality Management (QM) team. The QM team then conducts an analysis of the request to understand its implications. Following this, the QM team builds a catalogue of specific questions that need to be answered to determine if the change is necessary.
+Once the questions are prepared, the process splits into three parallel tasks. The commercial team answers questions related to the financial scope. Simultaneously, the manufacturing team addresses questions concerning the production scope, and the construction team tackles questions about the technical scope. All these tasks are carried out at the same time.
+After these parallel tasks are completed, the QM team, along with all stakeholders, makes a decision based on the gathered information. This decision leads to a branching point where two outcomes are possible. If the request is declined, the process moves directly to the final examination by the QM team. If the request is accepted, the construction team clarifies whether other parts of the project are affected.
+If the construction team finds that other parts are not violated, they proceed to build a new part. They then determine if the form, fit, or function is violated. If so, they assign a new part number; otherwise, they increase the index. This leads to the development of an operation chart by the manufacturing team.
+The commercial team then calculates the cost for the exchange based on the operation chart. Following this, the manufacturing team implements the new operation chart and releases the request.
+The QM team conducts a final examination to ensure everything is effective. The process concludes with the QM team marking the change request as accomplished, resulting in the completion of the process.</t>
+  </si>
+  <si>
+    <t>efda927d1da24b49b9f5dd4be6b579f1</t>
+  </si>
+  <si>
     <t>The process begins with a student joining a team. Once the student has joined, the team collectively agrees on a domain for their project. After agreeing on the domain, a student creates a process model for the project.
 Next, a lecturer checks the process model. At this point, there is a decision to be made. If the process model is not satisfactory, the lecturer assigns negative points, and the student must fix the problem in the next session. After fixing the problem, the student extends the process to levels 2 and 3.
 If the process model is satisfactory, the student proceeds to extend the process to levels 2 and 3 without delay. Following this, the student encounters another decision point. The student can either analyze the field of study or check the process and assign points. If the student chooses to analyze the field of study, the team then assigns roles within the team. Each student then performs work according to their assigned role.
@@ -212,21 +1833,70 @@
 If the student chooses to check the process and assign points, they return to perform work according to their role, and the process continues as described above.</t>
   </si>
   <si>
-    <t>0b9081e19b964ee69de5d673f318709a</t>
-  </si>
-  <si>
-    <t>The process begins with the customer initiating a request for a printing service through an app. The customer then fills in the necessary metadata required for the print request. Afterward, the customer locates the desired printing location and submits the print request.
-Once the request is submitted, the printer receives it and proceeds to load the appropriate paper and ink. The printer then prints the document based on the specified requirements. After printing, the printer validates the print request.
-At this point, a decision is made to determine if the request is for delivery. If it is a delivery request, the printer notifies the customer that the print request is ready for delivery. The printer then delivers the print request at the requested time. Upon delivery, another decision is made to check if the customer is home. If the customer is home, the printer hands the print request to the customer. If the customer is not home, the printer leaves the print request on the customer's doorstep and informs the customer via email with a picture of the drop-off.
-If the print request is not for delivery, the printer sends a notification to the customer that the print request is ready for pick-up. The customer receives the print completion notice and leaves to pick up the print request at the specified location during the pick-up window. The customer then receives the print request.
-After receiving the print request, the customer acknowledges in the app that the print request has been received and rates the print service. Simultaneously, the printer acknowledges that the print service has been provided to the customer. The process concludes with both the customer and the printer marking the print service as complete.</t>
+    <t>d8691da54de64a01a6058a8d97d2a9ce</t>
+  </si>
+  <si>
+    <t>The journey to becoming a professional documentary photographer begins with a decision made by the aspiring photographer. Once the decision is made, the first step is to purchase the necessary equipment, including a DSLR camera. With the equipment in hand, the photographer then takes the time to learn and explore the camera's functions.
+Following this, the photographer simultaneously embarks on two paths. One path involves learning the basics of photography, while the other involves analyzing the work of the best photographers to gain inspiration and understanding. After gaining this foundational knowledge, the photographer begins taking photos in their favorite category, exploring and refining their skills through practice. This process is repeated multiple times to build expertise.
+In parallel, the photographer studies advanced materials and theories to deepen their understanding of photography. Feedback is then sought from social media, which is used to improve their work. This feedback loop is continuous, allowing for ongoing improvement.
+The photographer then defines interesting projects and gathers a collection of their work. At this point, a decision is made between two paths. One option is to build a portfolio from the collection and send it to news agencies and publishers. Feedback from professionals is received and used to make further improvements, ultimately leading to landing a contract with a favorite agency.
+Alternatively, the photographer can start a professional page on photography websites, interact with the community to gain followers, and participate in contests to earn money. Both paths lead to the ultimate goal of becoming a professional documentary photographer.</t>
+  </si>
+  <si>
+    <t>637b02be69fa4798a393726121614721</t>
+  </si>
+  <si>
+    <t>The process begins with the interviewer receiving the result from the selection process. The interviewer then picks a preferred candidate. After selecting the candidate, there are two possible paths: the interviewer can either put together an offer or the recruiter can do so. 
+Once the offer is prepared, it is sent to the candidate via email. The candidate then decides whether to accept the offer. If the candidate declines, the recruiter considers whether to revise the offer. If the decision is to revise, the recruiter prepares a new offer. If not, a rejection email is sent to the candidate.
+If the candidate accepts the offer, the recruiter checks if reference checks are needed. If reference checks are not required, the recruiter prepares the contract. The contract is then sent to the candidate for signing. Once signed, the onboarding process begins.
+If reference checks are needed, the recruiter arranges them and requests the necessary information from the candidate. After gathering the information, the recruiter checks the references. If the candidate passes the reference checks, the recruiter prepares the contract. If the candidate does not pass, a rejection email is sent to the candidate. 
+Throughout the process, decisions are made by either the recruiter or the interviewer, depending on the task at hand. The process concludes with the candidate signing the contract and the onboarding process starting.</t>
+  </si>
+  <si>
+    <t>07487a4aebe8436d85b618c2ac2a9f25</t>
+  </si>
+  <si>
+    <t>The process begins when a notice is received by phone. This notice is documented and then answered by the responsible person. After answering the notice, the next step is to request the medical file related to the notice.
+Once the request for the medical file is made, two tasks occur simultaneously. One task involves recording the notice, followed by storing and printing it. If the patient is known, the process continues to close the case. If the patient is unknown, a new patient file is created before closing the case.
+Meanwhile, the medical file is awaited. Once received, the medical file is used to update the patient file. After updating the patient file, a meeting with the second intaker is planned. The meeting date is set, and the meeting with the second intaker takes place. The conversation from this meeting is typed out, and the file is completed with the second intaker's information.
+Simultaneously, after closing the case, on Wednesday morning, intakers are assigned, and the assignment is stored. Cards are handed out, and meetings with both the first and second intakers are planned. The meeting with the first intaker is scheduled, and after the meeting, the file is completed with the first intaker's information.
+Finally, on the following Wednesday morning, the treatment is determined, marking the completion of the intake process.</t>
+  </si>
+  <si>
+    <t>9bfd42a80a7f4cb4b61387bc2c7a52bf</t>
+  </si>
+  <si>
+    <t>The process of planning a party begins with determining how many people will attend. Once the number of participants is known, the process splits into two parallel paths based on the expected number of attendees.
+If the number of participants is 10 or fewer, the next step is to buy ingredients for 10 people. After purchasing the ingredients, three tasks are carried out simultaneously: preparing zakouskis with vegetables and dip sauce, preparing mini-quiches, and preparing all three types of snacks. Once these tasks are completed, the snacks are served, and the party starts with good snacks.
+If the number of participants is between 10 and 15, the process involves buying ingredients for 15 people. Following this, three tasks are executed in parallel: preparing zakouskis with vegetables and dip sauce, preparing mini-quiches, and preparing all three types of snacks. After these preparations, the snacks are served, leading to the start of the party with good snacks.
+In both scenarios, the preparation tasks are carried out simultaneously to ensure that all snacks are ready to be served at the same time, marking the successful start of the party.</t>
+  </si>
+  <si>
+    <t>3beb6668e50a4805988cc64e3576091c</t>
+  </si>
+  <si>
+    <t>The process begins with the Risk Manager initiating the procedure. The first task for the Risk Manager is to perform a credit check. Once the credit check is completed, the Risk Manager proceeds to confirm the credibility check.
+After confirming the credibility check, the process reaches a decision point. Here, the Risk Manager evaluates the credibility assessment. If the assessment is rejected, the Administrator sends a rejection letter to the client, and the process concludes. If the assessment is accepted, the Customer Contact is responsible for calling the client to gather additional information.
+Following the call, the Customer Contact creates a loan offer. This offer is then checked by the Customer Contact to ensure accuracy before being sent to the client. After sending the loan offer, the process reaches another decision point.
+At this point, there are two possible paths. If the offer is accepted, the Customer Contact receives the accepted offer, and the process continues. If there is no immediate response, a timer is set for one hour. After this period, the Customer Contact reminds the client, and the process loops back to the decision point.
+Once the offer is accepted, the process splits into two parallel tasks. The Finance department activates the loan application and validates the loan activation. Simultaneously, the Administrator sends a welcome letter to the client.
+After the loan activation is validated, the Finance department executes the initial payment. Following this, the Administrator returns the necessary documents to the client. Finally, the process concludes with the Administrator marking the end of the procedure.</t>
+  </si>
+  <si>
+    <t>ccbdb0d979974cebb16597191785a0a4</t>
+  </si>
+  <si>
+    <t>The process begins with the Sales Department receiving an order. Once the order is received, the Sales Department sends an order request to the warehouse.
+The Warehouse Department then receives the order and checks the quantity using an automated system. At this point, a decision is made: if there is enough stock, the warehouse takes the product, scans the RFID tag, and transfers the data to the software. This leads to two simultaneous actions: updating the stock and informing the customer that the order is being processed.
+If there is not enough stock, two actions occur simultaneously: the warehouse informs the customer about the stock shortage and notifies the system about the low stock. The supplier then receives an order to replenish the stock and sends the products to the warehouse. Upon arrival, the warehouse scans the RFID tags and monitors the stock through the automated system. The Quality Control Department checks the quality of the products. If there are no defective garments, the warehouse stocks the products and updates the stock. If there are defective garments, the supplier receives the product back and replaces the defective items, after which the process of sending products is repeated.
+The process concludes when the stock is updated and there is enough stock, or when the customer is informed about the stock status.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,14 +1908,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -278,7 +1940,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -290,12 +1952,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -592,7 +2248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H211"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="3" customWidth="1"/>
@@ -631,213 +2287,222 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="345">
+    <row r="2" spans="1:8" ht="270">
       <c r="A2" s="3">
-        <v>238292</v>
+        <v>182497</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H2"/>
     </row>
-    <row r="3" spans="1:8" ht="195">
+    <row r="3" spans="1:8" ht="255">
       <c r="A3" s="3">
-        <v>243766</v>
+        <v>10842</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H3"/>
     </row>
-    <row r="4" spans="1:8" ht="255">
+    <row r="4" spans="1:8" ht="270">
       <c r="A4" s="3">
-        <v>10842</v>
+        <v>22450</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H4"/>
     </row>
     <row r="5" spans="1:8" ht="270">
       <c r="A5" s="3">
-        <v>384021</v>
+        <v>9388</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H5"/>
     </row>
-    <row r="6" spans="1:8" ht="300">
+    <row r="6" spans="1:8" ht="210">
       <c r="A6" s="3">
-        <v>346775</v>
+        <v>50794</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H6"/>
     </row>
-    <row r="7" spans="1:8" ht="195">
+    <row r="7" spans="1:8" ht="255">
       <c r="A7" s="3">
-        <v>365762</v>
+        <v>203267</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H7"/>
     </row>
     <row r="8" spans="1:8" ht="185.25" customHeight="1">
       <c r="A8" s="3">
-        <v>67486</v>
+        <v>149510</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8"/>
+    </row>
+    <row r="9" spans="1:8" ht="225">
+      <c r="A9" s="3">
+        <v>172563</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9"/>
+    </row>
+    <row r="10" spans="1:8" ht="270">
+      <c r="A10" s="3">
+        <v>384021</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H8"/>
-    </row>
-    <row r="9" spans="1:8" ht="270">
-      <c r="A9" s="3">
-        <v>4747</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H10"/>
+    </row>
+    <row r="11" spans="1:8" ht="225">
+      <c r="A11" s="3">
+        <v>257047</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H9"/>
-    </row>
-    <row r="10" spans="1:8" ht="334.5" customHeight="1">
-      <c r="A10" s="3">
-        <v>15086</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:8" ht="240">
-      <c r="A11" s="3">
-        <v>260593</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>17</v>
@@ -847,499 +2512,3379 @@
       </c>
       <c r="H11"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" ht="285">
+      <c r="A12" s="3">
+        <v>367129</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="H12"/>
     </row>
     <row r="13" spans="1:8" ht="328.5" customHeight="1">
+      <c r="A13" s="3">
+        <v>192025</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="H13"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" ht="270">
+      <c r="A14" s="3">
+        <v>211483</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="H14"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" ht="255">
+      <c r="A15" s="3">
+        <v>402973</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="H15"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" ht="270">
+      <c r="A16" s="3">
+        <v>317474</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="H16"/>
     </row>
-    <row r="17" spans="8:8" ht="382.5" customHeight="1">
+    <row r="17" spans="1:8" ht="382.5" customHeight="1">
+      <c r="A17" s="3">
+        <v>98856</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="H17"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="1:8" ht="270">
+      <c r="A18" s="3">
+        <v>324648</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="H18"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="1:8" ht="270">
+      <c r="A19" s="3">
+        <v>66092</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="H19"/>
     </row>
-    <row r="20" spans="8:8" ht="350.25" customHeight="1">
+    <row r="20" spans="1:8" ht="350.25" customHeight="1">
+      <c r="A20" s="3">
+        <v>165426</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="H20"/>
     </row>
-    <row r="21" spans="8:8">
+    <row r="21" spans="1:8" ht="210">
+      <c r="A21" s="3">
+        <v>224821</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="H21"/>
     </row>
-    <row r="22" spans="8:8">
+    <row r="22" spans="1:8" ht="315">
+      <c r="A22" s="3">
+        <v>342078</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="H22"/>
     </row>
-    <row r="23" spans="8:8">
+    <row r="23" spans="1:8" ht="255">
+      <c r="A23" s="3">
+        <v>255040</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="H23"/>
     </row>
-    <row r="24" spans="8:8">
+    <row r="24" spans="1:8" ht="210">
+      <c r="A24" s="3">
+        <v>194121</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="H24"/>
     </row>
-    <row r="25" spans="8:8">
+    <row r="25" spans="1:8" ht="240">
+      <c r="A25" s="3">
+        <v>294474</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="H25"/>
     </row>
-    <row r="26" spans="8:8">
+    <row r="26" spans="1:8" ht="195">
+      <c r="A26" s="3">
+        <v>102995</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="H26"/>
     </row>
-    <row r="27" spans="8:8">
+    <row r="27" spans="1:8" ht="210">
+      <c r="A27" s="3">
+        <v>140884</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="H27"/>
     </row>
-    <row r="28" spans="8:8">
+    <row r="28" spans="1:8" ht="285">
+      <c r="A28" s="3">
+        <v>402517</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="H28"/>
     </row>
-    <row r="29" spans="8:8">
+    <row r="29" spans="1:8" ht="315">
+      <c r="A29" s="3">
+        <v>346710</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="H29"/>
     </row>
-    <row r="30" spans="8:8">
+    <row r="30" spans="1:8" ht="240">
+      <c r="A30" s="3">
+        <v>42070</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="H30"/>
     </row>
-    <row r="31" spans="8:8" ht="266.25" customHeight="1">
+    <row r="31" spans="1:8" ht="266.25" customHeight="1">
+      <c r="A31" s="3">
+        <v>130649</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="H31"/>
     </row>
-    <row r="32" spans="8:8">
+    <row r="32" spans="1:8" ht="225">
+      <c r="A32" s="3">
+        <v>266842</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="H32"/>
     </row>
-    <row r="33" spans="8:8">
+    <row r="33" spans="1:8" ht="255">
+      <c r="A33" s="3">
+        <v>218719</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="H33"/>
     </row>
-    <row r="34" spans="8:8">
+    <row r="34" spans="1:8" ht="240">
+      <c r="A34" s="3">
+        <v>181858</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="H34"/>
     </row>
-    <row r="35" spans="8:8">
+    <row r="35" spans="1:8" ht="255">
+      <c r="A35" s="3">
+        <v>194148</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="H35"/>
     </row>
-    <row r="36" spans="8:8">
+    <row r="36" spans="1:8" ht="285">
+      <c r="A36" s="3">
+        <v>136804</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="H36"/>
     </row>
-    <row r="37" spans="8:8">
+    <row r="37" spans="1:8" ht="210">
+      <c r="A37" s="3">
+        <v>93286</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="H37"/>
     </row>
-    <row r="38" spans="8:8">
+    <row r="38" spans="1:8" ht="240">
+      <c r="A38" s="3">
+        <v>51309</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="H38"/>
     </row>
-    <row r="39" spans="8:8">
+    <row r="39" spans="1:8" ht="300">
+      <c r="A39" s="3">
+        <v>263279</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="H39"/>
     </row>
-    <row r="40" spans="8:8">
+    <row r="40" spans="1:8" ht="240">
+      <c r="A40" s="3">
+        <v>87671</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>92</v>
+      </c>
       <c r="H40"/>
     </row>
-    <row r="41" spans="8:8" ht="230.25" customHeight="1">
+    <row r="41" spans="1:8" ht="230.25" customHeight="1">
+      <c r="A41" s="3">
+        <v>277629</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="H41"/>
     </row>
-    <row r="42" spans="8:8">
+    <row r="42" spans="1:8" ht="195">
+      <c r="A42" s="3">
+        <v>353409</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="H42"/>
     </row>
-    <row r="43" spans="8:8">
+    <row r="43" spans="1:8" ht="255">
+      <c r="A43" s="3">
+        <v>3202</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="H43"/>
     </row>
-    <row r="44" spans="8:8">
+    <row r="44" spans="1:8" ht="360">
+      <c r="A44" s="3">
+        <v>370825</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>100</v>
+      </c>
       <c r="H44"/>
     </row>
-    <row r="45" spans="8:8">
+    <row r="45" spans="1:8" ht="255">
+      <c r="A45" s="3">
+        <v>79501</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="H45"/>
     </row>
-    <row r="46" spans="8:8">
+    <row r="46" spans="1:8" ht="405">
+      <c r="A46" s="3">
+        <v>18578</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="H46"/>
     </row>
-    <row r="47" spans="8:8">
+    <row r="47" spans="1:8" ht="240">
+      <c r="A47" s="3">
+        <v>244372</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="H47"/>
     </row>
-    <row r="48" spans="8:8">
+    <row r="48" spans="1:8" ht="300">
+      <c r="A48" s="3">
+        <v>346775</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="H48"/>
     </row>
-    <row r="49" spans="8:8">
+    <row r="49" spans="1:8" ht="300">
+      <c r="A49" s="3">
+        <v>161949</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="H49"/>
     </row>
-    <row r="50" spans="8:8" ht="338.25" customHeight="1">
+    <row r="50" spans="1:8" ht="338.25" customHeight="1">
+      <c r="A50" s="3">
+        <v>392356</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="H50"/>
     </row>
-    <row r="51" spans="8:8">
+    <row r="51" spans="1:8" ht="195">
+      <c r="A51" s="3">
+        <v>331941</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="H51"/>
     </row>
-    <row r="52" spans="8:8">
+    <row r="52" spans="1:8" ht="240">
+      <c r="A52" s="3">
+        <v>281255</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="H52"/>
     </row>
-    <row r="53" spans="8:8" ht="294" customHeight="1">
+    <row r="53" spans="1:8" ht="294" customHeight="1">
+      <c r="A53" s="3">
+        <v>79016</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>118</v>
+      </c>
       <c r="H53"/>
     </row>
-    <row r="54" spans="8:8">
+    <row r="54" spans="1:8" ht="240">
+      <c r="A54" s="3">
+        <v>105640</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="H54"/>
     </row>
-    <row r="55" spans="8:8">
+    <row r="55" spans="1:8" ht="330">
+      <c r="A55" s="3">
+        <v>221352</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>122</v>
+      </c>
       <c r="H55"/>
     </row>
-    <row r="56" spans="8:8">
+    <row r="56" spans="1:8" ht="330">
+      <c r="A56" s="3">
+        <v>257708</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="H56"/>
     </row>
-    <row r="57" spans="8:8">
+    <row r="57" spans="1:8" ht="255">
+      <c r="A57" s="3">
+        <v>201398</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="H57"/>
     </row>
-    <row r="58" spans="8:8" ht="345.75" customHeight="1">
+    <row r="58" spans="1:8" ht="345.75" customHeight="1">
+      <c r="A58" s="3">
+        <v>25271</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>128</v>
+      </c>
       <c r="H58"/>
     </row>
-    <row r="59" spans="8:8" ht="390.75" customHeight="1">
+    <row r="59" spans="1:8" ht="390.75" customHeight="1">
+      <c r="A59" s="3">
+        <v>47289</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="H59"/>
     </row>
-    <row r="60" spans="8:8">
+    <row r="60" spans="1:8" ht="240">
+      <c r="A60" s="3">
+        <v>139970</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="H60"/>
     </row>
-    <row r="61" spans="8:8">
+    <row r="61" spans="1:8" ht="195">
+      <c r="A61" s="3">
+        <v>365762</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="H61"/>
     </row>
-    <row r="62" spans="8:8">
+    <row r="62" spans="1:8" ht="210">
+      <c r="A62" s="3">
+        <v>185542</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="H62"/>
     </row>
-    <row r="63" spans="8:8">
+    <row r="63" spans="1:8" ht="225">
+      <c r="A63" s="3">
+        <v>257736</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="H63"/>
     </row>
-    <row r="64" spans="8:8">
+    <row r="64" spans="1:8" ht="315">
+      <c r="A64" s="3">
+        <v>6864</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>140</v>
+      </c>
       <c r="H64"/>
     </row>
-    <row r="65" spans="8:8">
+    <row r="65" spans="1:8" ht="255">
+      <c r="A65" s="3">
+        <v>7889</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>142</v>
+      </c>
       <c r="H65"/>
     </row>
-    <row r="66" spans="8:8">
+    <row r="66" spans="1:8" ht="210">
+      <c r="A66" s="3">
+        <v>245456</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="H66"/>
     </row>
-    <row r="67" spans="8:8">
+    <row r="67" spans="1:8" ht="240">
+      <c r="A67" s="3">
+        <v>10466</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>146</v>
+      </c>
       <c r="H67"/>
     </row>
-    <row r="68" spans="8:8">
+    <row r="68" spans="1:8" ht="255">
+      <c r="A68" s="3">
+        <v>161011</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="H68"/>
     </row>
-    <row r="69" spans="8:8">
+    <row r="69" spans="1:8" ht="255">
+      <c r="A69" s="3">
+        <v>352499</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>150</v>
+      </c>
       <c r="H69"/>
     </row>
-    <row r="70" spans="8:8">
+    <row r="70" spans="1:8" ht="240">
+      <c r="A70" s="3">
+        <v>235261</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="H70"/>
     </row>
-    <row r="71" spans="8:8">
+    <row r="71" spans="1:8" ht="210">
+      <c r="A71" s="3">
+        <v>169725</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>154</v>
+      </c>
       <c r="H71"/>
     </row>
-    <row r="72" spans="8:8">
+    <row r="72" spans="1:8" ht="300">
+      <c r="A72" s="3">
+        <v>385791</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="H72"/>
     </row>
-    <row r="73" spans="8:8">
+    <row r="73" spans="1:8" ht="300">
+      <c r="A73" s="3">
+        <v>258307</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>158</v>
+      </c>
       <c r="H73"/>
     </row>
-    <row r="74" spans="8:8">
+    <row r="74" spans="1:8" ht="195">
+      <c r="A74" s="3">
+        <v>198918</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="H74"/>
     </row>
-    <row r="75" spans="8:8">
+    <row r="75" spans="1:8" ht="225">
+      <c r="A75" s="3">
+        <v>97035</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>162</v>
+      </c>
       <c r="H75"/>
     </row>
-    <row r="76" spans="8:8">
+    <row r="76" spans="1:8" ht="270">
+      <c r="A76" s="3">
+        <v>339216</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>164</v>
+      </c>
       <c r="H76"/>
     </row>
-    <row r="77" spans="8:8">
+    <row r="77" spans="1:8" ht="300">
+      <c r="A77" s="3">
+        <v>219417</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="H77"/>
     </row>
-    <row r="78" spans="8:8" ht="377.25" customHeight="1">
+    <row r="78" spans="1:8" ht="377.25" customHeight="1">
+      <c r="A78" s="3">
+        <v>96027</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>168</v>
+      </c>
       <c r="H78"/>
     </row>
-    <row r="79" spans="8:8">
+    <row r="79" spans="1:8" ht="225">
+      <c r="A79" s="3">
+        <v>106785</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>170</v>
+      </c>
       <c r="H79"/>
     </row>
-    <row r="80" spans="8:8">
+    <row r="80" spans="1:8" ht="210">
+      <c r="A80" s="3">
+        <v>17188</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="H80"/>
     </row>
-    <row r="81" spans="8:8">
+    <row r="81" spans="1:8" ht="195">
+      <c r="A81" s="3">
+        <v>102700</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>174</v>
+      </c>
       <c r="H81"/>
     </row>
-    <row r="82" spans="8:8">
+    <row r="82" spans="1:8" ht="225">
+      <c r="A82" s="3">
+        <v>302388</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="H82"/>
     </row>
-    <row r="83" spans="8:8">
+    <row r="83" spans="1:8" ht="240">
+      <c r="A83" s="3">
+        <v>349496</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>178</v>
+      </c>
       <c r="H83"/>
     </row>
-    <row r="84" spans="8:8">
+    <row r="84" spans="1:8" ht="225">
+      <c r="A84" s="3">
+        <v>327996</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="H84"/>
     </row>
-    <row r="85" spans="8:8" ht="294.75" customHeight="1">
+    <row r="85" spans="1:8" ht="294.75" customHeight="1">
+      <c r="A85" s="3">
+        <v>383302</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="H85"/>
     </row>
-    <row r="86" spans="8:8">
+    <row r="86" spans="1:8" ht="195">
+      <c r="A86" s="3">
+        <v>90959</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="H86"/>
     </row>
-    <row r="87" spans="8:8">
+    <row r="87" spans="1:8" ht="225">
+      <c r="A87" s="3">
+        <v>239953</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>186</v>
+      </c>
       <c r="H87"/>
     </row>
-    <row r="88" spans="8:8">
+    <row r="88" spans="1:8" ht="240">
+      <c r="A88" s="3">
+        <v>303969</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>188</v>
+      </c>
       <c r="H88"/>
     </row>
-    <row r="89" spans="8:8">
+    <row r="89" spans="1:8" ht="240">
+      <c r="A89" s="3">
+        <v>122212</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="H89"/>
     </row>
-    <row r="90" spans="8:8">
+    <row r="90" spans="1:8" ht="225">
+      <c r="A90" s="3">
+        <v>355693</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="H90"/>
     </row>
-    <row r="91" spans="8:8">
+    <row r="91" spans="1:8" ht="240">
+      <c r="A91" s="3">
+        <v>343411</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="H91"/>
     </row>
-    <row r="92" spans="8:8">
+    <row r="92" spans="1:8" ht="225">
+      <c r="A92" s="3">
+        <v>160629</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="H92"/>
     </row>
-    <row r="93" spans="8:8">
+    <row r="93" spans="1:8" ht="409.5">
+      <c r="A93" s="3">
+        <v>224630</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>198</v>
+      </c>
       <c r="H93"/>
     </row>
-    <row r="94" spans="8:8">
+    <row r="94" spans="1:8" ht="315">
+      <c r="A94" s="3">
+        <v>162679</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="H94"/>
     </row>
-    <row r="95" spans="8:8">
+    <row r="95" spans="1:8" ht="255">
+      <c r="A95" s="3">
+        <v>150905</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="H95"/>
     </row>
-    <row r="96" spans="8:8">
+    <row r="96" spans="1:8" ht="285">
+      <c r="A96" s="3">
+        <v>131460</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="H96"/>
     </row>
-    <row r="97" spans="8:8">
+    <row r="97" spans="1:8" ht="255">
+      <c r="A97" s="3">
+        <v>82317</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="H97"/>
     </row>
-    <row r="98" spans="8:8">
+    <row r="98" spans="1:8" ht="285">
+      <c r="A98" s="3">
+        <v>172430</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="H98"/>
     </row>
-    <row r="99" spans="8:8">
+    <row r="99" spans="1:8" ht="240">
+      <c r="A99" s="3">
+        <v>51087</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="H99"/>
     </row>
-    <row r="100" spans="8:8">
+    <row r="100" spans="1:8" ht="240">
+      <c r="A100" s="3">
+        <v>274321</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="H100"/>
     </row>
-    <row r="101" spans="8:8">
+    <row r="101" spans="1:8" ht="270">
+      <c r="A101" s="3">
+        <v>272277</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="H101"/>
     </row>
-    <row r="102" spans="8:8">
+    <row r="102" spans="1:8" ht="270">
+      <c r="A102" s="3">
+        <v>269717</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="H102"/>
     </row>
-    <row r="103" spans="8:8">
+    <row r="103" spans="1:8" ht="270">
+      <c r="A103" s="3">
+        <v>387479</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>218</v>
+      </c>
       <c r="H103"/>
     </row>
-    <row r="104" spans="8:8">
+    <row r="104" spans="1:8" ht="240">
+      <c r="A104" s="3">
+        <v>336285</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="H104"/>
     </row>
-    <row r="105" spans="8:8">
+    <row r="105" spans="1:8" ht="255">
+      <c r="A105" s="3">
+        <v>67486</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="H105"/>
     </row>
-    <row r="106" spans="8:8" ht="152.25" customHeight="1">
+    <row r="106" spans="1:8" ht="152.25" customHeight="1">
+      <c r="A106" s="3">
+        <v>294304</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="H106"/>
     </row>
-    <row r="107" spans="8:8" ht="319.5" customHeight="1">
+    <row r="107" spans="1:8" ht="319.5" customHeight="1">
+      <c r="A107" s="3">
+        <v>157096</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>226</v>
+      </c>
       <c r="H107"/>
     </row>
-    <row r="108" spans="8:8">
+    <row r="108" spans="1:8" ht="270">
+      <c r="A108" s="3">
+        <v>107962</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>228</v>
+      </c>
       <c r="H108"/>
     </row>
-    <row r="109" spans="8:8">
+    <row r="109" spans="1:8" ht="225">
+      <c r="A109" s="3">
+        <v>61394</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="H109"/>
     </row>
-    <row r="110" spans="8:8">
+    <row r="110" spans="1:8" ht="225">
+      <c r="A110" s="3">
+        <v>147410</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="H110"/>
     </row>
-    <row r="111" spans="8:8">
+    <row r="111" spans="1:8" ht="210">
+      <c r="A111" s="3">
+        <v>381910</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="H111"/>
     </row>
-    <row r="112" spans="8:8">
+    <row r="112" spans="1:8" ht="330">
+      <c r="A112" s="3">
+        <v>119770</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="H112"/>
     </row>
-    <row r="113" spans="8:8">
+    <row r="113" spans="1:8" ht="285">
+      <c r="A113" s="3">
+        <v>378843</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="H113"/>
     </row>
-    <row r="114" spans="8:8">
+    <row r="114" spans="1:8" ht="240">
+      <c r="A114" s="3">
+        <v>306656</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>240</v>
+      </c>
       <c r="H114"/>
     </row>
-    <row r="115" spans="8:8">
+    <row r="115" spans="1:8" ht="210">
+      <c r="A115" s="3">
+        <v>371172</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="H115"/>
     </row>
-    <row r="116" spans="8:8">
+    <row r="116" spans="1:8" ht="195">
+      <c r="A116" s="3">
+        <v>330218</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="H116"/>
     </row>
-    <row r="117" spans="8:8">
+    <row r="117" spans="1:8" ht="255">
+      <c r="A117" s="3">
+        <v>31568</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="H117"/>
     </row>
-    <row r="118" spans="8:8">
+    <row r="118" spans="1:8" ht="330">
+      <c r="A118" s="3">
+        <v>115775</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>248</v>
+      </c>
       <c r="H118"/>
     </row>
-    <row r="119" spans="8:8">
+    <row r="119" spans="1:8" ht="270">
+      <c r="A119" s="3">
+        <v>138911</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="H119"/>
     </row>
-    <row r="120" spans="8:8">
+    <row r="120" spans="1:8" ht="240">
+      <c r="A120" s="3">
+        <v>390121</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="H120"/>
     </row>
-    <row r="121" spans="8:8">
+    <row r="121" spans="1:8" ht="285">
+      <c r="A121" s="3">
+        <v>376242</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="H121"/>
     </row>
-    <row r="122" spans="8:8">
+    <row r="122" spans="1:8" ht="300">
+      <c r="A122" s="3">
+        <v>400</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>256</v>
+      </c>
       <c r="H122"/>
     </row>
-    <row r="123" spans="8:8">
+    <row r="123" spans="1:8" ht="270">
+      <c r="A123" s="3">
+        <v>104064</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>258</v>
+      </c>
       <c r="H123"/>
     </row>
-    <row r="124" spans="8:8">
+    <row r="124" spans="1:8" ht="210">
+      <c r="A124" s="3">
+        <v>262785</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="H124"/>
     </row>
-    <row r="125" spans="8:8">
+    <row r="125" spans="1:8" ht="225">
+      <c r="A125" s="3">
+        <v>313605</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="H125"/>
     </row>
-    <row r="126" spans="8:8">
+    <row r="126" spans="1:8" ht="255">
+      <c r="A126" s="3">
+        <v>259720</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>264</v>
+      </c>
       <c r="H126"/>
     </row>
-    <row r="127" spans="8:8">
+    <row r="127" spans="1:8" ht="285">
+      <c r="A127" s="3">
+        <v>130057</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="H127"/>
     </row>
-    <row r="128" spans="8:8">
+    <row r="128" spans="1:8" ht="330">
+      <c r="A128" s="3">
+        <v>354057</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>268</v>
+      </c>
       <c r="H128"/>
     </row>
-    <row r="129" spans="8:8">
+    <row r="129" spans="1:8" ht="270">
+      <c r="A129" s="3">
+        <v>4747</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>270</v>
+      </c>
       <c r="H129"/>
     </row>
-    <row r="130" spans="8:8">
+    <row r="130" spans="1:8" ht="255">
+      <c r="A130" s="3">
+        <v>119437</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="H130"/>
     </row>
-    <row r="131" spans="8:8">
+    <row r="131" spans="1:8" ht="255">
+      <c r="A131" s="3">
+        <v>355854</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="H131"/>
     </row>
-    <row r="132" spans="8:8" ht="409.5" customHeight="1">
+    <row r="132" spans="1:8" ht="409.5" customHeight="1">
+      <c r="A132" s="3">
+        <v>371989</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="H132"/>
     </row>
-    <row r="133" spans="8:8">
+    <row r="133" spans="1:8" ht="225">
+      <c r="A133" s="3">
+        <v>193528</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="H133"/>
     </row>
-    <row r="134" spans="8:8">
+    <row r="134" spans="1:8" ht="270">
+      <c r="A134" s="3">
+        <v>105366</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>280</v>
+      </c>
       <c r="H134"/>
     </row>
-    <row r="135" spans="8:8">
+    <row r="135" spans="1:8" ht="300">
+      <c r="A135" s="3">
+        <v>304792</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>282</v>
+      </c>
       <c r="H135"/>
     </row>
-    <row r="136" spans="8:8">
+    <row r="136" spans="1:8" ht="225">
+      <c r="A136" s="3">
+        <v>321693</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="H136"/>
     </row>
-    <row r="137" spans="8:8">
+    <row r="137" spans="1:8" ht="270">
+      <c r="A137" s="3">
+        <v>178601</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="H137"/>
     </row>
-    <row r="138" spans="8:8">
+    <row r="138" spans="1:8" ht="270">
+      <c r="A138" s="3">
+        <v>73005</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>288</v>
+      </c>
       <c r="H138"/>
     </row>
-    <row r="139" spans="8:8">
+    <row r="139" spans="1:8" ht="270">
+      <c r="A139" s="3">
+        <v>339248</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="H139"/>
     </row>
-    <row r="140" spans="8:8">
+    <row r="140" spans="1:8" ht="255">
+      <c r="A140" s="3">
+        <v>102321</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>292</v>
+      </c>
       <c r="H140"/>
     </row>
-    <row r="141" spans="8:8">
+    <row r="141" spans="1:8" ht="270">
+      <c r="A141" s="3">
+        <v>89778</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>294</v>
+      </c>
       <c r="H141"/>
     </row>
-    <row r="142" spans="8:8">
+    <row r="142" spans="1:8" ht="285">
+      <c r="A142" s="3">
+        <v>41653</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="H142"/>
     </row>
-    <row r="143" spans="8:8">
+    <row r="143" spans="1:8" ht="315">
+      <c r="A143" s="3">
+        <v>245815</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="H143"/>
     </row>
-    <row r="144" spans="8:8">
+    <row r="144" spans="1:8" ht="255">
+      <c r="A144" s="3">
+        <v>195128</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="H144"/>
     </row>
-    <row r="145" spans="8:8">
+    <row r="145" spans="1:8" ht="240">
+      <c r="A145" s="3">
+        <v>302394</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="H145"/>
     </row>
-    <row r="146" spans="8:8">
+    <row r="146" spans="1:8" ht="240">
+      <c r="A146" s="3">
+        <v>278844</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>304</v>
+      </c>
       <c r="H146"/>
     </row>
-    <row r="147" spans="8:8">
+    <row r="147" spans="1:8" ht="210">
+      <c r="A147" s="3">
+        <v>77628</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="H147"/>
     </row>
-    <row r="148" spans="8:8">
+    <row r="148" spans="1:8" ht="315">
+      <c r="A148" s="3">
+        <v>393801</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>308</v>
+      </c>
       <c r="H148"/>
     </row>
-    <row r="149" spans="8:8">
+    <row r="149" spans="1:8" ht="285">
+      <c r="A149" s="3">
+        <v>105417</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>310</v>
+      </c>
       <c r="H149"/>
     </row>
-    <row r="150" spans="8:8" ht="344.25" customHeight="1">
+    <row r="150" spans="1:8" ht="344.25" customHeight="1">
+      <c r="A150" s="3">
+        <v>11091</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>312</v>
+      </c>
       <c r="H150"/>
     </row>
-    <row r="151" spans="8:8">
+    <row r="151" spans="1:8" ht="255">
+      <c r="A151" s="3">
+        <v>24661</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>314</v>
+      </c>
       <c r="H151"/>
     </row>
-    <row r="152" spans="8:8">
+    <row r="152" spans="1:8" ht="225">
+      <c r="A152" s="3">
+        <v>124120</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>316</v>
+      </c>
       <c r="H152"/>
     </row>
-    <row r="153" spans="8:8">
+    <row r="153" spans="1:8" ht="255">
+      <c r="A153" s="3">
+        <v>322264</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="H153"/>
     </row>
-    <row r="154" spans="8:8">
+    <row r="154" spans="1:8" ht="285">
+      <c r="A154" s="3">
+        <v>54235</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>320</v>
+      </c>
       <c r="H154"/>
     </row>
-    <row r="155" spans="8:8">
+    <row r="155" spans="1:8" ht="300">
+      <c r="A155" s="3">
+        <v>411099</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>322</v>
+      </c>
       <c r="H155"/>
     </row>
-    <row r="156" spans="8:8">
+    <row r="156" spans="1:8" ht="300">
+      <c r="A156" s="3">
+        <v>133085</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="H156"/>
     </row>
-    <row r="157" spans="8:8">
+    <row r="157" spans="1:8" ht="225">
+      <c r="A157" s="3">
+        <v>221791</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>326</v>
+      </c>
       <c r="H157"/>
     </row>
-    <row r="158" spans="8:8" ht="409.5" customHeight="1">
+    <row r="158" spans="1:8" ht="409.5" customHeight="1">
+      <c r="A158" s="3">
+        <v>79074</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>328</v>
+      </c>
       <c r="H158"/>
     </row>
-    <row r="159" spans="8:8">
+    <row r="159" spans="1:8" ht="300">
+      <c r="A159" s="3">
+        <v>208509</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="H159"/>
     </row>
-    <row r="160" spans="8:8" ht="334.5" customHeight="1">
+    <row r="160" spans="1:8" ht="334.5" customHeight="1">
+      <c r="A160" s="3">
+        <v>163326</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>332</v>
+      </c>
       <c r="H160"/>
     </row>
-    <row r="161" spans="8:8">
+    <row r="161" spans="1:8" ht="255">
+      <c r="A161" s="3">
+        <v>47850</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>334</v>
+      </c>
       <c r="H161"/>
     </row>
-    <row r="162" spans="8:8">
+    <row r="162" spans="1:8" ht="240">
+      <c r="A162" s="3">
+        <v>15086</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>336</v>
+      </c>
       <c r="H162"/>
     </row>
-    <row r="163" spans="8:8">
+    <row r="163" spans="1:8" ht="285">
+      <c r="A163" s="3">
+        <v>154224</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="H163"/>
     </row>
-    <row r="164" spans="8:8">
+    <row r="164" spans="1:8" ht="240">
+      <c r="A164" s="3">
+        <v>260593</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>340</v>
+      </c>
       <c r="H164"/>
     </row>
-    <row r="165" spans="8:8">
+    <row r="165" spans="1:8" ht="270">
+      <c r="A165" s="3">
+        <v>365171</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>342</v>
+      </c>
       <c r="H165"/>
     </row>
-    <row r="166" spans="8:8">
+    <row r="166" spans="1:8" ht="255">
+      <c r="A166" s="3">
+        <v>236023</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>344</v>
+      </c>
       <c r="H166"/>
     </row>
-    <row r="167" spans="8:8">
+    <row r="167" spans="1:8" ht="255">
+      <c r="A167" s="3">
+        <v>126712</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="H167"/>
     </row>
-    <row r="168" spans="8:8">
+    <row r="168" spans="1:8" ht="225">
+      <c r="A168" s="3">
+        <v>99581</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="H168"/>
     </row>
-    <row r="169" spans="8:8">
+    <row r="169" spans="1:8" ht="285">
+      <c r="A169" s="3">
+        <v>11774</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>350</v>
+      </c>
       <c r="H169"/>
     </row>
-    <row r="170" spans="8:8">
+    <row r="170" spans="1:8" ht="240">
+      <c r="A170" s="3">
+        <v>317810</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>352</v>
+      </c>
       <c r="H170"/>
     </row>
-    <row r="171" spans="8:8">
+    <row r="171" spans="1:8">
       <c r="H171"/>
     </row>
-    <row r="172" spans="8:8">
+    <row r="172" spans="1:8">
       <c r="H172"/>
     </row>
-    <row r="173" spans="8:8">
+    <row r="173" spans="1:8">
       <c r="H173"/>
     </row>
-    <row r="174" spans="8:8">
+    <row r="174" spans="1:8">
       <c r="H174"/>
     </row>
-    <row r="175" spans="8:8">
+    <row r="175" spans="1:8">
       <c r="H175"/>
     </row>
-    <row r="176" spans="8:8">
+    <row r="176" spans="1:8">
       <c r="H176"/>
     </row>
     <row r="177" spans="8:8">
@@ -1417,10 +5962,10 @@
     <row r="201" spans="8:8">
       <c r="H201"/>
     </row>
-    <row r="202" spans="8:8">
+    <row r="202" spans="8:8" ht="365.25" customHeight="1">
       <c r="H202"/>
     </row>
-    <row r="203" spans="8:8" ht="365.25" customHeight="1">
+    <row r="203" spans="8:8">
       <c r="H203"/>
     </row>
     <row r="204" spans="8:8">
@@ -1438,14 +5983,11 @@
     <row r="208" spans="8:8">
       <c r="H208"/>
     </row>
-    <row r="209" spans="8:8">
+    <row r="209" spans="8:8" ht="409.5" customHeight="1">
       <c r="H209"/>
     </row>
-    <row r="210" spans="8:8" ht="409.5" customHeight="1">
+    <row r="210" spans="8:8" ht="298.5" customHeight="1">
       <c r="H210"/>
-    </row>
-    <row r="211" spans="8:8" ht="298.5" customHeight="1">
-      <c r="H211"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/res/data/annotate/sap sam/sap_sam_models.xlsx
+++ b/res/data/annotate/sap sam/sap_sam_models.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="437">
   <si>
     <t>ID</t>
   </si>
@@ -42,13 +42,178 @@
     <t>Comment</t>
   </si>
   <si>
+    <t>355dd7c8cfb740938efdd65917ae9246</t>
+  </si>
+  <si>
     <t>SAP SAM</t>
   </si>
   <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>5529cc06ce3d450a9cea2a2773c54f55</t>
+  </si>
+  <si>
+    <t>ac33a55a91b84d4b8a98293c20bc3c40</t>
+  </si>
+  <si>
+    <t>ffd38dc2057446e9908fadab3f3408ee</t>
+  </si>
+  <si>
+    <t>42e471e451fc4dda9cf4616b05636c46</t>
+  </si>
+  <si>
+    <t>e702ca78db194e5eb7e9ab810f1446d6</t>
+  </si>
+  <si>
+    <t>1b3bacff096245bfb3f309ae7540d56d</t>
+  </si>
+  <si>
+    <t>ad8a5c9b1e5c4e38aea666f54255c64e</t>
+  </si>
+  <si>
+    <t>1bda33b9c1294050846f421d22b10bee</t>
+  </si>
+  <si>
+    <t>057673f857ff45d4aacc6a3fa117158d</t>
+  </si>
+  <si>
+    <t>40837a04ab104d009ef36d34e24139ab</t>
+  </si>
+  <si>
+    <t>65514bf9a5f749699611692d8b66248f</t>
+  </si>
+  <si>
+    <t>d9330b9a8f82447fa7b334df04b8c4c6</t>
+  </si>
+  <si>
+    <t>ddc0afbe0c2c48df8bea682bb0f15dca</t>
+  </si>
+  <si>
+    <t>68c82ee88258471a9f97db3df07827b5</t>
+  </si>
+  <si>
+    <t>9de921bf797c477aa4331384be9d2321</t>
+  </si>
+  <si>
+    <t>96b28d73860d4582a670de26d29244f3</t>
+  </si>
+  <si>
+    <t>47b22c3a19ce4d9cbf7617a757d1aee4</t>
+  </si>
+  <si>
+    <t>bdc6f8f1d9bb4b58a80bde8aedd9b0dc</t>
+  </si>
+  <si>
+    <t>9a63d05f68f54711a9fff09bd71d2143</t>
+  </si>
+  <si>
+    <t>e8d4376594f140e4b65ab41eca1b784a</t>
+  </si>
+  <si>
+    <t>b41fb8c4f3934d32b9f6863788d6245b</t>
+  </si>
+  <si>
+    <t>11fbdf09c3cf4a7295e927826bf648a4</t>
+  </si>
+  <si>
+    <t>b51d14e62ccf4c5d83bd5dcfb56c2368</t>
+  </si>
+  <si>
+    <t>b2f2f868d7374bf5b9052cee433ff2d5</t>
+  </si>
+  <si>
+    <t>6a5d530a50f54f0c91f4775246b0343f</t>
+  </si>
+  <si>
+    <t>da894799c9044d4ca996055fd98b61a3</t>
+  </si>
+  <si>
+    <t>3ca5c78eb3c040339280d75ff82dcf99</t>
+  </si>
+  <si>
+    <t>8a6b2d20e86341bdaf829d41ed8533cb</t>
+  </si>
+  <si>
+    <t>Language = English
+Gateway Check = True
+Has Unknown = False
+Has OR-Gateway = False
+Connectivity = 0-1
+Amount of Gateways = 0
+Amount of Basic Elems = 10-25
+Amount of Events = 0-10
+Rate Useless Elems Max = 0.1
+Rate Basic Elems Min = 0.30
+Average Element Degree = 1.5-2.5
+Average Element Length = 15.0-30.0
+Structural Elems = 0-5</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>Manual</t>
+    <t>Language = English
+Gateway Check = True
+Has Unknown = False
+Has OR-Gateway = False
+Connectivity = 0-1
+Amount of Gateways = 2-4
+Amount of Basic Elems = 10-25
+Amount of Events = 2-10
+Rate Useless Elems Max = 0.1
+Rate Basic Elems Min = 0.30
+Average Element Degree = 1.5-2.5
+Average Element Length = 15.0-30.0
+Structural Elems = 0-5</t>
+  </si>
+  <si>
+    <t>0bf87340df414493a68e52cd31c0c7bc</t>
+  </si>
+  <si>
+    <t>18a3ab537e4d49679c2ff33182087b54</t>
+  </si>
+  <si>
+    <t>18b833935a0e4b68973e3d21c47539b5</t>
+  </si>
+  <si>
+    <t>e8a0c5f657e9417db24f2bf1451aebe5</t>
+  </si>
+  <si>
+    <t>Language = English
+Gateway Check = True
+Has Unknown = False
+Has OR-Gateway = False
+Connectivity = 0-1
+Amount of Gateways = 2-4
+Amount of Basic Elems = 10-25
+Amount of Events = 2-10
+Rate Useless Elems Max = 0.1
+Rate Basic Elems Min = 0.3
+Average Element Degree = 1.5-2.5
+Average Element Length = 12.0-30.0
+Structural Elems = 0-5</t>
+  </si>
+  <si>
+    <t>2d07e6fc23504412b3e27dd09719609d</t>
+  </si>
+  <si>
+    <t>b60972404d5e49f49b9d86e62c7f46ac</t>
+  </si>
+  <si>
+    <t>c7752226579945cca2777c5394b5b8ad</t>
+  </si>
+  <si>
+    <t>a0435f8f0cf24a98aebbb13ae6eb5b64</t>
+  </si>
+  <si>
+    <t>59b47af424674fe5a038d309d7d53c47</t>
+  </si>
+  <si>
+    <t>f5189d751e1f45da979be9b4ddf2b337</t>
+  </si>
+  <si>
+    <t>81769145ee034a208900ac1fb2974705</t>
   </si>
   <si>
     <t>77428c7083cb43e0b6b90e250971b80b</t>
@@ -69,22 +234,7 @@
 Structural Elems = 0-5</t>
   </si>
   <si>
-    <t>The process begins with a user starting the task of selecting a bank. The user can choose a bank using a specific method, which is noted as "Selection via BLZ."
-Once the bank is selected, the user encounters a decision point to determine if the bank was found. If the bank is found, the user proceeds to enter bank credentials. If the bank is not found, an error message is displayed to the user. After displaying the error message, the user decides whether to contact support. If the user chooses not to contact support, the process ends. If the user decides to contact support, they can either fill out a form or call the service, after which the process ends.
-If the bank is found and the user enters the bank credentials, the next step is to connect with the bank. After attempting to connect, there is another decision point to check if the connection was successful. If the connection fails, an error message is shown, and the user is directed back to the step of entering bank credentials. The error messages that might be shown include "Bank connection not found," "An unexpected error occurred," and "Incorrect authorization."
-If the connection is successful, the user retrieves all transactions. The user has the option to categorize transactions themselves or allow the system to categorize them. After retrieving transactions, the user searches for a possible renter. If a renter is found, the user selects the renter and transaction, then views a payment overview, and the process ends. If no renter is found, a message is shown, and the user manually selects transactions, views the payment overview, and the process ends. 
-Throughout the process, the "App System" is associated with various tasks, including showing error messages, connecting with the bank, retrieving transactions, finding possible renters, and showing messages.</t>
-  </si>
-  <si>
     <t>3b5958b76ac44674970c5b7c4592a27f</t>
-  </si>
-  <si>
-    <t>The process begins when a Level 1 Employee at the IT Helpdesk receives a request. The first task for the Level 1 Employee is to determine if the solution to the problem is already known. 
-If the solution is known, the Level 1 Employee proceeds to solve the problem and then informs the customer that the problem has been solved, concluding the process.
-If the solution is unknown, the Level 1 Employee forwards the request to a Level 2 Employee. The Level 2 Employee receives the request and evaluates it. After evaluating the request, the Level 2 Employee assigns a priority level to it. This priority level is then entered into the Job Tracking System.
-The Job Tracking System assigns the request to a Level 2 Employee, who receives it and begins researching and developing a solution. Once a solution is developed, the Level 2 Employee sends it back to the Level 1 Employee.
-The Level 1 Employee receives the solution and tests it. If the test is successful, the Level 1 Employee informs the customer that the problem has been solved, and the process ends.
-If the test is unsuccessful, the Level 1 Employee sends the request back to the Level 2 Employee for further research and development. This cycle continues until a successful solution is found and the customer is informed.</t>
   </si>
   <si>
     <t>00f027dd6b1e404591f85c0daa4bf2b9</t>
@@ -105,20 +255,6 @@
 Structural Elems = 0-5</t>
   </si>
   <si>
-    <t>The business process begins when the Sales department receives a purchase order from a customer. The Sales team then enters the order data into the system. Following this, the Accounting/Finance department performs a credit check on the customer.
-At this point, there is a decision to be made based on the credit check results. If the credit check fails, the process moves to setting the order status to blocked. The Accounting/Finance team then refers the case to a specialist for further evaluation. The specialist evaluates the case and makes another decision. If the case remains blocked, the Accounting/Finance department informs the customer why the sales order is blocked.
-If the credit check passes, the order is approved, and the Accounting/Finance team checks the availability of the items. If the items are available, the process continues with the Shipping/Receiving department releasing the sales order. If the items are not available, a purchase requisition is created and referred to the Procurement department.
-The Procurement department reviews the purchase requisition and decides whether to approve it. If not approved, the Procurement team informs the Sales department, which then informs the customer about the blocked order. If approved, the Procurement team chooses a vendor and converts the purchase requisition into a purchase order, which is then transmitted to the vendor.
-Once the vendor sends the materials, the Shipping/Receiving department receives them and proceeds to pick the materials, arrange transportation, and ship them to the customer. Meanwhile, the Accounting/Finance department sends an invoice to the customer.
-After the customer receives the invoice, they make a payment, which the Accounting/Finance department receives and processes. Finally, the receivable is cleared, and the sales order is marked as completed, concluding the process.</t>
-  </si>
-  <si>
-    <t>3a76ddad69984f23ad28f2cf09a48ee4</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
     <t>Language = English
 Gateway Check = True
 Has Unknown = False
@@ -134,6 +270,895 @@
 Structural Elems = 0-5</t>
   </si>
   <si>
+    <t>3a76ddad69984f23ad28f2cf09a48ee4</t>
+  </si>
+  <si>
+    <t>f1571a41756f429485487f475cb2865d</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>959768fda5984592ae8e7bcf771bf9e2</t>
+  </si>
+  <si>
+    <t>0dd8931c54064aa0812834e68a614c86</t>
+  </si>
+  <si>
+    <t>8022ba7914cf4693925c6674490ee56c</t>
+  </si>
+  <si>
+    <t>c5cd15f5fd3f443eaff73696b9ecd6cc</t>
+  </si>
+  <si>
+    <t>d6b33aca297248d1aeee6bb064181975</t>
+  </si>
+  <si>
+    <t>d98f4d3b681c431eada23a0a5f99664f</t>
+  </si>
+  <si>
+    <t>b6a319ff222e460db7e2f7c32a8de60e</t>
+  </si>
+  <si>
+    <t>5709e97013004689a5250805f039b04c</t>
+  </si>
+  <si>
+    <t>314244d1f81a488ab13e5821970fd533</t>
+  </si>
+  <si>
+    <t>cc88d8b942aa4cf7b21fcfb651a14594</t>
+  </si>
+  <si>
+    <t>9b8e781476924f6aaa6c92069724476b</t>
+  </si>
+  <si>
+    <t>ab698d0d639f48568d0706f87391e4d1</t>
+  </si>
+  <si>
+    <t>1e3e8c5fe7ad46158e89fb38c8be6fb8</t>
+  </si>
+  <si>
+    <t>793cb97cb029428eb376629063898c2c</t>
+  </si>
+  <si>
+    <t>2aaf9036d6214edfa70ef0100eac7b5b</t>
+  </si>
+  <si>
+    <t>1af7cca2da4d496985fab343d02809f9</t>
+  </si>
+  <si>
+    <t>d56fc0ce496946e1a88a391b2c2e6d50</t>
+  </si>
+  <si>
+    <t>744cddfa416b49d5987ba90e0cea0cdd</t>
+  </si>
+  <si>
+    <t>20bd5cf84b6547f5a201e289e676d8a9</t>
+  </si>
+  <si>
+    <t>7b04fdc80c4144d6856687b6d970609b</t>
+  </si>
+  <si>
+    <t>7139592663a7445d9acc8619e04db06c</t>
+  </si>
+  <si>
+    <t>30f804a3e5e64ef298266e67acfecc4b</t>
+  </si>
+  <si>
+    <t>c0266568845e41b8ab7a99baa359b612</t>
+  </si>
+  <si>
+    <t>c8d11f6234f549bcbcea682c891da632</t>
+  </si>
+  <si>
+    <t>9ff5bb3ce2c843dba9e1562c641365fd</t>
+  </si>
+  <si>
+    <t>6c5d8483fb51405096a01946d550b55d</t>
+  </si>
+  <si>
+    <t>e29280012da84bd3a14aceaee0d6d114</t>
+  </si>
+  <si>
+    <t>76d9bdc2ae634edbaa67e809182e3688</t>
+  </si>
+  <si>
+    <t>74538661264347fb8cdfbfbd5476d950</t>
+  </si>
+  <si>
+    <t>c6cf1da7e789466993ca214fa9e41763</t>
+  </si>
+  <si>
+    <t>096954d076984050902e9c92035a331c</t>
+  </si>
+  <si>
+    <t>f1aaad76e4d845a2bd7e45dda90e32af</t>
+  </si>
+  <si>
+    <t>1240884060c64c629dc7c13357555caa</t>
+  </si>
+  <si>
+    <t>92541a4399cf48429283280ba0f30594</t>
+  </si>
+  <si>
+    <t>599bc5727aa347d28056f245abc3fd6c</t>
+  </si>
+  <si>
+    <t>a922ed6455094ebca47ab19950189ab4</t>
+  </si>
+  <si>
+    <t>1dafcaa36034450d98dd6c785ed4e026</t>
+  </si>
+  <si>
+    <t>4fa9326b71d94920993720520b2712e5</t>
+  </si>
+  <si>
+    <t>49a24f70597040208f977637c5f4ba2f</t>
+  </si>
+  <si>
+    <t>c1f695e4abf74245b749b0b443c699e8</t>
+  </si>
+  <si>
+    <t>4812b60389444ba4b480cdcd51c9eb2c</t>
+  </si>
+  <si>
+    <t>c02fd526a0d4465db1c26aa174c9c85d</t>
+  </si>
+  <si>
+    <t>1075135c161b40e7a6655dd68aa1c5e0</t>
+  </si>
+  <si>
+    <t>fd2c9f678fea49218a54235507d654bb</t>
+  </si>
+  <si>
+    <t>7df0261769274726b341a9a2ab2dcdd2</t>
+  </si>
+  <si>
+    <t>9864e8a829b54588bf70ed08b9049979</t>
+  </si>
+  <si>
+    <t>495162891d3747a98b9da1b50a7a1336</t>
+  </si>
+  <si>
+    <t>7ca4ed9ebdca4945b21aa9c71b974b1e</t>
+  </si>
+  <si>
+    <t>2880b7e234cf4d1cae1cdd1ec36abee1</t>
+  </si>
+  <si>
+    <t>ee048ea75e6948c7bdc72b40427d6dfd</t>
+  </si>
+  <si>
+    <t>947b47653378445eb06f47d4363d848d</t>
+  </si>
+  <si>
+    <t>a30afaed2e524845ae093459f3f503a3</t>
+  </si>
+  <si>
+    <t>dd81de6e1cf147b79457934cc6480968</t>
+  </si>
+  <si>
+    <t>875870ab3de2450e830d6243f8f9d212</t>
+  </si>
+  <si>
+    <t>d8c408c7e7504253bf052eceb786e676</t>
+  </si>
+  <si>
+    <t>69a6f00c8edb4c44874fe1f7181fdc23</t>
+  </si>
+  <si>
+    <t>ee097c609dea4c52a6e7a941627332a6</t>
+  </si>
+  <si>
+    <t>659bdd2ae4ce46af834eaecdf4a26038</t>
+  </si>
+  <si>
+    <t>663ef9193c9b471a87c214bf2ea14489</t>
+  </si>
+  <si>
+    <t>e8fc095af9734c7598bbd88eaac97421</t>
+  </si>
+  <si>
+    <t>3b239cd2ee9a422687c65c2558f81462</t>
+  </si>
+  <si>
+    <t>0fe73faca0fd4b85b7b1ba795871ff46</t>
+  </si>
+  <si>
+    <t>a8902208793d43d5854db238120279f1</t>
+  </si>
+  <si>
+    <t>6301a8f360854cf39e9df4f0341990ec</t>
+  </si>
+  <si>
+    <t>0396fb06704347bf9bf47c2aa4f79379</t>
+  </si>
+  <si>
+    <t>a601e32c53c4467d8ed98f9621036ff4</t>
+  </si>
+  <si>
+    <t>ee5fa56b9ef74ed3b1f85dcab54fb9b9</t>
+  </si>
+  <si>
+    <t>3db43399d426454eb42ba9bd4030bf2f</t>
+  </si>
+  <si>
+    <t>cefef269825442389ec099316243fd76</t>
+  </si>
+  <si>
+    <t>192c32688fd843d5b6e0a17118135705</t>
+  </si>
+  <si>
+    <t>e2fd6ab82aa74bce9c6fa852e9b17f68</t>
+  </si>
+  <si>
+    <t>ce5eea23801144bbafcfe5bc8539c76a</t>
+  </si>
+  <si>
+    <t>a06503d2a935460f930219a268165a14</t>
+  </si>
+  <si>
+    <t>c112d84b30bb4ea4beb8f319c4eabada</t>
+  </si>
+  <si>
+    <t>9ddec87747bf4637b51924e14ca31107</t>
+  </si>
+  <si>
+    <t>552fceee752c4d9988ace97e9463f344</t>
+  </si>
+  <si>
+    <t>b8475caa0a3f4fe7a1873247964f8a5a</t>
+  </si>
+  <si>
+    <t>8cf7ace8e12f4f29acb30bb9910b53a4</t>
+  </si>
+  <si>
+    <t>c55ede3b5d854c99bcd96dacf4b0c1b9</t>
+  </si>
+  <si>
+    <t>080284b2437741a89d278a23b13b51ce</t>
+  </si>
+  <si>
+    <t>365f66984b454c18a8d3438487cda5a9</t>
+  </si>
+  <si>
+    <t>381801f4fae447889fb0ea36001c27be</t>
+  </si>
+  <si>
+    <t>b154d4c8fa2a4677b37d02f8108b92bd</t>
+  </si>
+  <si>
+    <t>ffd1d4e5b137499f8bbd7be5e113887b</t>
+  </si>
+  <si>
+    <t>257ede1b23f94c839202dc36f26473d8</t>
+  </si>
+  <si>
+    <t>0fa69773765e45a68b15a31c52f9dc36</t>
+  </si>
+  <si>
+    <t>2a8f497c99b345b68f74158e8e35e9a4</t>
+  </si>
+  <si>
+    <t>10ec5606971a42bba3dbf7b7c3eda017</t>
+  </si>
+  <si>
+    <t>0eb6dbd2f0ae4339b3bcaa58648ddbfc</t>
+  </si>
+  <si>
+    <t>99045ae01e524bfbb067dae6996637d3</t>
+  </si>
+  <si>
+    <t>4b69ca8c3ed1435a92b24d9e0d7d5086</t>
+  </si>
+  <si>
+    <t>8010792df10c43dfab130131e36744d6</t>
+  </si>
+  <si>
+    <t>f186ed179743406583486f9665f9b14a</t>
+  </si>
+  <si>
+    <t>e64bd459cfd4440fabc1a78bc921f073</t>
+  </si>
+  <si>
+    <t>85fc17ee78494a77bab34650f7c5566d</t>
+  </si>
+  <si>
+    <t>6e22c064ee534815a0594cb2cdf5e31e</t>
+  </si>
+  <si>
+    <t>a708b49aa0dd41cc98a263d1c95e1403</t>
+  </si>
+  <si>
+    <t>82ae37ec8d4244d48283ea0ba54f07d7</t>
+  </si>
+  <si>
+    <t>1f19f57766fe482499fff95b4b5ee172</t>
+  </si>
+  <si>
+    <t>bbc0fcd2383844fe8ef1bd70502843b5</t>
+  </si>
+  <si>
+    <t>6eac3421b2d448748b5097eb336fda1f</t>
+  </si>
+  <si>
+    <t>a128b8b197314ab3a26fa23f68daa8ee</t>
+  </si>
+  <si>
+    <t>e13ef73f335d49a8a7af3fe561737987</t>
+  </si>
+  <si>
+    <t>b446c2a196c14b55957c421adab5638e</t>
+  </si>
+  <si>
+    <t>c486e638c1de49de9b20bd38e8f81d49</t>
+  </si>
+  <si>
+    <t>afce9b024b3c4172adcb4f6b1757335f</t>
+  </si>
+  <si>
+    <t>42edc42c2e6c415c87b6dec2b2d1c91f</t>
+  </si>
+  <si>
+    <t>39b43a25682f4a69aebe0584ab703040</t>
+  </si>
+  <si>
+    <t>4fde031ee7a14df6a5f90accda243051</t>
+  </si>
+  <si>
+    <t>8e5b81a49145488693e735e32eb48da5</t>
+  </si>
+  <si>
+    <t>3fde31e153584d039958ab3af001f339</t>
+  </si>
+  <si>
+    <t>e4152a44e9774d1e994b822c3aef83df</t>
+  </si>
+  <si>
+    <t>c811897bb46e487da757021bced7119d</t>
+  </si>
+  <si>
+    <t>bd01e5bdb1714f83a8d42d4b135186f9</t>
+  </si>
+  <si>
+    <t>415ebec39c364b5f90299aed9b11bb98</t>
+  </si>
+  <si>
+    <t>1be181ba148f4caab708fab443332493</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>7baeb920f88745eea8fb739bd925b455</t>
+  </si>
+  <si>
+    <t>11ef1dbacfab4ed784a40315315aea76</t>
+  </si>
+  <si>
+    <t>45694a407bed4df1b789e16fc0ea5ec6</t>
+  </si>
+  <si>
+    <t>ef4c027c3a8041f1a6939966b06ca682</t>
+  </si>
+  <si>
+    <t>9f992e72a99044318c76da9c3e88cc1d</t>
+  </si>
+  <si>
+    <t>a990204e0055488383f86b9af9e20150</t>
+  </si>
+  <si>
+    <t>644ff4ec9fd244879fd60f823763bf88</t>
+  </si>
+  <si>
+    <t>af94d71112594cefb93817d8bc844362</t>
+  </si>
+  <si>
+    <t>ffe9c97d57014ec5864fb39153a6fab6</t>
+  </si>
+  <si>
+    <t>2d5a6476e6184d16bbeb5c916d82b3da</t>
+  </si>
+  <si>
+    <t>73edc1dd255c4ad38cecd191878300b3</t>
+  </si>
+  <si>
+    <t>7c7b1963e2314bf0baf144becb5abc9d</t>
+  </si>
+  <si>
+    <t>3895e2c8df2e414095ba527b5d31ef77</t>
+  </si>
+  <si>
+    <t>f9df2d36f7d04843b613f94e8de928f4</t>
+  </si>
+  <si>
+    <t>274a2b2a8f29408e8904cfdffb41980a</t>
+  </si>
+  <si>
+    <t>f779331026664514925cdd5915e9ddcc</t>
+  </si>
+  <si>
+    <t>1930f3f9837b4c40ab088a610f3f81bd</t>
+  </si>
+  <si>
+    <t>9da4a71e3def4f41bc2d94f53689d384</t>
+  </si>
+  <si>
+    <t>939514e86660450ba99ada89f9a1d85f</t>
+  </si>
+  <si>
+    <t>c88f2aa1750c49af9bc3327391d94dee</t>
+  </si>
+  <si>
+    <t>e9336283b37b4486b47ca392e53bbe6e</t>
+  </si>
+  <si>
+    <t>74ed36054c7c41c8a2ef358dfb75ea9a</t>
+  </si>
+  <si>
+    <t>55314a432dc444398c06093eb63c55c5</t>
+  </si>
+  <si>
+    <t>96de873b8681432b900ac2ca5fe17c4d</t>
+  </si>
+  <si>
+    <t>68f04cb4b8c74e89b09fd4d76ec1f589</t>
+  </si>
+  <si>
+    <t>fe0d9816a88e4ee6b7fa362e1a74eed5</t>
+  </si>
+  <si>
+    <t>7c82d73ef986488b927e6c1b186f1761</t>
+  </si>
+  <si>
+    <t>3b7d6afa91d94ac6907693e3a02f1d58</t>
+  </si>
+  <si>
+    <t>0254a74de2614dfda2b6d6594dfd98c6</t>
+  </si>
+  <si>
+    <t>05ab849c028f470ba5e240712b68a116</t>
+  </si>
+  <si>
+    <t>fa33f504903b4253850d1995fd07af2a</t>
+  </si>
+  <si>
+    <t>5f94d7b0879f445593bde225410e865f</t>
+  </si>
+  <si>
+    <t>e7913c15552c491296aa55e04d14b953</t>
+  </si>
+  <si>
+    <t>9a05b77363944304b7e9372e520b4a28</t>
+  </si>
+  <si>
+    <t>28c5aedad9f347528214b9a6cb74dc3c</t>
+  </si>
+  <si>
+    <t>495a5ccccc184034aea09b1866194dc0</t>
+  </si>
+  <si>
+    <t>d4dc0f1a4fc94a49bb55631dc05f205b</t>
+  </si>
+  <si>
+    <t>11535b315b1e49b7a1e97cb49ce87871</t>
+  </si>
+  <si>
+    <t>dddce5647c6a4c84a69ad91cfadfb6f9</t>
+  </si>
+  <si>
+    <t>0b9081e19b964ee69de5d673f318709a</t>
+  </si>
+  <si>
+    <t>d17524f4567a4903aa503b48a4ec1d1e</t>
+  </si>
+  <si>
+    <t>efda927d1da24b49b9f5dd4be6b579f1</t>
+  </si>
+  <si>
+    <t>ccbdb0d979974cebb16597191785a0a4</t>
+  </si>
+  <si>
+    <t>d8691da54de64a01a6058a8d97d2a9ce</t>
+  </si>
+  <si>
+    <t>637b02be69fa4798a393726121614721</t>
+  </si>
+  <si>
+    <t>07487a4aebe8436d85b618c2ac2a9f25</t>
+  </si>
+  <si>
+    <t>9bfd42a80a7f4cb4b61387bc2c7a52bf</t>
+  </si>
+  <si>
+    <t>3beb6668e50a4805988cc64e3576091c</t>
+  </si>
+  <si>
+    <t>The process begins with the Sales Manager at Allganic's initiating the workflow. The first step involves the Sales Manager receiving an order request. Following this, the Sales Manager gathers information from the farm to proceed with the order.
+Next, the Sales Manager checks both the order and the product to ensure everything is in order. After this verification, the Sales Manager also checks the customer's order details. Once these checks are completed, the Sales Manager sends the farm's address to the Transportation team.
+The Transportation team receives the farm's address and arranges a time to collect the product from the farm. They then prepare a vehicle to transport the product from the farm. After the preparations, the Transportation team sends the transportation cost details to the Sales Manager.
+Upon receiving the transportation cost, the Sales Manager calculates the total cost of the order. The Sales Manager then sends the total price to the customer. After communicating the total price, the Sales Manager records the order details.
+The Manager at Allganic's reads the report generated from the recorded order and signs the necessary documents. Meanwhile, the Transportation team proceeds to collect the product from the farm.
+Once the product is collected, the Transportation team delivers it to the customer. After the delivery, the Transportation team sends a record of the sales transaction.
+The Market Research team at Allganic's receives the sales data for recording purposes. They analyze the sales data and write a summary report based on their analysis.
+Finally, the Sales Manager closes the sale, marking the end of the process. The process concludes with the Sales Manager at Allganic's completing the workflow.</t>
+  </si>
+  <si>
+    <t>The process begins with the planting and harvesting team initiating the sequence. They start by harvesting the necessary materials. Once the harvesting is complete, the same team proceeds to sort the harvested materials to ensure quality and consistency.
+Following the sorting, the team moves on to cleaning the materials. This step is crucial to prepare the materials for the next stages of the process. After cleaning, the materials are loaded up for transportation.
+The next phase involves the processing tobacco team. They begin by unloading the materials that have been transported. Once unloaded, the team cures the tobacco, a vital step to enhance its properties for further processing.
+After curing, the team adds the necessary ingredients to the tobacco. This step is essential to achieve the desired flavor and quality. Once the ingredients are added, the tobacco is packaged and sent to the factory for further processing.
+At the factory, the cigarette manufacturing team takes over. They start by unloading the packaged tobacco. The team then proceeds to produce cigarettes from the tobacco. This is followed by a quality control check to ensure that the cigarettes meet the required standards.
+Once the quality is assured, the preparing the final pack team packages the cigarettes. The cigarettes are then wrapped with a protective film to maintain their freshness and quality. Finally, the packs are placed in cartons and stored until they are ready for distribution.
+The process concludes with the final packs being placed in storage, marking the end of the sequence.</t>
+  </si>
+  <si>
+    <t>The process begins when a patient feels unwell and decides to request a doctor's appointment. The patient sends a request to the doctor's office. This request is received by the receptionist, who then processes it.
+The receptionist at the doctor's office receives the doctor's request and proceeds to send an availability request to the doctor. This involves checking if the doctor is available for an appointment. The doctor receives this availability request and responds by sending back their availability status to the receptionist.
+Once the receptionist receives the doctor's availability, they proceed to book the appointment. The receptionist sends a booking confirmation to the doctor, who then acknowledges the booking.
+Simultaneously, the receptionist sends an appointment confirmation to the patient, informing them of the scheduled appointment with the doctor. The patient receives this appointment confirmation and prepares to visit the doctor.
+On the day of the appointment, the patient sends their symptoms to the doctor's office. The doctor receives the symptoms and prepares a prescription based on the patient's condition. The doctor then sends a prescription preparation request to the receptionist.
+The receptionist receives the prescription preparation request and processes it. The doctor then sends a message to the patient, informing them that their prescription is ready for pickup and that they can leave after collecting it.
+The patient receives the prescription pickup message and sends a request to the receptionist for their medicine. The receptionist receives this medicine request and sends the medicine to the patient.
+The patient receives the medicine, marking the end of the process. The process concludes with the patient having received their medicine and the doctor's office having completed the necessary steps to address the patient's medical needs.</t>
+  </si>
+  <si>
+    <t>The process begins with the Purchaser initiating the task. The Purchaser starts by creating a return purchase order. Once the return purchase order is created, the process moves to the Return Management Assistant, who conducts an overview of the returns for supplier returns.
+Following this, the Warehouse Clerk takes over to create an outbound delivery. After the outbound delivery is created, the process returns to the Return Management Assistant for another overview of the returns for supplier returns.
+Next, the Warehouse Clerk is responsible for creating a transfer order. Once the transfer order is created, the Warehouse Clerk proceeds to post the goods issue. After posting the goods issue, the process returns once more to the Return Management Assistant for a further overview of the returns for supplier returns.
+The Return Management Assistant then enters the material inspection. After entering the material inspection, the process returns again to the Return Management Assistant for another overview of the returns for supplier returns.
+Subsequently, the Accounts Payable Accountant performs the task of invoice verification. Once the invoice verification is completed, the process returns to the Return Management Assistant to enter the material inspection once more.
+Finally, the process concludes with the Return Management Assistant marking the end of the process.</t>
+  </si>
+  <si>
+    <t>The process begins with a museum professional initiating the task of identifying the various departments within the museum. Once the departments are identified, the museum professional proceeds to identify key exhibits that are significant to the museum's collection.
+Following this, a serious game developer takes over to research popular game mechanics that could be incorporated into a game. After gathering insights on game mechanics, the developer designs game concepts and creates a prototype of the game.
+The prototype is then validated by the serious game developer, who also involves a potential user to gather feedback. After validation, the developer selects an appropriate game engine and platform to build the game.
+With the engine and platform chosen, the serious game developer develops the game. Once the development is complete, the game undergoes testing to ensure it functions correctly and meets the desired standards.
+After successful testing, the game is deployed by the serious game developer. The museum professional then reviews and accepts the serious game, ensuring it aligns with the museum's objectives.
+Following acceptance, the museum professional promotes the serious game to attract interest and engagement. As a result of the promotion, there is an anticipated increase in visitor numbers, which the museum professional accommodates by making necessary adjustments.
+The process concludes with the museum professional completing the task, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>The process begins with me browsing available flights for my trip to Los Angeles. After reviewing the options, I proceed to choose a flight that suits my schedule and preferences. Once the flight is selected, I book the flight and seats, which results in the generation of a round flight ticket.
+With the flight booked, I then browse hotel offers in the area to find suitable accommodation. After considering the options, I choose a hotel and proceed to reserve a hotel room. This reservation generates a booking confirmation document.
+Next, I browse car renting offers to arrange transportation during my stay. After evaluating the available cars, I choose one and reserve the car rental, which results in a rental confirmation document.
+Both the round flight ticket and the booking confirmation are necessary for the next step, which is going on the trip. The rental confirmation is also associated with this step. Once the trip is completed, I return home, concluding the process.</t>
+  </si>
+  <si>
+    <t>The process begins when a claim is moved, and the Claim Handler Senior at We-Insure initiates the process. The first task involves the Claim Handler Senior making a call to a non-partner workshop. This task is supported by the use of a telephone system.
+Following this, the Claim Handler Senior confirms the validity of the claim. Once the validity is confirmed, the next step is to confirm the amount related to the claim.
+After confirming the amount, the Claim Handler Senior proceeds to call a partner workshop, again utilizing the telephone system for this task.
+The next step involves checking the customer's location. This task is associated with a map, which aids in determining the location.
+Once the location is checked, the Claim Handler Senior collates times for an on-site inspection. After gathering the inspection times, the Claim Handler Senior forwards the inspection dates and an explanation text to the relevant parties. This information is sent via email.
+The process then involves waiting for a reply. If the claimant refuses the inspection, the Claim Handler Senior proceeds to pay the maximum limit allowed for the claim.
+If a reply is received and the claimant agrees to the inspection, the Claim Handler Senior books the inspection. Following the booking, the Claim Handler Senior receives a quote from the partner.
+The next step is to compare two quotations. After comparing the quotations, the Claim Handler Senior applies a business rule to determine the next course of action.
+Once the business rule is applied, the Claim Handler Senior notifies the claimant of the decision. This notification is sent via email, and the email system is used to facilitate this communication.
+After notifying the claimant, the Claim Handler Senior approves the claim. Following approval, the Claim Handler Senior receives an invoice from the non-partner workshop, which is scanned and associated with the task.
+The process concludes with the claim being approved, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>The process begins with the Purchasing Department initiating the procedure. The first step involves the Purchasing Department logging into the system. Once logged in, the legacy Procurement System displays the main menu.
+Next, the Purchasing Department checks the stock. Following this, the legacy Procurement System retrieves the stock details. The Purchasing Department then reads these stock details.
+After reviewing the stock, the Purchasing Department requests a purchase requisition. They proceed by entering the necessary information. The legacy Procurement System then generates a purchase requisition (PR).
+The Purchasing Department places the PR, and the legacy Procurement System saves it. Subsequently, the system displays a list of vendors.
+The Purchasing Department selects a vendor from the list and requests a quotation. The legacy Procurement System sends the request for quotation (RFQ) to the selected vendor.
+Once the vendor responds, the legacy Procurement System receives the quotation. The Purchasing Department compares the received quotations.
+After comparing, the Purchasing Department places a purchase order. The legacy Procurement System sends the purchase order (PO) to the vendor.
+The process continues with the Purchasing Department receiving the goods. They also receive the invoice from the vendor.
+Finally, the Purchasing Department makes the payment, concluding the process.</t>
+  </si>
+  <si>
+    <t>The process begins with the initiation of creating a new customer by Global Elite. This is the starting point where the need for a new customer is identified.
+Next, Global Elite proceeds to create the new customer. This task involves entering the necessary details to establish the customer in the system.
+Following the creation of the customer, Global Elite creates a contact person for the customer. This step ensures that there is a designated individual associated with the customer for communication and transactions.
+After establishing the contact person, Global Elite performs any necessary changes to the customer information. This task allows for updates or corrections to the customer details as needed.
+Once the customer information is finalized, Global Elite creates a customer inquiry. This document serves as a formal request for information or services from the customer.
+Subsequently, Global Elite generates a customer quotation. This document provides the customer with a detailed offer, including pricing and terms, based on the inquiry.
+With the quotation in place, Global Elite creates a sales order that references the quotation. This task involves converting the quotation into a formal order for processing.
+The process then involves checking the stock status, which is carried out by the Plant. This step ensures that the necessary products are available to fulfill the sales order.
+After confirming stock availability, Global Elite displays the sales order. This task involves reviewing the order details to ensure accuracy and completeness.
+The next step is to start the delivery process, which is also handled by Global Elite. This task initiates the logistics required to deliver the products to the customer.
+The Plant then checks the stock status again to confirm the availability of items for delivery. This step is crucial to ensure that the delivery can proceed without issues.
+Global Elite proceeds to pick the materials listed on the delivery note. This task involves gathering the products from inventory in preparation for shipment.
+The Plant then posts the goods issue, which officially records the removal of items from inventory for delivery to the customer.
+Following the goods issue, the Plant checks the stock status once more to update inventory records and ensure accuracy.
+The Financial Department takes over to create an invoice for the customer. This document outlines the charges for the products and services provided.
+After the invoice is created, the Financial Department displays the billing document and customer invoice. This task involves reviewing the financial documents for accuracy.
+The Financial Department then posts the receipt of customer payment. This step records the payment received from the customer against the invoice.
+Finally, Global Elite reviews the document flow. This task involves examining the entire process documentation to ensure everything is in order.
+The process concludes with the display of the document flow by Global Elite, marking the end of the business process.</t>
+  </si>
+  <si>
+    <t>The process begins when a patient experiences an illness. The patient then sends a request to see a doctor. This request is received by the receptionist at the doctor's office. The receptionist sends an availability request to the doctor to check if they are available for an appointment.
+The doctor receives the availability request and responds by sending their availability status back to the receptionist. Upon receiving the doctor's availability, the receptionist proceeds to book an appointment for the patient. The doctor is informed about the booking, and the receptionist sends an appointment confirmation to the patient, instructing them to go see the doctor.
+Once the patient receives the appointment confirmation, they send their symptoms to the doctor. The doctor receives the symptoms and prepares a prescription. The receptionist receives the prescription preparation instructions from the doctor.
+The doctor then sends a message to the patient, informing them that their medicine is ready for pickup and that they can leave. The patient receives this message and sends a request to the receptionist for their medicine. The receptionist receives the medicine request and sends the medicine to the patient.
+The patient receives the medicine, marking the end of their process. Meanwhile, the receptionist's process concludes after sending the medicine to the patient.</t>
+  </si>
+  <si>
+    <t>The process begins when a patient experiences an illness. The patient sends a request to see a doctor. This request is received by the receptionist at the doctor's office. The receptionist then sends a request to the doctor to check their availability. The doctor receives this request and responds with their availability. The receptionist receives the doctor's availability and proceeds to book an appointment for the patient. The doctor receives the booking confirmation.
+The receptionist then sends the appointment details to the patient, instructing them to go see the doctor. The patient receives the appointment information and proceeds to send their symptoms to the doctor. The doctor receives the symptoms and prepares a prescription for the patient. The receptionist receives the prescription preparation instructions from the doctor.
+The doctor sends a message to the patient, informing them that their prescription is ready for pickup. The patient receives this message and sends a request to the receptionist for their medicine. The receptionist receives the medicine request and sends the medicine to the patient. The patient receives the medicine, and the process concludes.</t>
+  </si>
+  <si>
+    <t>The process begins when a customer initiates contact by calling the company. The first step involves the customer service representative making a call to the company. Following this, the representative explains the problem to the relevant department.
+Next, the customer is transferred to the accounting department. If the accounting department cannot solve the problem, they request the customer to call the logistics department.
+The customer then calls the logistics department and explains the problem again. If the logistics department has not yet received the order form from the production department, they attempt to communicate with the production department.
+If the logistics department cannot solve the problem and cannot reach the finishing department, they call the customer back as soon as possible. The logistics department then writes an inquiry and sends it to the finishing department.
+Two days later, the process continues with a follow-up call to the customer. During this call, the reason for the failure is explained to the customer. Finally, the necessary information or resolution is sent to the customer as soon as possible, concluding the process.</t>
+  </si>
+  <si>
+    <t>The process begins when GMA initiates a project. The first task for GMA is to draft a Non-Disclosure Agreement (NDA). Once the NDA is drafted, GMA provides it to the research site for their review. This involves sending the NDA as a message to the research site.
+After the research site reviews the NDA, GMA receives it back from them. The next step for GMA is to send the received NDA to the legal contact for further processing.
+The legal contact then receives the NDA and proceeds to review it. After reviewing, the legal contact sends the NDA back to the research site. This involves sending the NDA as a message to the research site.
+Once the research site has signed the NDA, GMA receives the signed document. GMA then signs the NDA and sends it back to the legal contact.
+Finally, the legal contact receives the signed NDA, marking the completion of the process. Throughout this process, the research site is involved in reviewing and signing the NDA, interacting with both GMA and the legal contact through message exchanges.</t>
+  </si>
+  <si>
+    <t>The process begins with a person visiting the Amazon homepage. Once on the homepage, the individual searches for a book. After finding the desired book, they click on the link for used books, specifically the option that shows "22 used" books available.
+Next, the person selects the second book on the list by clicking "Add to Cart." After adding the book to the cart, they proceed by clicking on the "Proceed to Checkout" button.
+At the checkout stage, the individual enters their email address and selects the option indicating they are a new customer. They then click on "Sign in using our secure server" to continue.
+The next step involves entering customer details, followed by clicking "Create account" to establish a new account. After creating the account, the person enters their shipping details and clicks "Continue" to proceed.
+The individual then selects their preferred shipping options and clicks "Continue" again. Moving forward, they select a payment method and enter their credit card details. After entering the payment information, they click on "Add your card."
+Following this, the person clicks "Continue" to move to the next step, where they choose a billing address. They select "Use this address" to confirm their billing information.
+Finally, the individual completes the process by clicking "Place your order in AUD," which concludes the transaction. The process ends successfully with the order being placed.</t>
+  </si>
+  <si>
+    <t>The process begins when a product is received. The person responsible for this task ensures that the product is physically present and ready for the next steps.
+Next, the product information is entered into the system. This task is handled by a data entry operator who inputs all relevant details about the product into the company's database.
+Once the product information is entered, a sticker is generated. This sticker contains important information such as product identification and tracking details.
+The next step involves placing the sticker on the boxes. An employee carefully affixes the sticker to ensure it is visible and secure.
+Following this, the barcode on the sticker is scanned. This task is performed by a warehouse worker who uses a barcode scanner to register the product in the inventory system.
+After scanning, possible orders are combined. This involves organizing and grouping products based on pending customer orders, which is done by an order manager.
+The products are then put away in the warehouse. A warehouse staff member places the products in their designated storage locations.
+Subsequently, the loading pallet is scanned. This task is carried out by a logistics worker who ensures that the pallet is correctly identified and ready for shipment.
+The next step is to check the orders. An order checker verifies that all products are correctly packed and ready for dispatch according to customer requirements.
+Order picking follows, where a picker selects the products from the storage area based on the orders to be fulfilled.
+The process then involves waiting for a truck. During this time, the logistics team ensures that everything is ready for loading once the truck arrives.
+Once the truck is ready, the loading process begins. A loading crew transfers the products onto the truck, ensuring they are securely placed for transport.
+After loading, the driver receives a declaration. This document contains all necessary information for the transport and delivery of the products.
+The driver then collects the papers required for the journey. These documents include shipping manifests and any other necessary paperwork.
+With the papers in hand, the driver proceeds to the vessel. The driver ensures that the products are delivered to the correct location for further transportation.
+Upon arrival, the vessel receives the order. The vessel's crew takes charge of the products, preparing them for the next leg of their journey.
+A representative then boards the vessel to check the boxes. This person verifies that all products are accounted for and in good condition.
+Finally, payment for the tobacco products is processed. This task is handled by the finance department, ensuring that all financial transactions are completed.
+The process concludes successfully, marking the end of this business operation.</t>
+  </si>
+  <si>
+    <t>The process begins when a user initiates the online registration process. The user starts by accessing the registration system. Once the process is initiated, the online website takes over and begins registering end users. The website opens a window for registration, allowing the user to proceed with providing the necessary registration data.
+After the user submits the required data, the online website receives this information. The website then creates a registration record in its repository to store the user's details securely. Following this, the website proceeds to make an account for the end user, ensuring that the user is now registered within the system.
+Once the account is created, the user is prompted with a welcome message, acknowledging their successful registration. The user is then asked to provide an email address for registration confirmation. This step ensures that the user receives a confirmation email, verifying their registration.
+Finally, the online website completes the registration process, marking the end of the procedure. The process concludes successfully, with the user now having an active account and a confirmation email sent to their provided address.</t>
+  </si>
+  <si>
+    <t>The process begins with planning activities that are scheduled 2-3 years ahead. This initial step is managed by OASIS at De La Salle University. 
+The first task involves coordinating a meeting with the graduation workforce, which is also handled by OASIS. Following this, OASIS contacts suppliers to ensure all necessary materials and services are arranged for the graduation event.
+Next, OASIS confirms the list of graduates, ensuring that all eligible students are accounted for. After confirming the graduates, OASIS verifies the completeness of awards and diplomas that will be distributed during the ceremony.
+Once the awards and diplomas are verified, OASIS prepares the program invitation, which is an essential document for inviting guests to the graduation ceremony. Following the invitation preparation, OASIS creates the graduation script, detailing the sequence of events and speeches for the ceremony.
+Subsequently, OASIS prepares a rehearsal kit, which includes all necessary materials and instructions for the graduation rehearsal. The rehearsal is then conducted to ensure that all participants are familiar with the proceedings.
+After the rehearsal, a graduation dry run is performed by OASIS to finalize the event's logistics and timing. This ensures that the actual ceremony will proceed smoothly.
+In parallel, OASIS prepares the souvenir program, which serves as a memento for attendees and includes details about the ceremony and graduates. 
+Finally, OASIS facilitates the returning of togas after the ceremony, ensuring that all rented garments are collected and accounted for. The process concludes with this final task, marking the end of the graduation preparation activities.</t>
+  </si>
+  <si>
+    <t>The process begins with a customer looking for the CKH website. Once the customer finds the website, they proceed to create a Request for Quotation (RFQ) on the CKH website. After creating the RFQ, the customer completes and submits it. During this step, RFQ information data is generated.
+Next, the process moves to the CHK Company, where a sales assistant finalizes the RFQ. After finalizing, the sales assistant prints the RFQ. Following the printing, the sales assistant sends the RFQ to the estimator.
+The estimator at CHK Company receives the RFQ and then draws and adjusts the draw plan. Once the draw plan is adjusted, the estimator completes the draw plan and prepares a quote. After completing these tasks, the sales assistant mails all the documents, including the draw plan and quote, to the customer.
+The customer receives all the documents sent by the sales assistant. Finally, the process concludes with the customer responding to CHK Company.</t>
+  </si>
+  <si>
+    <t>The process begins when the assessment team initiates the Digital Transformation Maturity Improvement Project. The first task for the assessment team is to document the assessment plan. Once the plan is documented, it is sent to the company for approval. The company then reviews and approves the assessment plan.
+After the plan is approved, the company conducts interviews to gather necessary information. The results of these interviews are sent back to the assessment team. With the gathered information, the assessment team proceeds to analyze the documents.
+Following the document analysis, the assessment team rates the process attributes. Based on these ratings, they determine the capability levels of the processes. The next step involves determining the overall Digital Transformation (DX) maturity level.
+Once the DX maturity level is established, the assessment team conducts a gap analysis to identify areas for improvement. They then prioritize the improvement opportunities based on the gap analysis findings.
+The assessment team compiles their findings and priorities into an assessment report. This report is shared with the company, and it includes a roadmap for improving the current DX maturity level.
+The company then derives an action plan based on the assessment report. With the action plan in place, the company implements the necessary improvements to enhance their digital transformation maturity level.
+The process concludes when the company's digital transformation maturity level is improved, marking the successful completion of the project.</t>
+  </si>
+  <si>
+    <t>The process begins when the supplier ships products to SysInteg. Once the products arrive, the first task is to receive, open, and sort them. This task is handled by the receiving team.
+After sorting, the next step is to schedule and pick the products for inspection. This task is managed by the scheduling team, ensuring that the products are ready for the inspection process.
+Following the scheduling, the first article inspection reporting is conducted. This task involves documenting the initial inspection results and is carried out by the inspection team.
+Next, a dimensional inspection is performed. This task involves measuring the products to ensure they meet the required specifications and is also handled by the inspection team.
+Subsequently, the team travels to the supplier's location to conduct an on-site inspection. This task ensures that the supplier's processes and products meet the necessary standards.
+After the on-site inspection, the process certification is reviewed. This task involves verifying that all processes comply with the required certifications and is conducted by the quality assurance team.
+Once the certification is reviewed, the products are accepted by the quality team. This task confirms that the products meet all quality standards.
+Following acceptance, the products are picked for further processing. This task is managed by the logistics team.
+The next step is a source inspection, where the products are inspected at their origin. This task ensures that the products are in good condition before moving forward.
+After the source inspection, the XSQS task is performed. This task involves a specific quality check to ensure product standards are maintained.
+If any issues are found, the vendor is contacted for correction. This task involves communicating with the vendor to address any discrepancies.
+The vendor then responds with a correction plan. This task involves reviewing the vendor's response to ensure the issues are resolved.
+If further assistance is needed, tech help is provided online. This task involves offering technical support to address any remaining issues.
+The supplier is then involved in the process to ensure all corrections are made. This task involves collaboration with the supplier to finalize the corrections.
+The ERP system is updated with the latest information. This task involves entering all relevant data into the enterprise resource planning system.
+The XS task is then performed, which involves another specific quality check to ensure all standards are met.
+Finally, the products are packed and shipped. This task involves preparing the products for delivery and is managed by the shipping team.
+The process concludes with the successful shipment of the products, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>The process begins with the Master initiating the workflow. The first task for the Master is to read the initial database, referred to as D. Once the database is read, the Master proceeds to divide D into a specified number of grids, denoted as p. Following this, the Master assigns each data point from the database to one of these grids.
+Next, the Master identifies which grids are dense and which are not. After identifying the grid densities, the Master marks the non-dense grids as complex. Additionally, any dense grids that are adjacent to each other are also marked as complex.
+The Master then creates a task pool, which is subsequently populated with the complex grids. Following this, the Master creates worker threads to handle the tasks. The Master assigns these tasks to the workers, sending a message to each worker with their respective tasks.
+Once the tasks are assigned, the Master destroys the task pool. The Master then sends an end notification to the workers, indicating the completion of task assignments.
+Meanwhile, the workers apply the DBSCAN algorithm on their assigned tasks, which are the grids. After processing, the workers populate a result pool with their findings and send a message back to the Master.
+The Master then merges the clusters obtained from the workers' results. Finally, the Master returns the final spatial clusters, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>The process begins when a technician at the pharmacy receives a prescription. The technician then enters the prescription details into the system. Following this, a pharmacist conducts an interview with the patient to gather necessary information and ensure the prescription is appropriate.
+After the interview, the technician refills the prescription as required. Once the prescription is refilled, the pharmacy management system transmits a claim to the relevant parties. The pharmacist then handles the adjudication of the claim, ensuring that it is processed correctly.
+Next, the pharmacy management system manages the point of sale, where the patient makes any necessary payments. Following the payment, the system calculates the balance of the claim that needs to be covered by the payer.
+The pharmacy management system then follows up on accounts receivable to ensure that all payments are collected. After this, the system processes any outstanding payments.
+If any issues arise during the payment processing, a pharmacist steps in to resolve these problems. Finally, the process concludes with the collection of all payments, marking the end of the transaction.</t>
+  </si>
+  <si>
+    <t>The business process begins with the task of supplying raw materials. Once the raw materials are supplied, they are stored. After storage, there are two possible paths: the raw materials can either undergo quality control or be set up for production.
+If the raw materials go through quality control, they are then prepared for the product mixing stage. If they are set up for production directly, they also proceed to product mixing. After mixing, the materials are melted. Following the melting process, the materials are sent to a reactor.
+Once the reactor process is complete, the materials are separated into different products. From the separation stage, there are several possible outcomes. One outcome is that the materials are identified as wide spec material, which concludes the production process. Another outcome is that the materials undergo quality control output. If the products are deemed unusable during quality control, the production process ends.
+If the products pass quality control, they can either be purified or stored as finished products. If purified, they continue to the finished product storage. Finally, the finished products are moved to sales, completing the process.</t>
+  </si>
+  <si>
+    <t>The process begins when the Retail Supply Chain Manager (RSCM) identifies that training is needed. The RSCM then fills in the training details, ensuring all necessary information is documented. Following this, the RSCM selects a suitable schedule for the training sessions. Once the schedule is set, the RSCM chooses the participants who will attend the training.
+After selecting the participants, the responsibility shifts to the Admin HQ Retail Support &amp; Retail team. They upload the necessary training materials to prepare for the sessions. Subsequently, the Admin HQ team submits a test for assessment purposes, ensuring that the training content is ready for evaluation.
+Next, the Admin HQ team selects the participants who will receive an invitation notification email. This email is sent to the frontliners, who are the participants of the training. Upon receiving the invitation, the frontliners are informed about the start of the training.
+When the training begins, the frontliners actively participate in the training sessions. After completing the training, they proceed to do an assessment to evaluate their understanding and retention of the training material.
+Once the training has ended, the Admin HQ Retail Support &amp; Retail team collects the results of the training assessment. This marks the completion of the training process, ensuring that all participants have been evaluated and the training objectives have been met. The process concludes with the training being officially completed.</t>
+  </si>
+  <si>
+    <t>The process begins with a pharmacist initiating the procedure. The first step involves the dispensing software creating a claim and filling in all necessary fields. Once the claim is prepared, the pharmacist submits the claim and sends the prescriptions.
+Next, the Department of Human Services checks the validity of the prescription. If the prescription is valid, they proceed to give advice regarding the claim. Following this, the pharmacist attempts to correct any issues with the claim based on the advice received.
+After attempting corrections, the dispensing software removes any faulty prescriptions from the claim closure. The Department of Human Services then confirms the corrections made by the pharmacist.
+Once the corrections are confirmed, the Department of Human Services processes the payment. The pharmacist then receives the payment. Finally, the pharmacist stores the prescriptions, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>The process begins when you feel hungry at home. The first step is to decide where you want to order your pizza from. Once you have chosen a place, the next step is to search online for the phone number of the pizza place.
+After finding the phone number, you call the pizza place from home to place your order. Once the order is made, you need to get your keys and wallet and leave your home.
+You then walk to the pizza place. Upon arrival, you enter the pizza place and inform the manager that you are there and ready to pick up your pizza. You wait at the store until your pizza is ready.
+Once you have your pizza, you walk back home. When you arrive home, you place the pizza on a table. Finally, you can eat and enjoy your pizza.</t>
+  </si>
+  <si>
+    <t>The process begins when an engineer at RUAG approves an Engineering Change Request (ECR). Once the ECR is approved, the engineer proceeds to use the Engineering Change Management (ECM) system. Following this, the engineer selects the appropriate material master record. After selecting the material master record, the engineer chooses the necessary document templates.
+Next, the engineer selects the Engineering Bill of Materials (EBOM). Once the EBOM is selected, the task of changing the EBOM is carried out by SAP/ProNovia. After the EBOM is changed, a new Engineering Change Notice (ECN) is created by the workflow system.
+The engineer then releases the change of the EBOM. Following this, the workflow system sends the ECN. The process continues with the production planning team making changes to the Manufacturing Bill of Materials (MBOM). After the MBOM is changed, the production planning team releases the change of the MBOM.
+Finally, the workflow system closes the ECM, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>The process begins with the initiation of the task to turn on the document overview. Once this is completed, the next step involves clicking on the selection variation. Following this, the task requires clicking on "my purchase requisitions."
+After accessing the purchase requisitions, the next step is to select the correct purchase requisition in the "Create PO" screen. Once the correct requisition is selected, the task is to click "Adopt."
+The process then moves to reviewing the requisition information. After the review, the next task is to enter the vendor and purchasing organization details. Once these details are entered, the task is to save the information.
+Following the save action, the process involves validating the purchase order (PO) with tolerance limits. After validation, the task is to generate the PO. Once the PO is generated, it needs to be verified against the tolerance limits.
+The next step is to update the purchase requisition. After updating the requisition, the task is to update the material inventory. Once the inventory is updated, the final task is to send the PO to the vendor.
+The process concludes with the completion of sending the PO to the vendor, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>The process begins with the contractor, specifically a second-sourced contractor, identifying and flagging a defect. Once the defect is flagged, the contractor creates a work order for a general body repair person. This work order is then communicated to the TTC foreperson, who contacts the general body repair person to release the work order.
+The general body repair person, who is also part of the second-sourced contractor team, reviews the flagged work order. At this point, there are two possible actions. The repair person can either schedule the repair work or check the parts and materials required for the repair.
+If the repair work is scheduled, the contractor proceeds to complete the repair work. After the repair work is completed, a message is sent to the TTC foreperson for review. The TTC foreperson then reviews the quality of the repair work and signs off on the work completion. Once the work is approved, the bus is released back into service.
+Alternatively, if the general body repair person decides to check the parts and materials required, this task is carried out by the contractor.
+In a separate but related process, the TTC itself can also flag a defect. When this occurs, the TTC foreperson creates a work order. This work order is then sent to the general body repair person, following the same communication process as before, where the TTC foreperson contacts the repair person to release the work order. The process then continues as previously described, with the repair person reviewing the work order and deciding on the next steps.</t>
+  </si>
+  <si>
+    <t>The process begins when a report is made. This report is then received by the designated recipient. Once the report is received, it is recorded in the current system to ensure proper documentation and tracking.
+Following the recording, a maintenance request is sent to the Fleet Maintenance team. The Fleet Maintenance team receives this request and must determine whether it is a general maintenance request. If it is a general maintenance request, the team proceeds to perform general maintenance, concluding this branch of the process.
+If the request is not for general maintenance, the urgency of the repair is assessed by the Maintenance Supervisor. If the repair is deemed urgent, it is scheduled in the current system's urgent workflow. The Maintenance Crew then receives the urgent request.
+At this point, the process splits into two parallel tasks. The Maintenance Crew performs the necessary work, and simultaneously, a report summary and status are updated in the current system. Once both tasks are completed, the requests are closed, marking the end of this branch of the process.
+If the repair is not urgent, it is scheduled in the current system's non-urgent workflow. The Maintenance Crew receives the non-urgent request, and the process continues with the same parallel tasks as the urgent workflow: performing the work and updating the report summary and status. After these tasks are completed, the requests are closed, concluding the process.</t>
+  </si>
+  <si>
+    <t>The process begins when an online application is received by the university's information system. The system records the application and then creates a PDF document of it. After creating the document, the system notifies a junior officer about the new application.
+The junior officer then checks the completeness of the application. At this point, there are two possible outcomes:
+1. If any document is missing, the junior officer notifies the student about the missing documents. Once the student provides the missing documents, the junior officer receives them and rechecks the completeness of the application.
+2. If the application is complete, the junior officer sends the document to a senior officer for further review.
+Once the senior officer receives the document, they check the validity and equivalence of the degree. This leads to another decision point with two possible outcomes:
+1. If the degree is found to be invalid or not equivalent, the senior officer rejects the application. The information system then notifies the student about the rejection, and the process ends with the application being rejected.
+2. If the degree is valid, the senior officer approves the application. The junior officer then prepares a welcoming package for the student. After the package is prepared, the information system informs the student about the approval, and the process concludes with the application being approved.</t>
+  </si>
+  <si>
+    <t>The process begins with taking the lesson. After this, there is a decision point where two paths can be taken. 
+The first path involves being assigned to a project. Once assigned, you must inform your instructor about your project. Following this, you need to determine the business canvas model for your project. After determining the model, you prepare your first presentation. Once the presentation is ready, you present it. After presenting, you take feedback from your instructor and friends. Using this feedback, you try to improve your project. Next, you determine all costs associated with your project. After costs are determined, you identify all potential revenues. With this information, you write your report. Following the report, you prepare your final presentation. Once the final presentation is ready, you present it. The process concludes with taking a grade.
+The second path involves selecting a project. After selecting a project, you follow the same steps as the first path, starting with informing your instructor about your project and continuing through to taking a grade.</t>
+  </si>
+  <si>
+    <t>The process begins with the Administration &amp; Customer Service team initiating the procedure. The first task is performed by the Risk Management &amp; Finance team, who conduct a credit check. Once the credit check is completed, the same team confirms the results of the credibility check.
+Following this, there is a decision point managed by the Administration &amp; Customer Service team. If the credibility assessment is accepted, the process continues with a call to the client to gather additional information. If the assessment is rejected, a rejection letter is sent to the client, concluding this path of the process.
+If the credibility assessment is accepted, after calling the client, the Administration &amp; Customer Service team creates a loan offer. This offer is then checked by the same team before being sent to the client.
+After sending the loan offer, there is another decision point. If the client accepts the offer, the process moves forward with the Administration &amp; Customer Service team receiving the accepted offer. If there is no immediate response, a timer is set for one hour, after which the client is reminded.
+Upon receiving the accepted offer, the Administration &amp; Customer Service team sends a welcome letter to the client. The process then transitions to the Risk Management &amp; Finance team, who activate the loan application. They also validate the loan activation and execute the initial payment.
+Finally, the Administration &amp; Customer Service team returns the necessary documents to the client, marking the end of the process.</t>
+  </si>
+  <si>
+    <t>The process begins when a customer arrives at the restaurant. The waiter greets the customer warmly. After welcoming the customer, the waiter checks if the customer has a reservation. 
+At this point, there is a decision to be made. If the customer does not have a reservation, which happens 1% of the time, the waiter will proceed to reject the customer, leading to the customer leaving the restaurant. If the customer has a reservation, which occurs 99% of the time, the waiter shows the customer to their table.
+Once seated, the waiter explains the dining rules to the customer. After explaining the rules, the waiter confirms the customer's orders. 
+Following the order confirmation, two activities occur simultaneously. The chef's assistant begins preparing the ingredients, while the sommelier introduces themselves to the customer. The sommelier then serves wine to the customer. 
+Meanwhile, the chef's assistant completes the preparation of ingredients, and the head chef composes and finalizes the dish. The waiter then serves the food to the customer.
+After serving the food, the waiter waits for the customer to call for the bill. Once called, the waiter brings the bill to the customer and collects the payment. The process concludes with the customer being served successfully.</t>
+  </si>
+  <si>
+    <t>The process of buying a flat begins with the buyer initiating the journey. The first step involves the buyer conducting research on the buying processes. Following this, the buyer determines a list of criteria that are important for selecting a flat. This results in the creation of a document called the "List of Criteria."
+Next, the buyer calculates the maximum price they are willing to pay for the flat. With this information, the buyer contacts the bank to get pre-qualified and pre-approved for a home loan. This step produces a "Loan Contract" document.
+The process then reaches a decision point where the buyer checks if they have been approved for the loan. If approved, the buyer proceeds to search for a real estate agent. If not approved, the buyer must fulfill any missing requirements and then contact the bank again.
+Once the buyer finds a real estate agent, they contact the selected agent. The agent then decides whether to accept the buyer's request. If accepted, the agent consults with the buyer and prepares a list of flats that meet the buyer's criteria, resulting in a "List of Flats" document. If not accepted, the buyer searches for another real estate agent.
+The buyer reviews the list of flats and selects potential options. The agent then contacts the seller of these flats and makes appointments for the buyer to visit them. After visiting the flats, the buyer decides if they have found the perfect flat. If not, the buyer reviews the list of flats again.
+If the buyer finds the perfect flat, they decide to buy it and the agent negotiates with the seller. The buyer then makes an offer. At this point, the buyer checks if there are any other offers. If there are other offers, the buyer negotiates a counteroffer. If there are no other offers, the buyer seeks final approval.
+Once final approval is obtained, the agent walks the buyer through the necessary paperwork. The buyer then finalizes the financing and signs the documents, completing the process. The journey ends with the buyer successfully purchasing the flat.</t>
+  </si>
+  <si>
+    <t>The process begins with the Change Manager initiating a new change. The Change Manager then assesses the change to understand its implications and requirements. Following this, the Change Manager filters the changes to categorize them appropriately.
+At this point, the Change Manager determines the type of change. There are four possible categories: Standard, Minor, Significant, and Emergency.
+1. **Standard Change**: 
+   - The Change Manager handles standard changes by identifying preapproved changes. 
+   - These changes are then implemented by the Implementers.
+   - After implementation, the Implementers conduct a post-implementation review to ensure everything is functioning as expected.
+   - The process concludes here for standard changes.
+2. **Minor Change**:
+   - The Change Manager approves and schedules minor changes.
+   - The Change Board reviews the risks and recommendations associated with these changes.
+   - The Change Board then decides whether to approve the changes. If approved, the Change Manager forwards the schedule of change to the Implementers for implementation.
+   - If not approved, the process returns to the assessment stage for further review.
+3. **Significant Change**:
+   - Significant changes follow the same path as minor changes, starting with approval and scheduling by the Change Manager.
+   - The Change Board reviews the risks and recommendations.
+   - Approval by the Change Board leads to forwarding the schedule of change for implementation. If not approved, the process loops back to reassessment.
+4. **Emergency Change**:
+   - For emergency changes, the Change Manager requests recommendations from the board.
+   - The Change Board reviews the risks and recommendations.
+   - The approval process is similar to minor and significant changes, where the Change Board decides on the approval. If approved, the schedule is forwarded for implementation. If not, it returns to the assessment phase.
+The process ensures that all changes are carefully assessed, categorized, and implemented with appropriate oversight and review to maintain system integrity and efficiency.</t>
+  </si>
+  <si>
+    <t>The process begins when a truck arrives with chickens, managed by internal operations. The first task is to attach the chickens to a conveyor belt. Once attached, the chickens are drugged to prepare them for the next step. Following this, the chickens are slaughtered.
+After slaughtering, the chickens undergo heating and washing. The next step involves plucking the chickens. Once plucked, the process continues with the removal of the guts, which is handled as a separate subprocess.
+The chickens are then cooled down. After cooling, they are sorted, and a photograph is taken for documentation. At this point, a decision is made based on the quality of the chickens. If the chickens are graded as "A grade," they are weighed and sorted according to their weight. If they are graded as "B grade," they are cut up.
+For the "B grade" chickens, the process splits into two simultaneous tasks. One task involves sorting chicken wings, legs, and drumsticks, while the other task involves filleting the chicken breast. Both tasks lead to packaging.
+Once packaged, the chickens are transported to a cooling cell. After reaching the cooling cell, orders are prepared for transportation. The process concludes with the transportation of orders to the customer.
+Throughout the process, internal operations manage each task, ensuring the chickens are processed efficiently and according to their grade. The final step involves delivering the prepared orders to the customer, completing the business process.</t>
+  </si>
+  <si>
+    <t>The process begins with starting the machine. Once the machine is started, information is collected from it. After collecting the information, the next step is to calculate the Overall Equipment Effectiveness (OEE). Following the calculation, the machine's status is checked.
+At this point, a decision is made based on the machine's connection status. If the machine is connected, another decision is made regarding the OEE value. If the OEE is below a certain percentage, an email is sent to an engineer. If the OEE is greater than or equal to the required percentage, the process loops back to collecting information from the machine.
+If the machine is disconnected, the machine is stopped, and the process ends.
+When the engineer receives the email, two tasks are carried out simultaneously. The engineer searches for irregularities and checks the OEE percentage. After searching for irregularities, the engineer updates the settings and restarts the machine, which leads back to collecting information from the machine. Meanwhile, after checking the OEE percentage, the engineer looks into the machine information, which also leads to updating the settings.</t>
+  </si>
+  <si>
+    <t>The process begins when a client needs a loan. The client starts by submitting a loan application. After submitting the application, the client must decide whether to proceed with an online application. If the client chooses to apply online, they submit the online application, which is then captured by a loan officer at ACME Bank. The loan officer sends a receipt back to the client, confirming the application has been received.
+If the client decides not to apply online, they must talk with a loan officer directly. The loan officer then receives the loan application receipt and creates a customer record in the CRM system. Following this, the lending operations team at ACME Bank performs a background check on the client.
+Once the background check is completed, a decision is made on whether the background check is accepted. If the background check is not accepted, the lending operations team denies the loan application, and the client receives a letter informing them that their application was rejected, ending the process with no loan received.
+If the background check is accepted, the loan officer collects information on the property the client is interested in. The loan officer then assesses the credit risk of the applicant and reviews all inputs. Based on this review, the loan officer makes a decision on the application.
+If the application is denied, the loan officer informs the client by sending a letter stating that their application was rejected, and the process ends with no loan received. If the application is accepted, the loan officer notifies the client with a letter confirming the acceptance of their application. The application is then moved to underwriting for further processing, and the process ends with the application accepted.</t>
+  </si>
+  <si>
+    <t>The process begins when an After-Sales Service Clerk receives a new disturbance report. The clerk is responsible for accepting the disturbance report and then transmitting the relevant data to a form.
+Next, the Service Manager decides on the next steps. At this point, a decision is made on whether the problem is well-known. If the problem is well-known, the Service Manager attempts to solve the problem via telephone. After this attempt, another decision is made to determine if the problem was successfully solved. If it was successful, the Service Manager creates a matching note on the disturbance report form and places this note in the matching customer briefcase.
+If the problem is not well-known, the Service Manager informs the Service Clerk, who then proceeds to solve the problem onsite. The Service Clerk enquires about any missing information and makes an appointment with the customer. The Service Clerk then meets the customer to solve the problem and returns to the factory to file a report.
+Once the report is filed, two tasks occur simultaneously. The Service Clerk finishes the report, and the Finance department creates an invoice. The invoice is then sent to the customer.
+Finally, the process concludes with the disturbance being resolved, overseen by the Service Manager.</t>
+  </si>
+  <si>
+    <t>The process begins with a user starting the task of selecting a bank. The user can choose a bank using a specific method, which is noted as "Selection via BLZ."
+Once the bank is selected, the user encounters a decision point to determine if the bank was found. If the bank is found, the user proceeds to enter bank credentials. If the bank is not found, an error message is displayed to the user. After displaying the error message, the user decides whether to contact support. If the user chooses not to contact support, the process ends. If the user decides to contact support, they can either fill out a form or call the service, after which the process ends.
+If the bank is found and the user enters the bank credentials, the next step is to connect with the bank. After attempting to connect, there is another decision point to check if the connection was successful. If the connection fails, an error message is shown, and the user is directed back to the step of entering bank credentials. The error messages that might be shown include "Bank connection not found," "An unexpected error occurred," and "Incorrect authorization."
+If the connection is successful, the user retrieves all transactions. The user has the option to categorize transactions themselves or allow the system to categorize them. After retrieving transactions, the user searches for a possible renter. If a renter is found, the user selects the renter and transaction, then views a payment overview, and the process ends. If no renter is found, a message is shown, and the user manually selects transactions, views the payment overview, and the process ends. 
+Throughout the process, the "App System" is associated with various tasks, including showing error messages, connecting with the bank, retrieving transactions, finding possible renters, and showing messages.</t>
+  </si>
+  <si>
+    <t>The process begins when a Level 1 Employee at the IT Helpdesk receives a request. The first task for the Level 1 Employee is to determine if the solution to the problem is already known. 
+If the solution is known, the Level 1 Employee proceeds to solve the problem and then informs the customer that the problem has been solved, concluding the process.
+If the solution is unknown, the Level 1 Employee forwards the request to a Level 2 Employee. The Level 2 Employee receives the request and evaluates it. After evaluating the request, the Level 2 Employee assigns a priority level to it. This priority level is then entered into the Job Tracking System.
+The Job Tracking System assigns the request to a Level 2 Employee, who receives it and begins researching and developing a solution. Once a solution is developed, the Level 2 Employee sends it back to the Level 1 Employee.
+The Level 1 Employee receives the solution and tests it. If the test is successful, the Level 1 Employee informs the customer that the problem has been solved, and the process ends.
+If the test is unsuccessful, the Level 1 Employee sends the request back to the Level 2 Employee for further research and development. This cycle continues until a successful solution is found and the customer is informed.</t>
+  </si>
+  <si>
+    <t>The business process begins when the Sales department receives a purchase order from a customer. The Sales team then enters the order data into the system. Following this, the Accounting/Finance department performs a credit check on the customer.
+At this point, there is a decision to be made based on the credit check results. If the credit check fails, the process moves to setting the order status to blocked. The Accounting/Finance team then refers the case to a specialist for further evaluation. The specialist evaluates the case and makes another decision. If the case remains blocked, the Accounting/Finance department informs the customer why the sales order is blocked.
+If the credit check passes, the order is approved, and the Accounting/Finance team checks the availability of the items. If the items are available, the process continues with the Shipping/Receiving department releasing the sales order. If the items are not available, a purchase requisition is created and referred to the Procurement department.
+The Procurement department reviews the purchase requisition and decides whether to approve it. If not approved, the Procurement team informs the Sales department, which then informs the customer about the blocked order. If approved, the Procurement team chooses a vendor and converts the purchase requisition into a purchase order, which is then transmitted to the vendor.
+Once the vendor sends the materials, the Shipping/Receiving department receives them and proceeds to pick the materials, arrange transportation, and ship them to the customer. Meanwhile, the Accounting/Finance department sends an invoice to the customer.
+After the customer receives the invoice, they make a payment, which the Accounting/Finance department receives and processes. Finally, the receivable is cleared, and the sales order is marked as completed, concluding the process.</t>
+  </si>
+  <si>
     <t>The process begins with the domain registration team at ACME Inc. initiating the project. They start by specifying and discussing the details of the website. Once the discussion is complete, they document the blueprints and prepare a proposal. After finalizing the proposal, they conclude the meeting about the specifications.
 Next, the team proceeds to create a prototype of the website. Following this, the process splits into two parallel activities. The first activity involves the team designing the website wireframe, while the second activity focuses on structuring the information architecture. Both activities are carried out simultaneously.
 Once the wireframe is ready, the team gathers the necessary content. At the same time, they also work on designing the website graphics. After these tasks, the team seeks client approval for the website.
@@ -142,16 +1167,10 @@
 Finally, the site launch team launches the website, marking the end of the process.</t>
   </si>
   <si>
-    <t>f1571a41756f429485487f475cb2865d</t>
-  </si>
-  <si>
     <t>The process begins when an employee submits an expense form. This form is then received by a finance officer, who is responsible for handling the report. Once the report is received, the finance officer simultaneously performs two tasks: they notify the employee that the report has been received and review the expense report.
 After reviewing the expense report, the finance officer encounters a decision point. If there is no previous file associated with the report, the finance officer creates an account. If there is a previous file, they use that file. Regardless of the path taken, the next step is for the finance officer to verify the report.
 Following the verification, the finance officer reviews the amount requested. At this point, another decision is made based on the amount. If the amount is less than 2000, the process concludes with the employee receiving the reimbursement. If the amount is above 2000, the report is forwarded to the finance manager for approval.
 The finance manager reviews the request and makes a decision. If the request is rejected, the finance manager sends a rejection notice, ending the process with the reimbursement being rejected. If the request is approved, the finance officer records the details of the reimbursement. Subsequently, the employee transfers the requested amount, and the process concludes with the employee receiving the reimbursement.</t>
-  </si>
-  <si>
-    <t>959768fda5984592ae8e7bcf771bf9e2</t>
   </si>
   <si>
     <t>The process begins when the supplier receives an invoice. The supplier then sends this invoice to the accounting department. The accounting department forwards the invoice to the business unit, which receives it and proceeds to order the necessary goods or services.
@@ -159,9 +1178,6 @@
 At this point, the process splits into three simultaneous tasks handled by the accounting department: assigning a project number, determining tax codes, and identifying the cost code. All three tasks must be completed before proceeding to the next step.
 After these tasks are completed, the accounting department proceeds to inform the supplier and updates the accounts payable. This marks the end of the process for the accounting department.
 If the invoice is not approved, the business unit informs the accounting department, which then sends a notification to the supplier. The supplier is informed, and this marks the end of the process for the supplier.</t>
-  </si>
-  <si>
-    <t>0dd8931c54064aa0812834e68a614c86</t>
   </si>
   <si>
     <t>The process begins with the restaurant manager initiating the receiving process. The first task for the restaurant manager is to check if the items received are complete and undamaged. 
@@ -172,16 +1188,10 @@
 If the items are still incomplete or damaged, the process would start again from the point of rechecking the items upon arrival.</t>
   </si>
   <si>
-    <t>8022ba7914cf4693925c6674490ee56c</t>
-  </si>
-  <si>
     <t>The process begins when a customer's purchase order is received. The first task is to check if the product is available. If the product is available, the inventory is updated, and a payment request is sent to the customer. Once the payment is requested, the product is delivered, and the process ends.
 If the product is not available, the customer is asked if they want to place an order. If the customer decides to place an order, a quote is made and sent to the customer. The customer's response is then checked. If the customer agrees to the quote, the materials are checked to ensure there is enough stock. If there is enough stock, the units are produced, and a notification is sent that the units are ready. The process then continues with updating the inventory, requesting payment, and delivering the product.
 If there is not enough stock, a purchase order is sent, and the needed materials are bought. After acquiring the materials, the units are produced, and a notification is sent that the units are ready. The process then continues with updating the inventory, requesting payment, and delivering the product.
 If the customer does not want to place an order or does not agree to the quote, the process ends without further action.</t>
-  </si>
-  <si>
-    <t>c5cd15f5fd3f443eaff73696b9ecd6cc</t>
   </si>
   <si>
     <t>The process begins with the Risk Management team initiating the procedure. They start by performing a credit check. Once the credit check is completed, the Risk Management team confirms the credibility check.
@@ -192,16 +1202,10 @@
 The process ends with the Administration team sending a welcome letter and returning documents to the client, marking the completion of the entire procedure.</t>
   </si>
   <si>
-    <t>d6b33aca297248d1aeee6bb064181975</t>
-  </si>
-  <si>
     <t>The process begins with the warehouse initiating the task of checking the quantity of stock using an automated system. This task is performed by the warehouse staff with the help of robotic process automation (RPA). Once the stock levels are checked, the process moves to a decision point where it is determined if there is enough stock available.
 If there is enough stock, the process concludes successfully. However, if there is not enough stock, the warehouse proceeds to check if a requested order has already been placed with the supplier. This leads to another decision point: if the products have been ordered, the process ends. If not, the warehouse sends a request to the supplier to order the necessary products.
 Upon receiving the order request, the supplier processes the order and sends the products to the warehouse. Once the products arrive at the warehouse, they are received and then checked for quality by the quality control department. At this stage, another decision is made to determine if there are any defective garments.
 If a defective garment is found, the product is sent back to the supplier, who then replaces the product and sends it back to the warehouse. If no defects are found, the warehouse scans the RFID tags of the products and updates the stock levels using RPA. Finally, the products are stocked in, completing the cycle and returning to the initial task of checking stock quantity.</t>
-  </si>
-  <si>
-    <t>d98f4d3b681c431eada23a0a5f99664f</t>
   </si>
   <si>
     <t>The process begins when a request is received by the Project Manager. The Manager of Learning Spaces then reviews the job for allocation. After the review, the process splits into two parallel tasks. The first task involves the Project Manager liaising with the client to facilitate a walkthrough. Simultaneously, the Executive allocates a vendor.
@@ -212,17 +1216,11 @@
 If the client gives the go-ahead for installation, the Project Manager schedules the installation and commissions it as per the user brief. This leads to the vendor sending an invoice, and the process continues with the submission of the invoice for payment.</t>
   </si>
   <si>
-    <t>b6a319ff222e460db7e2f7c32a8de60e</t>
-  </si>
-  <si>
     <t>The process begins when a clerk receives an order. The clerk's first task is to check the parts inventory. After checking the inventory, the process reaches a decision point. Here, the clerk determines whether the necessary parts are available.
 If the parts are unavailable, which happens 4% of the time, the clerk checks if the relevant parts are in order and reschedules the assembly order for the next day, or cancels the assembly. This leads directly to logging the order and notifying the client and shipper.
 If the parts are available, which occurs 96% of the time, the assembly floor manager requests the parts from the warehouse. The process then waits for a worker to pick up the parts. Once the parts are picked up and logged by the warehouse, they are delivered to the assembly floor manager.
 The assembly floor manager oversees the assembly process. After the assembly is complete, the finished items wait to be sent to the warehouse. The assembly floor manager then sends the items to the warehouse, where they are placed in finished goods storage.
 Finally, the clerk logs the order and notifies both the client and the shipper. This marks the end of the process.</t>
-  </si>
-  <si>
-    <t>5709e97013004689a5250805f039b04c</t>
   </si>
   <si>
     <t>The process begins when a junior salesman in the sales department receives a request for a quotation. The junior salesman first clarifies the request to ensure all necessary details are understood. After clarifying, the junior salesman determines whether the request is simple or complex.
@@ -233,17 +1231,11 @@
 Finally, the junior salesman sends the prepared quotation to the customer, concluding the process.</t>
   </si>
   <si>
-    <t>314244d1f81a488ab13e5821970fd533</t>
-  </si>
-  <si>
     <t>The process begins with an administrator at Acme Manufacturing initiating an engineering change request. This task sets the process in motion.
 Next, the administrator encounters a decision point where the nature of the change is evaluated. If the change is deemed minor, the draftsmen proceed to make the change. If the change is considered major, an engineer is tasked with analyzing the change and making recommendations.
 For a major change, after the engineer analyzes and recommends, they initiate an approval process. A manager then processes this approval. Following the manager's decision, there is another decision point. If the change is accepted, the draftsmen document the changes and check them into the PLM system, completing the process. If the change is rejected, the process is terminated.
 For a minor change, the draftsmen make the change and then initiate an approval process. The manager processes this approval, leading to another decision point. If the change is accepted, the draftsmen check the changes into the PLM system, completing the process. If the change is rejected, the process is terminated.
 In summary, the process involves initiating a change request, evaluating the change, processing approvals, and either completing the change or terminating the process based on the approval outcomes.</t>
-  </si>
-  <si>
-    <t>cc88d8b942aa4cf7b21fcfb651a14594</t>
   </si>
   <si>
     <t>The process begins when a pharmacist receives a claim. The pharmacist then enters the claim details into the system. After entering the details, the pharmacist checks the form of the prescription to ensure it is correct. Once the form is verified, the pharmacy dispensing software checks the data of the prescription.
@@ -254,9 +1246,6 @@
 The Office of Human Service then sends the close claim transaction and receives a return message. Following this, the Office of Human Service prepares a separate claim and completes the necessary claim paperwork. Finally, the process concludes with the Office of Human Service.</t>
   </si>
   <si>
-    <t>9b8e781476924f6aaa6c92069724476b</t>
-  </si>
-  <si>
     <t>The process begins with the initiation of a resupply cycle. The first step involves checking the inventory level to determine the current stock status.
 After checking the inventory, a decision is made based on the inventory level. If the inventory level is above the minimum required, the process ends there. However, if the inventory level is at or below the minimum, a purchase order is created.
 Once the purchase order is created, it is reviewed. During the review, another decision is made. If the purchase order is approved, the process continues. If it is rejected, the purchase order is marked as rejected, and it is sent back for reworking. After reworking, the purchase order is reviewed again.
@@ -265,9 +1254,6 @@
 After recording the documents, the reserved funds are released. Finally, payment is issued to the supplier, and the process concludes.</t>
   </si>
   <si>
-    <t>ab698d0d639f48568d0706f87391e4d1</t>
-  </si>
-  <si>
     <t>The process begins when a Level 1 employee at the IT help desk receives a help request. The Level 1 employee then checks if there is a known solution to the problem. At this point, there is a decision to be made:
 1. If the solution is known, the Level 1 employee proceeds to solve the problem and then informs the customer that the problem has been solved, concluding the process.
 2. If the solution is unknown, the Level 1 employee forwards the request to a Level 2 employee. The Level 2 employee receives the request and evaluates it. After evaluation, the Level 2 employee assigns a priority level to the request and enters this information into the job tracking system. The job tracking system then assigns the request back to a Level 2 employee, who receives it and begins researching and developing a solution.
@@ -276,9 +1262,6 @@
 2. If the test is unsuccessful, the Level 1 employee sends the request back to the Level 2 staff for further research and development, repeating the cycle until a successful solution is found and the customer is informed.</t>
   </si>
   <si>
-    <t>1e3e8c5fe7ad46158e89fb38c8be6fb8</t>
-  </si>
-  <si>
     <t>The process begins with the reception of parts by the warehouse team. Once the parts are received, an operator in the designated zone checks the part list. This task involves verifying the parts against a provided list, which is documented in a Part List File.
 After checking the part list, the process reaches a decision point. If the checklist is not okay, the warehouse team is tasked with obtaining the missing part. Once the missing part is acquired, the process returns to the operator, who then assembles the applicator.
 If the checklist is okay, the operator proceeds directly to assemble the applicator. Following the assembly, the operator undertakes the adjustment of the applicator in a subprocess.
@@ -287,9 +1270,6 @@
 After measuring the samples, the operator performs an assembly report, documenting the entire process. Finally, the process concludes with the completion of the assembly report, marking the end of the process.</t>
   </si>
   <si>
-    <t>793cb97cb029428eb376629063898c2c</t>
-  </si>
-  <si>
     <t>The process begins when the client exits the vehicle. The first task is to check if the keys are present. If the keys are not in the car, the process ends with a task to retrieve the keys.
 If the keys are in the car, the next step is to measure the vehicle's emissions. Following this, the registration papers are examined to ensure they are in order. The process continues with checking the odometer to record the vehicle's mileage.
 Next, the gearing system is checked to ensure it is functioning correctly. The headlights are then inspected to confirm they are operational. Following this, the windshield is checked for any damage or obstructions.
@@ -298,16 +1278,10 @@
 The towing device is then checked. If there is no towing device, the process ends with the completion of the inspection at Base 2. If a towing device is present, it is inspected further. The database is checked for any records related to the towing device. Once this is done, the inspection at Base 2 is completed, marking the end of the process.</t>
   </si>
   <si>
-    <t>2aaf9036d6214edfa70ef0100eac7b5b</t>
-  </si>
-  <si>
     <t>The process begins when the notification department of the Car Insurer receives a claim. The notification department then checks the documentation to ensure it is complete. Once the documentation is verified, the claim is registered by the same department.
 Next, the handling department picks up the claim and checks the insurance details. At this point, a decision is made: if the claim is covered, the process continues; if not, the claim is rejected. If the claim is not covered, the handling department rejects the claim, and the process ends with the claim being marked as rejected.
 If the claim is covered, the handling department performs an assessment. Following the assessment, another decision is made based on the results: if the results are negative, the claim is rejected; if positive, the handling department contacts the garage to authorize repairs.
 After authorizing repairs, the handling department schedules the payment. Subsequently, a letter is sent to the customer, and the assessment results are communicated. The process concludes with the claim being assessed.</t>
-  </si>
-  <si>
-    <t>1af7cca2da4d496985fab343d02809f9</t>
   </si>
   <si>
     <t>The process begins when a sales engineer receives a customer purchase order. The sales engineer then checks the purchase order to ensure all the data is correct. At this point, there are three possible outcomes:
@@ -323,9 +1297,6 @@
 Once the shipment is scheduled, the sales engineer ships the product, and the customer is notified that the product has been shipped. The process concludes when the customer purchase order is fulfilled.</t>
   </si>
   <si>
-    <t>d56fc0ce496946e1a88a391b2c2e6d50</t>
-  </si>
-  <si>
     <t>The process begins when a mechanic at Frumherji LTD. identifies a new vehicle at Base 2. The mechanic then checks if the keys are in the car. If the keys are not in the car, the mechanic goes to the reception to collect them. Once the keys are available, the mechanic proceeds to inspect the vehicle at Base 2.
 After the inspection at Base 2, the mechanic records the outcome of the inspection. Following this, the mechanic moves the vehicle to Base 3 for another inspection. The inspection at Base 3 typically takes between 1 to 2 minutes. Once the inspection is completed, the mechanic records the outcome.
 Next, the mechanic moves the vehicle to Base 4 for further inspection. This inspection usually takes between 4 to 12 minutes. After completing the inspection at Base 4, the mechanic records the outcome and then moves the vehicle to the Inspection Hall.
@@ -333,16 +1304,10 @@
 Finally, the process concludes with the customer leaving the station. Meanwhile, the mechanic's task of completing the inspection is also marked as finished.</t>
   </si>
   <si>
-    <t>744cddfa416b49d5987ba90e0cea0cdd</t>
-  </si>
-  <si>
     <t>The process begins with an undergraduate student starting the application for IMIS. The student first checks the application procedure. After this, the student must determine if they are an EU applicant.
 If the student is not an EU applicant, they proceed as a non-EU or international applicant. The student then applies via Uni-Assist and sends the required documents to Uni-Assist. After submitting the documents, the student waits for a decision, which takes approximately 10 to 12 weeks. The process concludes with the student receiving either an admission or rejection letter.
 If the student is an EU applicant, the process splits into two simultaneous paths. In one path, the student, if they are an FH-SWF graduate, applies via the FH-SWF online portal and contacts the IMIS office. The student then waits for a decision, which takes about 4 to 6 weeks, before receiving the admission or rejection letter.
 In the other path, the EU applicant applies via the FH-SWF online portal and sends the required documents. The student then contacts the IMIS office and waits for a decision, which also takes about 4 to 6 weeks. Finally, the student receives the admission or rejection letter.</t>
-  </si>
-  <si>
-    <t>20bd5cf84b6547f5a201e289e676d8a9</t>
   </si>
   <si>
     <t>The process begins when an Account Manager acknowledges that a sale has been made. Following this, the Account Manager reviews the sale details with the vendor to ensure everything is in order. After the review, the Account Manager creates a case in the CRM system to document the transaction and any necessary follow-up actions.
@@ -352,24 +1317,15 @@
 The Integration Specialist follows up by sending an introduction email to the vendor, marking the end of the process.</t>
   </si>
   <si>
-    <t>7b04fdc80c4144d6856687b6d970609b</t>
-  </si>
-  <si>
     <t>The process begins with the supplier initiating the procedure. The first step involves the supplier acquiring cash. Once the cash is acquired, the supplier forwards it for validity checking.
 The financial body then checks if the money is present in the account. At this point, a decision is made based on the account balance. If the cash is not enough, the financial body detects this insufficiency and proceeds to decline the payment. Following this, the financial body notifies the provider about the declined payment. Consequently, the supplier declines the shipment of items, and the process concludes.
 On the other hand, if the cash is sufficient, the financial body detects the adequacy of funds and determines the provider. The supplier then receives the necessary credentials. After receiving the credentials, the dispatcher ships the required items, leading to the end of the process.</t>
-  </si>
-  <si>
-    <t>7139592663a7445d9acc8619e04db06c</t>
   </si>
   <si>
     <t>The process begins when a Level 1 employee at the IT Helpdesk receives a help request. The first task for the Level 1 employee is to check if the solution to the problem is already known. 
 At this point, there is a decision to be made. If the solution is known, the Level 1 employee proceeds to solve the problem. After solving the problem, the Level 1 employee informs the customer, and the request is then closed.
 If the solution is unknown, the Level 1 employee forwards the request to a Level 2 employee. The Level 2 employee receives the request and evaluates it. Following the evaluation, the Level 2 employee assigns a priority level to the request and enters this information into the job tracking system. The job tracking system then assigns the request to a Level 2 employee, who receives it and begins researching and developing a solution.
 Once the solution is developed, the Level 2 employee sends it back to the Level 1 employee. The Level 1 employee receives the solution and tests it. Another decision point occurs here. If the test is successful, the Level 1 employee informs the customer, and the process ends with the customer being informed. If the test is unsuccessful, the Level 1 employee sends the request back to the Level 2 employee for further action, and the process continues from there.</t>
-  </si>
-  <si>
-    <t>30f804a3e5e64ef298266e67acfecc4b</t>
   </si>
   <si>
     <t>The process begins when a Level 1 Employee at the IT help desk receives a help request. The employee then checks if they know the solution to the problem. At this point, there are two possible paths:
@@ -379,9 +1335,6 @@
 - If the test is successful, the Level 1 Employee informs the customer that the request has been fulfilled, ending the process.
 - If the test is unsuccessful, the Level 1 Employee sends the request back to the Level 2 staff for further research and development. This cycle continues until a successful solution is found and the customer is informed.
 Throughout the process, communication and task assignments are managed by the IT help desk, ensuring that each step is completed efficiently and effectively.</t>
-  </si>
-  <si>
-    <t>c0266568845e41b8ab7a99baa359b612</t>
   </si>
   <si>
     <t>The process begins with the initiation of the press process at perslijn7. The first step involves determining the type of ingredients. This decision point leads to four possible paths:
@@ -396,17 +1349,11 @@
 Upon completion of the process, the pressed product is allocated to one of the five press drain lines by an IT system.</t>
   </si>
   <si>
-    <t>c8d11f6234f549bcbcea682c891da632</t>
-  </si>
-  <si>
     <t>The process begins with the initiation of the program. Once the program is running, a decision point is reached where two paths are possible. 
 The first path involves selecting a file to scan. After selecting the file, the file is scanned, and the process continues to the next step, which is displaying the data.
 The second path involves selecting an option to display data directly. Once the option is selected, the data is displayed.
 After the data is displayed, the user can select the data they want to change by double-clicking on it. The selected data is then changed, and the change is validated. Once validated, the data is saved.
 After saving the data, another decision point is reached with three possible outcomes. The first outcome leads to the end of the process. The second outcome involves filtering and searching within the scanned database. The third outcome involves running table maintenance. Each of these outcomes represents a different path the process can take after saving the data.</t>
-  </si>
-  <si>
-    <t>9ff5bb3ce2c843dba9e1562c641365fd</t>
   </si>
   <si>
     <t>The process begins with a student opening an application. Once the application is opened, the application itself welcomes the student. After the welcome message, the student enters the student section of the application.
@@ -418,16 +1365,10 @@
 Upon arrival, the application sends a notification. This notification is sent simultaneously to both the student and a manager. The student receives the notification and subsequently closes the application. Similarly, the manager receives the notification, concluding their part in the process.</t>
   </si>
   <si>
-    <t>6c5d8483fb51405096a01946d550b55d</t>
-  </si>
-  <si>
     <t>The process begins with a message that initiates the workflow. Following this, there is a point where two tasks are carried out simultaneously.
 The first task involves deploying the database tier. Once this is completed, the next step is to deploy a virtual machine specifically for Apache. After the virtual machine is set up, the operating system for Apache is deployed. Following this, the Apache web server itself is deployed. The process continues with the deployment of PHP modules. After the PHP modules are in place, the SugarCRM application is deployed. The final step in this sequence is connecting the SugarCRM application to the database.
 Simultaneously, the second task involves deploying the web tier. After this, a virtual machine for mySQL is deployed. Once the virtual machine is ready, the operating system for mySQL is deployed. Following this, mySQL itself is deployed. The next step is to create the SugarCRM database. This sequence concludes by connecting to the task where the SugarCRM application is connected to the database.
 The process ends once the SugarCRM application is successfully connected to the database.</t>
-  </si>
-  <si>
-    <t>e29280012da84bd3a14aceaee0d6d114</t>
   </si>
   <si>
     <t>The process begins with a storing employee checking the quality of a product. Once the quality check is complete, the storing employee proceeds to determine the product family.
@@ -438,9 +1379,6 @@
 The process concludes with the product being stored, marking the end of the process.</t>
   </si>
   <si>
-    <t>76d9bdc2ae634edbaa67e809182e3688</t>
-  </si>
-  <si>
     <t>The process begins when an online order is received by the order reception team at Online Orders Ltd. Once the order is received, the team prepares the order to be shipped.
 Next, there is a decision point to determine if bubble protection is needed for the shipment. If bubble protection is required, the order reception team adds bubble protection to the shipment. After adding bubble protection, or if it is not needed, the package is passed to the warehouse.
 In the warehouse, the team checks whether the package should be sent via normal post or fast courier. If the decision is to use a fast courier, the warehouse fills out the post label. If the decision is to use normal post, the warehouse gets a quote from the contracted courier.
@@ -448,17 +1386,11 @@
 After the paperwork is combined with the package, the courier picks up the package. Finally, the package is sent, marking the end of the process.</t>
   </si>
   <si>
-    <t>74538661264347fb8cdfbfbd5476d950</t>
-  </si>
-  <si>
     <t>The process begins when a vehicle is prepared for inspection. The first step involves opening the customer file, which is handled by an employee. This task is followed by creating a digital inspection file, also managed by the same employee. Once the digital file is ready, the next step is to insert a sensor into the vehicle's exhaust pipe, which is performed by a technician.
 Following this, the vehicle undergoes an interior inspection, which is a subprocess involving various checks inside the vehicle. After the interior inspection, the vehicle's exterior is inspected, which is another subprocess focusing on the outside of the vehicle.
 Next, a technician checks for the presence of a towing device on the vehicle. At this point, a decision is made based on whether a towing device is installed. If a towing device is present, it is inspected to ensure it meets safety standards. This inspection is documented with a note to check if safety standards are met. After inspecting the towing device, the registration status of the vehicle is checked against the database to ensure it is up to date.
 If no towing device is installed, or after the registration status is checked, the digital inspection file is updated with the results of the inspection. This task is performed by an employee using the Frumherji IT system.
 Finally, the vehicle is driven to Base 3, marking the completion of the overall vehicle inspection process. The process concludes with the vehicle inspection being completed.</t>
-  </si>
-  <si>
-    <t>c6cf1da7e789466993ca214fa9e41763</t>
   </si>
   <si>
     <t>The process begins with a driver needing to create an account. The driver starts by registering a driver account and setting a password. After this, the driver chooses the type of driver they want to be. Next, the driver must accept the cookies policy.
@@ -469,15 +1401,9 @@
 If the driver is not approved, Uber sends a rejection letter, ending the process for that driver.</t>
   </si>
   <si>
-    <t>096954d076984050902e9c92035a331c</t>
-  </si>
-  <si>
     <t>The process begins when a customer sends a prescription to the pharmacy. A pharmacy technician receives the prescription and checks the method of delivery. There are two possible methods: immediate delivery or pickup. If the delivery is immediate, the technician inputs the prescription details into the system. If the pickup method is chosen, the technician stores the prescription along with the scheduled hour of pickup. One hour before the pickup time, the technician inputs the prescription details.
 Once the prescription details are entered, the pharmacy system performs Drug Utilization Review checks, followed by an insurance check. After these checks, the pharmacy technician collects the drugs. The pharmacist then double-checks the drugs to ensure accuracy. If the drugs are correct, the pharmacist prepares them for pickup. If there is an error, the pharmacist requests the technician to re-collect the drugs, and the process of collecting and checking the drugs is repeated.
 When the customer arrives at the pharmacy, the pharmacy technician determines if a payment is required. If no payment is needed, the technician proceeds to deliver the drugs to the customer. If payment is required, the technician collects the payment before delivering the drugs. Upon delivery, a receipt is sent to the customer, and the process concludes with the drugs being successfully delivered.</t>
-  </si>
-  <si>
-    <t>f1aaad76e4d845a2bd7e45dda90e32af</t>
   </si>
   <si>
     <t>The process begins when an Administrator from the Product Development Department decides to change a design. The Administrator initiates a change request, which takes approximately 30 minutes.
@@ -485,9 +1411,6 @@
 At this point, another decision is made regarding acceptance. If the changes are accepted, which occurs 95% of the time, the Draftsman checks the changes, a task that takes 1.5 hours, and the process ends. If the changes are not accepted, which happens 5% of the time, the process ends without further action.
 Returning to the earlier decision point, if the change is major, which occurs 30% of the time, Engineers analyze the changes and make recommendations, a task that takes approximately 8 hours with a possible variation of 25%. Following this, Engineers initiate an approval process in the PLM system, taking 1 hour. The Engineers' manager then waits for the approval process to be completed, which takes about 1 hour with a possible variation of 15 minutes.
 Another decision is made regarding acceptance. If the changes are accepted, which happens 60% of the time, a Draftsman documents the changes, a task that takes 8 hours. The Draftsman then checks the changes into the PLM system, taking 1.5 hours, and the process ends. If the changes are not accepted, which occurs 40% of the time, the process ends without further action.</t>
-  </si>
-  <si>
-    <t>1240884060c64c629dc7c13357555caa</t>
   </si>
   <si>
     <t>The process begins with the Administrator initiating the registration of a new administrator member. Once the registration task is completed, the Online Group Purchasing System takes over to verify the input provided. 
@@ -499,9 +1422,6 @@
 Each of these branches concludes with the Online Group Purchasing System marking the end of the respective process paths.</t>
   </si>
   <si>
-    <t>92541a4399cf48429283280ba0f30594</t>
-  </si>
-  <si>
     <t>The process begins with operator 1 initiating the task. The first step involves a parallel action where two separate tasks are carried out simultaneously.
 In the first branch, operator 1 places a glass panel on the work station. Following this, the glass panel is cleaned by operator 1. After cleaning, operator 1 applies primer to the glass panel. The glass panel is then placed in a curing area for 5 minutes by operator 1.
 Simultaneously, in the second branch, operator 2 places brackets on the work station. Operator 2 then cleans the brackets. After cleaning, primer is added to the brackets by operator 2. The brackets are then placed in a curing area for 5 minutes by operator 2.
@@ -509,9 +1429,6 @@
 Next, a machine adds glue to the panel. The machine then presses the panel upon the brackets. The panel and brackets are allowed to dry by the machine. Finally, the machine places the glued panel in a batch, marking the end of the process.</t>
   </si>
   <si>
-    <t>599bc5727aa347d28056f245abc3fd6c</t>
-  </si>
-  <si>
     <t>The process begins when a claim is submitted. The first task involves submitting the claim, which is handled by the claimant. Once the claim is submitted, the process splits into two parallel tasks.
 The first parallel task is to post the original documents, which is the responsibility of the claimant. After posting the documents, the next step is to retrieve and record the claim, managed by the claims processor. Following this, the claims processor triggers the payment, leading to the completion of the claim process.
 Simultaneously, the second parallel task involves verifying the policy's validity, conducted by the policy verifier. If the policy is found to be invalid, the policy verifier must double-check the policy. After double-checking, a decision is made: if the policy is valid, the process continues to verify the claim's completeness. If the policy remains invalid, the customer is notified, and the claim is rejected.
@@ -519,16 +1436,10 @@
 This process ensures that all necessary steps are taken to handle a claim efficiently, from submission to completion or rejection.</t>
   </si>
   <si>
-    <t>a922ed6455094ebca47ab19950189ab4</t>
-  </si>
-  <si>
     <t>The process begins when employees require training. The supervisor is responsible for selecting the appropriate training. Once the training is selected, the supervisor submits a training request.
 Next, the director evaluates the training request. At this point, a decision is made to determine if the correct training has been chosen. If the training is incorrect, the request is denied, and the supervisor is notified with the reason for denial. This concludes the process.
 If the correct training is chosen, the director then evaluates whether the training fits within the budget. If the training is over budget, the request is denied, and the supervisor is notified with the reason for denial. This also concludes the process.
 If the training fits within the budget, the supervisor is notified of the approval. The process ends with the supervisor scheduling the training.</t>
-  </si>
-  <si>
-    <t>1dafcaa36034450d98dd6c785ed4e026</t>
   </si>
   <si>
     <t>The process begins when a customer enters the restaurant and places an order. The customer first decides on their preferred sandwich. After choosing the sandwich, the customer selects their preferred type of bread. Following this, the customer decides on the type of cheese they would like.
@@ -536,9 +1447,6 @@
 Once the sandwich is in the oven, there is a waiting period until the sandwich is ready. After the waiting period, the customer takes the order out of the oven. The customer then specifies their preferred toppings.
 Next, the process checks if the customer wants sauce. If the customer wants sauce, they decide on their preferred sauce. After deciding on the sauce, or if no sauce is desired, the customer decides whether to eat in the store or take the order away.
 Following this decision, the customer chooses their payment method. The customer then performs the payment. Finally, the ordering process ends.</t>
-  </si>
-  <si>
-    <t>4fa9326b71d94920993720520b2712e5</t>
   </si>
   <si>
     <t>The process begins with the China Warehouse receiving a message to start the operation. The first task is for the China Warehouse to scan the label of the tracking number. Once the label is scanned, the next step is to identify the customer associated with the parcel.
@@ -552,18 +1460,12 @@
 If the parcel is to be sent by sea, the China Warehouse calculates the fee according to sea freight rates and follows the same steps as for air transport, leading to the same potential outcomes.</t>
   </si>
   <si>
-    <t>49a24f70597040208f977637c5f4ba2f</t>
-  </si>
-  <si>
     <t>The process begins with the Auction Service initiating a timer. Once the timer starts, the Auction Service checks the duration time to determine if the auction period has ended.
 At this point, there is a decision to be made. If the time is up, the Auction Service proceeds to inform the winner of the auction. After informing the winner, the process concludes with a message indicating the end of the auction.
 If the time is not up, the Auction Service checks if there is a new bidder. If there is no new bidder, the process loops back to checking the duration time again.
 If there is a new bidder, the Auction Service receives the buyer's maximum price. The next step involves comparing this maximum price with the highest bidders' prices.
 Another decision point arises here. If the buyer's maximum is not the highest, the Auction Service increases the buyer's maximum by one increment and then outbids the buyer. Following this, a notification is sent to the buyer, and the process ends with a message indicating the conclusion of this action.
 If the buyer's maximum is the highest, the Auction Service bids on behalf of the buyer by a small increment above the closest competitor's highest bid. Subsequently, the previous maximum is set as a new minimum, and the process loops back to checking the duration time again.</t>
-  </si>
-  <si>
-    <t>c1f695e4abf74245b749b0b443c699e8</t>
   </si>
   <si>
     <t>The process begins with the initiation of change management. Once this is triggered, four tasks are carried out simultaneously:
@@ -582,17 +1484,11 @@
 Finally, the change management process concludes, marking the end of the process.</t>
   </si>
   <si>
-    <t>4812b60389444ba4b480cdcd51c9eb2c</t>
-  </si>
-  <si>
     <t>The process begins when a revised purchase order is received. The first step involves retrieving the details of the order. Once the order details are retrieved, the next step is to check if the product is in stock.
 At this point, there is a decision to be made based on the stock availability. If the product is in stock, the process continues with confirming that the product is available. Following this, the order is processed, and the system waits for order confirmation.
 Once the order is confirmed, two tasks occur simultaneously. One task involves emitting an invoice, which is followed by confirming payment by the customer. After payment is confirmed, the order is archived, marking the completion of the process.
 Simultaneously, the other task involves awaiting the shipment address. Once the shipment address is received, the requested product(s) are shipped. After shipping, the process also leads to archiving the order, completing the process.
 If the product is not in stock, the order is rejected, and the process ends there.</t>
-  </si>
-  <si>
-    <t>c02fd526a0d4465db1c26aa174c9c85d</t>
   </si>
   <si>
     <t>The process begins with an administrator initiating the workflow. The first task involves the administrator performing an automated credit check. Once the credit check is completed, the administrator confirms the credibility check.
@@ -604,9 +1500,6 @@
 Throughout the process, the administrator is responsible for each task, ensuring that all steps are completed efficiently and accurately.</t>
   </si>
   <si>
-    <t>1075135c161b40e7a6655dd68aa1c5e0</t>
-  </si>
-  <si>
     <t>The process begins with the task of defining the country on the Citrix Active Directory. Once the country is defined, the next step is to prepare the infrastructure. After the infrastructure is prepared, two tasks are initiated simultaneously.
 The first task involves creating roles on the Fiori LaunchPad. Following this, the on-set IT team is trained on these Active Directory groups. After the training, contact is made with the MO (Management Office). During this contact, a document is generated that includes finding the responsible local person, checking their responsibilities, organizing training, and creating an application to assign to roles. Subsequently, the MO and local IT provide the required apps template. This is followed by testing with local pilot groups.
 Simultaneously, the second task involves creating Active Directory groups. After this task, the process continues with training the on-set IT on these groups, similar to the first branch.
@@ -616,9 +1509,6 @@
 The third task is to create a communication package, which includes a training package, upfront. This task also leads to onboarding the end-users, marking the end of the process.</t>
   </si>
   <si>
-    <t>fd2c9f678fea49218a54235507d654bb</t>
-  </si>
-  <si>
     <t>The process begins when the customer receives an acceptance pack. The customer then opens the acceptance pack and reads the repayment schedule included within it. After reviewing the schedule, the customer must decide whether they agree with the terms.
 If the customer agrees, they proceed to sign the document. Once signed, the customer sends the signed document back. This action triggers a notification to the loan provider, indicating that the customer has responded.
 If the customer does not agree with the terms, they choose to ignore the document. Subsequently, the customer informs the loan provider officer about their decision. This notification prompts the loan provider to verify the repayment agreement.
@@ -627,16 +1517,10 @@
 Separately, when a loan application is approved, the loan provider prepares an acceptance pack and sends it to the customer. This pack includes the terms and conditions, along with the repayment schedule. The customer then receives this pack, which initiates the process described above.</t>
   </si>
   <si>
-    <t>7df0261769274726b341a9a2ab2dcdd2</t>
-  </si>
-  <si>
     <t>The process begins when the supplier receives an invoice. The supplier then sends the invoice to the accounting department. Once the accounting department receives the invoice, they forward it to the business unit.
 The business unit checks the invoice for approval. At this point, there are two possible outcomes:
 1. If the invoice is approved, the business unit sends it back to the accounting department. The accounting department then fills in the necessary accounting information. After this, two tasks occur simultaneously: the accounting department pays the supplier and updates the accounts payable. Once both tasks are completed, the process ends with the invoice marked as completed.
 2. If the invoice is not approved, the business unit informs the accounting department. The accounting department then informs the supplier that the invoice was not approved. The process concludes with the invoice being declined.</t>
-  </si>
-  <si>
-    <t>9864e8a829b54588bf70ed08b9049979</t>
   </si>
   <si>
     <t>The process begins when Bob is hungry, and Jane Doe, who is responsible for making a peanut butter and jelly sandwich, starts the process. Jane decides that Bob wants a peanut butter and jelly sandwich.
@@ -644,9 +1528,6 @@
 If Jane chooses wheat bread, she proceeds to look for peanut butter. At this point, she must decide between creamy or chunky peanut butter. If she selects chunky peanut butter, she applies it along with jelly to the bread, and the process concludes with a happy Jane Doe.
 If Jane opts for creamy peanut butter, she checks if there are bananas and apples available. She then decides whether to use bananas or apples. If she chooses bananas, she toasts the wheat bread, applies creamy peanut butter, and places bananas on the toast. This leads to the end of the process with a happy Jane Doe.
 If Jane decides to use apples, she applies peanut butter and jelly to the wheat bread and adds the apples. This also results in a happy Jane Doe at the end of the process.</t>
-  </si>
-  <si>
-    <t>495162891d3747a98b9da1b50a7a1336</t>
   </si>
   <si>
     <t>The process begins when an agent at the Transport Agency identifies the need for a full driver's license. The agent first asks the customer to provide an application form. Once the application form is received, the agent requests the customer's identification. After obtaining the ID, the agent copies the necessary information and inputs it into the database.
@@ -662,17 +1543,11 @@
 Throughout this process, the agent and the agent's assistant work together to ensure all necessary steps are completed, and the Driver's License System provides support by checking the database and notifying the agent as needed.</t>
   </si>
   <si>
-    <t>7ca4ed9ebdca4945b21aa9c71b974b1e</t>
-  </si>
-  <si>
     <t>The process begins with the Performance Manager initiating the task of editing focus improvement. The first step involves accessing the focus improvement page. During this step, a list of focus improvements is referenced.
 Next, the Performance Manager selects a specific improvement from the list. Following this, the manager proceeds to edit the chosen focus improvement. After making the necessary edits, the manager updates the data form related to the focus improvement.
 At this point, a decision needs to be made. The manager can either choose to cancel the process or save the changes. If the decision is to cancel, the process loops back to the focus improvement page. If the decision is to save, the manager previews the edited focus improvement. During this preview, a verification pop-up is displayed.
 Another decision point arises after the preview. The manager can either update the changes or cancel them. If the manager decides to update, the process moves forward to the focus improvement page again, eventually leading to the end of the process. If the decision is to cancel, the process returns to the step of editing the data form for focus improvement.
 The process concludes once the manager has successfully updated the focus improvement and returned to the focus improvement page.</t>
-  </si>
-  <si>
-    <t>2880b7e234cf4d1cae1cdd1ec36abee1</t>
   </si>
   <si>
     <t>The process begins with the customer initiating the action. The customer places an order, which involves queuing and informing the cashier of their desired items. This action generates a document detailing the queue and the order specifics.
@@ -682,9 +1557,6 @@
 During the payment process, the customer decides on the payment method. They can choose between using an e-wallet, a debit/credit card, or cash. If the customer chooses to pay with cash, the cashier receives the cash and checks if change is needed. If change is needed, the cashier returns the change to the customer. If no change is needed, the cashier returns the receipt to the customer. In both cases, the customer waits for their meal to be prepared.
 If the customer chooses to pay with a debit/credit card, they enter their password, and the cashier returns the receipt. If the customer opts for an e-wallet, they scan a QR code, and the cashier returns the receipt. After receiving the receipt, the customer waits for their meal to be prepared.
 Throughout the process, the customer and the cashier communicate through various message flows, ensuring that each step is completed before moving on to the next. The process concludes with the customer collecting their order.</t>
-  </si>
-  <si>
-    <t>ee048ea75e6948c7bdc72b40427d6dfd</t>
   </si>
   <si>
     <t>The process begins with a customer initiating a request to make a reservation. This is the starting point of the process.
@@ -699,9 +1571,6 @@
 Finally, the process concludes with the airline company completing the necessary actions based on the payment outcome, marking the end of the process.</t>
   </si>
   <si>
-    <t>947b47653378445eb06f47d4363d848d</t>
-  </si>
-  <si>
     <t>The process begins with students at GG Institute of Arts starting the application procedure. The first step involves students filling out an online form. Once the form is completed, students submit it online. After submission, students are required to print and sign a PDF document. This signed document, along with any necessary attachments, is then posted by the students.
 The next step involves a staff member or clerk at GG Institute of Arts checking the completeness of the submitted documents. If the documents are not complete, the staff member sends an email notification to the students, informing them of the missing documents. The students then need to post the missing documents, after which the completeness check is repeated.
 If the documents are complete, the process moves to the executive of the admission office, who verifies the validity of the certified documents. If the documents are not valid, the executive sends a rejection notification via email, and the process ends there for those applications.
@@ -709,9 +1578,6 @@
 For applications that are rejected due to invalid documents, the executive of the admission office sends a rejection notification by email, concluding the process for those applicants.</t>
   </si>
   <si>
-    <t>a30afaed2e524845ae093459f3f503a3</t>
-  </si>
-  <si>
     <t>The process begins with the foreman initiating the task of picking up a component known as the Längsträger. Once the Längsträger is picked up, the foreman inserts it into a device called Poka Yoke. The Poka Yoke then scans the pair of components.
 At this point, the process checks if the pair is correct. If the pair is not correct, the Poka Yoke substitutes the incorrect pair and the scanning process is repeated. If the pair is correct, the foreman proceeds to clip an RFID label onto the component.
 After clipping the RFID label, the Poka Yoke reads the RFID label. This reading is also communicated to an IT system known as AC4+. The process then checks if the RFID label is correct. If the RFID label is not correct, the Poka Yoke substitutes the RFID and the label reading is repeated. If the RFID label is correct, the foreman loads the component into an expedition container.
@@ -719,15 +1585,9 @@
 Finally, the process concludes with the foreman completing the task, marking the end of the process.</t>
   </si>
   <si>
-    <t>dd81de6e1cf147b79457934cc6480968</t>
-  </si>
-  <si>
     <t>The process begins with the initiation of the workflow. The first task is performed by an actor who joins data, utilizing three data objects: DM_WUR_PERCEEL_V2, DM_WUR_NDVI_V2, and DM_WUR_GEWAS_V2. Once the data is joined, the next task involves extracting non-centroid parcels. Following this, a user-written task is executed to identify differences.
 After identifying differences, the process reaches a point where two tasks are carried out simultaneously. One task involves extracting total sums, while the other involves extracting maaimomenten. The task of extracting total sums leads to another task where data is joined again. This is followed by extracting weighted averages, and then filtering on grass. Subsequently, a user-written interpolation task is performed, resulting in the creation of a data object labeled ALL_REGIO_GRASS_INTERPOLATED_V4.
 Simultaneously, the task of extracting maaimomenten is followed by extracting weekly differences, which then converges back to the task of joining data. The process concludes after the user-written interpolation task is completed, marking the end of the workflow.</t>
-  </si>
-  <si>
-    <t>875870ab3de2450e830d6243f8f9d212</t>
   </si>
   <si>
     <t>The process begins with the reception team at Hesthals initiating the reception process. The first task involves the reception calling the customer's number. Following this, the reception requests the necessary documents from the customer.
@@ -737,15 +1597,9 @@
 In parallel, after arranging payment, the reception changes the car status, which leads to restarting the process. The process concludes with the reception task being completed.</t>
   </si>
   <si>
-    <t>d8c408c7e7504253bf052eceb786e676</t>
-  </si>
-  <si>
     <t>The process begins with an engineer conducting regular engine checks. The engineer first selects an engine to work on. After selecting the engine, the engineer checks the engine's status.
 At this point, the engineer must decide based on the engine's condition. If a part needs to be replaced, the engineer selects the specific part. If maintenance is required, the engineer checks the end-of-life status of the parts and performs the necessary maintenance. After maintenance, the engineer scans the engine, and the process concludes with the problem being fixed.
 If a part replacement is necessary, the engineer selects the part and then faces another decision. If an overhaul is required, the engineer replaces the part and scans the new part. This leads back to the decision about whether an overhaul is needed. If no overhaul is needed and only damage is present, the engineer fills in a claim form, performs a warranty check, and sends the claim to MAN. The process ends with the claim being sent.</t>
-  </si>
-  <si>
-    <t>69a6f00c8edb4c44874fe1f7181fdc23</t>
   </si>
   <si>
     <t>The process begins with a barista who is ready to serve customers. When a customer arrives, the barista records the order in the register. Once the order is recorded, the process splits into two tasks that happen at the same time.
@@ -755,17 +1609,11 @@
 Finally, the process concludes with the customer receiving their receipt, marking the end of the transaction.</t>
   </si>
   <si>
-    <t>ee097c609dea4c52a6e7a941627332a6</t>
-  </si>
-  <si>
     <t>The process begins with Junior Ecologists selecting a species list. They then enter species information from an external source. This information is sent to an Excel Tool, which searches the "Base Data" for the species name.
 At this point, the process branches based on whether the species is found in the "Base Data." If the species is found, the Excel Tool sends a message saying "Right On!" and displays this message. If the species is not found, the Excel Tool sends a message saying "Fix it Dude" and displays this message.
 After displaying the message, Junior Ecologists receive feedback. They then check if the spelling of the species name is correct. If the spelling is correct, they move to the next section, and the process ends successfully.
 If the spelling is incorrect, Junior Ecologists check the spelling against the "Base Data." This leads to another decision point. If a similar name is found in the "Base Data," Junior Ecologists adjust the name in the "Species List" and move to the next section, ending the process successfully.
 If no similar name is found, Junior Ecologists notify a Senior Ecologist. The Senior Ecologist receives the notification and adjusts the "Base Data." They then save the changes and notify the Junior Ecologist. Upon receiving this notification, the Junior Ecologist restarts the process by entering species information from the external source again.</t>
-  </si>
-  <si>
-    <t>659bdd2ae4ce46af834eaecdf4a26038</t>
   </si>
   <si>
     <t>The process begins with the Human Resources Department identifying a job vacancy. They proceed to create a job advertisement. Once the advertisement is ready, it is placed by the Human Resources Department.
@@ -778,9 +1626,6 @@
 The process concludes with the Interviewing Panel ending their involvement after conducting interviews.</t>
   </si>
   <si>
-    <t>663ef9193c9b471a87c214bf2ea14489</t>
-  </si>
-  <si>
     <t>The business process begins with the Auction Service initiating a timer. Once the timer starts, the Auction Service checks the duration time to determine if the auction period has ended.
 At this point, a decision is made. If the time is up, the Auction Service proceeds to inform the winner of the auction. After informing the winner, the process concludes with a message indicating the end of the auction.
 If the time is not up, the Auction Service checks if there is a new bidder. If there is no new bidder, the process loops back to checking the duration time again.
@@ -789,16 +1634,10 @@
 If the buyer's maximum is the highest, the Auction Service bids on behalf of the buyer by a small increment above the closest competitor's highest bid. Subsequently, the previous maximum is set as a new minimum, and the process loops back to checking the duration time again.</t>
   </si>
   <si>
-    <t>e8fc095af9734c7598bbd88eaac97421</t>
-  </si>
-  <si>
     <t>The process begins when there is a need for training. The first step involves a supervisor selecting a training vendor. Once the vendor is chosen, the next task is to fill out a training request form. After completing the form, it is sent to the supervisor for review.
 The supervisor then checks if the proposed training is appropriate. At this point, there is a decision to be made. If the training is deemed appropriate, the process continues to the next step. If not, the approval is denied, and the reason for denial is communicated. This concludes the process without scheduling the training.
 If the training is appropriate, the next step is to check if there is enough budget available. Another decision is made here. If the budget is sufficient, the training is approved. If the budget is not enough, the process follows the same path as when the training is not appropriate, leading to denial and communication of the reason.
 Once the training is approved, the supervisor is notified. Following this notification, the training is scheduled. The process concludes with the training being successfully scheduled.</t>
-  </si>
-  <si>
-    <t>3b239cd2ee9a422687c65c2558f81462</t>
   </si>
   <si>
     <t>The process begins with an employee initiating the procedure by sending a holiday application. Once the application is sent, an administrative assistant receives it. The assistant then files the application and forwards it to the current manager.
@@ -808,9 +1647,6 @@
 In summary, the process involves the employee, administrative assistant, supervisor, and HR department, each playing a specific role in handling the holiday application from submission to final notification. The process concludes once the employee is informed of the decision, whether it is an approval or a decline.</t>
   </si>
   <si>
-    <t>0fe73faca0fd4b85b7b1ba795871ff46</t>
-  </si>
-  <si>
     <t>The process begins when the information systems of Immigration Wonderland receive an online application. The information systems then fetch the details of this new application. After retrieving the details, the information systems create a PDF document of the application. Once the document is prepared, the information systems notify a junior officer about the new application.
 The junior officer receives the notification and proceeds to check the completeness of the document. At this point, there is a decision to be made based on the completeness of the application. If the application is incomplete, the junior officer notifies the applicant to provide the missing documents. The applicant then sends the missing documents back to the junior officer, who rechecks the document completeness.
 If the application is complete, the junior officer sends it to a senior officer. The senior officer receives the application and checks the validity of the information provided. Another decision point arises here. If the information is not valid, the senior officer rejects the application, and the information systems notify the applicant of the rejection. This concludes the process for applications with invalid information.
@@ -818,9 +1654,6 @@
 If the applicant has passed the test, the junior officer sends a confirmation to the applicant, marking the end of the process with the confirmation received by the applicant.</t>
   </si>
   <si>
-    <t>a8902208793d43d5854db238120279f1</t>
-  </si>
-  <si>
     <t>The process begins with a Function Developer initiating the task of collecting Lessons Learned (LL). Once the collection is complete, the Function Developer proceeds to check the LL.
 At this point, the Function Developer evaluates whether the LL is useful for other areas. If it is deemed useful, the Function Developer inserts and tracks the LL in the system. Following this, a Coordinator makes a decision about further handling.
 The process then splits into two parallel paths. In one path, the Coordinator checks for any LL issues. If issues are found, the Process Owner tracks the LL internally within the project. The Coordinator then checks the LL status. If the LL transfer is not complete, the process loops back to tracking the LL internally. If the transfer is complete, the Coordinator fixes any issues, leading to the end of this path.
@@ -828,9 +1661,6 @@
 If the LL is not useful for other areas, the Project Manager tracks the LL internally within the project. The Project Manager then discusses the matter with project management and fixes any project-related issues, concluding this path of the process.</t>
   </si>
   <si>
-    <t>6301a8f360854cf39e9df4f0341990ec</t>
-  </si>
-  <si>
     <t>The process begins when the lender initiates the business loan tracker. The lender then tracks the loan process files to ensure everything is in order. Following this, the lender sends the application status to the relevant parties. Next, the lender updates the customer's information in the tracker to keep records current.
 The process then moves to the risk assessment team, who carry out a loan assessment. After the assessment, a decision point is reached. If the file is assessed, the risk assessment team updates the status in the tracker. This update is then sent to the loan center, where the file is received, and customer information is processed. If there is no tracker update, the loan document processing occurs at the loan center.
 At the loan center, customer information is received, and any required customer documents are identified. Existing customer information is referenced as needed. If manual data entry is required, it is performed to ensure all data is accurate. Once the files are error-free, they are sent back to the lender for document re-checking.
@@ -838,17 +1668,11 @@
 Once the documents are reviewed again and verified by the lender, an intermediate message is sent to the customer for application approval. The lender then assesses the documents again for completeness and accuracy. Finally, the process concludes with the creation of the final loan document. Throughout the process, assumptions are made to streamline document checks once cleared by the risk assessment team, aiming to save time.</t>
   </si>
   <si>
-    <t>0396fb06704347bf9bf47c2aa4f79379</t>
-  </si>
-  <si>
     <t>The process begins when the picker receives an order displayed on their reader. This marks the start of the workflow.
 Next, the process splits into two parallel paths. In the first path, the picker takes a dry box. They then proceed to collect goods from the shelves and place them into the box. After gathering the items, the picker scans both the goods and the box. Once scanned, the picker places the box onto a conveyor belt. The conveyor belt, using barcodes, directs all goods of a single order to an assigned cash register. At this point, the cashier receives the sorted box.
 The cashier then checks out the order using the system. After checkout, the cashier places the items into bags. These bags are then put away into buffer areas located next to the cash registers.
 Simultaneously, in the second path, couriers (drivers) arrive at the ramp. They locate the orders in one assigned buffer, which is determined by the system. This path concludes when the order is ready to be picked up by the courier.
 Both paths eventually converge, ensuring that the order is prepared and ready for the courier to collect.</t>
-  </si>
-  <si>
-    <t>a601e32c53c4467d8ed98f9621036ff4</t>
   </si>
   <si>
     <t>The process begins when a customer makes a claim, which is handled by a Service Center Agent at the Fridge Service Center. The agent first gathers a description of the problem and the type of fridge involved. After obtaining this information, the agent opens a ticket to document the issue.
@@ -860,9 +1684,6 @@
 In one task, the Service Center Agent edits the ticket to include the customer's confirmation and then closes the ticket, marking the end of the process. In the other task, the agent asks the customer for a service rating. The customer's response is received, and the process concludes with the ticket closure.</t>
   </si>
   <si>
-    <t>ee5fa56b9ef74ed3b1f85dcab54fb9b9</t>
-  </si>
-  <si>
     <t>The process begins with the task of creating a map of application controls. Once this is completed, the next step is to identify the key processes involved. Following this, the control objectives are determined to ensure that the processes are aligned with the desired outcomes.
 After setting the control objectives, the key control is tested to verify its effectiveness. Subsequently, the assertions addressed by the control are also tested to ensure they meet the required standards.
 At this point, a decision is made regarding whether re-performance is needed. If re-performance is necessary, the task of executing re-performance is carried out. Once re-performance is executed, the process continues with understanding and documenting the transaction flow.
@@ -872,25 +1693,16 @@
 If the audit evidences are not sufficient, sampling procedures are used to test individual items further. After this additional testing, the process returns to reviewing corrective actions and inquiring about their follow-up, eventually leading to the conclusion of the process.</t>
   </si>
   <si>
-    <t>3db43399d426454eb42ba9bd4030bf2f</t>
-  </si>
-  <si>
     <t>The process begins when a customer arrives at the restaurant. Upon arrival, the staff checks if the customer has a reservation. If the customer has a reservation, the staff confirms it and then takes the customer to their table. If the customer does not have a reservation, the staff checks for available tables. Once a table is available, the staff takes the customer to the table.
 After the customer is seated, the staff introduces the menu to the customer. The customer then places their order, which the staff takes. Once the order is taken, the staff serves the dishes to the customer.
 After the meal, the staff prepares the bill. The bill is then brought to the customer's table. The customer makes the payment for their meal. Once the payment is completed, the customer leaves the restaurant.
 After the customer leaves, the staff cleans the table to prepare it for the next customer. This marks the end of the process.</t>
   </si>
   <si>
-    <t>cefef269825442389ec099316243fd76</t>
-  </si>
-  <si>
     <t>The process begins with a Claim Officer receiving a claim. The Claim Officer then checks if the claimant is insured. At this point, there are two possible outcomes:
 1. If the claimant is insured, the process continues with a Senior Claim Officer evaluating the severity of the claim. Following this evaluation, the Senior Claim Officer sends the relevant forms, which could be simple or complex, to the claimant via the SAP system. Once the forms are returned, the Senior Claim Officer checks them for completeness. If the forms are complete, the claim is registered in the claims management system, and the process is complete. If the forms are not complete, the claimant is informed via the SAP system to update the forms, and the process loops back to the step where the forms are sent to the claimant.
 2. If the claimant is not insured, the Claim Officer informs the claimant that the claim has been rejected via the SAP system, and the process is complete.
 Throughout the process, the Claim Officer and Senior Claim Officer are responsible for ensuring that all necessary steps are followed and that the claimant is kept informed of the status of their claim. The process concludes once the claim is either registered in the system or the claimant is informed of the rejection.</t>
-  </si>
-  <si>
-    <t>192c32688fd843d5b6e0a17118135705</t>
   </si>
   <si>
     <t>The process begins with the China Warehouse receiving a start message. The first task is for the China Warehouse to scan the label of the tracking number. Once the label is scanned, the next step is to identify the customer associated with the parcel.
@@ -899,9 +1711,6 @@
 If the parcel is ready for delivery, the China Warehouse receives confirmation from the customer for the parcel list to be sent to New Zealand. Another decision is made regarding the mode of transport: by sea or by air. If by sea, the fee is calculated according to sea freight rules. If by air, the fee is calculated according to air freight rules. In both cases, an email detailing the fee is sent to the accountant.
 The accountant then generates an invoice and sends a message to the customer. Upon receiving payment, the accountant notifies the China Warehouse that the order is ready to ship. The China Warehouse repackages the parcels and decides again on the mode of transport: by sea or by air. If by sea, the parcels are put into a container; if by air, they are placed on a pallet.
 The parcels are then sent to the agent freight company warehouse, and a notification is sent to the New Zealand operation team. The New Zealand operation team prepares the clearance document and sends it to New Zealand customs. If the parcel is approved by customs, the New Zealand operation team receives confirmation to release the parcels and dispatches them to the customer's address, completing the order. If not approved, the customer is notified, and the parcel is discarded, ending the process with the order declined.</t>
-  </si>
-  <si>
-    <t>e2fd6ab82aa74bce9c6fa852e9b17f68</t>
   </si>
   <si>
     <t>The process begins with the Production Designer initiating the task of informing the Purchasing Officer that a component is required. Once informed, the Purchasing Officer checks the availability of the stock.
@@ -914,9 +1723,6 @@
 The process concludes with the Production Planning Manager either stopping or continuing production based on the outcomes of the decision points.</t>
   </si>
   <si>
-    <t>ce5eea23801144bbafcfe5bc8539c76a</t>
-  </si>
-  <si>
     <t>The process begins when a student receives an email about their eligibility to graduate. The student must then decide whether they intend to graduate. If the student chooses not to graduate, they are removed from the list, and the process ends for them.
 If the student decides to graduate, they must declare their intent to graduate. Once this declaration is made, the registrar pulls audits from the eDDS system. After obtaining the audits, the registrar sends graduation verification to the relevant schools.
 The program chair receives the verification form and completes it. Once completed, the form is returned to the registrar. At this point, the registrar checks if the graduation is approved. If the graduation is approved, the registrar updates the Yellow List, and the process concludes with the commencement.
@@ -924,42 +1730,27 @@
 If the requirements are met, the student updates the registrar. The registrar then updates the Yellow List, leading to the commencement, which marks the end of the process.</t>
   </si>
   <si>
-    <t>a06503d2a935460f930219a268165a14</t>
-  </si>
-  <si>
     <t>The process begins when a customer approaches the Fly-High Kiosk to initiate a check-in request. The first step involves the kiosk scanning the customer's online ticket. Once the ticket is scanned, the kiosk prompts the customer to confirm their name and flight number.
 At this point, the process reaches a decision point. If the customer indicates that the details are incorrect, the kiosk advises them to proceed to the counter for assistance. If the details are correct, the customer clicks a button to confirm this. If no information is received from the customer, the kiosk remains inactive for five minutes and then displays a message indicating that the process was not fulfilled.
 If the customer confirms that the flight details are correct, the process continues to another decision point regarding luggage. If the customer has luggage to check in, they confirm the number of items at the kiosk. The kiosk then prints baggage tags and advises the customer to proceed to the bag-drop area. The customer takes the baggage tags and their luggage to the bag-drop, completing the check-in process for their luggage.
 If the customer does not have any luggage to check in, they confirm this at the kiosk. The kiosk then advises the customer to proceed directly to the security check, concluding the check-in process for customers without luggage.</t>
   </si>
   <si>
-    <t>c112d84b30bb4ea4beb8f319c4eabada</t>
-  </si>
-  <si>
     <t>The process begins with the ACME Warehouse initiating the resupply cycle. The first task is to check the inventory level. If the inventory is at or below the minimum required level, the process continues to create a purchase order. If the inventory is above the minimum level, the process ends.
 When a purchase order is created, it is then reviewed. During the review, there are two possible outcomes: the purchase order can be approved or rejected. If the purchase order is rejected, it is sent back for rework, after which it is reviewed again. If the purchase order is approved, the next step is to reserve funds for the purchase.
 Once the funds are reserved, the purchase order is sent to the supplier. After sending the purchase order, two tasks occur simultaneously: receiving the invoice and receiving the packaging slip. Both tasks lead to recording the information.
 After recording the information, the reserved funds are released, and payment is issued to the supplier. This marks the end of the process.</t>
   </si>
   <si>
-    <t>9ddec87747bf4637b51924e14ca31107</t>
-  </si>
-  <si>
     <t>The process begins when a customer submits a loan application. Once the application is received, a clerk checks it for completeness. If the application is incomplete, it is returned to the customer for completion. If the application is complete, the clerk proceeds to check the customer's credit history.
 After the credit history is checked, a loan officer assesses the loan application. At this point, there are two possible outcomes. If the credit is denied, the customer is notified of the decision. Following this notification, there is a possibility for the customer to request a review of the decision. If a review is requested, the process loops back to the loan assessment by the loan officer. If no review is requested, the loan is considered processed, and the process ends.
 If the credit is extended, a packet containing the offer is sent to the customer. Once the packet is sent, the loan is considered processed, and the process concludes.</t>
-  </si>
-  <si>
-    <t>552fceee752c4d9988ace97e9463f344</t>
   </si>
   <si>
     <t>The airport check-in process begins with the passenger deciding how they would like to check in. There are two options available: online check-in or in-person check-in.
 If the passenger chooses online check-in, they must submit and verify their documents online. Once this is completed, they receive their boarding pass. After obtaining the boarding pass, the passenger proceeds to the airport. Upon arrival at the airport, the passenger must determine if they have any luggage. If they do not have luggage, they proceed directly to the security screening of the passenger. If they have luggage, the luggage undergoes a security screening before the passenger proceeds to the security screening.
 If the passenger opts for in-person check-in, they go to the appropriate check-in desk at the airport. At this point, they must decide if they have any luggage. If they do not have luggage, they proceed to document verification. After verifying their documents, they receive their boarding pass. If they have luggage, the luggage undergoes a security check before the passenger proceeds to document verification and receives their boarding pass.
 After receiving the boarding pass, regardless of the check-in method, the passenger undergoes security screening. Following the security screening, the passenger proceeds to the appropriate gate. Finally, the passenger boards the plane, concluding the check-in process.</t>
-  </si>
-  <si>
-    <t>b8475caa0a3f4fe7a1873247964f8a5a</t>
   </si>
   <si>
     <t>The process begins when the Supply Chain Department receives a request to issue materials. The department then navigates to the goods issue section. Once there, they click on the goods issue option.
@@ -970,16 +1761,10 @@
 Following the posting of the goods issue, the ERP System generates a document number. The process concludes with the materials being issued. Additionally, a production order is associated with the goods issue posting.</t>
   </si>
   <si>
-    <t>8cf7ace8e12f4f29acb30bb9910b53a4</t>
-  </si>
-  <si>
     <t>The process begins with the staff from another department identifying the need to make a purchase. They start by selecting a sub-module relevant to their needs. Once the sub-module is selected, they reach a decision point where they must choose one of three paths: creating a Material Request (MR), a Bill of Materials (BOM), or a Purchase Request (PR).
 If the decision is to create a PR, the staff enters the PR details and then submits the PR. The Purchase Manager retrieves the submitted PR and reviews it. After reviewing, the Purchase Manager decides whether to approve it. If approved, the Purchase Manager completes the PR, and the process ends. If not approved, the Purchase Manager sends it back to the staff with the reason for rejection, and the process ends there.
 If the decision is to create a BOM, a Product Engineer enters the BOM details and submits it. Once submitted, the process successfully concludes with the creation of the BOM.
 If the decision is to create an MR, the staff enters the MR details and submits it. The Purchase Manager retrieves and reviews the MR, following the same approval process as with the PR. If approved, the Purchase Manager completes the MR, and the process ends. If not approved, it is sent back to the staff with the reason for rejection, concluding the process.</t>
-  </si>
-  <si>
-    <t>c55ede3b5d854c99bcd96dacf4b0c1b9</t>
   </si>
   <si>
     <t>The business process begins with checking the inventory. Once the inventory is checked, an order is created. After creating the order, it is reviewed. 
@@ -991,25 +1776,16 @@
 Finally, the process concludes after the payment is issued.</t>
   </si>
   <si>
-    <t>080284b2437741a89d278a23b13b51ce</t>
-  </si>
-  <si>
     <t>The process begins with the candidate sending a registration form. Once the form is sent, the election commission receives the applicant form. The election cell then determines the applicant's qualifications.
 At this point, a decision is made by the election cell. If the applicant is not qualified, the election cell detects this and informs the applicant of the reasons for their disqualification. This concludes the process for unqualified applicants.
 If the applicant is qualified, the election cell detects this and notifies the election authority. The election commission then thoroughly reviews the applications. If any application is found to be faulty, the election commission notifies the relevant parties.
 Following this, the election cell generates the outcomes. These outcomes are processed in parallel. One branch involves the election cell publishing the outcome online. Simultaneously, the election cell forwards the outcome to the applicant. Both branches lead to the conclusion of the process.</t>
   </si>
   <si>
-    <t>365f66984b454c18a8d3438487cda5a9</t>
-  </si>
-  <si>
     <t>The hospital procurement process begins with the hospital labeling RFID tags for existing products. Once the products are labeled, the hospital automatically tracks and manages these items. Following this, the hospital conducts an assessment of order requirements. During this task, details of suppliers are referenced.
 Next, the process reaches a decision point. If items are out of stock, the E-Procurement system automatically calculates the forecasted cost and creates a new order. The system then checks long-term suppliers using RFID tags and updates the inventory automatically. Another decision point follows: if items are in stock, the process proceeds to email suppliers. If items are out of stock, the E-Procurement system selects suppliers based on business rules, confirms the new supplier, and cancels the old order before emailing suppliers.
 If the items are in stock after the inventory update, the process continues with the supplier receiving the order along with a Goods Received Note (GRN) form. The E-Procurement system then uses RFID tags to track items and checks if they meet product requirements. If they do, the supplier is contacted to solve any problems. If they do not meet requirements, the system adds items to the system and emails a receipt of e-invoices.
 The process then checks whether e-invoices match with the Purchase Order (PO) and GRN. If there are errors, the E-Procurement system contacts suppliers to resolve them. If there are no errors, the supplier is paid, marking the end of the process. Throughout the process, various documents such as invitations to tender and e-invoices are generated and referenced.</t>
-  </si>
-  <si>
-    <t>381801f4fae447889fb0ea36001c27be</t>
   </si>
   <si>
     <t>The process begins when a customer arrives. The first step involves the customer selecting a coffee or pastry. Once the selection is made, the customer proceeds to order the chosen coffee or pastry.
@@ -1019,25 +1795,16 @@
 The process concludes once the payment is completed and the customer receives their order and receipt.</t>
   </si>
   <si>
-    <t>b154d4c8fa2a4677b37d02f8108b92bd</t>
-  </si>
-  <si>
     <t>The process begins when the accounting department receives an online order. The first step involves the accounting department sending an invoice to the business unit. Once the business unit receives the invoice, they proceed to order the goods or services.
 After placing the order, the business unit encounters a decision point. They must decide whether to approve the order or not. If the order is approved, the business unit sends the invoice back to the accounting department. If the order is not approved, the business unit also sends the invoice back to the accounting department, but with a note indicating the lack of approval.
 Upon receiving the invoice, the accounting department staff acknowledges receipt and fills in the necessary accounting information on the invoice. Following this, the accounting department pays the supplier and simultaneously updates the accounts payable records.
 The process then reaches another decision point within the accounting department. They must determine if the payment and updates are approved. If approved, the process concludes with the accounting department marking the transaction as approved. If not approved, the accounting department informs the business unit, who then informs the supplier about the situation, bringing the process to an end.</t>
   </si>
   <si>
-    <t>ffd1d4e5b137499f8bbd7be5e113887b</t>
-  </si>
-  <si>
     <t>The process begins when the information system of the company receives an order. Once the order is received, the information system sends a confirmation email to the customer. After sending the confirmation email, the order fulfillment department takes over to pack the product.
 Following the packing of the product, the order fulfillment department checks if bubble packaging is required. This leads to a decision point. If bubble packaging is needed, the order fulfillment department adds bubble protection to the package. If it is not needed, the process skips this step.
 After the decision regarding bubble packaging, the product is passed on to the warehouse staff. The warehouse department then checks the type of courier required for shipping. This leads to another decision point. If a normal courier is chosen, the warehouse department fills in the post label. If a fast courier is selected, the warehouse department prepares the necessary courier paperwork and gets a quote from the contracted courier.
 Regardless of the courier type, the next step involves combining the post paperwork with the packaged goods. Finally, the order is prepared for the warehouse staff to pick up, marking the end of the process.</t>
-  </si>
-  <si>
-    <t>257ede1b23f94c839202dc36f26473d8</t>
   </si>
   <si>
     <t>The process begins when the sales consultant receives the documents for a car rental request. The sales consultant then validates these documents. If the documents are valid, the process continues; if they are invalid, the process ends.
@@ -1047,16 +1814,10 @@
 Later, the returning person returns the car and signs the return papers. Once the return papers are signed, the process is considered fulfilled and comes to an end.</t>
   </si>
   <si>
-    <t>0fa69773765e45a68b15a31c52f9dc36</t>
-  </si>
-  <si>
     <t>The process begins with the start of the season. The first task is to analyze the field, which is carried out by a designated actor. After analyzing the field, a decision is made to determine if the field is ready. If the field is not ready, the task of pruning the tree is performed, followed by applying chemicals. Once these tasks are completed, the process loops back to analyzing the field again.
 If the field is ready, the next step is to remove small fruits. After removing the small fruits, the fruits are collected. Following the collection, the safety standards are checked. If the safety standards are not met, the workers are consulted, and the process returns to the task of removing small fruits.
 If the safety standards are met, the fruits are calibrated. After calibration, the quality of the fruits is controlled. Once the quality control is completed, a decision is made regarding where to export the fruits. If the decision is to package the fruits for national distribution, the fruits are packaged accordingly, and sellers are contacted to complete the process.
 If the decision is to package the fruits for international distribution, the fruits are packaged for international delivery. After packaging, the order is delivered, marking the end of the process.</t>
-  </si>
-  <si>
-    <t>2a8f497c99b345b68f74158e8e35e9a4</t>
   </si>
   <si>
     <t>The process begins with the passenger at home initiating the journey. The passenger has two options for checking in: using a mobile check-in or a web check-in.
@@ -1084,9 +1845,6 @@
 After passing through security, the passenger heads to the boarding gate for departure. This marks the end of the process, and the passenger is ready to board their flight.</t>
   </si>
   <si>
-    <t>10ec5606971a42bba3dbf7b7c3eda017</t>
-  </si>
-  <si>
     <t>The process begins when a truck arrives at the goods entry point. The goods entry team is responsible for this initial step.
 Next, the goods entry team assigns an unloading location for the truck. Once the location is assigned, the team proceeds to unload the truck.
 After unloading, the goods entry team checks the goods to ensure everything is complete. Following this, the quality control team takes over to perform a sample control of the goods.
@@ -1096,17 +1854,11 @@
 If the goods have not been picked up, the goods entry team scratches the goods, which also leads to the end of the process with the goods being rejected.</t>
   </si>
   <si>
-    <t>0eb6dbd2f0ae4339b3bcaa58648ddbfc</t>
-  </si>
-  <si>
     <t>The process begins with the front office receiving an order. Once the order is received, a front office employee prepares the product specification. After the specification is ready, the front office checks if there are enough materials in the inventory.
 Next, the process splits into two parallel tasks handled by the manufacturing department. One task involves a specialist preparing the active substance, while the other involves a technician preparing the basis of the product. Both tasks proceed independently and simultaneously.
 For the active substance preparation, after the specialist completes this task, they update the inventory. Following the inventory update, the specialist prepares a sample of the product. This sample is then tested by the specialist. If the test fails, the process loops back to the preparation of the active substance. If the test is successful, the specialist prepares the product for the customer.
 Simultaneously, for the basis preparation, after the technician completes this task, they also update the inventory. The basis is then tested, and the process waits for the result. If the result is not satisfactory, the process loops back to the preparation of the basis. If the result is satisfactory, the process continues to the preparation of the sample.
 Once both the active substance and the basis are successfully prepared and tested, the manufacturing department hands over the product to the front office. The front office then prepares the package for the customer. Finally, the process concludes with the completion of the package preparation.</t>
-  </si>
-  <si>
-    <t>99045ae01e524bfbb067dae6996637d3</t>
   </si>
   <si>
     <t>The process begins with the execution of a project. Once the project is initiated, several tasks are carried out simultaneously.
@@ -1118,17 +1870,11 @@
 All these tasks, once completed, lead to the conclusion of the project.</t>
   </si>
   <si>
-    <t>4b69ca8c3ed1435a92b24d9e0d7d5086</t>
-  </si>
-  <si>
     <t>The process begins when a tax consultant receives documents from a client. The tax consultant then checks the completeness of these documents. If the documents are complete, the tax consultant sends them to their assistant. The assistant receives the documents and familiarizes themselves with them.
 At this point, the assistant decides whether they have any questions. If there are no questions, the assistant proceeds to create the tax declaration and sends it to the IRS. The IRS receives the tax declaration, processes it, and creates the client's tax return. The IRS then sends the tax return back to the assistant.
 Upon receiving the tax return, the assistant checks it. After checking, two tasks occur simultaneously: the assistant makes a copy of the tax return for the tax consulting office and sends the tax return to the client. This marks the end of the process.
 If the assistant has questions after familiarizing themselves with the documents, they note these questions on a pad and send them to the tax consultant. The tax consultant answers the questions and sends the responses back to the assistant, who then continues with the process of creating the tax declaration.
 If the initial check by the tax consultant finds that the documents are incomplete, they create a list of missing documents and send a letter to the client. The process then waits for the client's response before returning to the step of checking the completeness of the documents.</t>
-  </si>
-  <si>
-    <t>8010792df10c43dfab130131e36744d6</t>
   </si>
   <si>
     <t>The process begins when a customer identifies the need for a locker. The customer then searches for locker providers. Upon finding potential providers, the customer contacts our company. Our company responds by identifying the client's needs and submitting offers.
@@ -1139,9 +1885,6 @@
 Simultaneously, our company places a manufacturing order. HansaAB AS, a partner company, handles the locker manufacturing, assembly, and delivery. Finally, HansaAB AS installs the locker. The process concludes with the customer's acceptance testing of the installed locker and software.</t>
   </si>
   <si>
-    <t>f186ed179743406583486f9665f9b14a</t>
-  </si>
-  <si>
     <t>The process begins when a person submits a request for legal help. This request is then reviewed by a legal assistant to determine the legal requirements associated with it. At this point, the process reaches a decision point where the legal assistant evaluates whether the request for help is possible.
 If the request is deemed not possible, the legal assistant proceeds to refuse the legal help request. This refusal is then communicated to the relevant parties.
 If the request is possible, the legal assistant identifies the specific requirements and provides a reference for the customer. Following this, the legal assistant outlines the necessities of the request and prepares a statement of legal facts. An application bill is then identified, and the legal help documents are signed.
@@ -1149,17 +1892,11 @@
 If the request is not complete, the legal authority refuses the legal help request. If the request is complete, the legal authority proceeds with making a decision. The result of this decision is then shared by the legal assistant, marking the end of the process.</t>
   </si>
   <si>
-    <t>e64bd459cfd4440fabc1a78bc921f073</t>
-  </si>
-  <si>
     <t>The process begins when a customer places an order. The first step involves gathering orders from all sales channels. Once all orders are collected, the next task is to check the inventory to ensure that the items are available.
 At this point, a decision is made based on the inventory check. If the stock is sufficient, the order information is sent to the warehouse. The warehouse then picks the items needed for the order. After picking the items, they are parked as parcels.
 Following this, the process splits into four simultaneous tasks. The first task is to load the parcels onto a truck. The second task involves giving delivery instructions to the transporter. The third task is to update the shipping status. The fourth task is to adjust the stock level to reflect the items that have been picked and shipped.
 If the initial inventory check reveals that the stock is insufficient, an inventory order is created. This order is then sent to a supplier. Another decision point occurs here: if the supplier can fulfill the request, the inventory is sent to the warehouse, and the process continues with picking the items. If the supplier cannot fulfill the request, another supplier is chosen, and the order is sent again.
 The process concludes when all tasks are completed, and the order is shipped.</t>
-  </si>
-  <si>
-    <t>85fc17ee78494a77bab34650f7c5566d</t>
   </si>
   <si>
     <t>The process begins when an employee submits a travel request. The first step is to determine if the travel advance requested is under the specified limit. If the advance is not under the limit, the employee must modify the travel request. If the advance is under the limit, the request moves forward for validation by a manager.
@@ -1170,9 +1907,6 @@
 If at any point the booking validation is not completed within seven days, the request is automatically rejected.</t>
   </si>
   <si>
-    <t>6e22c064ee534815a0594cb2cdf5e31e</t>
-  </si>
-  <si>
     <t>The process begins with a data collector needing to determine the verified default date. The data collector starts by copying the customer ID from a template. Next, they proceed to the Archives II - KUUA to continue the process. Once there, the data collector pastes the ID into the search function to find relevant documents.
 After pasting the ID, the data collector opens all documents found related to the customer. The next step involves searching for the document with the earliest date when the risk grade dropped to zero.
 At this point, the process branches based on whether a date is found. If a date is found, the data collector uses the exact date when the risk grade goes from one to zero as the verified default date. If a date is not found, the data collector checks the CMS 12-months overview.
@@ -1181,9 +1915,6 @@
 The process concludes with the verified default date being determined.</t>
   </si>
   <si>
-    <t>a708b49aa0dd41cc98a263d1c95e1403</t>
-  </si>
-  <si>
     <t>The process begins when a help request is received by the Level 1 Support Staff at the IT Help Desk. The first task for the Level 1 Support Staff is to check if the solution to the problem is already known. 
 At this point, there is a decision to be made. If the solution is found, the Level 1 Support Staff proceeds to solve the problem and then informs the customer that the problem is solved, concluding the process.
 If the solution is unknown, the Level 1 Support Staff forwards the request to the Level 2 Support Staff. The Level 2 Support Staff receives the request and evaluates it. After evaluation, they assign a priority level to the request and enter this information into the job tracking system. The job tracking system then assigns the request to a Level 2 Support Staff member.
@@ -1192,9 +1923,6 @@
 Throughout this process, communication between the support staff and the customer is maintained to ensure the problem is resolved efficiently.</t>
   </si>
   <si>
-    <t>82ae37ec8d4244d48283ea0ba54f07d7</t>
-  </si>
-  <si>
     <t>The process begins with a coordinator or intern checking for any new clients or changes. If there are new clients or changes, the coordinator or intern inputs the client information into the database. Once this is done, or if there are no new clients or changes, the coordinator or intern prints all weekly lists, bag tags, and delivery instructions.
 Next, the shift captain collects food. After collecting the food, the shift captain plans the meals. Once the meals are planned, the shift captain cooks the food. After cooking, the shift captain packages the meals.
 Following the packaging, the shift captain drives to the client's home. At this point, there is a decision to be made: if the client is home, the shift captain delivers the meal and food. If the client is not home, the shift captain hangs a door tag.
@@ -1202,9 +1930,6 @@
 Finally, the process concludes with the coordinator or intern updating the reports.</t>
   </si>
   <si>
-    <t>1f19f57766fe482499fff95b4b5ee172</t>
-  </si>
-  <si>
     <t>The process begins with the PR department initiating the assessment of the company's needs. Once the company's needs are assessed, the process moves forward to a point where two tasks are carried out simultaneously. The PR department assesses the market situation, including offers and feelings, while also assessing customers' feelings and needs.
 After these assessments, the PR department proceeds to create or revise the advertising plan. Following this, the PR department selects the target audience for the advertising efforts.
 At this stage, a decision is made regarding the type of customers to target. If the target is current VIP customers, the PR department creates personalized offers. If the target is current customers, the PR department creates general offers. If the target is potential customers, the PR department creates commercials and advertisements.
@@ -1212,25 +1937,16 @@
 Finally, the process concludes with the PR department ending the monitoring phase, marking the end of the process.</t>
   </si>
   <si>
-    <t>bbc0fcd2383844fe8ef1bd70502843b5</t>
-  </si>
-  <si>
     <t>The process begins with the Senior Risk Manager initiating the procedure. The first task involves the Senior Risk Manager performing an automated BKR check. Once this check is completed, the Senior Risk Manager proceeds to perform an automated Jane Doe check. Following this, the Senior Risk Manager conducts a manual credibility check. After the manual check, the Senior Risk Manager confirms the results of the credibility check.
 At this point, a decision is made based on the outcome of the credibility assessment. If the assessment is rejected, the Administrator sends a rejection letter, concluding this branch of the process. If the assessment is accepted, the Customer Responsible contacts the client to gather additional information. After obtaining the necessary information, the Customer Responsible creates a loan offer and subsequently sends it to the client.
 Once the loan offer is sent, there is a decision point. If the client accepts the offer, the Administrator receives the accepted offer. The Administrator then sends a welcome letter to the client. Following this, the Finance Manager activates the loan application and executes the initial payment. Finally, the Administrator returns the documents to the client, marking the end of this branch of the process.
 If there is no immediate response from the client after the loan offer is sent, a timer is set for one hour. After this period, the Customer Responsible reminds the client. This reminder loops back to the decision point regarding the client's response to the loan offer. The process continues until a response is received, leading to either the acceptance or rejection path.</t>
   </si>
   <si>
-    <t>6eac3421b2d448748b5097eb336fda1f</t>
-  </si>
-  <si>
     <t>The process begins when a client identifies a need for help. The client initiates the process by calling the help desk. The IT Help Desk at Level 1 receives the request and gathers the necessary information.
 Next, the IT Help Desk at Level 1 determines whether the request is known. If the request is known, the IT Help Desk at Level 1 sends the developed resolution to the client. If the request is not known, the IT Help Desk at Level 1 emails the request to Level 2 for further assistance.
 Upon receiving the request, the IT Help Desk at Level 2 conducts research and evaluates the situation. After developing a resolution, they send it back to Level 1. The IT Help Desk at Level 1 then receives the developed resolution and sends it to the client.
 The client tests the resolution to see if it resolves the issue. After testing, the client notifies the outcome via email. The IT Help Desk at Level 1 checks if the issue is fixed. If the issue is resolved, the process is marked as complete. If the issue is not resolved, the IT Help Desk at Level 1 sends the request for further action, looping back to the point where Level 2 receives the request for additional evaluation and resolution development. The process continues until the issue is resolved and marked as complete.</t>
-  </si>
-  <si>
-    <t>a128b8b197314ab3a26fa23f68daa8ee</t>
   </si>
   <si>
     <t>The process begins with the customer initiating a request for help. The customer reaches out to the organization to describe the problem they are experiencing.
@@ -1241,9 +1957,6 @@
 Finally, the customer receives the answer from the organization, marking the end of the process.</t>
   </si>
   <si>
-    <t>e13ef73f335d49a8a7af3fe561737987</t>
-  </si>
-  <si>
     <t>The process begins with a medic examining a patient. After the examination, a decision is made regarding the patient's health status. If the patient is deemed healthy, an exam form is created, and the patient is released.
 If the patient is not healthy, the process continues with the medic making an exam. Following this, a treatment order is created, and then a petition form is prepared. The patient is then informed about the risks involved.
 At this point, the patient must decide whether to agree to the proposed actions. If the patient does not agree, they are released from the process. If the patient agrees, a delegate arranges an appointment for further procedures.
@@ -1251,25 +1964,16 @@
 After the sample analysis, the results are validated. Based on the validated results, a diagnostic is made. Finally, a therapy is prescribed, concluding the process.</t>
   </si>
   <si>
-    <t>b446c2a196c14b55957c421adab5638e</t>
-  </si>
-  <si>
     <t>The process begins when an employee makes a product purchase. Following this, the employee is responsible for filling out an expense claim. Once the claim is filled out, the employee submits the expense claim form.
 Next, the system checks if the employee has an existing account. At this point, there is a decision to be made: if the employee has an account, the process continues to the financial employee for a report review. If the employee does not have an account, they must create a new account before proceeding to the report review.
 After the report is reviewed by the financial employee, the system evaluates the amount of the claim. If the claim is less than $200, the system automatically approves it. If the claim exceeds $200, a supervisor reviews the approval of the claim.
 The supervisor's review leads to another decision point: if the claim approval is accepted, the system deposits the reimbursement, and the process concludes with the reimbursement claim being completed. If the claim is rejected, the supervisor formally rejects the reimbursement, and the employee receives an email notification about the rejection. The process then ends with the reimbursement claim being completed.</t>
   </si>
   <si>
-    <t>c486e638c1de49de9b20bd38e8f81d49</t>
-  </si>
-  <si>
     <t>The process begins when there is a need for employee training. The first step involves the supervisor selecting a vendor for the training. Once the vendor is chosen, the supervisor fills out a training request form that needs to be approved.
 After the form is completed, two tasks occur simultaneously. The director checks the budget for the training, and the department director evaluates the training itself. These tasks are independent and happen at the same time.
 Once both tasks are completed, a decision is made based on the outcomes. If both the budget check and the training evaluation are satisfactory, the director approves the training. The supervisor is then notified of this approval, and they proceed to schedule the training. This marks the end of the process.
 However, if either the budget check or the training evaluation is not satisfactory, the director does not approve the training. In this case, the supervisor is notified of the disapproval, and they are informed of the reasons for the denial. This also concludes the process.</t>
-  </si>
-  <si>
-    <t>afce9b024b3c4172adcb4f6b1757335f</t>
   </si>
   <si>
     <t>The process begins with a pharmacist reviewing the situation. After this initial review, the pharmacist encounters a decision point. At this decision point, there are two possible paths:
@@ -1283,9 +1987,6 @@
 Finally, the process concludes with the application being filled, marking the end of the pharmacist's tasks.</t>
   </si>
   <si>
-    <t>42edc42c2e6c415c87b6dec2b2d1c91f</t>
-  </si>
-  <si>
     <t>The process begins when a client identifies the need for a loan. The client then submits a loan application. At this point, a decision is made on whether the application is submitted online. If the application is not submitted online, the client talks to a loan officer directly. If the application is submitted online, the client proceeds to submit the online application.
 Once the online application is submitted, it is captured by a loan officer at ACME Bank. The loan officer uses the Mortgage Orientation System to assist in capturing the application details. After capturing the application, the loan officer sends an application receipt to the client.
 The loan officer then receives the application and creates a customer record, utilizing the CRM Platform for this task. Following this, the lending operations team at ACME Bank performs a background check on the applicant.
@@ -1294,34 +1995,22 @@
 Another decision point occurs to determine if the application is approved. If the application is not approved, the process follows the same path as a legal rejection, with the client receiving a rejection letter. If the application is approved, the loan officer accepts the loan application, and the client receives a letter informing them of the approval. This concludes the process with the application being accepted.</t>
   </si>
   <si>
-    <t>39b43a25682f4a69aebe0584ab703040</t>
-  </si>
-  <si>
     <t>The process begins with an Admin starting the procedure. The Admin then spends 30 minutes initiating a change request. Following this, the Admin must determine whether the change is major or minor. If the change is considered minor, which happens 70% of the time, a Draftsman takes over to make the necessary changes, a task that takes 2 hours. After making the changes, the Draftsman initiates an approval process, which takes 1 hour. A Manager then conducts the approval process, which can take between 20 to 40 minutes.
 Once the approval process is complete, the Draftsman checks if the changes are accepted. If accepted, which occurs 95% of the time, the Draftsman spends 1 hour and 30 minutes checking the changes into the PLM system, concluding this path of the process. If the changes are not accepted, which happens 5% of the time, the process ends without further action.
 If the change is determined to be major, which occurs 30% of the time, Engineers spend approximately 8 hours analyzing and making recommendations. The time can vary by 25%. After the analysis, a Draftsman initiates another approval process, taking 1 hour. The Manager then conducts this approval process, which can take between 45 minutes to 1 hour and 15 minutes.
 Following the approval, the Manager checks if the changes are accepted. If accepted, which happens 60% of the time, the Draftsman documents or updates the changes, a task that takes 8 hours. After documentation, the Draftsman spends 1 hour and 30 minutes checking the changes into the PLM system, concluding this path of the process. If the changes are not accepted, which occurs 40% of the time, the process ends without further action.</t>
   </si>
   <si>
-    <t>4fde031ee7a14df6a5f90accda243051</t>
-  </si>
-  <si>
     <t>The process begins with a Level 1 Employee initiating a client call. After the call, the same employee checks the client's request. At this point, a decision is made: if the request is solvable, the Level 1 Employee proceeds to resolve the issue. If there are no immediate resolutions, the request is forwarded to a Level 2 Employee.
 When the request is forwarded, the Level 2 Employee receives it and evaluates the situation. They then create a priority level for the request and conduct research to understand the problem better. Following this, the Level 2 Employee creates a resolution and sends it back to the Level 1 Employee.
 The Level 1 Employee then reverts back to the client with the resolution. After this, they check the client's feedback. If the issue is resolved according to the client's feedback, the process is marked as complete. If the issue is not resolved, the request is forwarded again to a Level 2 Employee for further evaluation.
 Throughout this process, communication with the client is maintained, ensuring that the client is kept informed and their feedback is considered. The process concludes when the issue is resolved and marked as complete by the Level 1 Employee.</t>
   </si>
   <si>
-    <t>8e5b81a49145488693e735e32eb48da5</t>
-  </si>
-  <si>
     <t>The process begins when a user decides to withdraw cash. The first step involves opening the Sonect feature on the Point of Sale (POS) system. Once this feature is activated, two tasks occur simultaneously.
 The first task is to open the barcode scanner. After the scanner is opened, the cash till is also opened. Following this, a confirmation is obtained, and then the cash is handed out to the user. This sequence of actions concludes the process.
 Simultaneously, the second task involves asking the user for the barcode. The user then generates or displays the barcode on their side. Once the barcode is available, it is scanned. After scanning, the amount to be withdrawn is verified. The correct amount of cash is then prepared. Finally, the request is confirmed through Strong Customer Authentication (SCA), and the process loops back to obtaining confirmation before handing out the cash.
 The process ends once the cash is successfully handed out to the user.</t>
-  </si>
-  <si>
-    <t>3fde31e153584d039958ab3af001f339</t>
   </si>
   <si>
     <t>The process begins when a course request is received. The first task is to book a room, which is handled by the responsible person. Once the room is booked, the next step is to create an account, which is also managed by the designated individual.
@@ -1329,9 +2018,6 @@
 Once these tasks are completed, the process continues with closing the registrations. After closing the registrations, a decision point is reached. If there are insufficient registrations, the course is canceled. The responsible person then cancels the scheduled course and notifies the registered participants, marking the end of the process with the course being canceled.
 If there are sufficient registrations, the process moves forward to manage payments. After managing payments, the process again splits into three parallel tasks. The first task is to print name badges. The second task is to create a blackboard website. The third task is to arrange catering. These tasks are handled by the respective team members.
 Once these tasks are completed, the final step is to deliver the course. After the course is delivered, the process concludes with the course being successfully delivered.</t>
-  </si>
-  <si>
-    <t>e4152a44e9774d1e994b822c3aef83df</t>
   </si>
   <si>
     <t>The process begins with the Hackathon Team planning a hackathon. Once the planning is complete, the team prepares for the hackathon. After preparation, the doors are opened to welcome guests. The Hackathon Team then welcomes the guests and briefs them about the event.
@@ -1343,9 +2029,6 @@
 Meanwhile, the feedback collection concludes with a debriefing session by the Hackathon Team.</t>
   </si>
   <si>
-    <t>c811897bb46e487da757021bced7119d</t>
-  </si>
-  <si>
     <t>The process begins on March 1st, initiated by the management team of ACME Inc. The first task involves the management specifying the budget for an upcoming event. Once the budget is set, the management team proceeds to establish a date for the event. Following this, the marketing team takes over to specify the event schedule.
 Next, the marketing team is responsible for finding a suitable location for the event. Once a location is identified, they proceed to book it. After booking the location, the process splits into two parallel tasks. The marketing team simultaneously books the catering services and the DJ for the event.
 Once both the catering and DJ are booked, the marketing team enters the final costs into the system. This information is then sent to the management team, who receives the plan and budget details. The management team then decides on the event's placement and checks the plan against the requirements.
@@ -1354,17 +2037,11 @@
 If the plan is not approved, the marketing team cancels the booking, and the process concludes with the decision that the celebration will not be approved.</t>
   </si>
   <si>
-    <t>bd01e5bdb1714f83a8d42d4b135186f9</t>
-  </si>
-  <si>
     <t>The process begins when the Wedding Planner receives a cake order. The Wedding Planner then sends the client's requirements to Jane Doe. Jane Doe analyzes these requirements and prepares a sample. Once the sample is ready, the Assistant receives it and sends it to the client for approval.
 At this point, there is a decision to be made: if the client approves the sample, the process continues; if not, the requirements are sent back to Jane Doe for further analysis and sample preparation.
 If the sample is approved, the process splits into three parallel tasks. The Wedding Planner designs the cake, decides on the color scheme, and the Assistant emails guests to gather an allergy list. After these tasks are completed, the Assistant finalizes the cake plan and sends it to Jane Doe.
 The process then splits again into two parallel tasks. Jane Doe prepares the cake batter and creates the invoice for the cake. The invoice is documented as an output. Jane Doe then bakes the cake in the oven, prepares the cake filling, assembles the cake, and decorates it.
 After the cake is decorated, the Wedding Planner performs a quality check. Following the quality check, the Assistant arranges for the cake's delivery, marking the end of the process with the cake being delivered to the client.</t>
-  </si>
-  <si>
-    <t>415ebec39c364b5f90299aed9b11bb98</t>
   </si>
   <si>
     <t>The process begins when a customer hands a prescription to the pharmacist. The pharmacist receives the prescription and then asks the customer for their Medicare card. Once the card is provided, the pharmacist matches it with the prescription details.
@@ -1373,9 +2050,6 @@
 The pharmacist then prints labels needed to fill the prescription and obtains the medicine from the shelf. The pharmacist checks if the medicine is available. If it is not available, the pharmacist confirms the stock status in the inventory system. If the medicine is out of stock, the pharmacist informs the customer, and the process ends without the customer receiving the medicine. If the medicine is in stock, the pharmacist locates it.
 Once the medicine is available, the pharmacist scans the medicine's barcode and sticks the printed labels on the medicine box. The pharmacist also prints drug use instructions, which are provided to the customer along with the medicine.
 The pharmacist verifies the customer's medical conditions and provides a consultation on drug consumption. Afterward, the pharmacist hands over the medicine to the customer, who then proceeds to payment. The process concludes with the medicine being dispensed to the customer.</t>
-  </si>
-  <si>
-    <t>1be181ba148f4caab708fab443332493</t>
   </si>
   <si>
     <t>The process begins with the IT Centre receiving the requirement. Once the requirement is received, the IT Centre proceeds to analyze the market. After completing the market analysis, the IT Centre sends the analysis via email.
@@ -1387,9 +2061,6 @@
 Finally, once the strategy is successfully implemented across all online retail operations, the process concludes with the strategy being fulfilled.</t>
   </si>
   <si>
-    <t>7baeb920f88745eea8fb739bd925b455</t>
-  </si>
-  <si>
     <t>The process begins with a customer initiating the task of making a reservation. Once the reservation is made, the customer proceeds to choose their preference for the room.
 At this point, a decision is made to check if the customer's preferred room is fully booked. If the room is not fully booked, the customer can proceed to book the room. If the room is fully booked, the customer must reset their preference and check again if the new preference is fully booked. This cycle continues until a room is available.
 If a room is available, the customer can book the room. After booking, the customer needs to provide their information by typing it in. Following this, the customer must insert their card and input their password.
@@ -1398,25 +2069,16 @@
 If at any point there are no rooms available, the process ends by showing the nearest Hilton or logging out.</t>
   </si>
   <si>
-    <t>11ef1dbacfab4ed784a40315315aea76</t>
-  </si>
-  <si>
     <t>The process begins with the manager initiating the order preparation. The manager is responsible for tasting the cake, tasting the cream, and ensuring the decoration is appropriate. Once the manager has completed these tasks, a decision is made regarding the type of cake being prepared. 
 If the cake is a special cake, the cook takes over to prepare the cake. After the cake preparation, the process splits into two simultaneous tasks: baking the cake and preparing the cream. The oven bakes the cake, while the cook prepares the cream. Once both tasks are completed, the process continues with the cook making decorations and the helper spreading cream between different layers. The helper then covers the cake with frosting and adds decorations. 
 If the cake is a standard cake, the process also splits into two simultaneous tasks: the helper prepares the cake, and the cook prepares the cream. The oven bakes the cake, and once both tasks are completed, the process continues with the helper spreading cream between different layers. The helper then covers the cake with frosting and adds decorations.
 After the cake is decorated, the manager checks the quality of the finished product. If the quality is satisfactory, the manager updates the order status to 'finished.' Finally, the process concludes with the manager marking the end of the process.</t>
   </si>
   <si>
-    <t>45694a407bed4df1b789e16fc0ea5ec6</t>
-  </si>
-  <si>
     <t>The process begins with a user initiating the connection to the management system. Once connected, the stock management system reads an order from the system. The system then checks if this is the first order in stock. If it is not the first order, the stock management system contacts the wholesaler and places a reorder. If it is the first order, the system proceeds to browse the warehouse.
 After browsing, the stock management system withdraws the product from the warehouse. The system then evaluates the arrival time of the product. If the product is expected to arrive in more than 10 days, a delivery delay penalty is applied from the wholesaler. If the product arrives within 10 days, the stock management system gives the approval for the arrived product.
 Following approval, the product is registered in the management system. The user then checks if the product is ready for shipment. If it is not ready, the process loops back to reading the order from the system. If it is ready, two tasks are carried out simultaneously: the user requests a courier and packs the product.
 Once the product is packed, it is shipped for delivery. The process concludes with the successful delivery of the product.</t>
-  </si>
-  <si>
-    <t>ef4c027c3a8041f1a6939966b06ca682</t>
   </si>
   <si>
     <t>The process begins when a pharmacist receives a prescription. The pharmacist then examines the prescription to ensure its validity. If the prescription is not valid, the process ends with the prescription remaining unfilled. If the prescription is valid, the pharmacist proceeds to check the customer's details.
@@ -1424,9 +2086,6 @@
 Once the prescription details are added, the pharmacist prints the necessary labels. The pharmacist then checks if the prescribed drug is in stock. If the drug is out of stock, the pharmacist informs the customer of alternative options, and the process ends with the prescription unfilled. If the drug is in stock, the pharmacist picks up the drug.
 After picking up the drug, the pharmacist verifies that the correct drug has been picked up. If the wrong drug is picked up, the pharmacist retrieves the correct drug. Once the correct drug is confirmed, the pharmacist attaches the printed labels to the drug.
 The pharmacist then prints the Consumer Medicine Information (CMI) and prepares the prescription basket. Finally, the pharmacist provides the customer with directions for using the medication. The process concludes with the prescription being successfully filled for the patient.</t>
-  </si>
-  <si>
-    <t>9f992e72a99044318c76da9c3e88cc1d</t>
   </si>
   <si>
     <t>The process begins when Jane Doe receives a request. She starts by checking the computer. After this, she encounters a decision point where she must determine if the computer is new or used.
@@ -1436,9 +2095,6 @@
 If the computer is new, Jane Doe tags the item, adds the IP to BlueCat, and includes it in Baremetal in Ivanti. She then configures the BIOS and verifies or installs any necessary computer add-ons. Following this, she adds a description to the computer and checks for any client software requests.
 Again, if the client has software requests, Jane Doe adds the required software. If there are no requests, she activates the directory and checks for finalization. If finalized, the imaging is completed. If not, she transfers data and moves the IP in BlueCat to its previous location before completing the imaging.
 Throughout the process, Jane Doe is responsible for each task, ensuring that all steps are completed accurately and efficiently.</t>
-  </si>
-  <si>
-    <t>a990204e0055488383f86b9af9e20150</t>
   </si>
   <si>
     <t>The process begins with a passenger or traveler starting their journey at KLIA 2. The first step involves the passenger performing a self check-in. After completing the self check-in, the passenger reaches a decision point where they must choose one of three check-in methods: web check-in, mobile check-in, or kiosk check-in.
@@ -1451,9 +2107,6 @@
 After passing security screening, the passenger waits until 20 minutes before departure. At this point, they enter the boarding gate, marking the end of the process at KLIA 2.</t>
   </si>
   <si>
-    <t>644ff4ec9fd244879fd60f823763bf88</t>
-  </si>
-  <si>
     <t>The process begins with the ACME Warehouse initiating the resupply cycle. The first task is to check the current inventory. After checking the inventory, a decision is made to determine if the inventory is at or below the minimum required level.
 If the inventory is not at or below the minimum, the process ends. However, if the inventory is at or below the minimum, the ACME Warehouse proceeds to create a purchase order. Once the purchase order is created, it is reviewed. 
 Following the review, another decision is made to check if the purchase order is approved. If the purchase order is not approved, it is reworked and then reviewed again. If the purchase order is approved, the necessary funds are reserved.
@@ -1462,9 +2115,6 @@
 Simultaneously, after receiving the packing slip, it is recorded. This task also leads to the release of reserved funds and the issuance of payment to the supplier, marking the end of the process.</t>
   </si>
   <si>
-    <t>af94d71112594cefb93817d8bc844362</t>
-  </si>
-  <si>
     <t>The process begins when a formalized application is received. The first step involves conducting credit checks. If the credit check reveals an unacceptable risk, the application is rejected, and the process ends with the application being marked as rejected.
 If the credit check shows an acceptable risk, the next step is to arrange a customer reference report. Once the report is arranged, it is evaluated. If the reference report is unsatisfactory, the application is rejected, and the process concludes with the application being marked as rejected.
 If the reference report is satisfactory, the complete submission is reviewed. If the review is unsuccessful, the application is rejected, and the process ends with the application being marked as rejected.
@@ -1472,17 +2122,11 @@
 After the legal documents are prepared, and the initial loan fee is collected, an online customer profile is created. Following this, a document is sent to the loan center, marking the end of the process with the document being sent to the loan center.</t>
   </si>
   <si>
-    <t>ffe9c97d57014ec5864fb39153a6fab6</t>
-  </si>
-  <si>
     <t>The process begins when the sales department receives a purchase order. The sales team then checks the order to ensure everything is correct. At this point, a decision is made: if the order is not acceptable, the sales team will reject the order, and the process ends there. If the order is acceptable, the sales team confirms the order and inputs it into the ERP system.
 Once the order is in the ERP system, the system performs necessary IT tasks. Afterward, two activities occur simultaneously: the ERP system generates a production order for ME &amp; MII, and it also emits an invoice. The production team then initializes the process at the magazine.
 The production team checks if the product is black. If it is black, they proceed to load the magazine with the Bund cover. If it is not black, manual work is required to cover the Bund with a different color. Following this, the production team drills the necessary parts and assembles them using a robot. A camera check is then conducted to ensure quality.
 If the product passes the camera check, it moves on to packaging. If it does not pass, manual rework is required. After rework, if the product has been reworked less than three times, it goes back to the robot assembly stage. If it has been reworked three times, the product is scrapped, and the process ends.
 Once the product is packaged, the distribution team ships the goods, marking the order as fulfilled. Meanwhile, the ERP system waits for payment. Once payment is received, the process concludes with the shipment of goods.</t>
-  </si>
-  <si>
-    <t>2d5a6476e6184d16bbeb5c916d82b3da</t>
   </si>
   <si>
     <t>The process begins when a request to cancel a trip is made. The first step involves receiving the trip cancellation request. Once the request is received, the next step is to confirm that the cancellation request has been received.
@@ -1495,16 +2139,10 @@
 Finally, regardless of whether a refund is issued or not, the customer is notified of the trip cancellation. The process concludes with the trip being officially cancelled.</t>
   </si>
   <si>
-    <t>73edc1dd255c4ad38cecd191878300b3</t>
-  </si>
-  <si>
     <t>The process begins when a Junior Claims Officer receives a claim. The IT System then creates a record for this claim. Following this, the IT System retrieves the insurance details associated with the claim. Once the details are retrieved, a Junior Claims Officer checks the insurance information.
 At this point, the Junior Claims Officer determines whether the claim is insured. If the claim is not insured, the Junior Claims Officer informs the claimant that their claim has been rejected. The IT System then updates the record, and the process concludes.
 If the claim is insured, a Senior Claims Officer evaluates the claim. After evaluation, the Senior Claims Officer decides whether to accept the claim. If the claim is not accepted, the Senior Claims Officer rejects the claim, and the process returns to the Junior Claims Officer, who informs the claimant of the rejection, followed by updating the record and ending the process.
 If the claim is accepted, the Senior Claims Officer decides the benefit amount. The officer then prepares the claim discharge. After this, two tasks occur simultaneously: the Senior Claims Officer processes the payment and closes the claim. Once both tasks are completed, the IT System updates the record, and the process ends.</t>
-  </si>
-  <si>
-    <t>7c7b1963e2314bf0baf144becb5abc9d</t>
   </si>
   <si>
     <t>The process begins when a customer cannot find a product. The customer approaches a clerk to inquire about the product. This request is communicated to the clerk at the local shop, who then checks the stock availability.
@@ -1513,9 +2151,6 @@
 If the order is confirmed, the clerk verifies whether the customer exists in the ERP system. If the customer does not exist, the clerk creates a new client profile. Once the client is verified or created, the clerk proceeds to make the order.
 The order process involves two simultaneous tasks: printing the order and printing the invoice. After printing, the clerk waits for the payment. If the payment is received, the process continues. If no payment is received within two days, the order is canceled.
 Upon receiving the payment, the central warehouse is notified, and they send a message to the customer. After a waiting period of five days, the central warehouse delivers the product. The clerk at the local shop receives the product and informs the customer. Finally, the clerk delivers the product to the customer, marking the end of the process with the product being delivered.</t>
-  </si>
-  <si>
-    <t>3895e2c8df2e414095ba527b5d31ef77</t>
   </si>
   <si>
     <t>The process begins with the preparation of necessary implements. Once the implements are ready, the individual proceeds to wash their hands thoroughly. After hand washing, the next step is to get into sterile clothing to maintain a clean environment.
@@ -1527,16 +2162,10 @@
 The catheter is then advanced through the widened pathway. Once the catheter is in place, the guidewire is removed. The flow and reflow are checked to ensure proper function. Finally, the catheter position is verified to be correct, concluding the process.</t>
   </si>
   <si>
-    <t>f9df2d36f7d04843b613f94e8de928f4</t>
-  </si>
-  <si>
     <t>The process begins when a Junior Claims Officer receives a claim. The IT System then creates a record for this claim. Following this, the IT System retrieves the insurance details associated with the claim. Once the details are retrieved, a Junior Claims Officer checks the insurance information.
 At this point, the Junior Claims Officer determines whether the claimant is insured. If the claimant is not insured, the Junior Claims Officer informs the claimant that their claim has been rejected. The IT System then updates the record, and the process concludes.
 If the claimant is insured, the process continues with a Senior Claims Officer evaluating the claim. The Senior Claims Officer then decides whether to accept the claim. If the claim is not accepted, the Senior Claims Officer rejects the claim, and the Junior Claims Officer informs the claimant of the rejection. The IT System updates the record, and the process ends.
 If the claim is accepted, the Senior Claims Officer decides the benefit amount. The officer then prepares the claim discharge. After this, two tasks occur simultaneously: the Senior Claims Officer processes the payment and closes the claim. Once both tasks are completed, the IT System updates the record, marking the end of the process.</t>
-  </si>
-  <si>
-    <t>274a2b2a8f29408e8904cfdffb41980a</t>
   </si>
   <si>
     <t>The process begins when the call center receives a call. The call center then picks up the call and proceeds to ask the caller a series of questions. After gathering initial information, the call center evaluates whether they have enough information to proceed. If the information is insufficient, they will continue asking questions until they have gathered enough details.
@@ -1544,9 +2173,6 @@
 The process then moves to the Claim Handling Office, where they determine the liability associated with the claim. After determining liability, they assess the claim to decide whether it should be accepted or rejected. If the claim is rejected, the Claim Handling Office formally rejects the claim, and the process ends with the claim being marked as failed.
 If the claim is accepted, the process continues with two tasks happening simultaneously. The Claim Handling Office advises the customer of the claim amount and initiates the payment process. Advising the amount involves sending a message to the customer, while initiating the payment ensures the financial transaction is set in motion.
 After advising the amount and initiating the payment, the Claim Handling Office closes the claim. The process concludes with the claim being fulfilled, marking the successful completion of the claim handling process.</t>
-  </si>
-  <si>
-    <t>f779331026664514925cdd5915e9ddcc</t>
   </si>
   <si>
     <t>The process begins with the preparation of implements by a designated actor. Following this, the actor performs hand washing to ensure cleanliness. Next, the actor gets into sterile clothes to maintain a sterile environment. The puncture area is then cleaned thoroughly by the actor, followed by draping the area to keep it sterile.
@@ -1557,9 +2183,6 @@
 The actor then advances the catheter and removes the guidewire. The flow and reflow are checked to ensure proper function. Finally, the actor checks the catheter position to confirm it is correct. The process concludes successfully at this point.</t>
   </si>
   <si>
-    <t>1930f3f9837b4c40ab088a610f3f81bd</t>
-  </si>
-  <si>
     <t>The process begins when the pharmacy receives a prescription. Once the prescription is received, the pharmacy simultaneously verifies the prescription and checks if it is the customer's first time visiting.
 For the verification of the prescription, if any issues are identified, the pharmacy contacts the doctor to request details about the issue. The doctor then provides verification or authority and issues the necessary document to fulfill the dispensing. This document is sent back to the pharmacy for review. If no issues are identified, the pharmacy proceeds to review the prescription.
 After reviewing the prescription, the pharmacy checks if a generic brand is available. If a generic brand is available, the pharmacy recommends it to the customer. If not, the pharmacy proceeds with the prescribed brand. In both cases, the pharmacy inputs the details into the system and prints labels for the medication.
@@ -1568,9 +2191,6 @@
 The process concludes with the pharmacy either preparing and scanning the prescriptions if the stock is available or informing the customer if the stock is not available.</t>
   </si>
   <si>
-    <t>9da4a71e3def4f41bc2d94f53689d384</t>
-  </si>
-  <si>
     <t>The process begins with a patient examination. A healthcare professional examines the patient to assess their condition. Following the examination, a decision is made based on the patient's health status.
 If the patient is deemed healthy, the healthcare professional fills out an examination form documenting the findings. After completing the form, the patient is informed that they can leave, concluding the process.
 If the patient requires further examination or treatment, the healthcare professional orders additional tests and follow-up treatment. A request form is filled out to initiate these procedures. The patient is then informed about any potential risks associated with the upcoming tests or treatments.
@@ -1579,17 +2199,11 @@
 If the sample is adequate, it is received by the physician, who validates it. A technician then performs the necessary analysis on the sample. Based on the analysis, a physician makes a diagnosis and prescribes the appropriate therapy. After prescribing therapy, the patient is informed and can leave, marking the end of the process.</t>
   </si>
   <si>
-    <t>939514e86660450ba99ada89f9a1d85f</t>
-  </si>
-  <si>
     <t>The process begins with a candidate for study initiating the application for admission to bachelor studies. The candidate proceeds to apply for admission, which involves two simultaneous actions: filling out the application and paying the fee for the admission procedure.
 Once the application is filled, the candidate prints the filled application and confirms their high school evaluation. After these steps, the candidate sends the application along with the confirmation of payment to the study department of the chosen faculty.
 The study department then accepts the candidate's application and adds a confirmation about the fulfillment of prerequisites to the information system. At this point, the process reaches a decision point based on the candidate's marks. If the marks are not good enough, the study department sends an invitation for an entrance test. The candidate then takes a written test, which is evaluated by the study department. The process then returns to the decision about admission.
 If the candidate has good marks, the study department makes a decision about admission and sends this decision to the candidate. The candidate then faces another decision point. If accepted, the candidate appears for registration. The study department then accepts the candidate as a student and writes them into the information system, managing all state requirements. This leads to the end of the process.
 If the candidate is not accepted and disagrees with the decision, they can appeal the decision. The study department then reconsiders the decision, and the process loops back to the point where the decision is sent to the candidate. If the candidate agrees with the decision of not being accepted, the process ends.</t>
-  </si>
-  <si>
-    <t>c88f2aa1750c49af9bc3327391d94dee</t>
   </si>
   <si>
     <t>The process begins when a customer places an order. The customer initiates the order, selects the desired car model, and confirms the design and specifications. Once the order is confirmed, the plant gathers the necessary supplies for production.
@@ -1598,9 +2212,6 @@
 Following the electronics test, the plant checks if the car passes the emission test. If the car does not pass, it undergoes reconfiguration of the electronics and an engine check before being retested. If the car passes the emission test, it proceeds to a road test.
 The road test determines if the car is ready for delivery. If the car does not clear the road test, it is sent back for a comprehensive check and retesting. If the car clears the road test, it is moved to the delivery station.
 The delivery department then prepares for the order delivery. Finally, the car is delivered to the customer, marking the completion of the process.</t>
-  </si>
-  <si>
-    <t>e9336283b37b4486b47ca392e53bbe6e</t>
   </si>
   <si>
     <t>The process begins with a passenger or traveler starting their journey at KLIA 2. The first step involves the passenger performing a self check-in. After completing the self check-in, the passenger is presented with a choice of check-in options.
@@ -1613,9 +2224,6 @@
 Once security screening is complete, the process waits until 20 minutes before departure. Finally, the passenger enters the boarding gate, concluding the process at KLIA 2.</t>
   </si>
   <si>
-    <t>74ed36054c7c41c8a2ef358dfb75ea9a</t>
-  </si>
-  <si>
     <t>The process begins when a customer decides they want a cake. The customer then sends an inquiry to the patisserie to ask about the price of the cake. The manager at the patisserie receives this inquiry and calculates the price of the cake. After determining the price, the manager sends a response back to the customer with the price information.
 At this point, the customer has a decision to make. If the customer does not respond, the process ends with no order being placed. If the customer responds within five days, they have two options: they can either accept the offer or reject it. If the customer rejects the offer, the process ends with no order. If the customer accepts the offer, the manager updates the database to reflect the new order.
 Once the order is confirmed, the manager prepares the order details from the database. The manager then determines whether the order is for a standard cake or a design cake. If it is a design cake, the main cook begins creating the cake for baking. The process then splits into two parallel tasks: the main cook prepares the cream, and the cook's helper prepares the cake for baking. Once both tasks are completed, the cake is baked.
@@ -1623,9 +2231,6 @@
 Following decoration, the manager performs a quality check on the cake. If the cake passes the quality check, the manager informs the customer that the cake is ready. The customer then collects the cake from the patisserie. Finally, the manager updates the database to indicate that the order is finished, marking the end of the process.</t>
   </si>
   <si>
-    <t>55314a432dc444398c06093eb63c55c5</t>
-  </si>
-  <si>
     <t>The process begins when the resupply cycle is triggered. The first task involves an actor checking the inventory level. After checking the inventory, a decision point is reached. If the inventory is below the minimum required level, the process continues with creating a purchase order. If the inventory is above the minimum, the process ends.
 If a purchase order is created, it is then reviewed. At this point, another decision is made. The purchase order can either be approved or rejected. If it is rejected, the order is reworked and sent back for review. If the purchase order is approved, the process moves forward.
 Once approved, two tasks occur simultaneously. One task involves reserving funds, while the other involves sending the purchase order to the supplier. After sending the purchase order, another parallel set of tasks is initiated. One task involves receiving the package slip, and the other involves receiving the invoice.
@@ -1633,9 +2238,6 @@
 Throughout the process, each task is handled by specific actors responsible for ensuring the smooth flow of operations from start to finish.</t>
   </si>
   <si>
-    <t>96de873b8681432b900ac2ca5fe17c4d</t>
-  </si>
-  <si>
     <t>The process begins with an administrator initiating the workflow. Immediately, two tasks are carried out simultaneously. The first task involves the administrator performing a manual check on Jane Doe. The second task involves the administrator conducting a manual BKR check. 
 Once both tasks are completed, the administrator proceeds to perform an automated credibility check. Following this, the administrator confirms the results of the credibility check.
 Next, a decision point is reached. If the credibility assessment is accepted, the administrator calls the client to gather additional information. After this call, the administrator creates a loan offer and then sends it to the client. The process waits for the client to accept the offer. Once the offer is accepted, two actions occur simultaneously. The administrator activates the loan application and sends a welcome letter to the client.
@@ -1643,16 +2245,10 @@
 If the credibility assessment is rejected, the administrator sends a rejection letter to the client, which concludes this branch of the process.</t>
   </si>
   <si>
-    <t>68f04cb4b8c74e89b09fd4d76ec1f589</t>
-  </si>
-  <si>
     <t>The process begins with the appointment agency planning a screening. Once the screening is planned, the agency sends an invitation to the client. After sending the invitation, the agency checks if the client is satisfied with the appointment. If the client is satisfied, the process continues with the nurse going to the school.
 If the client is not satisfied, the client calls the appointment agency. The agency then determines if the client wants to cancel or reschedule the appointment. If the client chooses to cancel, the agency records the reason for cancellation in the system, and the process ends without a screening. If the client decides to reschedule, the process loops back to planning the screening again.
 When the client is satisfied, the nurse goes to the school and introduces themselves in the class. The nurse then explains the screening methods to the children. After the explanation, the nurse receives a questionnaire from the child and discusses the answers with them. Following this, the nurse measures the child's length and weight.
 Next, the nurse checks if both parents have an eye deviation or if there is a request for an eye test. If yes, the nurse conducts an eye test. If not, the nurse checks if a hearing test is requested by the parents, teacher, or the child. If a hearing test is requested, the nurse performs the hearing test. If no hearing test is requested, the nurse fills in a findings form and gives it to the child to take along. The process concludes with the screening ending.</t>
-  </si>
-  <si>
-    <t>fe0d9816a88e4ee6b7fa362e1a74eed5</t>
   </si>
   <si>
     <t>The process begins with the Risk Management team initiating the procedure. Immediately, two tasks are carried out simultaneously. The first task involves the Risk Management team performing a Jane Doe check. The second task involves the same team conducting a BKR check. 
@@ -1664,18 +2260,12 @@
 If the decision after confirming the credibility check is negative, the Administration team sends a rejection letter to the client, concluding the process.</t>
   </si>
   <si>
-    <t>7c82d73ef986488b927e6c1b186f1761</t>
-  </si>
-  <si>
     <t>The process begins when a customer enters the department store. Upon entering, the customer is expected to get a shopping cart or basket to carry their selected items. Next, the customer chooses the desired product they wish to purchase. After selecting a product, the customer examines it to ensure it meets their needs and preferences. The customer then checks the price of the product.
 At this point, the customer must decide whether they want to buy the product. If the customer decides not to purchase the product, they will put the item back. If the customer decides to buy the product, they proceed to the checkout area.
 Once at the checkout, the cashier determines the category of the product. If the product is a book, the cashier applies a 10% discount. If the product is electronics, no discount is applied. If the product is food, a 5% discount is applied.
 After determining the product category and applying any applicable discounts, the cashier assesses the customer's loyalty status. If the customer has a silver status, an additional 2% discount is applied. If the customer has a gold status, a 5% discount is applied. If the customer has a titanium status, a 10% discount is applied.
 Following the loyalty status assessment, the cashier checks if the customer qualifies for a special discount. If the customer is eligible, a student or veteran discount is applied. If not, the price remains constant.
 Finally, the process concludes, and the transaction is completed.</t>
-  </si>
-  <si>
-    <t>3b7d6afa91d94ac6907693e3a02f1d58</t>
   </si>
   <si>
     <t>The process begins with the initiation of engaging Dimuto for traceability solutions. The first step involves logging into the Dimuto account. Once logged in, the next task is to create user accounts for employees, ensuring they have access to the necessary tools and information.
@@ -1687,9 +2277,6 @@
 The process concludes when the buyer receives the goods, completing the transaction and ensuring that all parties are satisfied with the outcome.</t>
   </si>
   <si>
-    <t>0254a74de2614dfda2b6d6594dfd98c6</t>
-  </si>
-  <si>
     <t>The process begins when a customer arrives at the restaurant. Upon arrival, the customer faces a decision point: whether they are a walk-in or have a reservation. If the customer is a walk-in, they proceed to the task of walking in and then read through the menu. After reviewing the menu, the customer decides if they are satisfied with the food options. If satisfied, they place an order; if not, they leave the restaurant.
 If the customer has a reservation, they show their reservation information. A clerk then checks the reserved table and the meal ordered. The POS terminal tracks and displays the reservation information. The clerk then brings the customer to the reserved table and confirms the meal ordered. The customer gets seated and confirms their order, followed by placing the order.
 Once the order is placed, a clerk determines if the order is for a walk-in or a reserved customer. If it is a reserved order, the clerk confirms the order. The kitchen then prepares the food, and the clerk serves it to the customer. After enjoying the meal, the customer pays the bill, and the clerk checks out the order. The POS terminal displays the bill information, and the clerk prints the bill. The customer makes the payment, and the clerk receives it.
@@ -1697,9 +2284,6 @@
 If the kitchen finds there is not enough food supply, they notify the clerk, who then informs the customer. The customer decides whether to confirm the order with the available options or leave the restaurant. If the customer chooses to confirm, they replace the order, and the process continues with the clerk keying in the order details. If the customer decides not to confirm, they leave the restaurant, ending the process.</t>
   </si>
   <si>
-    <t>05ab849c028f470ba5e240712b68a116</t>
-  </si>
-  <si>
     <t>The process begins with the preparation of implements by the assigned individual. Following this, the same person performs hand washing to ensure cleanliness. Next, they put on sterile clothes to maintain a sterile environment.
 The process continues with cleaning the puncture area, followed by draping it to prepare for the procedure. The next step involves configuring the ultrasound equipment, after which gel is applied to the probe. The probe is then covered to maintain sterility, and sterile gel is applied to the area.
 The probe is positioned correctly, and the patient is positioned appropriately for the procedure. At this point, a decision is made between three options: compression identification, anatomic identification, or Doppler identification. Each of these tasks leads to the anesthetization of the patient.
@@ -1707,17 +2291,11 @@
 Another decision point arises, where the wire is checked in either the short axis or the long axis. If the wire is in a good position, the pathway is widened, and the catheter is advanced. The guidewire is then removed, and the flow and reflow are checked. Finally, the catheter position is verified, concluding the process.</t>
   </si>
   <si>
-    <t>fa33f504903b4253850d1995fd07af2a</t>
-  </si>
-  <si>
     <t>The process begins when a claims officer at the insurance company receives a claim. The first task for the claims officer is to review the application. After reviewing the application, the claims officer checks the validity of the claim.
 At this point, there is a decision to be made. If the claim is valid, the claims officer proceeds to check the completeness of the documents. If the claim is invalid, the claims officer rejects the claim and informs the claimant. The process ends with the claim being rejected.
 If the documents are complete, the claims officer assesses the complexity of the claim. If any documents are missing, the claims officer requests further documents from the claimant and waits to receive them. If there is an information mismatch, the fraud control team reassesses the claim and may request further documents, which they then receive and validate.
 Once the claim complexity is assessed, another decision is made. If the claim is deemed low complexity, the claims officer valuates the claim, processes the payment, and approves the payment, concluding with the claim being handled. If the claim is high complexity, a senior officer rechecks the application and validates the claim before it is passed back to the claims officer for valuation and payment processing.
 Throughout the process, communication with the claimant is maintained, especially when additional documents are required or when the claim is rejected. The process ensures that all claims are thoroughly reviewed, validated, and processed efficiently.</t>
-  </si>
-  <si>
-    <t>5f94d7b0879f445593bde225410e865f</t>
   </si>
   <si>
     <t>The process begins when a passenger arrives at the airport. The first step for the passenger is to check in. After checking in, the passenger encounters a decision point where they must choose one of three options for checking in: using a kiosk, using a mobile device, or using the web.
@@ -1726,9 +2304,6 @@
 If the passenger chooses to check in using the web, they print their boarding pass at home. After printing the boarding pass at home, they face the decision point about dropping baggage. If they need to drop baggage, they proceed to do so. If not, they move on to the next decision point, which determines whether their flight is international or domestic.
 If the passenger's flight is domestic, they go to the domestic departure gate and then proceed to boarding. Once boarding is complete, the process ends with the passenger's departure.
 If the passenger's flight is international, they go to the international departure gate. Here, they must check their documents, scan their passport and thumbprint, and perform a security check. After completing these steps, they proceed to the domestic departure gate, followed by boarding. The process concludes with the passenger's departure.</t>
-  </si>
-  <si>
-    <t>e7913c15552c491296aa55e04d14b953</t>
   </si>
   <si>
     <t>The process begins with the preparation of implements by the assigned actor. Once the implements are ready, the actor proceeds to wash their hands thoroughly. Following hand washing, the actor dresses in sterile clothes to maintain a clean environment.
@@ -1740,9 +2315,6 @@
 Following the pathway widening, the actor advances the catheter and then removes the guidewire. The actor checks the flow and reflow to ensure proper function. Finally, the catheter position is checked to confirm it is correctly placed. The process concludes successfully at this point.</t>
   </si>
   <si>
-    <t>9a05b77363944304b7e9372e520b4a28</t>
-  </si>
-  <si>
     <t>The process begins with the preparation of implements by a designated actor. Following this, the actor performs hand washing to ensure cleanliness. Next, the actor gets into sterile clothes to maintain a sterile environment.
 The process continues with the actor cleaning the puncture area, followed by draping the area to prepare for the procedure. The actor then configures the ultrasound equipment, applies gel to the probe, and covers the probe to maintain sterility. Afterward, the actor puts sterile gel on the puncture area and positions the probe correctly.
 Subsequently, the actor positions the patient appropriately for the procedure. At this point, a decision is made between three options: compression identification, anatomic identification, or Doppler identification. Each of these tasks leads to the anesthetization of the patient.
@@ -1752,16 +2324,10 @@
 The process concludes successfully once the catheter position is verified.</t>
   </si>
   <si>
-    <t>28c5aedad9f347528214b9a6cb74dc3c</t>
-  </si>
-  <si>
     <t>The process begins when a loan application is received. The first task involves checking the customer's details. Once this is completed, the process splits into two parallel tasks. One task involves appraising the property, while the other involves checking the customer's history. Both tasks proceed simultaneously.
 After the property appraisal is completed, the applicant's eligibility is assessed. Meanwhile, the customer's history check leads to an assessment of the customer's loan risk. Once both parallel tasks are completed, the process reaches a decision point where the applicant's eligibility is evaluated.
 If the applicant is not eligible, the application is rejected, and the process ends. If the applicant is eligible, an acceptance pack is prepared. This pack is then sent to the customer. The customer is expected to return signed documents, which are then received and processed.
 Following the receipt of signed documents, the payment agreement is verified. At this point, another decision is made. If the payment agreement is agreed upon, the application is approved. If the payment agreement is not agreed upon, the application is canceled, and the customer is notified. In both cases, the process concludes with the loan application process ending.</t>
-  </si>
-  <si>
-    <t>495a5ccccc184034aea09b1866194dc0</t>
   </si>
   <si>
     <t>The process begins when the information system receives a new visa application. The system then retrieves the details of this new application. After fetching the details, the system creates a PDF document containing the application information. Once the document is prepared, the system notifies a junior officer about the new application.
@@ -1769,9 +2335,6 @@
 The senior officer checks the validity of the application. If the application is not valid, the senior officer rejects it, and the information system notifies the applicant of the rejection. If the application is valid, the senior officer ensures it meets immigration requirements. Once the requirements are met, the senior officer approves the application.
 After approval, the junior officer conducts a "Lift in Wonderland" test. If the application passes this test, the junior officer sends a confirmation to the applicant, marking the application as approved. If the application does not pass the test, the information system notifies the applicant that the application has failed.
 The process concludes with either the application being approved or the applicant being informed of the failure.</t>
-  </si>
-  <si>
-    <t>d4dc0f1a4fc94a49bb55631dc05f205b</t>
   </si>
   <si>
     <t>The process begins when a guest contacts the room service manager to place an order. The room service manager takes down the order details and then checks the order for accuracy.
@@ -1783,16 +2346,10 @@
 Finally, the waiter delivers the ordered food and/or drinks to the guest's room, marking the end of the process with the meal being delivered.</t>
   </si>
   <si>
-    <t>11535b315b1e49b7a1e97cb49ce87871</t>
-  </si>
-  <si>
     <t>The process begins with the reception of loan details. Once the loan details are received, two tasks are carried out simultaneously. One task involves performing a BKR assessment, and the other involves performing a task labeled "Perform Jane Doe." 
 After the BKR assessment is completed, a credibility assessment is performed. Following this, the credibility assessment is checked. Based on the results of this check, a decision is made. If the credibility assessment is accepted, additional information is retrieved, leading to the creation of a loan offer. This loan offer is then sent out. If the offer is accepted, the process continues with two tasks happening at the same time: sending a welcome letter and activating the loan. 
 Once the loan is activated, an initial payment is executed, and documents are returned to the client. Both the sending of the welcome letter and the return of documents lead to the end of the process.
 If the credibility assessment is rejected, a rejection letter is sent, which also leads to the end of the process.</t>
-  </si>
-  <si>
-    <t>dddce5647c6a4c84a69ad91cfadfb6f9</t>
   </si>
   <si>
     <t>The process begins with the initiation of a purchase request. The first step involves creating a purchase request. Once the request is created, it is analyzed to ensure all necessary details are included. If any amendments are needed, the purchase request is amended accordingly.
@@ -1802,17 +2359,11 @@
 Once the purchase order is approved, two activities occur simultaneously. The goods are received, and an invoice is sent to the manager. After receiving the goods, the process concludes. Meanwhile, the manager handles the payment, which also leads to the conclusion of the process.</t>
   </si>
   <si>
-    <t>0b9081e19b964ee69de5d673f318709a</t>
-  </si>
-  <si>
     <t>The process begins with the customer initiating a request for a printing service through an app. The customer then fills in the necessary metadata required for the print request. Afterward, the customer locates the desired printing location and submits the print request.
 Once the request is submitted, the printer receives it and proceeds to load the appropriate paper and ink. The printer then prints the document based on the specified requirements. After printing, the printer validates the print request.
 At this point, a decision is made to determine if the request is for delivery. If it is a delivery request, the printer notifies the customer that the print request is ready for delivery. The printer then delivers the print request at the requested time. Upon delivery, another decision is made to check if the customer is home. If the customer is home, the printer hands the print request to the customer. If the customer is not home, the printer leaves the print request on the customer's doorstep and informs the customer via email with a picture of the drop-off.
 If the print request is not for delivery, the printer sends a notification to the customer that the print request is ready for pick-up. The customer receives the print completion notice and leaves to pick up the print request at the specified location during the pick-up window. The customer then receives the print request.
 After receiving the print request, the customer acknowledges in the app that the print request has been received and rates the print service. Simultaneously, the printer acknowledges that the print service has been provided to the customer. The process concludes with both the customer and the printer marking the print service as complete.</t>
-  </si>
-  <si>
-    <t>d17524f4567a4903aa503b48a4ec1d1e</t>
   </si>
   <si>
     <t>The process begins with a change request initiated by the Quality Management (QM) team. The QM team then conducts an analysis of the request to understand its implications. Following this, the QM team builds a catalogue of specific questions that need to be answered to determine if the change is necessary.
@@ -1823,9 +2374,6 @@
 The QM team conducts a final examination to ensure everything is effective. The process concludes with the QM team marking the change request as accomplished, resulting in the completion of the process.</t>
   </si>
   <si>
-    <t>efda927d1da24b49b9f5dd4be6b579f1</t>
-  </si>
-  <si>
     <t>The process begins with a student joining a team. Once the student has joined, the team collectively agrees on a domain for their project. After agreeing on the domain, a student creates a process model for the project.
 Next, a lecturer checks the process model. At this point, there is a decision to be made. If the process model is not satisfactory, the lecturer assigns negative points, and the student must fix the problem in the next session. After fixing the problem, the student extends the process to levels 2 and 3.
 If the process model is satisfactory, the student proceeds to extend the process to levels 2 and 3 without delay. Following this, the student encounters another decision point. The student can either analyze the field of study or check the process and assign points. If the student chooses to analyze the field of study, the team then assigns roles within the team. Each student then performs work according to their assigned role.
@@ -1833,9 +2381,6 @@
 If the student chooses to check the process and assign points, they return to perform work according to their role, and the process continues as described above.</t>
   </si>
   <si>
-    <t>d8691da54de64a01a6058a8d97d2a9ce</t>
-  </si>
-  <si>
     <t>The journey to becoming a professional documentary photographer begins with a decision made by the aspiring photographer. Once the decision is made, the first step is to purchase the necessary equipment, including a DSLR camera. With the equipment in hand, the photographer then takes the time to learn and explore the camera's functions.
 Following this, the photographer simultaneously embarks on two paths. One path involves learning the basics of photography, while the other involves analyzing the work of the best photographers to gain inspiration and understanding. After gaining this foundational knowledge, the photographer begins taking photos in their favorite category, exploring and refining their skills through practice. This process is repeated multiple times to build expertise.
 In parallel, the photographer studies advanced materials and theories to deepen their understanding of photography. Feedback is then sought from social media, which is used to improve their work. This feedback loop is continuous, allowing for ongoing improvement.
@@ -1843,9 +2388,6 @@
 Alternatively, the photographer can start a professional page on photography websites, interact with the community to gain followers, and participate in contests to earn money. Both paths lead to the ultimate goal of becoming a professional documentary photographer.</t>
   </si>
   <si>
-    <t>637b02be69fa4798a393726121614721</t>
-  </si>
-  <si>
     <t>The process begins with the interviewer receiving the result from the selection process. The interviewer then picks a preferred candidate. After selecting the candidate, there are two possible paths: the interviewer can either put together an offer or the recruiter can do so. 
 Once the offer is prepared, it is sent to the candidate via email. The candidate then decides whether to accept the offer. If the candidate declines, the recruiter considers whether to revise the offer. If the decision is to revise, the recruiter prepares a new offer. If not, a rejection email is sent to the candidate.
 If the candidate accepts the offer, the recruiter checks if reference checks are needed. If reference checks are not required, the recruiter prepares the contract. The contract is then sent to the candidate for signing. Once signed, the onboarding process begins.
@@ -1853,9 +2395,6 @@
 Throughout the process, decisions are made by either the recruiter or the interviewer, depending on the task at hand. The process concludes with the candidate signing the contract and the onboarding process starting.</t>
   </si>
   <si>
-    <t>07487a4aebe8436d85b618c2ac2a9f25</t>
-  </si>
-  <si>
     <t>The process begins when a notice is received by phone. This notice is documented and then answered by the responsible person. After answering the notice, the next step is to request the medical file related to the notice.
 Once the request for the medical file is made, two tasks occur simultaneously. One task involves recording the notice, followed by storing and printing it. If the patient is known, the process continues to close the case. If the patient is unknown, a new patient file is created before closing the case.
 Meanwhile, the medical file is awaited. Once received, the medical file is used to update the patient file. After updating the patient file, a meeting with the second intaker is planned. The meeting date is set, and the meeting with the second intaker takes place. The conversation from this meeting is typed out, and the file is completed with the second intaker's information.
@@ -1863,16 +2402,10 @@
 Finally, on the following Wednesday morning, the treatment is determined, marking the completion of the intake process.</t>
   </si>
   <si>
-    <t>9bfd42a80a7f4cb4b61387bc2c7a52bf</t>
-  </si>
-  <si>
     <t>The process of planning a party begins with determining how many people will attend. Once the number of participants is known, the process splits into two parallel paths based on the expected number of attendees.
 If the number of participants is 10 or fewer, the next step is to buy ingredients for 10 people. After purchasing the ingredients, three tasks are carried out simultaneously: preparing zakouskis with vegetables and dip sauce, preparing mini-quiches, and preparing all three types of snacks. Once these tasks are completed, the snacks are served, and the party starts with good snacks.
 If the number of participants is between 10 and 15, the process involves buying ingredients for 15 people. Following this, three tasks are executed in parallel: preparing zakouskis with vegetables and dip sauce, preparing mini-quiches, and preparing all three types of snacks. After these preparations, the snacks are served, leading to the start of the party with good snacks.
 In both scenarios, the preparation tasks are carried out simultaneously to ensure that all snacks are ready to be served at the same time, marking the successful start of the party.</t>
-  </si>
-  <si>
-    <t>3beb6668e50a4805988cc64e3576091c</t>
   </si>
   <si>
     <t>The process begins with the Risk Manager initiating the procedure. The first task for the Risk Manager is to perform a credit check. Once the credit check is completed, the Risk Manager proceeds to confirm the credibility check.
@@ -1881,9 +2414,6 @@
 At this point, there are two possible paths. If the offer is accepted, the Customer Contact receives the accepted offer, and the process continues. If there is no immediate response, a timer is set for one hour. After this period, the Customer Contact reminds the client, and the process loops back to the decision point.
 Once the offer is accepted, the process splits into two parallel tasks. The Finance department activates the loan application and validates the loan activation. Simultaneously, the Administrator sends a welcome letter to the client.
 After the loan activation is validated, the Finance department executes the initial payment. Following this, the Administrator returns the necessary documents to the client. Finally, the process concludes with the Administrator marking the end of the procedure.</t>
-  </si>
-  <si>
-    <t>ccbdb0d979974cebb16597191785a0a4</t>
   </si>
   <si>
     <t>The process begins with the Sales Department receiving an order. Once the order is received, the Sales Department sends an order request to the warehouse.
@@ -2287,3706 +2817,4486 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="270">
+    <row r="2" spans="1:8" ht="345">
       <c r="A2" s="3">
-        <v>182497</v>
+        <v>238292</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H2"/>
+    </row>
+    <row r="3" spans="1:8" ht="300">
+      <c r="A3" s="3">
+        <v>302355</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:8" ht="315">
+      <c r="A4" s="3">
+        <v>326001</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="H4"/>
+    </row>
+    <row r="5" spans="1:8" ht="255">
+      <c r="A5" s="3">
+        <v>355708</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H2"/>
-    </row>
-    <row r="3" spans="1:8" ht="255">
-      <c r="A3" s="3">
-        <v>10842</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H5"/>
+    </row>
+    <row r="6" spans="1:8" ht="300">
+      <c r="A6" s="3">
+        <v>378789</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H6"/>
+    </row>
+    <row r="7" spans="1:8" ht="210">
+      <c r="A7" s="3">
+        <v>410211</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H3"/>
-    </row>
-    <row r="4" spans="1:8" ht="270">
-      <c r="A4" s="3">
-        <v>22450</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4"/>
-    </row>
-    <row r="5" spans="1:8" ht="270">
-      <c r="A5" s="3">
-        <v>9388</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5"/>
-    </row>
-    <row r="6" spans="1:8" ht="210">
-      <c r="A6" s="3">
-        <v>50794</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6"/>
-    </row>
-    <row r="7" spans="1:8" ht="255">
-      <c r="A7" s="3">
-        <v>203267</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>26</v>
+        <v>233</v>
       </c>
       <c r="H7"/>
     </row>
     <row r="8" spans="1:8" ht="185.25" customHeight="1">
       <c r="A8" s="3">
-        <v>149510</v>
+        <v>342524</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="H8"/>
+    </row>
+    <row r="9" spans="1:8" ht="345">
+      <c r="A9" s="3">
+        <v>214523</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8"/>
-    </row>
-    <row r="9" spans="1:8" ht="225">
-      <c r="A9" s="3">
-        <v>172563</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>30</v>
+        <v>235</v>
       </c>
       <c r="H9"/>
     </row>
-    <row r="10" spans="1:8" ht="270">
+    <row r="10" spans="1:8" ht="409.5">
       <c r="A10" s="3">
-        <v>384021</v>
+        <v>342</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="H10"/>
     </row>
-    <row r="11" spans="1:8" ht="225">
+    <row r="11" spans="1:8" ht="255">
       <c r="A11" s="3">
-        <v>257047</v>
+        <v>123778</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>34</v>
+        <v>237</v>
       </c>
       <c r="H11"/>
     </row>
-    <row r="12" spans="1:8" ht="285">
+    <row r="12" spans="1:8" ht="195">
       <c r="A12" s="3">
-        <v>367129</v>
+        <v>32646</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>36</v>
+        <v>238</v>
       </c>
       <c r="H12"/>
     </row>
     <row r="13" spans="1:8" ht="328.5" customHeight="1">
       <c r="A13" s="3">
-        <v>192025</v>
+        <v>6415</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>38</v>
+        <v>239</v>
       </c>
       <c r="H13"/>
     </row>
-    <row r="14" spans="1:8" ht="270">
+    <row r="14" spans="1:8" ht="240">
       <c r="A14" s="3">
-        <v>211483</v>
+        <v>366496</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="G14" s="3" t="s">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="H14"/>
     </row>
-    <row r="15" spans="1:8" ht="255">
+    <row r="15" spans="1:8" ht="300">
       <c r="A15" s="3">
-        <v>402973</v>
+        <v>47659</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>42</v>
+        <v>241</v>
       </c>
       <c r="H15"/>
     </row>
-    <row r="16" spans="1:8" ht="270">
+    <row r="16" spans="1:8" ht="409.5">
       <c r="A16" s="3">
-        <v>317474</v>
+        <v>77360</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>44</v>
+        <v>242</v>
       </c>
       <c r="H16"/>
     </row>
     <row r="17" spans="1:8" ht="382.5" customHeight="1">
       <c r="A17" s="3">
-        <v>98856</v>
+        <v>127282</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="H17"/>
     </row>
-    <row r="18" spans="1:8" ht="270">
+    <row r="18" spans="1:8" ht="330">
       <c r="A18" s="3">
-        <v>324648</v>
+        <v>278580</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="H18"/>
     </row>
-    <row r="19" spans="1:8" ht="270">
+    <row r="19" spans="1:8" ht="195">
       <c r="A19" s="3">
-        <v>66092</v>
+        <v>243766</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>50</v>
+        <v>245</v>
       </c>
       <c r="H19"/>
     </row>
     <row r="20" spans="1:8" ht="350.25" customHeight="1">
       <c r="A20" s="3">
-        <v>165426</v>
+        <v>391355</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>52</v>
+        <v>246</v>
       </c>
       <c r="H20"/>
     </row>
-    <row r="21" spans="1:8" ht="210">
+    <row r="21" spans="1:8" ht="409.5">
       <c r="A21" s="3">
-        <v>224821</v>
+        <v>133694</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>54</v>
+        <v>247</v>
       </c>
       <c r="H21"/>
     </row>
-    <row r="22" spans="1:8" ht="315">
+    <row r="22" spans="1:8" ht="270">
       <c r="A22" s="3">
-        <v>342078</v>
+        <v>413133</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>56</v>
+        <v>248</v>
       </c>
       <c r="H22"/>
     </row>
     <row r="23" spans="1:8" ht="255">
       <c r="A23" s="3">
-        <v>255040</v>
+        <v>147154</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>58</v>
+        <v>249</v>
       </c>
       <c r="H23"/>
     </row>
-    <row r="24" spans="1:8" ht="210">
+    <row r="24" spans="1:8" ht="225">
       <c r="A24" s="3">
-        <v>194121</v>
+        <v>262866</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="H24"/>
     </row>
-    <row r="25" spans="1:8" ht="240">
+    <row r="25" spans="1:8" ht="255">
       <c r="A25" s="3">
-        <v>294474</v>
+        <v>189524</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>62</v>
+        <v>251</v>
       </c>
       <c r="H25"/>
     </row>
     <row r="26" spans="1:8" ht="195">
       <c r="A26" s="3">
-        <v>102995</v>
+        <v>145240</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>64</v>
+        <v>252</v>
       </c>
       <c r="H26"/>
     </row>
-    <row r="27" spans="1:8" ht="210">
+    <row r="27" spans="1:8" ht="195">
       <c r="A27" s="3">
-        <v>140884</v>
+        <v>186730</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>66</v>
+        <v>253</v>
       </c>
       <c r="H27"/>
     </row>
-    <row r="28" spans="1:8" ht="285">
+    <row r="28" spans="1:8" ht="210">
       <c r="A28" s="3">
-        <v>402517</v>
+        <v>283248</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>68</v>
+        <v>254</v>
       </c>
       <c r="H28"/>
     </row>
-    <row r="29" spans="1:8" ht="315">
+    <row r="29" spans="1:8" ht="270">
       <c r="A29" s="3">
-        <v>346710</v>
+        <v>197239</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>70</v>
+        <v>255</v>
       </c>
       <c r="H29"/>
     </row>
     <row r="30" spans="1:8" ht="240">
       <c r="A30" s="3">
-        <v>42070</v>
+        <v>250363</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>72</v>
+        <v>256</v>
       </c>
       <c r="H30"/>
     </row>
     <row r="31" spans="1:8" ht="266.25" customHeight="1">
       <c r="A31" s="3">
-        <v>130649</v>
+        <v>15758</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>74</v>
+        <v>257</v>
       </c>
       <c r="H31"/>
     </row>
-    <row r="32" spans="1:8" ht="225">
+    <row r="32" spans="1:8" ht="270">
       <c r="A32" s="3">
-        <v>266842</v>
+        <v>416618</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>76</v>
+        <v>258</v>
       </c>
       <c r="H32"/>
     </row>
-    <row r="33" spans="1:8" ht="255">
+    <row r="33" spans="1:8" ht="195">
       <c r="A33" s="3">
-        <v>218719</v>
+        <v>416745</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>78</v>
+        <v>259</v>
       </c>
       <c r="H33"/>
     </row>
-    <row r="34" spans="1:8" ht="240">
+    <row r="34" spans="1:8" ht="270">
       <c r="A34" s="3">
-        <v>181858</v>
+        <v>412831</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="H34"/>
     </row>
-    <row r="35" spans="1:8" ht="255">
+    <row r="35" spans="1:8" ht="270">
       <c r="A35" s="3">
-        <v>194148</v>
+        <v>400114</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="H35"/>
     </row>
-    <row r="36" spans="1:8" ht="285">
+    <row r="36" spans="1:8" ht="315">
       <c r="A36" s="3">
-        <v>136804</v>
+        <v>191042</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="H36"/>
     </row>
-    <row r="37" spans="1:8" ht="210">
+    <row r="37" spans="1:8" ht="409.5">
       <c r="A37" s="3">
-        <v>93286</v>
+        <v>137907</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>86</v>
+        <v>263</v>
       </c>
       <c r="H37"/>
     </row>
-    <row r="38" spans="1:8" ht="240">
+    <row r="38" spans="1:8" ht="255">
       <c r="A38" s="3">
-        <v>51309</v>
+        <v>131120</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="H38"/>
     </row>
-    <row r="39" spans="1:8" ht="300">
+    <row r="39" spans="1:8" ht="225">
       <c r="A39" s="3">
-        <v>263279</v>
+        <v>277797</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>90</v>
+        <v>265</v>
       </c>
       <c r="H39"/>
     </row>
     <row r="40" spans="1:8" ht="240">
       <c r="A40" s="3">
-        <v>87671</v>
+        <v>362707</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>92</v>
+        <v>266</v>
       </c>
       <c r="H40"/>
     </row>
     <row r="41" spans="1:8" ht="230.25" customHeight="1">
       <c r="A41" s="3">
-        <v>277629</v>
+        <v>174689</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>94</v>
+        <v>267</v>
       </c>
       <c r="H41"/>
     </row>
-    <row r="42" spans="1:8" ht="195">
+    <row r="42" spans="1:8" ht="270">
       <c r="A42" s="3">
-        <v>353409</v>
+        <v>182497</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>96</v>
+        <v>268</v>
       </c>
       <c r="H42"/>
     </row>
     <row r="43" spans="1:8" ht="255">
       <c r="A43" s="3">
-        <v>3202</v>
+        <v>10842</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>98</v>
+        <v>269</v>
       </c>
       <c r="H43"/>
     </row>
-    <row r="44" spans="1:8" ht="360">
+    <row r="44" spans="1:8" ht="270">
       <c r="A44" s="3">
-        <v>370825</v>
+        <v>22450</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="H44"/>
     </row>
-    <row r="45" spans="1:8" ht="255">
+    <row r="45" spans="1:8" ht="270">
       <c r="A45" s="3">
-        <v>79501</v>
+        <v>9388</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>102</v>
+        <v>271</v>
       </c>
       <c r="H45"/>
     </row>
-    <row r="46" spans="1:8" ht="405">
+    <row r="46" spans="1:8" ht="210">
       <c r="A46" s="3">
-        <v>18578</v>
+        <v>50794</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>104</v>
+        <v>272</v>
       </c>
       <c r="H46"/>
     </row>
-    <row r="47" spans="1:8" ht="240">
+    <row r="47" spans="1:8" ht="255">
       <c r="A47" s="3">
-        <v>244372</v>
+        <v>203267</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>106</v>
+        <v>273</v>
       </c>
       <c r="H47"/>
     </row>
-    <row r="48" spans="1:8" ht="300">
+    <row r="48" spans="1:8" ht="255">
       <c r="A48" s="3">
-        <v>346775</v>
+        <v>149510</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>108</v>
+        <v>274</v>
       </c>
       <c r="H48"/>
     </row>
-    <row r="49" spans="1:8" ht="300">
+    <row r="49" spans="1:8" ht="225">
       <c r="A49" s="3">
-        <v>161949</v>
+        <v>172563</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>110</v>
+        <v>275</v>
       </c>
       <c r="H49"/>
     </row>
     <row r="50" spans="1:8" ht="338.25" customHeight="1">
       <c r="A50" s="3">
-        <v>392356</v>
+        <v>384021</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>112</v>
+        <v>276</v>
       </c>
       <c r="H50"/>
     </row>
-    <row r="51" spans="1:8" ht="195">
+    <row r="51" spans="1:8" ht="225">
       <c r="A51" s="3">
-        <v>331941</v>
+        <v>257047</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>114</v>
+        <v>277</v>
       </c>
       <c r="H51"/>
     </row>
-    <row r="52" spans="1:8" ht="240">
+    <row r="52" spans="1:8" ht="285">
       <c r="A52" s="3">
-        <v>281255</v>
+        <v>367129</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>116</v>
+        <v>278</v>
       </c>
       <c r="H52"/>
     </row>
     <row r="53" spans="1:8" ht="294" customHeight="1">
       <c r="A53" s="3">
-        <v>79016</v>
+        <v>192025</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>118</v>
+        <v>279</v>
       </c>
       <c r="H53"/>
     </row>
-    <row r="54" spans="1:8" ht="240">
+    <row r="54" spans="1:8" ht="270">
       <c r="A54" s="3">
-        <v>105640</v>
+        <v>211483</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="H54"/>
     </row>
-    <row r="55" spans="1:8" ht="330">
+    <row r="55" spans="1:8" ht="255">
       <c r="A55" s="3">
-        <v>221352</v>
+        <v>402973</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>122</v>
+        <v>281</v>
       </c>
       <c r="H55"/>
     </row>
-    <row r="56" spans="1:8" ht="330">
+    <row r="56" spans="1:8" ht="270">
       <c r="A56" s="3">
-        <v>257708</v>
+        <v>317474</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>124</v>
+        <v>282</v>
       </c>
       <c r="H56"/>
     </row>
-    <row r="57" spans="1:8" ht="255">
+    <row r="57" spans="1:8" ht="270">
       <c r="A57" s="3">
-        <v>201398</v>
+        <v>98856</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>126</v>
+        <v>283</v>
       </c>
       <c r="H57"/>
     </row>
     <row r="58" spans="1:8" ht="345.75" customHeight="1">
       <c r="A58" s="3">
-        <v>25271</v>
+        <v>324648</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>128</v>
+        <v>284</v>
       </c>
       <c r="H58"/>
     </row>
     <row r="59" spans="1:8" ht="390.75" customHeight="1">
       <c r="A59" s="3">
-        <v>47289</v>
+        <v>66092</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>130</v>
+        <v>285</v>
       </c>
       <c r="H59"/>
     </row>
-    <row r="60" spans="1:8" ht="240">
+    <row r="60" spans="1:8" ht="285">
       <c r="A60" s="3">
-        <v>139970</v>
+        <v>165426</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>132</v>
+        <v>286</v>
       </c>
       <c r="H60"/>
     </row>
-    <row r="61" spans="1:8" ht="195">
+    <row r="61" spans="1:8" ht="210">
       <c r="A61" s="3">
-        <v>365762</v>
+        <v>224821</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>134</v>
+        <v>287</v>
       </c>
       <c r="H61"/>
     </row>
-    <row r="62" spans="1:8" ht="210">
+    <row r="62" spans="1:8" ht="315">
       <c r="A62" s="3">
-        <v>185542</v>
+        <v>342078</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>136</v>
+        <v>288</v>
       </c>
       <c r="H62"/>
     </row>
-    <row r="63" spans="1:8" ht="225">
+    <row r="63" spans="1:8" ht="255">
       <c r="A63" s="3">
-        <v>257736</v>
+        <v>255040</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>138</v>
+        <v>289</v>
       </c>
       <c r="H63"/>
     </row>
-    <row r="64" spans="1:8" ht="315">
+    <row r="64" spans="1:8" ht="210">
       <c r="A64" s="3">
-        <v>6864</v>
+        <v>194121</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>140</v>
+        <v>290</v>
       </c>
       <c r="H64"/>
     </row>
-    <row r="65" spans="1:8" ht="255">
+    <row r="65" spans="1:8" ht="240">
       <c r="A65" s="3">
-        <v>7889</v>
+        <v>294474</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>141</v>
+        <v>81</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>142</v>
+        <v>291</v>
       </c>
       <c r="H65"/>
     </row>
-    <row r="66" spans="1:8" ht="210">
+    <row r="66" spans="1:8" ht="195">
       <c r="A66" s="3">
-        <v>245456</v>
+        <v>102995</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>144</v>
+        <v>292</v>
       </c>
       <c r="H66"/>
     </row>
-    <row r="67" spans="1:8" ht="240">
+    <row r="67" spans="1:8" ht="210">
       <c r="A67" s="3">
-        <v>10466</v>
+        <v>140884</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>146</v>
+        <v>293</v>
       </c>
       <c r="H67"/>
     </row>
-    <row r="68" spans="1:8" ht="255">
+    <row r="68" spans="1:8" ht="285">
       <c r="A68" s="3">
-        <v>161011</v>
+        <v>402517</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>147</v>
+        <v>84</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>148</v>
+        <v>294</v>
       </c>
       <c r="H68"/>
     </row>
-    <row r="69" spans="1:8" ht="255">
+    <row r="69" spans="1:8" ht="315">
       <c r="A69" s="3">
-        <v>352499</v>
+        <v>346710</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>150</v>
+        <v>295</v>
       </c>
       <c r="H69"/>
     </row>
     <row r="70" spans="1:8" ht="240">
       <c r="A70" s="3">
-        <v>235261</v>
+        <v>42070</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>151</v>
+        <v>86</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>152</v>
+        <v>296</v>
       </c>
       <c r="H70"/>
     </row>
-    <row r="71" spans="1:8" ht="210">
+    <row r="71" spans="1:8" ht="240">
       <c r="A71" s="3">
-        <v>169725</v>
+        <v>130649</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>154</v>
+        <v>297</v>
       </c>
       <c r="H71"/>
     </row>
-    <row r="72" spans="1:8" ht="300">
+    <row r="72" spans="1:8" ht="225">
       <c r="A72" s="3">
-        <v>385791</v>
+        <v>266842</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>155</v>
+        <v>88</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>156</v>
+        <v>298</v>
       </c>
       <c r="H72"/>
     </row>
-    <row r="73" spans="1:8" ht="300">
+    <row r="73" spans="1:8" ht="255">
       <c r="A73" s="3">
-        <v>258307</v>
+        <v>218719</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>158</v>
+        <v>299</v>
       </c>
       <c r="H73"/>
     </row>
-    <row r="74" spans="1:8" ht="195">
+    <row r="74" spans="1:8" ht="240">
       <c r="A74" s="3">
-        <v>198918</v>
+        <v>181858</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="H74"/>
     </row>
-    <row r="75" spans="1:8" ht="225">
+    <row r="75" spans="1:8" ht="255">
       <c r="A75" s="3">
-        <v>97035</v>
+        <v>194148</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>161</v>
+        <v>91</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>162</v>
+        <v>301</v>
       </c>
       <c r="H75"/>
     </row>
-    <row r="76" spans="1:8" ht="270">
+    <row r="76" spans="1:8" ht="285">
       <c r="A76" s="3">
-        <v>339216</v>
+        <v>136804</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>164</v>
+        <v>302</v>
       </c>
       <c r="H76"/>
     </row>
-    <row r="77" spans="1:8" ht="300">
+    <row r="77" spans="1:8" ht="210">
       <c r="A77" s="3">
-        <v>219417</v>
+        <v>93286</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>165</v>
+        <v>93</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>166</v>
+        <v>303</v>
       </c>
       <c r="H77"/>
     </row>
     <row r="78" spans="1:8" ht="377.25" customHeight="1">
       <c r="A78" s="3">
-        <v>96027</v>
+        <v>51309</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>167</v>
+        <v>94</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>168</v>
+        <v>304</v>
       </c>
       <c r="H78"/>
     </row>
-    <row r="79" spans="1:8" ht="225">
+    <row r="79" spans="1:8" ht="300">
       <c r="A79" s="3">
-        <v>106785</v>
+        <v>263279</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>169</v>
+        <v>95</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>170</v>
+        <v>305</v>
       </c>
       <c r="H79"/>
     </row>
-    <row r="80" spans="1:8" ht="210">
+    <row r="80" spans="1:8" ht="240">
       <c r="A80" s="3">
-        <v>17188</v>
+        <v>87671</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>172</v>
+        <v>306</v>
       </c>
       <c r="H80"/>
     </row>
-    <row r="81" spans="1:8" ht="195">
+    <row r="81" spans="1:8" ht="240">
       <c r="A81" s="3">
-        <v>102700</v>
+        <v>277629</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>174</v>
+        <v>307</v>
       </c>
       <c r="H81"/>
     </row>
-    <row r="82" spans="1:8" ht="225">
+    <row r="82" spans="1:8" ht="195">
       <c r="A82" s="3">
-        <v>302388</v>
+        <v>353409</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>176</v>
+        <v>308</v>
       </c>
       <c r="H82"/>
     </row>
-    <row r="83" spans="1:8" ht="240">
+    <row r="83" spans="1:8" ht="255">
       <c r="A83" s="3">
-        <v>349496</v>
+        <v>3202</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>178</v>
+        <v>309</v>
       </c>
       <c r="H83"/>
     </row>
-    <row r="84" spans="1:8" ht="225">
+    <row r="84" spans="1:8" ht="360">
       <c r="A84" s="3">
-        <v>327996</v>
+        <v>370825</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>179</v>
+        <v>100</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>180</v>
+        <v>310</v>
       </c>
       <c r="H84"/>
     </row>
     <row r="85" spans="1:8" ht="294.75" customHeight="1">
       <c r="A85" s="3">
-        <v>383302</v>
+        <v>79501</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>181</v>
+        <v>101</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>182</v>
+        <v>311</v>
       </c>
       <c r="H85"/>
     </row>
-    <row r="86" spans="1:8" ht="195">
+    <row r="86" spans="1:8" ht="405">
       <c r="A86" s="3">
-        <v>90959</v>
+        <v>18578</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>184</v>
+        <v>312</v>
       </c>
       <c r="H86"/>
     </row>
-    <row r="87" spans="1:8" ht="225">
+    <row r="87" spans="1:8" ht="240">
       <c r="A87" s="3">
-        <v>239953</v>
+        <v>244372</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>185</v>
+        <v>103</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>186</v>
+        <v>313</v>
       </c>
       <c r="H87"/>
     </row>
-    <row r="88" spans="1:8" ht="240">
+    <row r="88" spans="1:8" ht="300">
       <c r="A88" s="3">
-        <v>303969</v>
+        <v>346775</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>187</v>
+        <v>104</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>188</v>
+        <v>314</v>
       </c>
       <c r="H88"/>
     </row>
-    <row r="89" spans="1:8" ht="240">
+    <row r="89" spans="1:8" ht="300">
       <c r="A89" s="3">
-        <v>122212</v>
+        <v>161949</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>189</v>
+        <v>105</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="H89"/>
     </row>
-    <row r="90" spans="1:8" ht="225">
+    <row r="90" spans="1:8" ht="285">
       <c r="A90" s="3">
-        <v>355693</v>
+        <v>392356</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>191</v>
+        <v>106</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>192</v>
+        <v>316</v>
       </c>
       <c r="H90"/>
     </row>
-    <row r="91" spans="1:8" ht="240">
+    <row r="91" spans="1:8" ht="195">
       <c r="A91" s="3">
-        <v>343411</v>
+        <v>331941</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>194</v>
+        <v>317</v>
       </c>
       <c r="H91"/>
     </row>
-    <row r="92" spans="1:8" ht="225">
+    <row r="92" spans="1:8" ht="240">
       <c r="A92" s="3">
-        <v>160629</v>
+        <v>281255</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>196</v>
+        <v>318</v>
       </c>
       <c r="H92"/>
     </row>
     <row r="93" spans="1:8" ht="409.5">
       <c r="A93" s="3">
-        <v>224630</v>
+        <v>79016</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>197</v>
+        <v>109</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>198</v>
+        <v>319</v>
       </c>
       <c r="H93"/>
     </row>
-    <row r="94" spans="1:8" ht="315">
+    <row r="94" spans="1:8" ht="240">
       <c r="A94" s="3">
-        <v>162679</v>
+        <v>105640</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>199</v>
+        <v>110</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="H94"/>
     </row>
-    <row r="95" spans="1:8" ht="255">
+    <row r="95" spans="1:8" ht="330">
       <c r="A95" s="3">
-        <v>150905</v>
+        <v>221352</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>201</v>
+        <v>111</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>202</v>
+        <v>321</v>
       </c>
       <c r="H95"/>
     </row>
-    <row r="96" spans="1:8" ht="285">
+    <row r="96" spans="1:8" ht="330">
       <c r="A96" s="3">
-        <v>131460</v>
+        <v>257708</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>203</v>
+        <v>112</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>204</v>
+        <v>322</v>
       </c>
       <c r="H96"/>
     </row>
     <row r="97" spans="1:8" ht="255">
       <c r="A97" s="3">
-        <v>82317</v>
+        <v>201398</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>205</v>
+        <v>113</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>206</v>
+        <v>323</v>
       </c>
       <c r="H97"/>
     </row>
-    <row r="98" spans="1:8" ht="285">
+    <row r="98" spans="1:8" ht="255">
       <c r="A98" s="3">
-        <v>172430</v>
+        <v>25271</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>207</v>
+        <v>114</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>208</v>
+        <v>324</v>
       </c>
       <c r="H98"/>
     </row>
-    <row r="99" spans="1:8" ht="240">
+    <row r="99" spans="1:8" ht="210">
       <c r="A99" s="3">
-        <v>51087</v>
+        <v>47289</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>209</v>
+        <v>115</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>210</v>
+        <v>325</v>
       </c>
       <c r="H99"/>
     </row>
     <row r="100" spans="1:8" ht="240">
       <c r="A100" s="3">
-        <v>274321</v>
+        <v>139970</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>211</v>
+        <v>116</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>212</v>
+        <v>326</v>
       </c>
       <c r="H100"/>
     </row>
-    <row r="101" spans="1:8" ht="270">
+    <row r="101" spans="1:8" ht="195">
       <c r="A101" s="3">
-        <v>272277</v>
+        <v>365762</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>213</v>
+        <v>117</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>214</v>
+        <v>327</v>
       </c>
       <c r="H101"/>
     </row>
-    <row r="102" spans="1:8" ht="270">
+    <row r="102" spans="1:8" ht="210">
       <c r="A102" s="3">
-        <v>269717</v>
+        <v>185542</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>215</v>
+        <v>118</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>216</v>
+        <v>328</v>
       </c>
       <c r="H102"/>
     </row>
-    <row r="103" spans="1:8" ht="270">
+    <row r="103" spans="1:8" ht="225">
       <c r="A103" s="3">
-        <v>387479</v>
+        <v>257736</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>217</v>
+        <v>119</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>218</v>
+        <v>329</v>
       </c>
       <c r="H103"/>
     </row>
-    <row r="104" spans="1:8" ht="240">
+    <row r="104" spans="1:8" ht="315">
       <c r="A104" s="3">
-        <v>336285</v>
+        <v>6864</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>219</v>
+        <v>120</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>220</v>
+        <v>330</v>
       </c>
       <c r="H104"/>
     </row>
     <row r="105" spans="1:8" ht="255">
       <c r="A105" s="3">
-        <v>67486</v>
+        <v>7889</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>221</v>
+        <v>121</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>222</v>
+        <v>331</v>
       </c>
       <c r="H105"/>
     </row>
     <row r="106" spans="1:8" ht="152.25" customHeight="1">
       <c r="A106" s="3">
-        <v>294304</v>
+        <v>245456</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>223</v>
+        <v>122</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>224</v>
+        <v>332</v>
       </c>
       <c r="H106"/>
     </row>
     <row r="107" spans="1:8" ht="319.5" customHeight="1">
       <c r="A107" s="3">
-        <v>157096</v>
+        <v>10466</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>225</v>
+        <v>123</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>226</v>
+        <v>333</v>
       </c>
       <c r="H107"/>
     </row>
-    <row r="108" spans="1:8" ht="270">
+    <row r="108" spans="1:8" ht="255">
       <c r="A108" s="3">
-        <v>107962</v>
+        <v>161011</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>227</v>
+        <v>124</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>228</v>
+        <v>334</v>
       </c>
       <c r="H108"/>
     </row>
-    <row r="109" spans="1:8" ht="225">
+    <row r="109" spans="1:8" ht="255">
       <c r="A109" s="3">
-        <v>61394</v>
+        <v>352499</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>230</v>
+        <v>335</v>
       </c>
       <c r="H109"/>
     </row>
-    <row r="110" spans="1:8" ht="225">
+    <row r="110" spans="1:8" ht="240">
       <c r="A110" s="3">
-        <v>147410</v>
+        <v>235261</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>231</v>
+        <v>126</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>232</v>
+        <v>336</v>
       </c>
       <c r="H110"/>
     </row>
     <row r="111" spans="1:8" ht="210">
       <c r="A111" s="3">
-        <v>381910</v>
+        <v>169725</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>233</v>
+        <v>127</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>234</v>
+        <v>337</v>
       </c>
       <c r="H111"/>
     </row>
-    <row r="112" spans="1:8" ht="330">
+    <row r="112" spans="1:8" ht="300">
       <c r="A112" s="3">
-        <v>119770</v>
+        <v>385791</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>236</v>
+        <v>338</v>
       </c>
       <c r="H112"/>
     </row>
-    <row r="113" spans="1:8" ht="285">
+    <row r="113" spans="1:8" ht="300">
       <c r="A113" s="3">
-        <v>378843</v>
+        <v>258307</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>237</v>
+        <v>129</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>238</v>
+        <v>339</v>
       </c>
       <c r="H113"/>
     </row>
-    <row r="114" spans="1:8" ht="240">
+    <row r="114" spans="1:8" ht="195">
       <c r="A114" s="3">
-        <v>306656</v>
+        <v>198918</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>239</v>
+        <v>130</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>240</v>
+        <v>340</v>
       </c>
       <c r="H114"/>
     </row>
-    <row r="115" spans="1:8" ht="210">
+    <row r="115" spans="1:8" ht="225">
       <c r="A115" s="3">
-        <v>371172</v>
+        <v>97035</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>241</v>
+        <v>131</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>242</v>
+        <v>341</v>
       </c>
       <c r="H115"/>
     </row>
-    <row r="116" spans="1:8" ht="195">
+    <row r="116" spans="1:8" ht="270">
       <c r="A116" s="3">
-        <v>330218</v>
+        <v>339216</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>244</v>
+        <v>342</v>
       </c>
       <c r="H116"/>
     </row>
-    <row r="117" spans="1:8" ht="255">
+    <row r="117" spans="1:8" ht="300">
       <c r="A117" s="3">
-        <v>31568</v>
+        <v>219417</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>245</v>
+        <v>133</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>246</v>
+        <v>343</v>
       </c>
       <c r="H117"/>
     </row>
-    <row r="118" spans="1:8" ht="330">
+    <row r="118" spans="1:8" ht="255">
       <c r="A118" s="3">
-        <v>115775</v>
+        <v>96027</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>247</v>
+        <v>134</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>248</v>
+        <v>344</v>
       </c>
       <c r="H118"/>
     </row>
-    <row r="119" spans="1:8" ht="270">
+    <row r="119" spans="1:8" ht="225">
       <c r="A119" s="3">
-        <v>138911</v>
+        <v>106785</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>249</v>
+        <v>135</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>250</v>
+        <v>345</v>
       </c>
       <c r="H119"/>
     </row>
-    <row r="120" spans="1:8" ht="240">
+    <row r="120" spans="1:8" ht="210">
       <c r="A120" s="3">
-        <v>390121</v>
+        <v>17188</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>251</v>
+        <v>136</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>252</v>
+        <v>346</v>
       </c>
       <c r="H120"/>
     </row>
-    <row r="121" spans="1:8" ht="285">
+    <row r="121" spans="1:8" ht="195">
       <c r="A121" s="3">
-        <v>376242</v>
+        <v>102700</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>253</v>
+        <v>137</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>254</v>
+        <v>347</v>
       </c>
       <c r="H121"/>
     </row>
-    <row r="122" spans="1:8" ht="300">
+    <row r="122" spans="1:8" ht="225">
       <c r="A122" s="3">
-        <v>400</v>
+        <v>302388</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>255</v>
+        <v>138</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>256</v>
+        <v>348</v>
       </c>
       <c r="H122"/>
     </row>
-    <row r="123" spans="1:8" ht="270">
+    <row r="123" spans="1:8" ht="240">
       <c r="A123" s="3">
-        <v>104064</v>
+        <v>349496</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>257</v>
+        <v>139</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>258</v>
+        <v>349</v>
       </c>
       <c r="H123"/>
     </row>
-    <row r="124" spans="1:8" ht="210">
+    <row r="124" spans="1:8" ht="225">
       <c r="A124" s="3">
-        <v>262785</v>
+        <v>327996</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>259</v>
+        <v>140</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="H124"/>
     </row>
-    <row r="125" spans="1:8" ht="225">
+    <row r="125" spans="1:8" ht="255">
       <c r="A125" s="3">
-        <v>313605</v>
+        <v>383302</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>261</v>
+        <v>141</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
       <c r="H125"/>
     </row>
-    <row r="126" spans="1:8" ht="255">
+    <row r="126" spans="1:8" ht="195">
       <c r="A126" s="3">
-        <v>259720</v>
+        <v>90959</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>263</v>
+        <v>142</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>264</v>
+        <v>352</v>
       </c>
       <c r="H126"/>
     </row>
-    <row r="127" spans="1:8" ht="285">
+    <row r="127" spans="1:8" ht="225">
       <c r="A127" s="3">
-        <v>130057</v>
+        <v>239953</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>265</v>
+        <v>143</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>266</v>
+        <v>353</v>
       </c>
       <c r="H127"/>
     </row>
-    <row r="128" spans="1:8" ht="330">
+    <row r="128" spans="1:8" ht="240">
       <c r="A128" s="3">
-        <v>354057</v>
+        <v>303969</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>267</v>
+        <v>144</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>268</v>
+        <v>354</v>
       </c>
       <c r="H128"/>
     </row>
-    <row r="129" spans="1:8" ht="270">
+    <row r="129" spans="1:8" ht="240">
       <c r="A129" s="3">
-        <v>4747</v>
+        <v>122212</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>269</v>
+        <v>145</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>270</v>
+        <v>355</v>
       </c>
       <c r="H129"/>
     </row>
-    <row r="130" spans="1:8" ht="255">
+    <row r="130" spans="1:8" ht="225">
       <c r="A130" s="3">
-        <v>119437</v>
+        <v>355693</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>271</v>
+        <v>146</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>272</v>
+        <v>356</v>
       </c>
       <c r="H130"/>
     </row>
-    <row r="131" spans="1:8" ht="255">
+    <row r="131" spans="1:8" ht="240">
       <c r="A131" s="3">
-        <v>355854</v>
+        <v>343411</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>273</v>
+        <v>147</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>274</v>
+        <v>357</v>
       </c>
       <c r="H131"/>
     </row>
     <row r="132" spans="1:8" ht="409.5" customHeight="1">
       <c r="A132" s="3">
-        <v>371989</v>
+        <v>160629</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>275</v>
+        <v>148</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>276</v>
+        <v>358</v>
       </c>
       <c r="H132"/>
     </row>
-    <row r="133" spans="1:8" ht="225">
+    <row r="133" spans="1:8" ht="409.5">
       <c r="A133" s="3">
-        <v>193528</v>
+        <v>224630</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>277</v>
+        <v>149</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>278</v>
+        <v>359</v>
       </c>
       <c r="H133"/>
     </row>
-    <row r="134" spans="1:8" ht="270">
+    <row r="134" spans="1:8" ht="315">
       <c r="A134" s="3">
-        <v>105366</v>
+        <v>162679</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>279</v>
+        <v>150</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="H134"/>
     </row>
-    <row r="135" spans="1:8" ht="300">
+    <row r="135" spans="1:8" ht="255">
       <c r="A135" s="3">
-        <v>304792</v>
+        <v>150905</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>281</v>
+        <v>151</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>282</v>
+        <v>361</v>
       </c>
       <c r="H135"/>
     </row>
-    <row r="136" spans="1:8" ht="225">
+    <row r="136" spans="1:8" ht="285">
       <c r="A136" s="3">
-        <v>321693</v>
+        <v>131460</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>283</v>
+        <v>152</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>284</v>
+        <v>362</v>
       </c>
       <c r="H136"/>
     </row>
-    <row r="137" spans="1:8" ht="270">
+    <row r="137" spans="1:8" ht="255">
       <c r="A137" s="3">
-        <v>178601</v>
+        <v>82317</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>285</v>
+        <v>153</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>286</v>
+        <v>363</v>
       </c>
       <c r="H137"/>
     </row>
-    <row r="138" spans="1:8" ht="270">
+    <row r="138" spans="1:8" ht="285">
       <c r="A138" s="3">
-        <v>73005</v>
+        <v>172430</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>287</v>
+        <v>154</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>288</v>
+        <v>364</v>
       </c>
       <c r="H138"/>
     </row>
-    <row r="139" spans="1:8" ht="270">
+    <row r="139" spans="1:8" ht="240">
       <c r="A139" s="3">
-        <v>339248</v>
+        <v>51087</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>289</v>
+        <v>155</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>290</v>
+        <v>365</v>
       </c>
       <c r="H139"/>
     </row>
-    <row r="140" spans="1:8" ht="255">
+    <row r="140" spans="1:8" ht="240">
       <c r="A140" s="3">
-        <v>102321</v>
+        <v>274321</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>291</v>
+        <v>156</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>292</v>
+        <v>366</v>
       </c>
       <c r="H140"/>
     </row>
     <row r="141" spans="1:8" ht="270">
       <c r="A141" s="3">
-        <v>89778</v>
+        <v>272277</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>293</v>
+        <v>157</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>294</v>
+        <v>367</v>
       </c>
       <c r="H141"/>
     </row>
-    <row r="142" spans="1:8" ht="285">
+    <row r="142" spans="1:8" ht="270">
       <c r="A142" s="3">
-        <v>41653</v>
+        <v>269717</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>295</v>
+        <v>158</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>296</v>
+        <v>368</v>
       </c>
       <c r="H142"/>
     </row>
-    <row r="143" spans="1:8" ht="315">
+    <row r="143" spans="1:8" ht="270">
       <c r="A143" s="3">
-        <v>245815</v>
+        <v>387479</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>297</v>
+        <v>159</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>298</v>
+        <v>369</v>
       </c>
       <c r="H143"/>
     </row>
-    <row r="144" spans="1:8" ht="255">
+    <row r="144" spans="1:8" ht="240">
       <c r="A144" s="3">
-        <v>195128</v>
+        <v>336285</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>299</v>
+        <v>160</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="H144"/>
     </row>
-    <row r="145" spans="1:8" ht="240">
+    <row r="145" spans="1:8" ht="255">
       <c r="A145" s="3">
-        <v>302394</v>
+        <v>67486</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>301</v>
+        <v>161</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>302</v>
+        <v>371</v>
       </c>
       <c r="H145"/>
     </row>
-    <row r="146" spans="1:8" ht="240">
+    <row r="146" spans="1:8" ht="225">
       <c r="A146" s="3">
-        <v>278844</v>
+        <v>294304</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>303</v>
+        <v>162</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>304</v>
+        <v>372</v>
       </c>
       <c r="H146"/>
     </row>
-    <row r="147" spans="1:8" ht="210">
+    <row r="147" spans="1:8" ht="225">
       <c r="A147" s="3">
-        <v>77628</v>
+        <v>157096</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>305</v>
+        <v>163</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>306</v>
+        <v>373</v>
       </c>
       <c r="H147"/>
     </row>
-    <row r="148" spans="1:8" ht="315">
+    <row r="148" spans="1:8" ht="270">
       <c r="A148" s="3">
-        <v>393801</v>
+        <v>107962</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>307</v>
+        <v>164</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>308</v>
+        <v>374</v>
       </c>
       <c r="H148"/>
     </row>
-    <row r="149" spans="1:8" ht="285">
+    <row r="149" spans="1:8" ht="225">
       <c r="A149" s="3">
-        <v>105417</v>
+        <v>61394</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>309</v>
+        <v>165</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>310</v>
+        <v>375</v>
       </c>
       <c r="H149"/>
     </row>
     <row r="150" spans="1:8" ht="344.25" customHeight="1">
       <c r="A150" s="3">
-        <v>11091</v>
+        <v>147410</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>311</v>
+        <v>166</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>312</v>
+        <v>376</v>
       </c>
       <c r="H150"/>
     </row>
-    <row r="151" spans="1:8" ht="255">
+    <row r="151" spans="1:8" ht="210">
       <c r="A151" s="3">
-        <v>24661</v>
+        <v>381910</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>313</v>
+        <v>167</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="H151"/>
     </row>
-    <row r="152" spans="1:8" ht="225">
+    <row r="152" spans="1:8" ht="330">
       <c r="A152" s="3">
-        <v>124120</v>
+        <v>119770</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>315</v>
+        <v>168</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="H152"/>
     </row>
-    <row r="153" spans="1:8" ht="255">
+    <row r="153" spans="1:8" ht="285">
       <c r="A153" s="3">
-        <v>322264</v>
+        <v>378843</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>317</v>
+        <v>169</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>318</v>
+        <v>379</v>
       </c>
       <c r="H153"/>
     </row>
-    <row r="154" spans="1:8" ht="285">
+    <row r="154" spans="1:8" ht="240">
       <c r="A154" s="3">
-        <v>54235</v>
+        <v>306656</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>319</v>
+        <v>170</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="H154"/>
     </row>
-    <row r="155" spans="1:8" ht="300">
+    <row r="155" spans="1:8" ht="210">
       <c r="A155" s="3">
-        <v>411099</v>
+        <v>371172</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>321</v>
+        <v>171</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="H155"/>
     </row>
-    <row r="156" spans="1:8" ht="300">
+    <row r="156" spans="1:8" ht="195">
       <c r="A156" s="3">
-        <v>133085</v>
+        <v>330218</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>323</v>
+        <v>172</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>324</v>
+        <v>382</v>
       </c>
       <c r="H156"/>
     </row>
-    <row r="157" spans="1:8" ht="225">
+    <row r="157" spans="1:8" ht="255">
       <c r="A157" s="3">
-        <v>221791</v>
+        <v>31568</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>325</v>
+        <v>173</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>326</v>
+        <v>383</v>
       </c>
       <c r="H157"/>
     </row>
     <row r="158" spans="1:8" ht="409.5" customHeight="1">
       <c r="A158" s="3">
-        <v>79074</v>
+        <v>115775</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>327</v>
+        <v>174</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>328</v>
+        <v>384</v>
       </c>
       <c r="H158"/>
     </row>
-    <row r="159" spans="1:8" ht="300">
+    <row r="159" spans="1:8" ht="270">
       <c r="A159" s="3">
-        <v>208509</v>
+        <v>138911</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>329</v>
+        <v>175</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>330</v>
+        <v>385</v>
       </c>
       <c r="H159"/>
     </row>
     <row r="160" spans="1:8" ht="334.5" customHeight="1">
       <c r="A160" s="3">
-        <v>163326</v>
+        <v>390121</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>332</v>
+        <v>386</v>
       </c>
       <c r="H160"/>
     </row>
-    <row r="161" spans="1:8" ht="255">
+    <row r="161" spans="1:8" ht="285">
       <c r="A161" s="3">
-        <v>47850</v>
+        <v>376242</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>333</v>
+        <v>177</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>334</v>
+        <v>387</v>
       </c>
       <c r="H161"/>
     </row>
-    <row r="162" spans="1:8" ht="240">
+    <row r="162" spans="1:8" ht="300">
       <c r="A162" s="3">
-        <v>15086</v>
+        <v>400</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>335</v>
+        <v>178</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>336</v>
+        <v>388</v>
       </c>
       <c r="H162"/>
     </row>
-    <row r="163" spans="1:8" ht="285">
+    <row r="163" spans="1:8" ht="270">
       <c r="A163" s="3">
-        <v>154224</v>
+        <v>104064</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>337</v>
+        <v>180</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>338</v>
+        <v>389</v>
       </c>
       <c r="H163"/>
     </row>
-    <row r="164" spans="1:8" ht="240">
+    <row r="164" spans="1:8" ht="210">
       <c r="A164" s="3">
-        <v>260593</v>
+        <v>262785</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>339</v>
+        <v>181</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>340</v>
+        <v>390</v>
       </c>
       <c r="H164"/>
     </row>
-    <row r="165" spans="1:8" ht="270">
+    <row r="165" spans="1:8" ht="225">
       <c r="A165" s="3">
-        <v>365171</v>
+        <v>313605</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>341</v>
+        <v>182</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="H165"/>
     </row>
     <row r="166" spans="1:8" ht="255">
       <c r="A166" s="3">
+        <v>259720</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="H166"/>
+    </row>
+    <row r="167" spans="1:8" ht="285">
+      <c r="A167" s="3">
+        <v>130057</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="H167"/>
+    </row>
+    <row r="168" spans="1:8" ht="330">
+      <c r="A168" s="3">
+        <v>354057</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="H168"/>
+    </row>
+    <row r="169" spans="1:8" ht="270">
+      <c r="A169" s="3">
+        <v>4747</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="H169"/>
+    </row>
+    <row r="170" spans="1:8" ht="255">
+      <c r="A170" s="3">
+        <v>119437</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="H170"/>
+    </row>
+    <row r="171" spans="1:8" ht="255">
+      <c r="A171" s="3">
+        <v>355854</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="H171"/>
+    </row>
+    <row r="172" spans="1:8" ht="315">
+      <c r="A172" s="3">
+        <v>371989</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H172"/>
+    </row>
+    <row r="173" spans="1:8" ht="225">
+      <c r="A173" s="3">
+        <v>193528</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="H173"/>
+    </row>
+    <row r="174" spans="1:8" ht="270">
+      <c r="A174" s="3">
+        <v>105366</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="H174"/>
+    </row>
+    <row r="175" spans="1:8" ht="300">
+      <c r="A175" s="3">
+        <v>304792</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H175"/>
+    </row>
+    <row r="176" spans="1:8" ht="225">
+      <c r="A176" s="3">
+        <v>321693</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="H176"/>
+    </row>
+    <row r="177" spans="1:8" ht="270">
+      <c r="A177" s="3">
+        <v>178601</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="H177"/>
+    </row>
+    <row r="178" spans="1:8" ht="270">
+      <c r="A178" s="3">
+        <v>73005</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H178"/>
+    </row>
+    <row r="179" spans="1:8" ht="270">
+      <c r="A179" s="3">
+        <v>339248</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="H179"/>
+    </row>
+    <row r="180" spans="1:8" ht="255">
+      <c r="A180" s="3">
+        <v>102321</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="H180"/>
+    </row>
+    <row r="181" spans="1:8" ht="270">
+      <c r="A181" s="3">
+        <v>89778</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="H181"/>
+    </row>
+    <row r="182" spans="1:8" ht="285">
+      <c r="A182" s="3">
+        <v>41653</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="H182"/>
+    </row>
+    <row r="183" spans="1:8" ht="315">
+      <c r="A183" s="3">
+        <v>245815</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="H183"/>
+    </row>
+    <row r="184" spans="1:8" ht="255">
+      <c r="A184" s="3">
+        <v>195128</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="H184"/>
+    </row>
+    <row r="185" spans="1:8" ht="240">
+      <c r="A185" s="3">
+        <v>302394</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="H185"/>
+    </row>
+    <row r="186" spans="1:8" ht="240">
+      <c r="A186" s="3">
+        <v>278844</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="H186"/>
+    </row>
+    <row r="187" spans="1:8" ht="210">
+      <c r="A187" s="3">
+        <v>77628</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H187"/>
+    </row>
+    <row r="188" spans="1:8" ht="315">
+      <c r="A188" s="3">
+        <v>393801</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="H188"/>
+    </row>
+    <row r="189" spans="1:8" ht="285">
+      <c r="A189" s="3">
+        <v>105417</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="H189"/>
+    </row>
+    <row r="190" spans="1:8" ht="315">
+      <c r="A190" s="3">
+        <v>11091</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="H190"/>
+    </row>
+    <row r="191" spans="1:8" ht="255">
+      <c r="A191" s="3">
+        <v>24661</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="H191"/>
+    </row>
+    <row r="192" spans="1:8" ht="225">
+      <c r="A192" s="3">
+        <v>124120</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="H192"/>
+    </row>
+    <row r="193" spans="1:8" ht="255">
+      <c r="A193" s="3">
+        <v>322264</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H193"/>
+    </row>
+    <row r="194" spans="1:8" ht="285">
+      <c r="A194" s="3">
+        <v>54235</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="H194"/>
+    </row>
+    <row r="195" spans="1:8" ht="300">
+      <c r="A195" s="3">
+        <v>411099</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="H195"/>
+    </row>
+    <row r="196" spans="1:8" ht="300">
+      <c r="A196" s="3">
+        <v>133085</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H196"/>
+    </row>
+    <row r="197" spans="1:8" ht="225">
+      <c r="A197" s="3">
+        <v>221791</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="H197"/>
+    </row>
+    <row r="198" spans="1:8" ht="255">
+      <c r="A198" s="3">
+        <v>79074</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="H198"/>
+    </row>
+    <row r="199" spans="1:8" ht="300">
+      <c r="A199" s="3">
+        <v>208509</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="H199"/>
+    </row>
+    <row r="200" spans="1:8" ht="210">
+      <c r="A200" s="3">
+        <v>163326</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H200"/>
+    </row>
+    <row r="201" spans="1:8" ht="255">
+      <c r="A201" s="3">
+        <v>47850</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="H201"/>
+    </row>
+    <row r="202" spans="1:8" ht="365.25" customHeight="1">
+      <c r="A202" s="3">
+        <v>15086</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="H202"/>
+    </row>
+    <row r="203" spans="1:8" ht="285">
+      <c r="A203" s="3">
+        <v>154224</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="H203"/>
+    </row>
+    <row r="204" spans="1:8" ht="240">
+      <c r="A204" s="3">
+        <v>260593</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="H204"/>
+    </row>
+    <row r="205" spans="1:8" ht="270">
+      <c r="A205" s="3">
+        <v>365171</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H205"/>
+    </row>
+    <row r="206" spans="1:8" ht="255">
+      <c r="A206" s="3">
         <v>236023</v>
       </c>
-      <c r="B166" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F166" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="H166"/>
-    </row>
-    <row r="167" spans="1:8" ht="255">
-      <c r="A167" s="3">
+      <c r="B206" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="H206"/>
+    </row>
+    <row r="207" spans="1:8" ht="255">
+      <c r="A207" s="3">
         <v>126712</v>
       </c>
-      <c r="B167" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F167" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="H167"/>
-    </row>
-    <row r="168" spans="1:8" ht="225">
-      <c r="A168" s="3">
+      <c r="B207" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="H207"/>
+    </row>
+    <row r="208" spans="1:8" ht="225">
+      <c r="A208" s="3">
         <v>99581</v>
       </c>
-      <c r="B168" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F168" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G168" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="H168"/>
-    </row>
-    <row r="169" spans="1:8" ht="285">
-      <c r="A169" s="3">
+      <c r="B208" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="H208"/>
+    </row>
+    <row r="209" spans="1:8" ht="409.5" customHeight="1">
+      <c r="A209" s="3">
         <v>11774</v>
       </c>
-      <c r="B169" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E169" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F169" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G169" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="H169"/>
-    </row>
-    <row r="170" spans="1:8" ht="240">
-      <c r="A170" s="3">
+      <c r="B209" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="H209"/>
+    </row>
+    <row r="210" spans="1:8" ht="298.5" customHeight="1">
+      <c r="A210" s="3">
         <v>317810</v>
       </c>
-      <c r="B170" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C170" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E170" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F170" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G170" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="H170"/>
-    </row>
-    <row r="171" spans="1:8">
-      <c r="H171"/>
-    </row>
-    <row r="172" spans="1:8">
-      <c r="H172"/>
-    </row>
-    <row r="173" spans="1:8">
-      <c r="H173"/>
-    </row>
-    <row r="174" spans="1:8">
-      <c r="H174"/>
-    </row>
-    <row r="175" spans="1:8">
-      <c r="H175"/>
-    </row>
-    <row r="176" spans="1:8">
-      <c r="H176"/>
-    </row>
-    <row r="177" spans="8:8">
-      <c r="H177"/>
-    </row>
-    <row r="178" spans="8:8">
-      <c r="H178"/>
-    </row>
-    <row r="179" spans="8:8">
-      <c r="H179"/>
-    </row>
-    <row r="180" spans="8:8">
-      <c r="H180"/>
-    </row>
-    <row r="181" spans="8:8">
-      <c r="H181"/>
-    </row>
-    <row r="182" spans="8:8">
-      <c r="H182"/>
-    </row>
-    <row r="183" spans="8:8">
-      <c r="H183"/>
-    </row>
-    <row r="184" spans="8:8">
-      <c r="H184"/>
-    </row>
-    <row r="185" spans="8:8">
-      <c r="H185"/>
-    </row>
-    <row r="186" spans="8:8">
-      <c r="H186"/>
-    </row>
-    <row r="187" spans="8:8">
-      <c r="H187"/>
-    </row>
-    <row r="188" spans="8:8">
-      <c r="H188"/>
-    </row>
-    <row r="189" spans="8:8">
-      <c r="H189"/>
-    </row>
-    <row r="190" spans="8:8">
-      <c r="H190"/>
-    </row>
-    <row r="191" spans="8:8">
-      <c r="H191"/>
-    </row>
-    <row r="192" spans="8:8">
-      <c r="H192"/>
-    </row>
-    <row r="193" spans="8:8">
-      <c r="H193"/>
-    </row>
-    <row r="194" spans="8:8">
-      <c r="H194"/>
-    </row>
-    <row r="195" spans="8:8">
-      <c r="H195"/>
-    </row>
-    <row r="196" spans="8:8">
-      <c r="H196"/>
-    </row>
-    <row r="197" spans="8:8">
-      <c r="H197"/>
-    </row>
-    <row r="198" spans="8:8">
-      <c r="H198"/>
-    </row>
-    <row r="199" spans="8:8">
-      <c r="H199"/>
-    </row>
-    <row r="200" spans="8:8">
-      <c r="H200"/>
-    </row>
-    <row r="201" spans="8:8">
-      <c r="H201"/>
-    </row>
-    <row r="202" spans="8:8" ht="365.25" customHeight="1">
-      <c r="H202"/>
-    </row>
-    <row r="203" spans="8:8">
-      <c r="H203"/>
-    </row>
-    <row r="204" spans="8:8">
-      <c r="H204"/>
-    </row>
-    <row r="205" spans="8:8">
-      <c r="H205"/>
-    </row>
-    <row r="206" spans="8:8">
-      <c r="H206"/>
-    </row>
-    <row r="207" spans="8:8">
-      <c r="H207"/>
-    </row>
-    <row r="208" spans="8:8">
-      <c r="H208"/>
-    </row>
-    <row r="209" spans="8:8" ht="409.5" customHeight="1">
-      <c r="H209"/>
-    </row>
-    <row r="210" spans="8:8" ht="298.5" customHeight="1">
+      <c r="B210" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>436</v>
+      </c>
       <c r="H210"/>
     </row>
   </sheetData>
